--- a/Intervention outcomes and spillover effects/Intervention outcomes and spillover effects.xlsx
+++ b/Intervention outcomes and spillover effects/Intervention outcomes and spillover effects.xlsx
@@ -30,7 +30,7 @@
       <sz val="12"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -47,6 +47,11 @@
         <fgColor rgb="007fffd4"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00ffffff"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -60,11 +65,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W157"/>
+  <dimension ref="A1:W161"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4071,85 +4077,81 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="inlineStr">
-        <is>
-          <t>GMHO:0000055</t>
-        </is>
-      </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>belief about tolerability of drug</t>
-        </is>
-      </c>
-      <c r="C58" s="2" t="inlineStr">
-        <is>
-          <t>A belief about the degree to which a drug results in unpleasant or bothersome bodily reactions.</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr">
-        <is>
-          <t>belief about drug-related adverse events</t>
-        </is>
-      </c>
-      <c r="E58" s="2" t="n"/>
-      <c r="F58" s="2" t="n"/>
-      <c r="G58" s="2" t="n"/>
-      <c r="H58" s="2" t="n"/>
-      <c r="I58" s="2" t="n"/>
-      <c r="J58" s="2" t="n"/>
-      <c r="K58" s="2" t="inlineStr">
-        <is>
-          <t>Based on Stanulović, V., Hodolic, M., Mitsikostas, D. D., and Papadopoulos, D. (2022). Drug tolerability: how much ambiguity can be tolerated? A systematic review of the assessment of tolerability in clinical studies. British Journal of Clinical Pharmacology, 88(2), 551-565.</t>
-        </is>
-      </c>
-      <c r="L58" s="2" t="n"/>
-      <c r="M58" s="2" t="n"/>
-      <c r="N58" s="2" t="n"/>
-      <c r="O58" s="2" t="n"/>
-      <c r="P58" s="2" t="n"/>
-      <c r="Q58" s="2" t="inlineStr">
-        <is>
-          <t>LSR 3</t>
-        </is>
-      </c>
-      <c r="R58" s="2" t="inlineStr">
-        <is>
-          <t>Intervention outcomes and spillover effects</t>
-        </is>
-      </c>
-      <c r="S58" s="2" t="n"/>
-      <c r="T58" s="2" t="inlineStr">
-        <is>
-          <t>Obsolete</t>
-        </is>
-      </c>
-      <c r="U58" s="2" t="n"/>
-      <c r="V58" s="2" t="n"/>
-      <c r="W58" s="2" t="inlineStr">
-        <is>
-          <t>PS</t>
-        </is>
-      </c>
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>GMHO:0000269</t>
+        </is>
+      </c>
+      <c r="B58" s="4" t="inlineStr">
+        <is>
+          <t>belief about quality of life scale</t>
+        </is>
+      </c>
+      <c r="C58" s="4" t="inlineStr">
+        <is>
+          <t>A measurement scale that is used to measure a belief about quality of life.</t>
+        </is>
+      </c>
+      <c r="D58" s="4" t="inlineStr">
+        <is>
+          <t>measurement scale</t>
+        </is>
+      </c>
+      <c r="E58" s="4" t="inlineStr"/>
+      <c r="F58" s="4" t="inlineStr"/>
+      <c r="G58" s="4" t="inlineStr"/>
+      <c r="H58" s="4" t="inlineStr"/>
+      <c r="I58" s="4" t="inlineStr"/>
+      <c r="J58" s="4" t="inlineStr">
+        <is>
+          <t>Intervention outcomes and spillover effects</t>
+        </is>
+      </c>
+      <c r="K58" s="4" t="inlineStr"/>
+      <c r="L58" s="4" t="inlineStr"/>
+      <c r="M58" s="4" t="inlineStr"/>
+      <c r="N58" s="4" t="inlineStr"/>
+      <c r="O58" s="4" t="inlineStr"/>
+      <c r="P58" s="4" t="inlineStr"/>
+      <c r="Q58" s="4" t="inlineStr">
+        <is>
+          <t>LSR 6</t>
+        </is>
+      </c>
+      <c r="R58" s="4" t="inlineStr">
+        <is>
+          <t>Intervention outcomes and spillover effects</t>
+        </is>
+      </c>
+      <c r="S58" s="4" t="inlineStr"/>
+      <c r="T58" s="4" t="inlineStr">
+        <is>
+          <t>Proposed</t>
+        </is>
+      </c>
+      <c r="U58" s="4" t="inlineStr"/>
+      <c r="V58" s="4" t="inlineStr"/>
+      <c r="W58" s="4" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>GMHO:0000222</t>
+          <t>GMHO:0000055</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>belief scale</t>
+          <t>belief about tolerability of drug</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>A measurement scale that is used to measure beliefs.</t>
+          <t>A belief about the degree to which a drug results in unpleasant or bothersome bodily reactions.</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>measurement scale</t>
+          <t>belief about drug-related adverse events</t>
         </is>
       </c>
       <c r="E59" s="2" t="n"/>
@@ -4157,12 +4159,12 @@
       <c r="G59" s="2" t="n"/>
       <c r="H59" s="2" t="n"/>
       <c r="I59" s="2" t="n"/>
-      <c r="J59" s="2" t="inlineStr">
-        <is>
-          <t>Intervention outcomes and spillover effects</t>
-        </is>
-      </c>
-      <c r="K59" s="2" t="n"/>
+      <c r="J59" s="2" t="n"/>
+      <c r="K59" s="2" t="inlineStr">
+        <is>
+          <t>Based on Stanulović, V., Hodolic, M., Mitsikostas, D. D., and Papadopoulos, D. (2022). Drug tolerability: how much ambiguity can be tolerated? A systematic review of the assessment of tolerability in clinical studies. British Journal of Clinical Pharmacology, 88(2), 551-565.</t>
+        </is>
+      </c>
       <c r="L59" s="2" t="n"/>
       <c r="M59" s="2" t="n"/>
       <c r="N59" s="2" t="n"/>
@@ -4173,7 +4175,11 @@
           <t>LSR 3</t>
         </is>
       </c>
-      <c r="R59" s="2" t="n"/>
+      <c r="R59" s="2" t="inlineStr">
+        <is>
+          <t>Intervention outcomes and spillover effects</t>
+        </is>
+      </c>
       <c r="S59" s="2" t="n"/>
       <c r="T59" s="2" t="inlineStr">
         <is>
@@ -4189,47 +4195,57 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>MF:0000032</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>bodily disposition</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>A bodily disposition is a disposition that inheres in some extended organism.</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>disposition</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>Intervention outcomes and spillover effects</t>
-        </is>
-      </c>
-      <c r="Q60" t="inlineStr">
-        <is>
-          <t>LSR 1</t>
-        </is>
-      </c>
-      <c r="R60" t="inlineStr">
-        <is>
-          <t>Intervention outcomes and spillover effects</t>
-        </is>
-      </c>
-      <c r="T60" t="inlineStr">
-        <is>
-          <t>External</t>
-        </is>
-      </c>
-      <c r="W60" t="inlineStr">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>GMHO:0000222</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>belief scale</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>A measurement scale that is used to measure beliefs.</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>measurement scale</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="n"/>
+      <c r="F60" s="2" t="n"/>
+      <c r="G60" s="2" t="n"/>
+      <c r="H60" s="2" t="n"/>
+      <c r="I60" s="2" t="n"/>
+      <c r="J60" s="2" t="inlineStr">
+        <is>
+          <t>Intervention outcomes and spillover effects</t>
+        </is>
+      </c>
+      <c r="K60" s="2" t="n"/>
+      <c r="L60" s="2" t="n"/>
+      <c r="M60" s="2" t="n"/>
+      <c r="N60" s="2" t="n"/>
+      <c r="O60" s="2" t="n"/>
+      <c r="P60" s="2" t="n"/>
+      <c r="Q60" s="2" t="inlineStr">
+        <is>
+          <t>LSR 3</t>
+        </is>
+      </c>
+      <c r="R60" s="2" t="n"/>
+      <c r="S60" s="2" t="n"/>
+      <c r="T60" s="2" t="inlineStr">
+        <is>
+          <t>Obsolete</t>
+        </is>
+      </c>
+      <c r="U60" s="2" t="n"/>
+      <c r="V60" s="2" t="n"/>
+      <c r="W60" s="2" t="inlineStr">
         <is>
           <t>PS</t>
         </is>
@@ -4238,110 +4254,96 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
+          <t>MF:0000032</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>bodily disposition</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>A bodily disposition is a disposition that inheres in some extended organism.</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>disposition</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>Intervention outcomes and spillover effects</t>
+        </is>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>LSR 1</t>
+        </is>
+      </c>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>Intervention outcomes and spillover effects</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>External</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>PS</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
           <t>OGMS:0000060</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr">
+      <c r="B62" t="inlineStr">
         <is>
           <t>bodily process</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr">
+      <c r="C62" t="inlineStr">
         <is>
           <t>A process in which at least one bodily component of an organism participates.</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr">
+      <c r="D62" t="inlineStr">
         <is>
           <t>process</t>
         </is>
       </c>
-      <c r="T61" t="inlineStr">
+      <c r="T62" t="inlineStr">
         <is>
           <t>External</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
-        <is>
-          <t>GMHO:0000056</t>
-        </is>
-      </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>body mass index</t>
-        </is>
-      </c>
-      <c r="C62" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">A data item that is derived by dividing the body weight be the square of the body height. </t>
-        </is>
-      </c>
-      <c r="D62" s="2" t="inlineStr">
-        <is>
-          <t>data item</t>
-        </is>
-      </c>
-      <c r="E62" s="2" t="n"/>
-      <c r="F62" s="2" t="n"/>
-      <c r="G62" s="2" t="n"/>
-      <c r="H62" s="2" t="n"/>
-      <c r="I62" s="2" t="n"/>
-      <c r="J62" s="2" t="n"/>
-      <c r="K62" s="2" t="inlineStr">
-        <is>
-          <t>Based on Nuttall F. Q. (2015). Body Mass Index: Obesity, BMI, and Health: A Critical Review. Nutrition today, 50(3), 117–128. https://doi.org/10.1097/NT.0000000000000092</t>
-        </is>
-      </c>
-      <c r="L62" s="2" t="n"/>
-      <c r="M62" s="2" t="n"/>
-      <c r="N62" s="2" t="n"/>
-      <c r="O62" s="2" t="n"/>
-      <c r="P62" s="2" t="n"/>
-      <c r="Q62" s="2" t="inlineStr">
-        <is>
-          <t>LSR 3</t>
-        </is>
-      </c>
-      <c r="R62" s="2" t="inlineStr">
-        <is>
-          <t>Intervention outcomes and spillover effects</t>
-        </is>
-      </c>
-      <c r="S62" s="2" t="n"/>
-      <c r="T62" s="2" t="inlineStr">
-        <is>
-          <t>Obsolete</t>
-        </is>
-      </c>
-      <c r="U62" s="2" t="n"/>
-      <c r="V62" s="2" t="n"/>
-      <c r="W62" s="2" t="inlineStr">
-        <is>
-          <t>PS</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>GMHO:0000057</t>
+          <t>GMHO:0000056</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>body weight</t>
+          <t>body mass index</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>Weight of an organism.</t>
+          <t xml:space="preserve">A data item that is derived by dividing the body weight be the square of the body height. </t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>weight</t>
+          <t>data item</t>
         </is>
       </c>
       <c r="E63" s="2" t="n"/>
@@ -4350,7 +4352,11 @@
       <c r="H63" s="2" t="n"/>
       <c r="I63" s="2" t="n"/>
       <c r="J63" s="2" t="n"/>
-      <c r="K63" s="2" t="n"/>
+      <c r="K63" s="2" t="inlineStr">
+        <is>
+          <t>Based on Nuttall F. Q. (2015). Body Mass Index: Obesity, BMI, and Health: A Critical Review. Nutrition today, 50(3), 117–128. https://doi.org/10.1097/NT.0000000000000092</t>
+        </is>
+      </c>
       <c r="L63" s="2" t="n"/>
       <c r="M63" s="2" t="n"/>
       <c r="N63" s="2" t="n"/>
@@ -4373,152 +4379,150 @@
         </is>
       </c>
       <c r="U63" s="2" t="n"/>
-      <c r="V63" s="2" t="inlineStr">
+      <c r="V63" s="2" t="n"/>
+      <c r="W63" s="2" t="inlineStr">
+        <is>
+          <t>PS</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>GMHO:0000057</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>body weight</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>Weight of an organism.</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>weight</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="n"/>
+      <c r="F64" s="2" t="n"/>
+      <c r="G64" s="2" t="n"/>
+      <c r="H64" s="2" t="n"/>
+      <c r="I64" s="2" t="n"/>
+      <c r="J64" s="2" t="n"/>
+      <c r="K64" s="2" t="n"/>
+      <c r="L64" s="2" t="n"/>
+      <c r="M64" s="2" t="n"/>
+      <c r="N64" s="2" t="n"/>
+      <c r="O64" s="2" t="n"/>
+      <c r="P64" s="2" t="n"/>
+      <c r="Q64" s="2" t="inlineStr">
+        <is>
+          <t>LSR 3</t>
+        </is>
+      </c>
+      <c r="R64" s="2" t="inlineStr">
+        <is>
+          <t>Intervention outcomes and spillover effects</t>
+        </is>
+      </c>
+      <c r="S64" s="2" t="n"/>
+      <c r="T64" s="2" t="inlineStr">
+        <is>
+          <t>Obsolete</t>
+        </is>
+      </c>
+      <c r="U64" s="2" t="n"/>
+      <c r="V64" s="2" t="inlineStr">
         <is>
           <t>Parent class needs to be imported as external entity</t>
         </is>
       </c>
-      <c r="W63" s="2" t="inlineStr">
-        <is>
-          <t>PS</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="3" t="inlineStr">
-        <is>
-          <t>GMHO:0000257</t>
-        </is>
-      </c>
-      <c r="B64" s="3" t="inlineStr">
-        <is>
-          <t>constipation adverse event following intervention</t>
-        </is>
-      </c>
-      <c r="C64" s="3" t="inlineStr">
-        <is>
-          <t>A digestive system adverse event following an intervention that involves the abnormally delayed or infrequent passage of dry hardened feces.</t>
-        </is>
-      </c>
-      <c r="D64" s="3" t="inlineStr">
-        <is>
-          <t>digestive system adverse event following intervention</t>
-        </is>
-      </c>
-      <c r="E64" s="3" t="n"/>
-      <c r="F64" s="3" t="n"/>
-      <c r="G64" s="3" t="n"/>
-      <c r="H64" s="3" t="n"/>
-      <c r="I64" s="3" t="n"/>
-      <c r="J64" s="3" t="inlineStr">
-        <is>
-          <t>Intervention outcomes and spillover effects</t>
-        </is>
-      </c>
-      <c r="K64" s="3" t="inlineStr">
-        <is>
-          <t>http://purl.obolibrary.org/obo/SYMP_0019180</t>
-        </is>
-      </c>
-      <c r="L64" s="3" t="inlineStr">
-        <is>
-          <t>SYMP:0019180</t>
-        </is>
-      </c>
-      <c r="M64" s="3" t="inlineStr">
-        <is>
-          <t>constipation</t>
-        </is>
-      </c>
-      <c r="N64" s="3" t="n"/>
-      <c r="O64" s="3" t="n"/>
-      <c r="P64" s="3" t="n"/>
-      <c r="Q64" s="3" t="inlineStr">
-        <is>
-          <t>LSR 1</t>
-        </is>
-      </c>
-      <c r="R64" s="3" t="inlineStr">
-        <is>
-          <t>Intervention outcomes and spillover effects</t>
-        </is>
-      </c>
-      <c r="S64" s="3" t="n"/>
-      <c r="T64" s="3" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="U64" s="3" t="n"/>
-      <c r="V64" s="3" t="n"/>
-      <c r="W64" s="3" t="n"/>
+      <c r="W64" s="2" t="inlineStr">
+        <is>
+          <t>PS</t>
+        </is>
+      </c>
     </row>
     <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>IAO:0000027</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>data item</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>An information content entity that is intended to be a truthful statement about something (modulo, e.g., measurement precision or other systematic errors) and is constructed/acquired by a method which reliably tends to produce (approximately) truthful statements.</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>information content entity</t>
-        </is>
-      </c>
-      <c r="J65" t="inlineStr">
-        <is>
-          <t>Intervention outcomes and spillover effects</t>
-        </is>
-      </c>
-      <c r="Q65" t="inlineStr">
-        <is>
-          <t>LSR 1</t>
-        </is>
-      </c>
-      <c r="R65" t="inlineStr">
-        <is>
-          <t>Intervention outcomes and spillover effects</t>
-        </is>
-      </c>
-      <c r="T65" t="inlineStr">
-        <is>
-          <t>External</t>
-        </is>
-      </c>
-      <c r="W65" t="inlineStr">
-        <is>
-          <t>PS</t>
-        </is>
-      </c>
+      <c r="A65" s="4" t="inlineStr">
+        <is>
+          <t>GMHO:0000270</t>
+        </is>
+      </c>
+      <c r="B65" s="4" t="inlineStr">
+        <is>
+          <t>cognitive bias scale</t>
+        </is>
+      </c>
+      <c r="C65" s="4" t="inlineStr">
+        <is>
+          <t>A measurement scale that is used to measure a cognitive bias.</t>
+        </is>
+      </c>
+      <c r="D65" s="4" t="inlineStr">
+        <is>
+          <t>measurement scale</t>
+        </is>
+      </c>
+      <c r="E65" s="4" t="inlineStr"/>
+      <c r="F65" s="4" t="inlineStr"/>
+      <c r="G65" s="4" t="inlineStr"/>
+      <c r="H65" s="4" t="inlineStr"/>
+      <c r="I65" s="4" t="inlineStr"/>
+      <c r="J65" s="4" t="inlineStr">
+        <is>
+          <t>Intervention outcomes and spillover effects</t>
+        </is>
+      </c>
+      <c r="K65" s="4" t="inlineStr"/>
+      <c r="L65" s="4" t="inlineStr"/>
+      <c r="M65" s="4" t="inlineStr"/>
+      <c r="N65" s="4" t="inlineStr"/>
+      <c r="O65" s="4" t="inlineStr"/>
+      <c r="P65" s="4" t="inlineStr"/>
+      <c r="Q65" s="4" t="inlineStr">
+        <is>
+          <t>LSR 6</t>
+        </is>
+      </c>
+      <c r="R65" s="4" t="inlineStr">
+        <is>
+          <t>Intervention outcomes and spillover effects</t>
+        </is>
+      </c>
+      <c r="S65" s="4" t="inlineStr"/>
+      <c r="T65" s="4" t="inlineStr">
+        <is>
+          <t>Proposed</t>
+        </is>
+      </c>
+      <c r="U65" s="4" t="inlineStr"/>
+      <c r="V65" s="4" t="inlineStr"/>
+      <c r="W65" s="4" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="3" t="inlineStr">
         <is>
-          <t>GMHO:0000256</t>
+          <t>GMHO:0000257</t>
         </is>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>datatype for outcome</t>
+          <t>constipation adverse event following intervention</t>
         </is>
       </c>
       <c r="C66" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">A directive information entity that indicates how outcomes of an intervention were obtained. </t>
+          <t>A digestive system adverse event following an intervention that involves the abnormally delayed or infrequent passage of dry hardened feces.</t>
         </is>
       </c>
       <c r="D66" s="3" t="inlineStr">
         <is>
-          <t>directive information entity</t>
+          <t>digestive system adverse event following intervention</t>
         </is>
       </c>
       <c r="E66" s="3" t="n"/>
@@ -4531,18 +4535,34 @@
           <t>Intervention outcomes and spillover effects</t>
         </is>
       </c>
-      <c r="K66" s="3" t="n"/>
-      <c r="L66" s="3" t="n"/>
-      <c r="M66" s="3" t="n"/>
+      <c r="K66" s="3" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/SYMP_0019180</t>
+        </is>
+      </c>
+      <c r="L66" s="3" t="inlineStr">
+        <is>
+          <t>SYMP:0019180</t>
+        </is>
+      </c>
+      <c r="M66" s="3" t="inlineStr">
+        <is>
+          <t>constipation</t>
+        </is>
+      </c>
       <c r="N66" s="3" t="n"/>
       <c r="O66" s="3" t="n"/>
       <c r="P66" s="3" t="n"/>
       <c r="Q66" s="3" t="inlineStr">
         <is>
-          <t>LSR 3</t>
-        </is>
-      </c>
-      <c r="R66" s="3" t="n"/>
+          <t>LSR 1</t>
+        </is>
+      </c>
+      <c r="R66" s="3" t="inlineStr">
+        <is>
+          <t>Intervention outcomes and spillover effects</t>
+        </is>
+      </c>
       <c r="S66" s="3" t="n"/>
       <c r="T66" s="3" t="inlineStr">
         <is>
@@ -4554,224 +4574,194 @@
       <c r="W66" s="3" t="n"/>
     </row>
     <row r="67">
-      <c r="A67" s="2" t="inlineStr">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>IAO:0000027</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>data item</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>An information content entity that is intended to be a truthful statement about something (modulo, e.g., measurement precision or other systematic errors) and is constructed/acquired by a method which reliably tends to produce (approximately) truthful statements.</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>information content entity</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>Intervention outcomes and spillover effects</t>
+        </is>
+      </c>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>LSR 1</t>
+        </is>
+      </c>
+      <c r="R67" t="inlineStr">
+        <is>
+          <t>Intervention outcomes and spillover effects</t>
+        </is>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>External</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>PS</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="3" t="inlineStr">
+        <is>
+          <t>GMHO:0000256</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="inlineStr">
+        <is>
+          <t>datatype for outcome</t>
+        </is>
+      </c>
+      <c r="C68" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A directive information entity that indicates how outcomes of an intervention were obtained. </t>
+        </is>
+      </c>
+      <c r="D68" s="3" t="inlineStr">
+        <is>
+          <t>directive information entity</t>
+        </is>
+      </c>
+      <c r="E68" s="3" t="n"/>
+      <c r="F68" s="3" t="n"/>
+      <c r="G68" s="3" t="n"/>
+      <c r="H68" s="3" t="n"/>
+      <c r="I68" s="3" t="n"/>
+      <c r="J68" s="3" t="inlineStr">
+        <is>
+          <t>Intervention outcomes and spillover effects</t>
+        </is>
+      </c>
+      <c r="K68" s="3" t="n"/>
+      <c r="L68" s="3" t="n"/>
+      <c r="M68" s="3" t="n"/>
+      <c r="N68" s="3" t="n"/>
+      <c r="O68" s="3" t="n"/>
+      <c r="P68" s="3" t="n"/>
+      <c r="Q68" s="3" t="inlineStr">
+        <is>
+          <t>LSR 3</t>
+        </is>
+      </c>
+      <c r="R68" s="3" t="n"/>
+      <c r="S68" s="3" t="n"/>
+      <c r="T68" s="3" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="U68" s="3" t="n"/>
+      <c r="V68" s="3" t="n"/>
+      <c r="W68" s="3" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
         <is>
           <t>GMHO:0000058</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
+      <c r="B69" s="2" t="inlineStr">
         <is>
           <t>death due to accidents following an intervention</t>
         </is>
       </c>
-      <c r="C67" s="2" t="inlineStr">
+      <c r="C69" s="2" t="inlineStr">
         <is>
           <t>A death following an intervention that involves a participant dying as a result of an accident.</t>
         </is>
       </c>
-      <c r="D67" s="2" t="inlineStr">
+      <c r="D69" s="2" t="inlineStr">
         <is>
           <t>death following an intervention</t>
         </is>
       </c>
-      <c r="E67" s="2" t="n"/>
-      <c r="F67" s="2" t="n"/>
-      <c r="G67" s="2" t="n"/>
-      <c r="H67" s="2" t="n"/>
-      <c r="I67" s="2" t="n"/>
-      <c r="J67" s="2" t="n"/>
-      <c r="K67" s="2" t="n"/>
-      <c r="L67" s="2" t="n"/>
-      <c r="M67" s="2" t="n"/>
-      <c r="N67" s="2" t="n"/>
-      <c r="O67" s="2" t="n"/>
-      <c r="P67" s="2" t="n"/>
-      <c r="Q67" s="2" t="inlineStr">
+      <c r="E69" s="2" t="n"/>
+      <c r="F69" s="2" t="n"/>
+      <c r="G69" s="2" t="n"/>
+      <c r="H69" s="2" t="n"/>
+      <c r="I69" s="2" t="n"/>
+      <c r="J69" s="2" t="n"/>
+      <c r="K69" s="2" t="n"/>
+      <c r="L69" s="2" t="n"/>
+      <c r="M69" s="2" t="n"/>
+      <c r="N69" s="2" t="n"/>
+      <c r="O69" s="2" t="n"/>
+      <c r="P69" s="2" t="n"/>
+      <c r="Q69" s="2" t="inlineStr">
         <is>
           <t>LSR 3</t>
         </is>
       </c>
-      <c r="R67" s="2" t="inlineStr">
-        <is>
-          <t>Intervention outcomes and spillover effects</t>
-        </is>
-      </c>
-      <c r="S67" s="2" t="n"/>
-      <c r="T67" s="2" t="inlineStr">
+      <c r="R69" s="2" t="inlineStr">
+        <is>
+          <t>Intervention outcomes and spillover effects</t>
+        </is>
+      </c>
+      <c r="S69" s="2" t="n"/>
+      <c r="T69" s="2" t="inlineStr">
         <is>
           <t>Obsolete</t>
         </is>
       </c>
-      <c r="U67" s="2" t="n"/>
-      <c r="V67" s="2" t="n"/>
-      <c r="W67" s="2" t="inlineStr">
-        <is>
-          <t>PS</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
-        <is>
-          <t>GMHO:0000059</t>
-        </is>
-      </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>death due to natural causes following an intervention</t>
-        </is>
-      </c>
-      <c r="C68" s="2" t="inlineStr">
-        <is>
-          <t>A death following an intervention that results from an illness or its complications or an internal bodily malfunction that is not directly caused by external events.</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr">
-        <is>
-          <t>death following an intervention</t>
-        </is>
-      </c>
-      <c r="E68" s="2" t="n"/>
-      <c r="F68" s="2" t="n"/>
-      <c r="G68" s="2" t="n"/>
-      <c r="H68" s="2" t="n"/>
-      <c r="I68" s="2" t="n"/>
-      <c r="J68" s="2" t="n"/>
-      <c r="K68" s="2" t="inlineStr">
-        <is>
-          <t>Based on https://en.wikipedia.org/wiki/Manner_of_death</t>
-        </is>
-      </c>
-      <c r="L68" s="2" t="n"/>
-      <c r="M68" s="2" t="n"/>
-      <c r="N68" s="2" t="n"/>
-      <c r="O68" s="2" t="n"/>
-      <c r="P68" s="2" t="n"/>
-      <c r="Q68" s="2" t="inlineStr">
-        <is>
-          <t>LSR 3</t>
-        </is>
-      </c>
-      <c r="R68" s="2" t="inlineStr">
-        <is>
-          <t>Intervention outcomes and spillover effects</t>
-        </is>
-      </c>
-      <c r="S68" s="2" t="n"/>
-      <c r="T68" s="2" t="inlineStr">
-        <is>
-          <t>Obsolete</t>
-        </is>
-      </c>
-      <c r="U68" s="2" t="n"/>
-      <c r="V68" s="2" t="n"/>
-      <c r="W68" s="2" t="inlineStr">
-        <is>
-          <t>PS</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="3" t="inlineStr">
-        <is>
-          <t>GMHO:0000060</t>
-        </is>
-      </c>
-      <c r="B69" s="3" t="inlineStr">
-        <is>
-          <t>death following an intervention</t>
-        </is>
-      </c>
-      <c r="C69" s="3" t="inlineStr">
-        <is>
-          <t>A serious adverse event following an intervention that has an outcome of death.</t>
-        </is>
-      </c>
-      <c r="D69" s="3" t="inlineStr">
-        <is>
-          <t>serious adverse event following an intervention</t>
-        </is>
-      </c>
-      <c r="E69" s="3" t="n"/>
-      <c r="F69" s="3" t="n"/>
-      <c r="G69" s="3" t="n"/>
-      <c r="H69" s="3" t="n"/>
-      <c r="I69" s="3" t="n"/>
-      <c r="J69" s="3" t="n"/>
-      <c r="K69" s="3" t="inlineStr">
-        <is>
-          <t>Based on http://purl.obolibrary.org/obo/OAE_0000632</t>
-        </is>
-      </c>
-      <c r="L69" s="3" t="inlineStr">
-        <is>
-          <t>http://purl.obolibrary.org/obo/OAE_0000632</t>
-        </is>
-      </c>
-      <c r="M69" s="3" t="inlineStr">
-        <is>
-          <t>death</t>
-        </is>
-      </c>
-      <c r="N69" s="3" t="n"/>
-      <c r="O69" s="3" t="n"/>
-      <c r="P69" s="3" t="n"/>
-      <c r="Q69" s="3" t="inlineStr">
-        <is>
-          <t>LSR 3</t>
-        </is>
-      </c>
-      <c r="R69" s="3" t="inlineStr">
-        <is>
-          <t>Intervention outcomes and spillover effects</t>
-        </is>
-      </c>
-      <c r="S69" s="3" t="n"/>
-      <c r="T69" s="3" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="U69" s="3" t="n"/>
-      <c r="V69" s="3" t="n"/>
-      <c r="W69" s="3" t="inlineStr">
-        <is>
-          <t>PS; MS</t>
+      <c r="U69" s="2" t="n"/>
+      <c r="V69" s="2" t="n"/>
+      <c r="W69" s="2" t="inlineStr">
+        <is>
+          <t>PS</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>GMHO:0000061</t>
+          <t>GMHO:0000059</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>depression symptom</t>
+          <t>death due to natural causes following an intervention</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>A symptom that is related to a depression diagnosis.</t>
+          <t>A death following an intervention that results from an illness or its complications or an internal bodily malfunction that is not directly caused by external events.</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>symptom</t>
+          <t>death following an intervention</t>
         </is>
       </c>
       <c r="E70" s="2" t="n"/>
       <c r="F70" s="2" t="n"/>
-      <c r="G70" s="2" t="inlineStr">
-        <is>
-          <t>depressive symptom</t>
-        </is>
-      </c>
+      <c r="G70" s="2" t="n"/>
       <c r="H70" s="2" t="n"/>
       <c r="I70" s="2" t="n"/>
       <c r="J70" s="2" t="n"/>
-      <c r="K70" s="2" t="n"/>
+      <c r="K70" s="2" t="inlineStr">
+        <is>
+          <t>Based on https://en.wikipedia.org/wiki/Manner_of_death</t>
+        </is>
+      </c>
       <c r="L70" s="2" t="n"/>
       <c r="M70" s="2" t="n"/>
       <c r="N70" s="2" t="n"/>
@@ -4804,22 +4794,22 @@
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>GMHO:0000062</t>
+          <t>GMHO:0000060</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>depression symptom severity</t>
+          <t>death following an intervention</t>
         </is>
       </c>
       <c r="C71" s="3" t="inlineStr">
         <is>
-          <t>Symptom severity that is associated with a depression symptom.</t>
+          <t>A serious adverse event following an intervention that has an outcome of death.</t>
         </is>
       </c>
       <c r="D71" s="3" t="inlineStr">
         <is>
-          <t>symptom severity</t>
+          <t>serious adverse event following an intervention</t>
         </is>
       </c>
       <c r="E71" s="3" t="n"/>
@@ -4828,9 +4818,21 @@
       <c r="H71" s="3" t="n"/>
       <c r="I71" s="3" t="n"/>
       <c r="J71" s="3" t="n"/>
-      <c r="K71" s="3" t="n"/>
-      <c r="L71" s="3" t="n"/>
-      <c r="M71" s="3" t="n"/>
+      <c r="K71" s="3" t="inlineStr">
+        <is>
+          <t>Based on http://purl.obolibrary.org/obo/OAE_0000632</t>
+        </is>
+      </c>
+      <c r="L71" s="3" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/OAE_0000632</t>
+        </is>
+      </c>
+      <c r="M71" s="3" t="inlineStr">
+        <is>
+          <t>death</t>
+        </is>
+      </c>
       <c r="N71" s="3" t="n"/>
       <c r="O71" s="3" t="n"/>
       <c r="P71" s="3" t="n"/>
@@ -4854,62 +4856,66 @@
       <c r="V71" s="3" t="n"/>
       <c r="W71" s="3" t="inlineStr">
         <is>
-          <t>PS</t>
+          <t>PS; MS</t>
         </is>
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="3" t="inlineStr">
-        <is>
-          <t>GMHO:0000223</t>
-        </is>
-      </c>
-      <c r="B72" s="3" t="inlineStr">
-        <is>
-          <t>depression symptom severity scale</t>
-        </is>
-      </c>
-      <c r="C72" s="3" t="inlineStr">
-        <is>
-          <t>A measurement scale that is used to measure depression symptom severity.</t>
-        </is>
-      </c>
-      <c r="D72" s="3" t="inlineStr">
-        <is>
-          <t>measurement scale</t>
-        </is>
-      </c>
-      <c r="E72" s="3" t="n"/>
-      <c r="F72" s="3" t="n"/>
-      <c r="G72" s="3" t="n"/>
-      <c r="H72" s="3" t="n"/>
-      <c r="I72" s="3" t="n"/>
-      <c r="J72" s="3" t="inlineStr">
-        <is>
-          <t>Intervention outcomes and spillover effects</t>
-        </is>
-      </c>
-      <c r="K72" s="3" t="n"/>
-      <c r="L72" s="3" t="n"/>
-      <c r="M72" s="3" t="n"/>
-      <c r="N72" s="3" t="n"/>
-      <c r="O72" s="3" t="n"/>
-      <c r="P72" s="3" t="n"/>
-      <c r="Q72" s="3" t="inlineStr">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>GMHO:0000061</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>depression symptom</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>A symptom that is related to a depression diagnosis.</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>symptom</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="n"/>
+      <c r="F72" s="2" t="n"/>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>depressive symptom</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="n"/>
+      <c r="I72" s="2" t="n"/>
+      <c r="J72" s="2" t="n"/>
+      <c r="K72" s="2" t="n"/>
+      <c r="L72" s="2" t="n"/>
+      <c r="M72" s="2" t="n"/>
+      <c r="N72" s="2" t="n"/>
+      <c r="O72" s="2" t="n"/>
+      <c r="P72" s="2" t="n"/>
+      <c r="Q72" s="2" t="inlineStr">
         <is>
           <t>LSR 3</t>
         </is>
       </c>
-      <c r="R72" s="3" t="n"/>
-      <c r="S72" s="3" t="n"/>
-      <c r="T72" s="3" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="U72" s="3" t="n"/>
-      <c r="V72" s="3" t="n"/>
-      <c r="W72" s="3" t="inlineStr">
+      <c r="R72" s="2" t="inlineStr">
+        <is>
+          <t>Intervention outcomes and spillover effects</t>
+        </is>
+      </c>
+      <c r="S72" s="2" t="n"/>
+      <c r="T72" s="2" t="inlineStr">
+        <is>
+          <t>Obsolete</t>
+        </is>
+      </c>
+      <c r="U72" s="2" t="n"/>
+      <c r="V72" s="2" t="n"/>
+      <c r="W72" s="2" t="inlineStr">
         <is>
           <t>PS</t>
         </is>
@@ -4918,22 +4924,22 @@
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>GMHO:0000178</t>
+          <t>GMHO:0000062</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>digestive system adverse event following intervention</t>
+          <t>depression symptom severity</t>
         </is>
       </c>
       <c r="C73" s="3" t="inlineStr">
         <is>
-          <t>An adverse event following an intervention that occurs in the digestive system.</t>
+          <t>Symptom severity that is associated with a depression symptom.</t>
         </is>
       </c>
       <c r="D73" s="3" t="inlineStr">
         <is>
-          <t>adverse event following an intervention</t>
+          <t>symptom severity</t>
         </is>
       </c>
       <c r="E73" s="3" t="n"/>
@@ -4942,28 +4948,15 @@
       <c r="H73" s="3" t="n"/>
       <c r="I73" s="3" t="n"/>
       <c r="J73" s="3" t="n"/>
-      <c r="K73" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">cross reference: http://purl.obolibrary.org/obo/OAE_0000439
-</t>
-        </is>
-      </c>
-      <c r="L73" s="3" t="inlineStr">
-        <is>
-          <t>http://purl.obolibrary.org/obo/OAE_0000439</t>
-        </is>
-      </c>
-      <c r="M73" s="3" t="inlineStr">
-        <is>
-          <t>digestive system adverse event</t>
-        </is>
-      </c>
+      <c r="K73" s="3" t="n"/>
+      <c r="L73" s="3" t="n"/>
+      <c r="M73" s="3" t="n"/>
       <c r="N73" s="3" t="n"/>
       <c r="O73" s="3" t="n"/>
       <c r="P73" s="3" t="n"/>
       <c r="Q73" s="3" t="inlineStr">
         <is>
-          <t>LSR 1</t>
+          <t>LSR 3</t>
         </is>
       </c>
       <c r="R73" s="3" t="inlineStr">
@@ -4981,51 +4974,81 @@
       <c r="V73" s="3" t="n"/>
       <c r="W73" s="3" t="inlineStr">
         <is>
-          <t>PS; MS</t>
+          <t>PS</t>
         </is>
       </c>
     </row>
     <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>IAO:0000033</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>directive information entity</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>An information content entity whose concretizations indicate to their bearer how to realize them in a process.</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>information content entity</t>
-        </is>
-      </c>
-      <c r="T74" t="inlineStr">
-        <is>
-          <t>External</t>
+      <c r="A74" s="3" t="inlineStr">
+        <is>
+          <t>GMHO:0000223</t>
+        </is>
+      </c>
+      <c r="B74" s="3" t="inlineStr">
+        <is>
+          <t>depression symptom severity scale</t>
+        </is>
+      </c>
+      <c r="C74" s="3" t="inlineStr">
+        <is>
+          <t>A measurement scale that is used to measure depression symptom severity.</t>
+        </is>
+      </c>
+      <c r="D74" s="3" t="inlineStr">
+        <is>
+          <t>measurement scale</t>
+        </is>
+      </c>
+      <c r="E74" s="3" t="n"/>
+      <c r="F74" s="3" t="n"/>
+      <c r="G74" s="3" t="n"/>
+      <c r="H74" s="3" t="n"/>
+      <c r="I74" s="3" t="n"/>
+      <c r="J74" s="3" t="inlineStr">
+        <is>
+          <t>Intervention outcomes and spillover effects</t>
+        </is>
+      </c>
+      <c r="K74" s="3" t="n"/>
+      <c r="L74" s="3" t="n"/>
+      <c r="M74" s="3" t="n"/>
+      <c r="N74" s="3" t="n"/>
+      <c r="O74" s="3" t="n"/>
+      <c r="P74" s="3" t="n"/>
+      <c r="Q74" s="3" t="inlineStr">
+        <is>
+          <t>LSR 3</t>
+        </is>
+      </c>
+      <c r="R74" s="3" t="n"/>
+      <c r="S74" s="3" t="n"/>
+      <c r="T74" s="3" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="U74" s="3" t="n"/>
+      <c r="V74" s="3" t="n"/>
+      <c r="W74" s="3" t="inlineStr">
+        <is>
+          <t>PS</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>GMHO:0000179</t>
+          <t>GMHO:0000178</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>dizziness following intervention</t>
+          <t>digestive system adverse event following intervention</t>
         </is>
       </c>
       <c r="C75" s="3" t="inlineStr">
         <is>
-          <t>An adverse event following an intervention that involves experiencing dizziness.</t>
+          <t>An adverse event following an intervention that occurs in the digestive system.</t>
         </is>
       </c>
       <c r="D75" s="3" t="inlineStr">
@@ -5041,18 +5064,18 @@
       <c r="J75" s="3" t="n"/>
       <c r="K75" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">cross reference: http://purl.obolibrary.org/obo/OAE_0000388
+          <t xml:space="preserve">cross reference: http://purl.obolibrary.org/obo/OAE_0000439
 </t>
         </is>
       </c>
       <c r="L75" s="3" t="inlineStr">
         <is>
-          <t>http://purl.obolibrary.org/obo/OAE_0000388</t>
+          <t>http://purl.obolibrary.org/obo/OAE_0000439</t>
         </is>
       </c>
       <c r="M75" s="3" t="inlineStr">
         <is>
-          <t>dizziness</t>
+          <t>digestive system adverse event</t>
         </is>
       </c>
       <c r="N75" s="3" t="n"/>
@@ -5060,7 +5083,7 @@
       <c r="P75" s="3" t="n"/>
       <c r="Q75" s="3" t="inlineStr">
         <is>
-          <t>LSR 1, LSR 3</t>
+          <t>LSR 1</t>
         </is>
       </c>
       <c r="R75" s="3" t="inlineStr">
@@ -5083,94 +5106,51 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="3" t="inlineStr">
-        <is>
-          <t>GMHO:0000063</t>
-        </is>
-      </c>
-      <c r="B76" s="3" t="inlineStr">
-        <is>
-          <t>drug-induced movement disorder following intervention</t>
-        </is>
-      </c>
-      <c r="C76" s="3" t="inlineStr">
-        <is>
-          <t>An adverse event following a pharmacological intervention that involves reduced abilities to control movements.</t>
-        </is>
-      </c>
-      <c r="D76" s="3" t="inlineStr">
-        <is>
-          <t>adverse event following an intervention</t>
-        </is>
-      </c>
-      <c r="E76" s="3" t="n"/>
-      <c r="F76" s="3" t="n"/>
-      <c r="G76" s="3" t="inlineStr">
-        <is>
-          <t>extrapyramidal symptom following intervention</t>
-        </is>
-      </c>
-      <c r="H76" s="3" t="n"/>
-      <c r="I76" s="3" t="n"/>
-      <c r="J76" s="3" t="n"/>
-      <c r="K76" s="3" t="inlineStr">
-        <is>
-          <t>"Based on https://www.ncbi.nlm.nih.gov/books/NBK534115/
-Based on http://purl.obolibrary.org/obo/OAE_0000581"</t>
-        </is>
-      </c>
-      <c r="L76" s="3" t="inlineStr">
-        <is>
-          <t>http://purl.obolibrary.org/obo/OAE_0000581</t>
-        </is>
-      </c>
-      <c r="M76" s="3" t="n"/>
-      <c r="N76" s="3" t="n"/>
-      <c r="O76" s="3" t="n"/>
-      <c r="P76" s="3" t="n"/>
-      <c r="Q76" s="3" t="inlineStr">
-        <is>
-          <t>LSR 3</t>
-        </is>
-      </c>
-      <c r="R76" s="3" t="inlineStr">
-        <is>
-          <t>Intervention outcomes and spillover effects</t>
-        </is>
-      </c>
-      <c r="S76" s="3" t="n"/>
-      <c r="T76" s="3" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="U76" s="3" t="n"/>
-      <c r="V76" s="3" t="n"/>
-      <c r="W76" s="3" t="inlineStr">
-        <is>
-          <t>PS; MS</t>
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>IAO:0000033</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>directive information entity</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>An information content entity whose concretizations indicate to their bearer how to realize them in a process.</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>information content entity</t>
+        </is>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>External</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="inlineStr">
         <is>
-          <t>GMHO:0000180</t>
+          <t>GMHO:0000179</t>
         </is>
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>dry mouth following intervention</t>
+          <t>dizziness following intervention</t>
         </is>
       </c>
       <c r="C77" s="3" t="inlineStr">
         <is>
-          <t>A digestive system adverse event following intervention that involves experiencing dry mouth.</t>
+          <t>An adverse event following an intervention that involves experiencing dizziness.</t>
         </is>
       </c>
       <c r="D77" s="3" t="inlineStr">
         <is>
-          <t>digestive system adverse event following intervention</t>
+          <t>adverse event following an intervention</t>
         </is>
       </c>
       <c r="E77" s="3" t="n"/>
@@ -5181,18 +5161,18 @@
       <c r="J77" s="3" t="n"/>
       <c r="K77" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">cross reference: http://purl.obolibrary.org/obo/OAE_0000505
+          <t xml:space="preserve">cross reference: http://purl.obolibrary.org/obo/OAE_0000388
 </t>
         </is>
       </c>
       <c r="L77" s="3" t="inlineStr">
         <is>
-          <t>http://purl.obolibrary.org/obo/OAE_0000505</t>
+          <t>http://purl.obolibrary.org/obo/OAE_0000388</t>
         </is>
       </c>
       <c r="M77" s="3" t="inlineStr">
         <is>
-          <t>dry mouth</t>
+          <t>dizziness</t>
         </is>
       </c>
       <c r="N77" s="3" t="n"/>
@@ -5200,7 +5180,7 @@
       <c r="P77" s="3" t="n"/>
       <c r="Q77" s="3" t="inlineStr">
         <is>
-          <t>LSR 1</t>
+          <t>LSR 1, LSR 3</t>
         </is>
       </c>
       <c r="R77" s="3" t="inlineStr">
@@ -5223,437 +5203,463 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="2" t="inlineStr">
+      <c r="A78" s="3" t="inlineStr">
+        <is>
+          <t>GMHO:0000063</t>
+        </is>
+      </c>
+      <c r="B78" s="3" t="inlineStr">
+        <is>
+          <t>drug-induced movement disorder following intervention</t>
+        </is>
+      </c>
+      <c r="C78" s="3" t="inlineStr">
+        <is>
+          <t>An adverse event following a pharmacological intervention that involves reduced abilities to control movements.</t>
+        </is>
+      </c>
+      <c r="D78" s="3" t="inlineStr">
+        <is>
+          <t>adverse event following an intervention</t>
+        </is>
+      </c>
+      <c r="E78" s="3" t="n"/>
+      <c r="F78" s="3" t="n"/>
+      <c r="G78" s="3" t="inlineStr">
+        <is>
+          <t>extrapyramidal symptom following intervention</t>
+        </is>
+      </c>
+      <c r="H78" s="3" t="n"/>
+      <c r="I78" s="3" t="n"/>
+      <c r="J78" s="3" t="n"/>
+      <c r="K78" s="3" t="inlineStr">
+        <is>
+          <t>"Based on https://www.ncbi.nlm.nih.gov/books/NBK534115/
+Based on http://purl.obolibrary.org/obo/OAE_0000581"</t>
+        </is>
+      </c>
+      <c r="L78" s="3" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/OAE_0000581</t>
+        </is>
+      </c>
+      <c r="M78" s="3" t="n"/>
+      <c r="N78" s="3" t="n"/>
+      <c r="O78" s="3" t="n"/>
+      <c r="P78" s="3" t="n"/>
+      <c r="Q78" s="3" t="inlineStr">
+        <is>
+          <t>LSR 3</t>
+        </is>
+      </c>
+      <c r="R78" s="3" t="inlineStr">
+        <is>
+          <t>Intervention outcomes and spillover effects</t>
+        </is>
+      </c>
+      <c r="S78" s="3" t="n"/>
+      <c r="T78" s="3" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="U78" s="3" t="n"/>
+      <c r="V78" s="3" t="n"/>
+      <c r="W78" s="3" t="inlineStr">
+        <is>
+          <t>PS; MS</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="3" t="inlineStr">
+        <is>
+          <t>GMHO:0000180</t>
+        </is>
+      </c>
+      <c r="B79" s="3" t="inlineStr">
+        <is>
+          <t>dry mouth following intervention</t>
+        </is>
+      </c>
+      <c r="C79" s="3" t="inlineStr">
+        <is>
+          <t>A digestive system adverse event following intervention that involves experiencing dry mouth.</t>
+        </is>
+      </c>
+      <c r="D79" s="3" t="inlineStr">
+        <is>
+          <t>digestive system adverse event following intervention</t>
+        </is>
+      </c>
+      <c r="E79" s="3" t="n"/>
+      <c r="F79" s="3" t="n"/>
+      <c r="G79" s="3" t="n"/>
+      <c r="H79" s="3" t="n"/>
+      <c r="I79" s="3" t="n"/>
+      <c r="J79" s="3" t="n"/>
+      <c r="K79" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cross reference: http://purl.obolibrary.org/obo/OAE_0000505
+</t>
+        </is>
+      </c>
+      <c r="L79" s="3" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/OAE_0000505</t>
+        </is>
+      </c>
+      <c r="M79" s="3" t="inlineStr">
+        <is>
+          <t>dry mouth</t>
+        </is>
+      </c>
+      <c r="N79" s="3" t="n"/>
+      <c r="O79" s="3" t="n"/>
+      <c r="P79" s="3" t="n"/>
+      <c r="Q79" s="3" t="inlineStr">
+        <is>
+          <t>LSR 1</t>
+        </is>
+      </c>
+      <c r="R79" s="3" t="inlineStr">
+        <is>
+          <t>Intervention outcomes and spillover effects</t>
+        </is>
+      </c>
+      <c r="S79" s="3" t="n"/>
+      <c r="T79" s="3" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="U79" s="3" t="n"/>
+      <c r="V79" s="3" t="n"/>
+      <c r="W79" s="3" t="inlineStr">
+        <is>
+          <t>PS; MS</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
         <is>
           <t>GMHO:0000064</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
+      <c r="B80" s="2" t="inlineStr">
         <is>
           <t>dyskinesias following an intervention</t>
         </is>
       </c>
-      <c r="C78" s="2" t="inlineStr">
+      <c r="C80" s="2" t="inlineStr">
         <is>
           <t>An adverse event following an intervention that involves dyskinesias.</t>
         </is>
       </c>
-      <c r="D78" s="2" t="inlineStr">
+      <c r="D80" s="2" t="inlineStr">
         <is>
           <t>adverse event following an intervention</t>
         </is>
       </c>
-      <c r="E78" s="2" t="n"/>
-      <c r="F78" s="2" t="n"/>
-      <c r="G78" s="2" t="n"/>
-      <c r="H78" s="2" t="n"/>
-      <c r="I78" s="2" t="n"/>
-      <c r="J78" s="2" t="n"/>
-      <c r="K78" s="2" t="n"/>
-      <c r="L78" s="2" t="n"/>
-      <c r="M78" s="2" t="n"/>
-      <c r="N78" s="2" t="n"/>
-      <c r="O78" s="2" t="n"/>
-      <c r="P78" s="2" t="n"/>
-      <c r="Q78" s="2" t="inlineStr">
+      <c r="E80" s="2" t="n"/>
+      <c r="F80" s="2" t="n"/>
+      <c r="G80" s="2" t="n"/>
+      <c r="H80" s="2" t="n"/>
+      <c r="I80" s="2" t="n"/>
+      <c r="J80" s="2" t="n"/>
+      <c r="K80" s="2" t="n"/>
+      <c r="L80" s="2" t="n"/>
+      <c r="M80" s="2" t="n"/>
+      <c r="N80" s="2" t="n"/>
+      <c r="O80" s="2" t="n"/>
+      <c r="P80" s="2" t="n"/>
+      <c r="Q80" s="2" t="inlineStr">
         <is>
           <t>LSR 3</t>
         </is>
       </c>
-      <c r="R78" s="2" t="inlineStr">
-        <is>
-          <t>Intervention outcomes and spillover effects</t>
-        </is>
-      </c>
-      <c r="S78" s="2" t="n"/>
-      <c r="T78" s="2" t="inlineStr">
+      <c r="R80" s="2" t="inlineStr">
+        <is>
+          <t>Intervention outcomes and spillover effects</t>
+        </is>
+      </c>
+      <c r="S80" s="2" t="n"/>
+      <c r="T80" s="2" t="inlineStr">
         <is>
           <t>Obsolete</t>
         </is>
       </c>
-      <c r="U78" s="2" t="n"/>
-      <c r="V78" s="2" t="n"/>
-      <c r="W78" s="2" t="inlineStr">
-        <is>
-          <t>PS</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
+      <c r="U80" s="2" t="n"/>
+      <c r="V80" s="2" t="n"/>
+      <c r="W80" s="2" t="inlineStr">
+        <is>
+          <t>PS</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
         <is>
           <t>STATO:0000471</t>
         </is>
       </c>
-      <c r="B79" t="inlineStr">
+      <c r="B81" t="inlineStr">
         <is>
           <t>estimate</t>
         </is>
       </c>
-      <c r="C79" t="inlineStr">
+      <c r="C81" t="inlineStr">
         <is>
           <t>a estimate is a data item which is computed from a dataset to provide an approximated value (an estimator) for a 'statistical parameter' (a 'characteristics/parameter' of the true underlying distribution) of a real population.</t>
         </is>
       </c>
-      <c r="D79" t="inlineStr">
+      <c r="D81" t="inlineStr">
         <is>
           <t>statistic</t>
         </is>
       </c>
-      <c r="J79" t="inlineStr">
-        <is>
-          <t>Intervention outcomes and spillover effects</t>
-        </is>
-      </c>
-      <c r="Q79" t="inlineStr">
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>Intervention outcomes and spillover effects</t>
+        </is>
+      </c>
+      <c r="Q81" t="inlineStr">
         <is>
           <t>LSR 3</t>
         </is>
       </c>
-      <c r="R79" t="inlineStr">
-        <is>
-          <t>Intervention outcomes and spillover effects</t>
-        </is>
-      </c>
-      <c r="T79" t="inlineStr">
+      <c r="R81" t="inlineStr">
+        <is>
+          <t>Intervention outcomes and spillover effects</t>
+        </is>
+      </c>
+      <c r="T81" t="inlineStr">
         <is>
           <t>External</t>
         </is>
       </c>
-      <c r="W79" t="inlineStr">
-        <is>
-          <t>PS</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>PATO:0001035</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>force</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>A physical quality inhering in a bearer by virtue of the bearer's rate of change of momentum.</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>physical quality</t>
-        </is>
-      </c>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>Intervention outcomes and spillover effects</t>
-        </is>
-      </c>
-      <c r="Q80" t="inlineStr">
-        <is>
-          <t>LSR 3</t>
-        </is>
-      </c>
-      <c r="R80" t="inlineStr">
-        <is>
-          <t>Intervention outcomes and spillover effects</t>
-        </is>
-      </c>
-      <c r="T80" t="inlineStr">
-        <is>
-          <t>External</t>
-        </is>
-      </c>
-      <c r="W80" t="inlineStr">
-        <is>
-          <t>PS</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="3" t="inlineStr">
-        <is>
-          <t>GMHO:0000181</t>
-        </is>
-      </c>
-      <c r="B81" s="3" t="inlineStr">
-        <is>
-          <t>headache following intervention</t>
-        </is>
-      </c>
-      <c r="C81" s="3" t="inlineStr">
-        <is>
-          <t>A pain following intervention that has an outcome of headache.</t>
-        </is>
-      </c>
-      <c r="D81" s="3" t="inlineStr">
-        <is>
-          <t>pain following intervention</t>
-        </is>
-      </c>
-      <c r="E81" s="3" t="n"/>
-      <c r="F81" s="3" t="n"/>
-      <c r="G81" s="3" t="n"/>
-      <c r="H81" s="3" t="n"/>
-      <c r="I81" s="3" t="n"/>
-      <c r="J81" s="3" t="n"/>
-      <c r="K81" s="3" t="inlineStr">
-        <is>
-          <t>cross-reference: http://purl.obolibrary.org/obo/OAE_0000377</t>
-        </is>
-      </c>
-      <c r="L81" s="3" t="inlineStr">
-        <is>
-          <t>http://purl.obolibrary.org/obo/OAE_0000377</t>
-        </is>
-      </c>
-      <c r="M81" s="3" t="inlineStr">
-        <is>
-          <t>headache</t>
-        </is>
-      </c>
-      <c r="N81" s="3" t="n"/>
-      <c r="O81" s="3" t="n"/>
-      <c r="P81" s="3" t="n"/>
-      <c r="Q81" s="3" t="inlineStr">
-        <is>
-          <t>LSR 1, LSR 3</t>
-        </is>
-      </c>
-      <c r="R81" s="3" t="inlineStr">
-        <is>
-          <t>Intervention outcomes and spillover effects</t>
-        </is>
-      </c>
-      <c r="S81" s="3" t="n"/>
-      <c r="T81" s="3" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="U81" s="3" t="n"/>
-      <c r="V81" s="3" t="n"/>
-      <c r="W81" s="3" t="inlineStr">
-        <is>
-          <t>PS; MS</t>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>PS</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
+          <t>PATO:0001035</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>force</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>A physical quality inhering in a bearer by virtue of the bearer's rate of change of momentum.</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>physical quality</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>Intervention outcomes and spillover effects</t>
+        </is>
+      </c>
+      <c r="Q82" t="inlineStr">
+        <is>
+          <t>LSR 3</t>
+        </is>
+      </c>
+      <c r="R82" t="inlineStr">
+        <is>
+          <t>Intervention outcomes and spillover effects</t>
+        </is>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>External</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>PS</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="3" t="inlineStr">
+        <is>
+          <t>GMHO:0000181</t>
+        </is>
+      </c>
+      <c r="B83" s="3" t="inlineStr">
+        <is>
+          <t>headache following intervention</t>
+        </is>
+      </c>
+      <c r="C83" s="3" t="inlineStr">
+        <is>
+          <t>A pain following intervention that has an outcome of headache.</t>
+        </is>
+      </c>
+      <c r="D83" s="3" t="inlineStr">
+        <is>
+          <t>pain following intervention</t>
+        </is>
+      </c>
+      <c r="E83" s="3" t="n"/>
+      <c r="F83" s="3" t="n"/>
+      <c r="G83" s="3" t="n"/>
+      <c r="H83" s="3" t="n"/>
+      <c r="I83" s="3" t="n"/>
+      <c r="J83" s="3" t="n"/>
+      <c r="K83" s="3" t="inlineStr">
+        <is>
+          <t>cross-reference: http://purl.obolibrary.org/obo/OAE_0000377</t>
+        </is>
+      </c>
+      <c r="L83" s="3" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/OAE_0000377</t>
+        </is>
+      </c>
+      <c r="M83" s="3" t="inlineStr">
+        <is>
+          <t>headache</t>
+        </is>
+      </c>
+      <c r="N83" s="3" t="n"/>
+      <c r="O83" s="3" t="n"/>
+      <c r="P83" s="3" t="n"/>
+      <c r="Q83" s="3" t="inlineStr">
+        <is>
+          <t>LSR 1, LSR 3</t>
+        </is>
+      </c>
+      <c r="R83" s="3" t="inlineStr">
+        <is>
+          <t>Intervention outcomes and spillover effects</t>
+        </is>
+      </c>
+      <c r="S83" s="3" t="n"/>
+      <c r="T83" s="3" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="U83" s="3" t="n"/>
+      <c r="V83" s="3" t="n"/>
+      <c r="W83" s="3" t="inlineStr">
+        <is>
+          <t>PS; MS</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
           <t>BCIO:015092</t>
         </is>
       </c>
-      <c r="B82" t="inlineStr">
+      <c r="B84" t="inlineStr">
         <is>
           <t>health status attribute</t>
         </is>
       </c>
-      <c r="C82" t="inlineStr">
+      <c r="C84" t="inlineStr">
         <is>
           <t>A personal attribute that is the state of an individual's mental or physical condition.</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr">
+      <c r="D84" t="inlineStr">
         <is>
           <t>personal attribute</t>
         </is>
       </c>
-      <c r="J82" t="inlineStr">
+      <c r="J84" t="inlineStr">
         <is>
           <t>intervention outcomes and spillover effects</t>
         </is>
       </c>
-      <c r="Q82" t="inlineStr">
+      <c r="Q84" t="inlineStr">
         <is>
           <t>LSR 3</t>
         </is>
       </c>
-      <c r="R82" t="inlineStr">
-        <is>
-          <t>Intervention outcomes and spillover effects</t>
-        </is>
-      </c>
-      <c r="T82" t="inlineStr">
+      <c r="R84" t="inlineStr">
+        <is>
+          <t>Intervention outcomes and spillover effects</t>
+        </is>
+      </c>
+      <c r="T84" t="inlineStr">
         <is>
           <t>External</t>
         </is>
       </c>
-      <c r="W82" t="inlineStr">
-        <is>
-          <t>PS</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>PS</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
         <is>
           <t>CMO:0000230</t>
         </is>
       </c>
-      <c r="B83" t="inlineStr">
+      <c r="B85" t="inlineStr">
         <is>
           <t>heart electrical conduction measurement</t>
         </is>
       </c>
-      <c r="C83" t="inlineStr">
+      <c r="C85" t="inlineStr">
         <is>
           <t>Any measurement of components of the electrical conduction system of the heart.The electrical conduction system of the heart transmits signals generated usually by the sinoatrial node to cause contraction of the heart muscle.</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr">
+      <c r="D85" t="inlineStr">
         <is>
           <t>heart measurement</t>
         </is>
       </c>
-      <c r="R83" t="inlineStr">
-        <is>
-          <t>Intervention outcomes and spillover effects</t>
-        </is>
-      </c>
-      <c r="T83" t="inlineStr">
+      <c r="R85" t="inlineStr">
+        <is>
+          <t>Intervention outcomes and spillover effects</t>
+        </is>
+      </c>
+      <c r="T85" t="inlineStr">
         <is>
           <t>External</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="2" t="inlineStr">
-        <is>
-          <t>GMHO:0000132</t>
-        </is>
-      </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>heart rate</t>
-        </is>
-      </c>
-      <c r="C84" s="2" t="inlineStr">
-        <is>
-          <t>A data item about the number of heart contractions within a temporal interval.</t>
-        </is>
-      </c>
-      <c r="D84" s="2" t="inlineStr">
-        <is>
-          <t>data item</t>
-        </is>
-      </c>
-      <c r="E84" s="2" t="n"/>
-      <c r="F84" s="2" t="n"/>
-      <c r="G84" s="2" t="n"/>
-      <c r="H84" s="2" t="n"/>
-      <c r="I84" s="2" t="n"/>
-      <c r="J84" s="2" t="n"/>
-      <c r="K84" s="2" t="n"/>
-      <c r="L84" s="2" t="n"/>
-      <c r="M84" s="2" t="n"/>
-      <c r="N84" s="2" t="n"/>
-      <c r="O84" s="2" t="n"/>
-      <c r="P84" s="2" t="n"/>
-      <c r="Q84" s="2" t="inlineStr">
-        <is>
-          <t>LSR 2</t>
-        </is>
-      </c>
-      <c r="R84" s="2" t="inlineStr">
-        <is>
-          <t>Intervention outcomes and spillover effects</t>
-        </is>
-      </c>
-      <c r="S84" s="2" t="n"/>
-      <c r="T84" s="2" t="inlineStr">
-        <is>
-          <t>Obsolete</t>
-        </is>
-      </c>
-      <c r="U84" s="2" t="n"/>
-      <c r="V84" s="2" t="n"/>
-      <c r="W84" s="2" t="inlineStr">
-        <is>
-          <t>PS</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="2" t="inlineStr">
-        <is>
-          <t>GMHO:0000065</t>
-        </is>
-      </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>homicide following an intervention</t>
-        </is>
-      </c>
-      <c r="C85" s="2" t="inlineStr">
-        <is>
-          <t>A death following an intervention that involves a participant being intentionally killed by another person.</t>
-        </is>
-      </c>
-      <c r="D85" s="2" t="inlineStr">
-        <is>
-          <t>death following an intervention</t>
-        </is>
-      </c>
-      <c r="E85" s="2" t="n"/>
-      <c r="F85" s="2" t="n"/>
-      <c r="G85" s="2" t="n"/>
-      <c r="H85" s="2" t="n"/>
-      <c r="I85" s="2" t="n"/>
-      <c r="J85" s="2" t="n"/>
-      <c r="K85" s="2" t="n"/>
-      <c r="L85" s="2" t="n"/>
-      <c r="M85" s="2" t="n"/>
-      <c r="N85" s="2" t="n"/>
-      <c r="O85" s="2" t="n"/>
-      <c r="P85" s="2" t="n"/>
-      <c r="Q85" s="2" t="inlineStr">
-        <is>
-          <t>LSR 3</t>
-        </is>
-      </c>
-      <c r="R85" s="2" t="inlineStr">
-        <is>
-          <t>Intervention outcomes and spillover effects</t>
-        </is>
-      </c>
-      <c r="S85" s="2" t="n"/>
-      <c r="T85" s="2" t="inlineStr">
-        <is>
-          <t>Obsolete</t>
-        </is>
-      </c>
-      <c r="U85" s="2" t="n"/>
-      <c r="V85" s="2" t="n"/>
-      <c r="W85" s="2" t="inlineStr">
-        <is>
-          <t>PS</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>GMHO:0000066</t>
+          <t>GMHO:0000132</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>hospitalization</t>
+          <t>heart rate</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>A health care process that involves a person being admitted to a hospital.</t>
+          <t>A data item about the number of heart contractions within a temporal interval.</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>health care process</t>
+          <t>data item</t>
         </is>
       </c>
       <c r="E86" s="2" t="n"/>
@@ -5663,18 +5669,14 @@
       <c r="I86" s="2" t="n"/>
       <c r="J86" s="2" t="n"/>
       <c r="K86" s="2" t="n"/>
-      <c r="L86" s="2" t="inlineStr">
-        <is>
-          <t>http://purl.obolibrary.org/obo/OGMS_0000098</t>
-        </is>
-      </c>
+      <c r="L86" s="2" t="n"/>
       <c r="M86" s="2" t="n"/>
       <c r="N86" s="2" t="n"/>
       <c r="O86" s="2" t="n"/>
       <c r="P86" s="2" t="n"/>
       <c r="Q86" s="2" t="inlineStr">
         <is>
-          <t>LSR 3</t>
+          <t>LSR 2</t>
         </is>
       </c>
       <c r="R86" s="2" t="inlineStr">
@@ -5697,110 +5699,118 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="3" t="inlineStr">
-        <is>
-          <t>GMHO:0000067</t>
-        </is>
-      </c>
-      <c r="B87" s="3" t="inlineStr">
-        <is>
-          <t>human functioning</t>
-        </is>
-      </c>
-      <c r="C87" s="3" t="inlineStr">
-        <is>
-          <t>A bodily disposition to realise processes that influence a person's life quality.</t>
-        </is>
-      </c>
-      <c r="D87" s="3" t="inlineStr">
-        <is>
-          <t>bodily disposition</t>
-        </is>
-      </c>
-      <c r="E87" s="3" t="n"/>
-      <c r="F87" s="3" t="n"/>
-      <c r="G87" s="3" t="n"/>
-      <c r="H87" s="3" t="n"/>
-      <c r="I87" s="3" t="n"/>
-      <c r="J87" s="3" t="n"/>
-      <c r="K87" s="3" t="n"/>
-      <c r="L87" s="3" t="n"/>
-      <c r="M87" s="3" t="n"/>
-      <c r="N87" s="3" t="n"/>
-      <c r="O87" s="3" t="n"/>
-      <c r="P87" s="3" t="n"/>
-      <c r="Q87" s="3" t="inlineStr">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>GMHO:0000065</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>homicide following an intervention</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>A death following an intervention that involves a participant being intentionally killed by another person.</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>death following an intervention</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="n"/>
+      <c r="F87" s="2" t="n"/>
+      <c r="G87" s="2" t="n"/>
+      <c r="H87" s="2" t="n"/>
+      <c r="I87" s="2" t="n"/>
+      <c r="J87" s="2" t="n"/>
+      <c r="K87" s="2" t="n"/>
+      <c r="L87" s="2" t="n"/>
+      <c r="M87" s="2" t="n"/>
+      <c r="N87" s="2" t="n"/>
+      <c r="O87" s="2" t="n"/>
+      <c r="P87" s="2" t="n"/>
+      <c r="Q87" s="2" t="inlineStr">
         <is>
           <t>LSR 3</t>
         </is>
       </c>
-      <c r="R87" s="3" t="inlineStr">
-        <is>
-          <t>Intervention outcomes and spillover effects</t>
-        </is>
-      </c>
-      <c r="S87" s="3" t="n"/>
-      <c r="T87" s="3" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="U87" s="3" t="n"/>
-      <c r="V87" s="3" t="n"/>
-      <c r="W87" s="3" t="inlineStr">
+      <c r="R87" s="2" t="inlineStr">
+        <is>
+          <t>Intervention outcomes and spillover effects</t>
+        </is>
+      </c>
+      <c r="S87" s="2" t="n"/>
+      <c r="T87" s="2" t="inlineStr">
+        <is>
+          <t>Obsolete</t>
+        </is>
+      </c>
+      <c r="U87" s="2" t="n"/>
+      <c r="V87" s="2" t="n"/>
+      <c r="W87" s="2" t="inlineStr">
         <is>
           <t>PS</t>
         </is>
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="3" t="inlineStr">
-        <is>
-          <t>GMHO:0000224</t>
-        </is>
-      </c>
-      <c r="B88" s="3" t="inlineStr">
-        <is>
-          <t>human functioning scale</t>
-        </is>
-      </c>
-      <c r="C88" s="3" t="inlineStr">
-        <is>
-          <t>A measurement scale that is used to measure human functioning.</t>
-        </is>
-      </c>
-      <c r="D88" s="3" t="inlineStr">
-        <is>
-          <t>measurement scale</t>
-        </is>
-      </c>
-      <c r="E88" s="3" t="n"/>
-      <c r="F88" s="3" t="n"/>
-      <c r="G88" s="3" t="n"/>
-      <c r="H88" s="3" t="n"/>
-      <c r="I88" s="3" t="n"/>
-      <c r="J88" s="3" t="inlineStr">
-        <is>
-          <t>Intervention outcomes and spillover effects</t>
-        </is>
-      </c>
-      <c r="K88" s="3" t="n"/>
-      <c r="L88" s="3" t="n"/>
-      <c r="M88" s="3" t="n"/>
-      <c r="N88" s="3" t="n"/>
-      <c r="O88" s="3" t="n"/>
-      <c r="P88" s="3" t="n"/>
-      <c r="Q88" s="3" t="n"/>
-      <c r="R88" s="3" t="n"/>
-      <c r="S88" s="3" t="n"/>
-      <c r="T88" s="3" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="U88" s="3" t="n"/>
-      <c r="V88" s="3" t="n"/>
-      <c r="W88" s="3" t="inlineStr">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>GMHO:0000066</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>hospitalization</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>A health care process that involves a person being admitted to a hospital.</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>health care process</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="n"/>
+      <c r="F88" s="2" t="n"/>
+      <c r="G88" s="2" t="n"/>
+      <c r="H88" s="2" t="n"/>
+      <c r="I88" s="2" t="n"/>
+      <c r="J88" s="2" t="n"/>
+      <c r="K88" s="2" t="n"/>
+      <c r="L88" s="2" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/OGMS_0000098</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="n"/>
+      <c r="N88" s="2" t="n"/>
+      <c r="O88" s="2" t="n"/>
+      <c r="P88" s="2" t="n"/>
+      <c r="Q88" s="2" t="inlineStr">
+        <is>
+          <t>LSR 3</t>
+        </is>
+      </c>
+      <c r="R88" s="2" t="inlineStr">
+        <is>
+          <t>Intervention outcomes and spillover effects</t>
+        </is>
+      </c>
+      <c r="S88" s="2" t="n"/>
+      <c r="T88" s="2" t="inlineStr">
+        <is>
+          <t>Obsolete</t>
+        </is>
+      </c>
+      <c r="U88" s="2" t="n"/>
+      <c r="V88" s="2" t="n"/>
+      <c r="W88" s="2" t="inlineStr">
         <is>
           <t>PS</t>
         </is>
@@ -5809,22 +5819,22 @@
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
         <is>
-          <t>GMHO:0000234</t>
+          <t>GMHO:0000067</t>
         </is>
       </c>
       <c r="B89" s="3" t="inlineStr">
         <is>
-          <t>hyperprolactinemia following intervention</t>
+          <t>human functioning</t>
         </is>
       </c>
       <c r="C89" s="3" t="inlineStr">
         <is>
-          <t>An adverse event following an intervention that involves experiencing hyperprolactinemia.</t>
+          <t>A bodily disposition to realise processes that influence a person's life quality.</t>
         </is>
       </c>
       <c r="D89" s="3" t="inlineStr">
         <is>
-          <t>adverse event following an intervention</t>
+          <t>bodily disposition</t>
         </is>
       </c>
       <c r="E89" s="3" t="n"/>
@@ -5832,18 +5842,10 @@
       <c r="G89" s="3" t="n"/>
       <c r="H89" s="3" t="n"/>
       <c r="I89" s="3" t="n"/>
-      <c r="J89" s="3" t="inlineStr">
-        <is>
-          <t>Intervention outcomes and spillover effects</t>
-        </is>
-      </c>
+      <c r="J89" s="3" t="n"/>
       <c r="K89" s="3" t="n"/>
       <c r="L89" s="3" t="n"/>
-      <c r="M89" s="3" t="inlineStr">
-        <is>
-          <t>hyperprolactinemia</t>
-        </is>
-      </c>
+      <c r="M89" s="3" t="n"/>
       <c r="N89" s="3" t="n"/>
       <c r="O89" s="3" t="n"/>
       <c r="P89" s="3" t="n"/>
@@ -5874,22 +5876,22 @@
     <row r="90">
       <c r="A90" s="3" t="inlineStr">
         <is>
-          <t>GMHO:0000235</t>
+          <t>GMHO:0000224</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
         <is>
-          <t>hypotension following intervention</t>
+          <t>human functioning scale</t>
         </is>
       </c>
       <c r="C90" s="3" t="inlineStr">
         <is>
-          <t>An adverse event following an intervention that involves experiencing low blood pressure.</t>
+          <t>A measurement scale that is used to measure human functioning.</t>
         </is>
       </c>
       <c r="D90" s="3" t="inlineStr">
         <is>
-          <t>adverse event following an intervention</t>
+          <t>measurement scale</t>
         </is>
       </c>
       <c r="E90" s="3" t="n"/>
@@ -5904,24 +5906,12 @@
       </c>
       <c r="K90" s="3" t="n"/>
       <c r="L90" s="3" t="n"/>
-      <c r="M90" s="3" t="inlineStr">
-        <is>
-          <t>hypotension</t>
-        </is>
-      </c>
+      <c r="M90" s="3" t="n"/>
       <c r="N90" s="3" t="n"/>
       <c r="O90" s="3" t="n"/>
       <c r="P90" s="3" t="n"/>
-      <c r="Q90" s="3" t="inlineStr">
-        <is>
-          <t>LSR 3</t>
-        </is>
-      </c>
-      <c r="R90" s="3" t="inlineStr">
-        <is>
-          <t>Intervention outcomes and spillover effects</t>
-        </is>
-      </c>
+      <c r="Q90" s="3" t="n"/>
+      <c r="R90" s="3" t="n"/>
       <c r="S90" s="3" t="n"/>
       <c r="T90" s="3" t="inlineStr">
         <is>
@@ -5937,47 +5927,65 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>IAO:0000030</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>information content entity</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>A generically dependent continuant that is about some thing.</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>generically dependent continuant</t>
-        </is>
-      </c>
-      <c r="J91" t="inlineStr">
-        <is>
-          <t>Intervention outcomes and spillover effects</t>
-        </is>
-      </c>
-      <c r="Q91" t="inlineStr">
-        <is>
-          <t>LSR 1</t>
-        </is>
-      </c>
-      <c r="R91" t="inlineStr">
-        <is>
-          <t>Intervention outcomes and spillover effects</t>
-        </is>
-      </c>
-      <c r="T91" t="inlineStr">
-        <is>
-          <t>External</t>
-        </is>
-      </c>
-      <c r="W91" t="inlineStr">
+      <c r="A91" s="3" t="inlineStr">
+        <is>
+          <t>GMHO:0000234</t>
+        </is>
+      </c>
+      <c r="B91" s="3" t="inlineStr">
+        <is>
+          <t>hyperprolactinemia following intervention</t>
+        </is>
+      </c>
+      <c r="C91" s="3" t="inlineStr">
+        <is>
+          <t>An adverse event following an intervention that involves experiencing hyperprolactinemia.</t>
+        </is>
+      </c>
+      <c r="D91" s="3" t="inlineStr">
+        <is>
+          <t>adverse event following an intervention</t>
+        </is>
+      </c>
+      <c r="E91" s="3" t="n"/>
+      <c r="F91" s="3" t="n"/>
+      <c r="G91" s="3" t="n"/>
+      <c r="H91" s="3" t="n"/>
+      <c r="I91" s="3" t="n"/>
+      <c r="J91" s="3" t="inlineStr">
+        <is>
+          <t>Intervention outcomes and spillover effects</t>
+        </is>
+      </c>
+      <c r="K91" s="3" t="n"/>
+      <c r="L91" s="3" t="n"/>
+      <c r="M91" s="3" t="inlineStr">
+        <is>
+          <t>hyperprolactinemia</t>
+        </is>
+      </c>
+      <c r="N91" s="3" t="n"/>
+      <c r="O91" s="3" t="n"/>
+      <c r="P91" s="3" t="n"/>
+      <c r="Q91" s="3" t="inlineStr">
+        <is>
+          <t>LSR 3</t>
+        </is>
+      </c>
+      <c r="R91" s="3" t="inlineStr">
+        <is>
+          <t>Intervention outcomes and spillover effects</t>
+        </is>
+      </c>
+      <c r="S91" s="3" t="n"/>
+      <c r="T91" s="3" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="U91" s="3" t="n"/>
+      <c r="V91" s="3" t="n"/>
+      <c r="W91" s="3" t="inlineStr">
         <is>
           <t>PS</t>
         </is>
@@ -5986,22 +5994,22 @@
     <row r="92">
       <c r="A92" s="3" t="inlineStr">
         <is>
-          <t>GMHO:0000203</t>
+          <t>GMHO:0000235</t>
         </is>
       </c>
       <c r="B92" s="3" t="inlineStr">
         <is>
-          <t>information on available followup data</t>
+          <t>hypotension following intervention</t>
         </is>
       </c>
       <c r="C92" s="3" t="inlineStr">
         <is>
-          <t>An information content entity about the followup data available for a study.</t>
+          <t>An adverse event following an intervention that involves experiencing low blood pressure.</t>
         </is>
       </c>
       <c r="D92" s="3" t="inlineStr">
         <is>
-          <t>information content entity</t>
+          <t>adverse event following an intervention</t>
         </is>
       </c>
       <c r="E92" s="3" t="n"/>
@@ -6009,16 +6017,24 @@
       <c r="G92" s="3" t="n"/>
       <c r="H92" s="3" t="n"/>
       <c r="I92" s="3" t="n"/>
-      <c r="J92" s="3" t="n"/>
+      <c r="J92" s="3" t="inlineStr">
+        <is>
+          <t>Intervention outcomes and spillover effects</t>
+        </is>
+      </c>
       <c r="K92" s="3" t="n"/>
       <c r="L92" s="3" t="n"/>
-      <c r="M92" s="3" t="n"/>
+      <c r="M92" s="3" t="inlineStr">
+        <is>
+          <t>hypotension</t>
+        </is>
+      </c>
       <c r="N92" s="3" t="n"/>
       <c r="O92" s="3" t="n"/>
       <c r="P92" s="3" t="n"/>
       <c r="Q92" s="3" t="inlineStr">
         <is>
-          <t>LSR 1, LSR 3</t>
+          <t>LSR 3</t>
         </is>
       </c>
       <c r="R92" s="3" t="inlineStr">
@@ -6041,196 +6057,197 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="3" t="inlineStr">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>IAO:0000030</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>information content entity</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>A generically dependent continuant that is about some thing.</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>generically dependent continuant</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>Intervention outcomes and spillover effects</t>
+        </is>
+      </c>
+      <c r="Q93" t="inlineStr">
+        <is>
+          <t>LSR 1</t>
+        </is>
+      </c>
+      <c r="R93" t="inlineStr">
+        <is>
+          <t>Intervention outcomes and spillover effects</t>
+        </is>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>External</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>PS</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="3" t="inlineStr">
+        <is>
+          <t>GMHO:0000203</t>
+        </is>
+      </c>
+      <c r="B94" s="3" t="inlineStr">
+        <is>
+          <t>information on available followup data</t>
+        </is>
+      </c>
+      <c r="C94" s="3" t="inlineStr">
+        <is>
+          <t>An information content entity about the followup data available for a study.</t>
+        </is>
+      </c>
+      <c r="D94" s="3" t="inlineStr">
+        <is>
+          <t>information content entity</t>
+        </is>
+      </c>
+      <c r="E94" s="3" t="n"/>
+      <c r="F94" s="3" t="n"/>
+      <c r="G94" s="3" t="n"/>
+      <c r="H94" s="3" t="n"/>
+      <c r="I94" s="3" t="n"/>
+      <c r="J94" s="3" t="n"/>
+      <c r="K94" s="3" t="n"/>
+      <c r="L94" s="3" t="n"/>
+      <c r="M94" s="3" t="n"/>
+      <c r="N94" s="3" t="n"/>
+      <c r="O94" s="3" t="n"/>
+      <c r="P94" s="3" t="n"/>
+      <c r="Q94" s="3" t="inlineStr">
+        <is>
+          <t>LSR 1, LSR 3</t>
+        </is>
+      </c>
+      <c r="R94" s="3" t="inlineStr">
+        <is>
+          <t>Intervention outcomes and spillover effects</t>
+        </is>
+      </c>
+      <c r="S94" s="3" t="n"/>
+      <c r="T94" s="3" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="U94" s="3" t="n"/>
+      <c r="V94" s="3" t="n"/>
+      <c r="W94" s="3" t="inlineStr">
+        <is>
+          <t>PS</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="3" t="inlineStr">
         <is>
           <t>GMHO:0000182</t>
         </is>
       </c>
-      <c r="B93" s="3" t="inlineStr">
+      <c r="B95" s="3" t="inlineStr">
         <is>
           <t>insomnia following intervention</t>
         </is>
       </c>
-      <c r="C93" s="3" t="inlineStr">
+      <c r="C95" s="3" t="inlineStr">
         <is>
           <t>An adverse event following an intervention in which there is an inability to fall asleep or to stay asleep as long as desired.</t>
         </is>
       </c>
-      <c r="D93" s="3" t="inlineStr">
+      <c r="D95" s="3" t="inlineStr">
         <is>
           <t>adverse event following an intervention</t>
         </is>
       </c>
-      <c r="E93" s="3" t="n"/>
-      <c r="F93" s="3" t="n"/>
-      <c r="G93" s="3" t="n"/>
-      <c r="H93" s="3" t="n"/>
-      <c r="I93" s="3" t="n"/>
-      <c r="J93" s="3" t="n"/>
-      <c r="K93" s="3" t="inlineStr">
+      <c r="E95" s="3" t="n"/>
+      <c r="F95" s="3" t="n"/>
+      <c r="G95" s="3" t="n"/>
+      <c r="H95" s="3" t="n"/>
+      <c r="I95" s="3" t="n"/>
+      <c r="J95" s="3" t="n"/>
+      <c r="K95" s="3" t="inlineStr">
         <is>
           <t>cross-reference: http://purl.obolibrary.org/obo/OAE_0002206</t>
         </is>
       </c>
-      <c r="L93" s="3" t="inlineStr">
+      <c r="L95" s="3" t="inlineStr">
         <is>
           <t>http://purl.obolibrary.org/obo/OAE_0002206</t>
         </is>
       </c>
-      <c r="M93" s="3" t="inlineStr">
+      <c r="M95" s="3" t="inlineStr">
         <is>
           <t>insomnia</t>
         </is>
       </c>
-      <c r="N93" s="3" t="n"/>
-      <c r="O93" s="3" t="n"/>
-      <c r="P93" s="3" t="n"/>
-      <c r="Q93" s="3" t="inlineStr">
+      <c r="N95" s="3" t="n"/>
+      <c r="O95" s="3" t="n"/>
+      <c r="P95" s="3" t="n"/>
+      <c r="Q95" s="3" t="inlineStr">
         <is>
           <t>LSR 1, LSR 3</t>
         </is>
       </c>
-      <c r="R93" s="3" t="inlineStr">
-        <is>
-          <t>Intervention outcomes and spillover effects</t>
-        </is>
-      </c>
-      <c r="S93" s="3" t="n"/>
-      <c r="T93" s="3" t="inlineStr">
+      <c r="R95" s="3" t="inlineStr">
+        <is>
+          <t>Intervention outcomes and spillover effects</t>
+        </is>
+      </c>
+      <c r="S95" s="3" t="n"/>
+      <c r="T95" s="3" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="U93" s="3" t="n"/>
-      <c r="V93" s="3" t="n"/>
-      <c r="W93" s="3" t="inlineStr">
+      <c r="U95" s="3" t="n"/>
+      <c r="V95" s="3" t="n"/>
+      <c r="W95" s="3" t="inlineStr">
         <is>
           <t>PS; MS</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>BCIO:039000</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>intervention outcome</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>An entity that is influenced by an intervention.</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>entity</t>
-        </is>
-      </c>
-      <c r="Q94" t="inlineStr">
-        <is>
-          <t>LSR 1; LSR 2; LSR 3</t>
-        </is>
-      </c>
-      <c r="R94" t="inlineStr">
-        <is>
-          <t>Intervention outcomes and spillover effects</t>
-        </is>
-      </c>
-      <c r="T94" t="inlineStr">
-        <is>
-          <t>External</t>
-        </is>
-      </c>
-      <c r="W94" t="inlineStr">
-        <is>
-          <t>PS</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="2" t="inlineStr">
-        <is>
-          <t>GMHO:0000133</t>
-        </is>
-      </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>lower bound of 95% confidence interval</t>
-        </is>
-      </c>
-      <c r="C95" s="2" t="inlineStr">
-        <is>
-          <t>A quantitative confidence value that denotes the lower endpoint of a 95% confidence interval and indicates the lowest value within a true parameter is likely to reside within the confidence interval.</t>
-        </is>
-      </c>
-      <c r="D95" s="2" t="inlineStr">
-        <is>
-          <t>quantitative confidence value</t>
-        </is>
-      </c>
-      <c r="E95" s="2" t="n"/>
-      <c r="F95" s="2" t="n"/>
-      <c r="G95" s="2" t="n"/>
-      <c r="H95" s="2" t="n"/>
-      <c r="I95" s="2" t="n"/>
-      <c r="J95" s="2" t="n"/>
-      <c r="K95" s="2" t="inlineStr">
-        <is>
-          <t>Based on Ross, S. M. (2017). Estimation. Introductory statistics ( p. 329-380). Academic Press.</t>
-        </is>
-      </c>
-      <c r="L95" s="2" t="n"/>
-      <c r="M95" s="2" t="n"/>
-      <c r="N95" s="2" t="n"/>
-      <c r="O95" s="2" t="n"/>
-      <c r="P95" s="2" t="n"/>
-      <c r="Q95" s="2" t="inlineStr">
-        <is>
-          <t>LSR 1; LSR 2</t>
-        </is>
-      </c>
-      <c r="R95" s="2" t="inlineStr">
-        <is>
-          <t>Intervention outcomes and spillover effects</t>
-        </is>
-      </c>
-      <c r="S95" s="2" t="n"/>
-      <c r="T95" s="2" t="inlineStr">
-        <is>
-          <t>Obsolete</t>
-        </is>
-      </c>
-      <c r="U95" s="2" t="n"/>
-      <c r="V95" s="2" t="n"/>
-      <c r="W95" s="2" t="inlineStr">
-        <is>
-          <t>PS</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>IAO:0000109</t>
+          <t>BCIO:039000</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>measurement datum</t>
+          <t>intervention outcome</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>A measurement datum is an information content entity that is a recording of the output of a measurement such as produced by a device.</t>
+          <t>An entity that is influenced by an intervention.</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>data item</t>
+          <t>entity</t>
         </is>
       </c>
       <c r="Q96" t="inlineStr">
@@ -6255,81 +6272,85 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="3" t="inlineStr">
-        <is>
-          <t>GMHO:0000204</t>
-        </is>
-      </c>
-      <c r="B97" s="3" t="inlineStr">
-        <is>
-          <t>measurement datum at post-intervention</t>
-        </is>
-      </c>
-      <c r="C97" s="3" t="inlineStr">
-        <is>
-          <t>Measurement datum that was recorded as post-intervention data in a study.</t>
-        </is>
-      </c>
-      <c r="D97" s="3" t="inlineStr">
-        <is>
-          <t>measurement datum</t>
-        </is>
-      </c>
-      <c r="E97" s="3" t="n"/>
-      <c r="F97" s="3" t="n"/>
-      <c r="G97" s="3" t="n"/>
-      <c r="H97" s="3" t="n"/>
-      <c r="I97" s="3" t="n"/>
-      <c r="J97" s="3" t="n"/>
-      <c r="K97" s="3" t="n"/>
-      <c r="L97" s="3" t="n"/>
-      <c r="M97" s="3" t="inlineStr">
-        <is>
-          <t>post-intervention</t>
-        </is>
-      </c>
-      <c r="N97" s="3" t="n"/>
-      <c r="O97" s="3" t="n"/>
-      <c r="P97" s="3" t="n"/>
-      <c r="Q97" s="3" t="inlineStr">
-        <is>
-          <t>LSR 1, LSR 2, LSR 3</t>
-        </is>
-      </c>
-      <c r="R97" s="3" t="n"/>
-      <c r="S97" s="3" t="n"/>
-      <c r="T97" s="3" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="U97" s="3" t="n"/>
-      <c r="V97" s="3" t="n"/>
-      <c r="W97" s="3" t="inlineStr">
-        <is>
-          <t>PS; MS</t>
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>GMHO:0000133</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>lower bound of 95% confidence interval</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>A quantitative confidence value that denotes the lower endpoint of a 95% confidence interval and indicates the lowest value within a true parameter is likely to reside within the confidence interval.</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>quantitative confidence value</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="n"/>
+      <c r="F97" s="2" t="n"/>
+      <c r="G97" s="2" t="n"/>
+      <c r="H97" s="2" t="n"/>
+      <c r="I97" s="2" t="n"/>
+      <c r="J97" s="2" t="n"/>
+      <c r="K97" s="2" t="inlineStr">
+        <is>
+          <t>Based on Ross, S. M. (2017). Estimation. Introductory statistics ( p. 329-380). Academic Press.</t>
+        </is>
+      </c>
+      <c r="L97" s="2" t="n"/>
+      <c r="M97" s="2" t="n"/>
+      <c r="N97" s="2" t="n"/>
+      <c r="O97" s="2" t="n"/>
+      <c r="P97" s="2" t="n"/>
+      <c r="Q97" s="2" t="inlineStr">
+        <is>
+          <t>LSR 1; LSR 2</t>
+        </is>
+      </c>
+      <c r="R97" s="2" t="inlineStr">
+        <is>
+          <t>Intervention outcomes and spillover effects</t>
+        </is>
+      </c>
+      <c r="S97" s="2" t="n"/>
+      <c r="T97" s="2" t="inlineStr">
+        <is>
+          <t>Obsolete</t>
+        </is>
+      </c>
+      <c r="U97" s="2" t="n"/>
+      <c r="V97" s="2" t="n"/>
+      <c r="W97" s="2" t="inlineStr">
+        <is>
+          <t>PS</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>OBCS:0000011</t>
+          <t>IAO:0000109</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>measurement scale</t>
+          <t>measurement datum</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>An information content entity that represents a type of scale on which a variable is measured, including nominal, ordinal, interval, ratio.</t>
+          <t>A measurement datum is an information content entity that is a recording of the output of a measurement such as produced by a device.</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>information content entity</t>
+          <t>data item</t>
         </is>
       </c>
       <c r="Q98" t="inlineStr">
@@ -6356,22 +6377,22 @@
     <row r="99">
       <c r="A99" s="3" t="inlineStr">
         <is>
-          <t>GMHO:0000205</t>
+          <t>GMHO:0000204</t>
         </is>
       </c>
       <c r="B99" s="3" t="inlineStr">
         <is>
-          <t>measurement scale at post-intervention</t>
+          <t>measurement datum at post-intervention</t>
         </is>
       </c>
       <c r="C99" s="3" t="inlineStr">
         <is>
-          <t>A measurement scale used to measure post-intervention data in a study.</t>
+          <t>Measurement datum that was recorded as post-intervention data in a study.</t>
         </is>
       </c>
       <c r="D99" s="3" t="inlineStr">
         <is>
-          <t>measurement scale</t>
+          <t>measurement datum</t>
         </is>
       </c>
       <c r="E99" s="3" t="n"/>
@@ -6382,11 +6403,19 @@
       <c r="J99" s="3" t="n"/>
       <c r="K99" s="3" t="n"/>
       <c r="L99" s="3" t="n"/>
-      <c r="M99" s="3" t="n"/>
+      <c r="M99" s="3" t="inlineStr">
+        <is>
+          <t>post-intervention</t>
+        </is>
+      </c>
       <c r="N99" s="3" t="n"/>
       <c r="O99" s="3" t="n"/>
       <c r="P99" s="3" t="n"/>
-      <c r="Q99" s="3" t="n"/>
+      <c r="Q99" s="3" t="inlineStr">
+        <is>
+          <t>LSR 1, LSR 2, LSR 3</t>
+        </is>
+      </c>
       <c r="R99" s="3" t="n"/>
       <c r="S99" s="3" t="n"/>
       <c r="T99" s="3" t="inlineStr">
@@ -6398,39 +6427,34 @@
       <c r="V99" s="3" t="n"/>
       <c r="W99" s="3" t="inlineStr">
         <is>
-          <t>PS</t>
+          <t>PS; MS</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>MF:0000020</t>
+          <t>OBCS:0000011</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>mental process</t>
+          <t>measurement scale</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>A bodily process that occurs in the brain, and that can of itself be conscious, or can give rise to a process that can of itself be conscious or can give rise to behaviour.</t>
+          <t>An information content entity that represents a type of scale on which a variable is measured, including nominal, ordinal, interval, ratio.</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>bodily process</t>
-        </is>
-      </c>
-      <c r="J100" t="inlineStr">
-        <is>
-          <t>Intervention outcomes and spillover effects</t>
+          <t>information content entity</t>
         </is>
       </c>
       <c r="Q100" t="inlineStr">
         <is>
-          <t xml:space="preserve">LSR 3 </t>
+          <t>LSR 1; LSR 2; LSR 3</t>
         </is>
       </c>
       <c r="R100" t="inlineStr">
@@ -6441,23 +6465,28 @@
       <c r="T100" t="inlineStr">
         <is>
           <t>External</t>
+        </is>
+      </c>
+      <c r="W100" t="inlineStr">
+        <is>
+          <t>PS</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="3" t="inlineStr">
         <is>
-          <t>GMHO:0000259</t>
+          <t>GMHO:0000205</t>
         </is>
       </c>
       <c r="B101" s="3" t="inlineStr">
         <is>
-          <t>mental process scale</t>
+          <t>measurement scale at post-intervention</t>
         </is>
       </c>
       <c r="C101" s="3" t="inlineStr">
         <is>
-          <t>A measurement scale that is used to measure mental processes.</t>
+          <t>A measurement scale used to measure post-intervention data in a study.</t>
         </is>
       </c>
       <c r="D101" s="3" t="inlineStr">
@@ -6470,27 +6499,15 @@
       <c r="G101" s="3" t="n"/>
       <c r="H101" s="3" t="n"/>
       <c r="I101" s="3" t="n"/>
-      <c r="J101" s="3" t="inlineStr">
-        <is>
-          <t>Intervention outcomes and spillover effects</t>
-        </is>
-      </c>
+      <c r="J101" s="3" t="n"/>
       <c r="K101" s="3" t="n"/>
       <c r="L101" s="3" t="n"/>
       <c r="M101" s="3" t="n"/>
       <c r="N101" s="3" t="n"/>
       <c r="O101" s="3" t="n"/>
       <c r="P101" s="3" t="n"/>
-      <c r="Q101" s="3" t="inlineStr">
-        <is>
-          <t>LSR 3</t>
-        </is>
-      </c>
-      <c r="R101" s="3" t="inlineStr">
-        <is>
-          <t>Intervention outcomes and spillover effects</t>
-        </is>
-      </c>
+      <c r="Q101" s="3" t="n"/>
+      <c r="R101" s="3" t="n"/>
       <c r="S101" s="3" t="n"/>
       <c r="T101" s="3" t="inlineStr">
         <is>
@@ -6499,88 +6516,73 @@
       </c>
       <c r="U101" s="3" t="n"/>
       <c r="V101" s="3" t="n"/>
-      <c r="W101" s="3" t="n"/>
+      <c r="W101" s="3" t="inlineStr">
+        <is>
+          <t>PS</t>
+        </is>
+      </c>
     </row>
     <row r="102">
-      <c r="A102" s="3" t="inlineStr">
-        <is>
-          <t>GMHO:0000236</t>
-        </is>
-      </c>
-      <c r="B102" s="3" t="inlineStr">
-        <is>
-          <t>midpoint estimate for the mean difference of an outcome between the intervention and comparison condition</t>
-        </is>
-      </c>
-      <c r="C102" s="3" t="inlineStr">
-        <is>
-          <t>A point estimate about the mean difference between an intervention and comparison condition in a study.</t>
-        </is>
-      </c>
-      <c r="D102" s="3" t="inlineStr">
-        <is>
-          <t>point estimate</t>
-        </is>
-      </c>
-      <c r="E102" s="3" t="n"/>
-      <c r="F102" s="3" t="n"/>
-      <c r="G102" s="3" t="n"/>
-      <c r="H102" s="3" t="n"/>
-      <c r="I102" s="3" t="n"/>
-      <c r="J102" s="3" t="inlineStr">
-        <is>
-          <t>Intervention outcomes and spillover effects</t>
-        </is>
-      </c>
-      <c r="K102" s="3" t="n"/>
-      <c r="L102" s="3" t="n"/>
-      <c r="M102" s="3" t="n"/>
-      <c r="N102" s="3" t="n"/>
-      <c r="O102" s="3" t="n"/>
-      <c r="P102" s="3" t="n"/>
-      <c r="Q102" s="3" t="inlineStr">
-        <is>
-          <t>LSR 3</t>
-        </is>
-      </c>
-      <c r="R102" s="3" t="inlineStr">
-        <is>
-          <t>Intervention outcomes and spillover effects</t>
-        </is>
-      </c>
-      <c r="S102" s="3" t="n"/>
-      <c r="T102" s="3" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="U102" s="3" t="n"/>
-      <c r="V102" s="3" t="n"/>
-      <c r="W102" s="3" t="inlineStr">
-        <is>
-          <t>PS</t>
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>MF:0000020</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>mental process</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>A bodily process that occurs in the brain, and that can of itself be conscious, or can give rise to a process that can of itself be conscious or can give rise to behaviour.</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>bodily process</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>Intervention outcomes and spillover effects</t>
+        </is>
+      </c>
+      <c r="Q102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">LSR 3 </t>
+        </is>
+      </c>
+      <c r="R102" t="inlineStr">
+        <is>
+          <t>Intervention outcomes and spillover effects</t>
+        </is>
+      </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>External</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="3" t="inlineStr">
         <is>
-          <t>GMHO:0000183</t>
+          <t>GMHO:0000259</t>
         </is>
       </c>
       <c r="B103" s="3" t="inlineStr">
         <is>
-          <t>nausea following intervention</t>
+          <t>mental process scale</t>
         </is>
       </c>
       <c r="C103" s="3" t="inlineStr">
         <is>
-          <t>A digestive system adverse event following intervention that has an outcome of nausea, a gastric discomfort associated with the inclination to vomit</t>
+          <t>A measurement scale that is used to measure mental processes.</t>
         </is>
       </c>
       <c r="D103" s="3" t="inlineStr">
         <is>
-          <t>digestive system adverse event following intervention</t>
+          <t>measurement scale</t>
         </is>
       </c>
       <c r="E103" s="3" t="n"/>
@@ -6588,29 +6590,20 @@
       <c r="G103" s="3" t="n"/>
       <c r="H103" s="3" t="n"/>
       <c r="I103" s="3" t="n"/>
-      <c r="J103" s="3" t="n"/>
-      <c r="K103" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">cross reference: http://purl.obolibrary.org/obo/OAE_0000600
-</t>
-        </is>
-      </c>
-      <c r="L103" s="3" t="inlineStr">
-        <is>
-          <t>http://purl.obolibrary.org/obo/OAE_0000600</t>
-        </is>
-      </c>
-      <c r="M103" s="3" t="inlineStr">
-        <is>
-          <t>nausea</t>
-        </is>
-      </c>
+      <c r="J103" s="3" t="inlineStr">
+        <is>
+          <t>Intervention outcomes and spillover effects</t>
+        </is>
+      </c>
+      <c r="K103" s="3" t="n"/>
+      <c r="L103" s="3" t="n"/>
+      <c r="M103" s="3" t="n"/>
       <c r="N103" s="3" t="n"/>
       <c r="O103" s="3" t="n"/>
       <c r="P103" s="3" t="n"/>
       <c r="Q103" s="3" t="inlineStr">
         <is>
-          <t>LSR 1</t>
+          <t>LSR 3</t>
         </is>
       </c>
       <c r="R103" s="3" t="inlineStr">
@@ -6626,68 +6619,64 @@
       </c>
       <c r="U103" s="3" t="n"/>
       <c r="V103" s="3" t="n"/>
-      <c r="W103" s="3" t="inlineStr">
-        <is>
-          <t>PS; MS</t>
-        </is>
-      </c>
+      <c r="W103" s="3" t="n"/>
     </row>
     <row r="104">
-      <c r="A104" s="2" t="inlineStr">
-        <is>
-          <t>GMHO:0000069</t>
-        </is>
-      </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>negative psychotic disorder symptom</t>
-        </is>
-      </c>
-      <c r="C104" s="2" t="inlineStr">
-        <is>
-          <t>A psychotic disorder symptom that is characterized by the absence or decrease in ability or motivation to initiate plans, speak, express emotion of find pleasure.</t>
-        </is>
-      </c>
-      <c r="D104" s="2" t="inlineStr">
-        <is>
-          <t>psychotic disorder symptom</t>
-        </is>
-      </c>
-      <c r="E104" s="2" t="n"/>
-      <c r="F104" s="2" t="n"/>
-      <c r="G104" s="2" t="n"/>
-      <c r="H104" s="2" t="n"/>
-      <c r="I104" s="2" t="n"/>
-      <c r="J104" s="2" t="n"/>
-      <c r="K104" s="2" t="inlineStr">
-        <is>
-          <t>Based on https://www.psychiatry.org/patients-families/schizophrenia/what-is-schizophrenia</t>
-        </is>
-      </c>
-      <c r="L104" s="2" t="n"/>
-      <c r="M104" s="2" t="n"/>
-      <c r="N104" s="2" t="n"/>
-      <c r="O104" s="2" t="n"/>
-      <c r="P104" s="2" t="n"/>
-      <c r="Q104" s="2" t="inlineStr">
+      <c r="A104" s="3" t="inlineStr">
+        <is>
+          <t>GMHO:0000236</t>
+        </is>
+      </c>
+      <c r="B104" s="3" t="inlineStr">
+        <is>
+          <t>midpoint estimate for the mean difference of an outcome between the intervention and comparison condition</t>
+        </is>
+      </c>
+      <c r="C104" s="3" t="inlineStr">
+        <is>
+          <t>A point estimate about the mean difference between an intervention and comparison condition in a study.</t>
+        </is>
+      </c>
+      <c r="D104" s="3" t="inlineStr">
+        <is>
+          <t>point estimate</t>
+        </is>
+      </c>
+      <c r="E104" s="3" t="n"/>
+      <c r="F104" s="3" t="n"/>
+      <c r="G104" s="3" t="n"/>
+      <c r="H104" s="3" t="n"/>
+      <c r="I104" s="3" t="n"/>
+      <c r="J104" s="3" t="inlineStr">
+        <is>
+          <t>Intervention outcomes and spillover effects</t>
+        </is>
+      </c>
+      <c r="K104" s="3" t="n"/>
+      <c r="L104" s="3" t="n"/>
+      <c r="M104" s="3" t="n"/>
+      <c r="N104" s="3" t="n"/>
+      <c r="O104" s="3" t="n"/>
+      <c r="P104" s="3" t="n"/>
+      <c r="Q104" s="3" t="inlineStr">
         <is>
           <t>LSR 3</t>
         </is>
       </c>
-      <c r="R104" s="2" t="inlineStr">
-        <is>
-          <t>Intervention outcomes and spillover effects</t>
-        </is>
-      </c>
-      <c r="S104" s="2" t="n"/>
-      <c r="T104" s="2" t="inlineStr">
-        <is>
-          <t>Obsolete</t>
-        </is>
-      </c>
-      <c r="U104" s="2" t="n"/>
-      <c r="V104" s="2" t="n"/>
-      <c r="W104" s="2" t="inlineStr">
+      <c r="R104" s="3" t="inlineStr">
+        <is>
+          <t>Intervention outcomes and spillover effects</t>
+        </is>
+      </c>
+      <c r="S104" s="3" t="n"/>
+      <c r="T104" s="3" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="U104" s="3" t="n"/>
+      <c r="V104" s="3" t="n"/>
+      <c r="W104" s="3" t="inlineStr">
         <is>
           <t>PS</t>
         </is>
@@ -6696,22 +6685,22 @@
     <row r="105">
       <c r="A105" s="3" t="inlineStr">
         <is>
-          <t>GMHO:0000070</t>
+          <t>GMHO:0000183</t>
         </is>
       </c>
       <c r="B105" s="3" t="inlineStr">
         <is>
-          <t>negative psychotic disorder symptom severity</t>
+          <t>nausea following intervention</t>
         </is>
       </c>
       <c r="C105" s="3" t="inlineStr">
         <is>
-          <t>Psychotic disorder symptom severity that is associated with negative psychotic disorder symptoms.</t>
+          <t>A digestive system adverse event following intervention that has an outcome of nausea, a gastric discomfort associated with the inclination to vomit</t>
         </is>
       </c>
       <c r="D105" s="3" t="inlineStr">
         <is>
-          <t>psychotic disorder symptom severity</t>
+          <t>digestive system adverse event following intervention</t>
         </is>
       </c>
       <c r="E105" s="3" t="n"/>
@@ -6719,20 +6708,29 @@
       <c r="G105" s="3" t="n"/>
       <c r="H105" s="3" t="n"/>
       <c r="I105" s="3" t="n"/>
-      <c r="J105" s="3" t="inlineStr">
-        <is>
-          <t>Intervention outcomes and spillover effects</t>
-        </is>
-      </c>
-      <c r="K105" s="3" t="n"/>
-      <c r="L105" s="3" t="n"/>
-      <c r="M105" s="3" t="n"/>
+      <c r="J105" s="3" t="n"/>
+      <c r="K105" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cross reference: http://purl.obolibrary.org/obo/OAE_0000600
+</t>
+        </is>
+      </c>
+      <c r="L105" s="3" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/OAE_0000600</t>
+        </is>
+      </c>
+      <c r="M105" s="3" t="inlineStr">
+        <is>
+          <t>nausea</t>
+        </is>
+      </c>
       <c r="N105" s="3" t="n"/>
       <c r="O105" s="3" t="n"/>
       <c r="P105" s="3" t="n"/>
       <c r="Q105" s="3" t="inlineStr">
         <is>
-          <t>LSR 3</t>
+          <t>LSR 1</t>
         </is>
       </c>
       <c r="R105" s="3" t="inlineStr">
@@ -6750,127 +6748,127 @@
       <c r="V105" s="3" t="n"/>
       <c r="W105" s="3" t="inlineStr">
         <is>
-          <t>PS</t>
+          <t>PS; MS</t>
         </is>
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="3" t="inlineStr">
-        <is>
-          <t>GMHO:0000225</t>
-        </is>
-      </c>
-      <c r="B106" s="3" t="inlineStr">
-        <is>
-          <t>negative psychotic disorder symptom severity scale</t>
-        </is>
-      </c>
-      <c r="C106" s="3" t="inlineStr">
-        <is>
-          <t>A psychotic disorder symptom severity scale that is associated with negative psychotic disorder symptoms.</t>
-        </is>
-      </c>
-      <c r="D106" s="3" t="inlineStr">
-        <is>
-          <t>psychotic disorder symptom severity scale</t>
-        </is>
-      </c>
-      <c r="E106" s="3" t="n"/>
-      <c r="F106" s="3" t="n"/>
-      <c r="G106" s="3" t="n"/>
-      <c r="H106" s="3" t="n"/>
-      <c r="I106" s="3" t="n"/>
-      <c r="J106" s="3" t="inlineStr">
-        <is>
-          <t>Intervention outcomes and spillover effects</t>
-        </is>
-      </c>
-      <c r="K106" s="3" t="n"/>
-      <c r="L106" s="3" t="n"/>
-      <c r="M106" s="3" t="n"/>
-      <c r="N106" s="3" t="n"/>
-      <c r="O106" s="3" t="n"/>
-      <c r="P106" s="3" t="n"/>
-      <c r="Q106" s="3" t="inlineStr">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>GMHO:0000069</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>negative psychotic disorder symptom</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>A psychotic disorder symptom that is characterized by the absence or decrease in ability or motivation to initiate plans, speak, express emotion of find pleasure.</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>psychotic disorder symptom</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="n"/>
+      <c r="F106" s="2" t="n"/>
+      <c r="G106" s="2" t="n"/>
+      <c r="H106" s="2" t="n"/>
+      <c r="I106" s="2" t="n"/>
+      <c r="J106" s="2" t="n"/>
+      <c r="K106" s="2" t="inlineStr">
+        <is>
+          <t>Based on https://www.psychiatry.org/patients-families/schizophrenia/what-is-schizophrenia</t>
+        </is>
+      </c>
+      <c r="L106" s="2" t="n"/>
+      <c r="M106" s="2" t="n"/>
+      <c r="N106" s="2" t="n"/>
+      <c r="O106" s="2" t="n"/>
+      <c r="P106" s="2" t="n"/>
+      <c r="Q106" s="2" t="inlineStr">
         <is>
           <t>LSR 3</t>
         </is>
       </c>
-      <c r="R106" s="3" t="inlineStr">
-        <is>
-          <t>Intervention outcomes and spillover effects</t>
-        </is>
-      </c>
-      <c r="S106" s="3" t="n"/>
-      <c r="T106" s="3" t="inlineStr">
+      <c r="R106" s="2" t="inlineStr">
+        <is>
+          <t>Intervention outcomes and spillover effects</t>
+        </is>
+      </c>
+      <c r="S106" s="2" t="n"/>
+      <c r="T106" s="2" t="inlineStr">
+        <is>
+          <t>Obsolete</t>
+        </is>
+      </c>
+      <c r="U106" s="2" t="n"/>
+      <c r="V106" s="2" t="n"/>
+      <c r="W106" s="2" t="inlineStr">
+        <is>
+          <t>PS</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="3" t="inlineStr">
+        <is>
+          <t>GMHO:0000070</t>
+        </is>
+      </c>
+      <c r="B107" s="3" t="inlineStr">
+        <is>
+          <t>negative psychotic disorder symptom severity</t>
+        </is>
+      </c>
+      <c r="C107" s="3" t="inlineStr">
+        <is>
+          <t>Psychotic disorder symptom severity that is associated with negative psychotic disorder symptoms.</t>
+        </is>
+      </c>
+      <c r="D107" s="3" t="inlineStr">
+        <is>
+          <t>psychotic disorder symptom severity</t>
+        </is>
+      </c>
+      <c r="E107" s="3" t="n"/>
+      <c r="F107" s="3" t="n"/>
+      <c r="G107" s="3" t="n"/>
+      <c r="H107" s="3" t="n"/>
+      <c r="I107" s="3" t="n"/>
+      <c r="J107" s="3" t="inlineStr">
+        <is>
+          <t>Intervention outcomes and spillover effects</t>
+        </is>
+      </c>
+      <c r="K107" s="3" t="n"/>
+      <c r="L107" s="3" t="n"/>
+      <c r="M107" s="3" t="n"/>
+      <c r="N107" s="3" t="n"/>
+      <c r="O107" s="3" t="n"/>
+      <c r="P107" s="3" t="n"/>
+      <c r="Q107" s="3" t="inlineStr">
+        <is>
+          <t>LSR 3</t>
+        </is>
+      </c>
+      <c r="R107" s="3" t="inlineStr">
+        <is>
+          <t>Intervention outcomes and spillover effects</t>
+        </is>
+      </c>
+      <c r="S107" s="3" t="n"/>
+      <c r="T107" s="3" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="U106" s="3" t="n"/>
-      <c r="V106" s="3" t="n"/>
-      <c r="W106" s="3" t="inlineStr">
-        <is>
-          <t>PS</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="2" t="inlineStr">
-        <is>
-          <t>GMHO:0000071</t>
-        </is>
-      </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">neuroleptic-induced parkinsonism following intervention </t>
-        </is>
-      </c>
-      <c r="C107" s="2" t="inlineStr">
-        <is>
-          <t>A drug-induced movement disorder following intervention that involves experiencing slowness of movement, tremors and rigidity.</t>
-        </is>
-      </c>
-      <c r="D107" s="2" t="inlineStr">
-        <is>
-          <t>drug-induced movement disorder following intervention</t>
-        </is>
-      </c>
-      <c r="E107" s="2" t="n"/>
-      <c r="F107" s="2" t="n"/>
-      <c r="G107" s="2" t="n"/>
-      <c r="H107" s="2" t="n"/>
-      <c r="I107" s="2" t="n"/>
-      <c r="J107" s="2" t="n"/>
-      <c r="K107" s="2" t="inlineStr">
-        <is>
-          <t>Based on https://link.springer.com/article/10.1007/s007020100006</t>
-        </is>
-      </c>
-      <c r="L107" s="2" t="n"/>
-      <c r="M107" s="2" t="n"/>
-      <c r="N107" s="2" t="n"/>
-      <c r="O107" s="2" t="n"/>
-      <c r="P107" s="2" t="n"/>
-      <c r="Q107" s="2" t="inlineStr">
-        <is>
-          <t>LSR 3</t>
-        </is>
-      </c>
-      <c r="R107" s="2" t="inlineStr">
-        <is>
-          <t>Intervention outcomes and spillover effects</t>
-        </is>
-      </c>
-      <c r="S107" s="2" t="n"/>
-      <c r="T107" s="2" t="inlineStr">
-        <is>
-          <t>Obsolete</t>
-        </is>
-      </c>
-      <c r="U107" s="2" t="n"/>
-      <c r="V107" s="2" t="n"/>
-      <c r="W107" s="2" t="inlineStr">
+      <c r="U107" s="3" t="n"/>
+      <c r="V107" s="3" t="n"/>
+      <c r="W107" s="3" t="inlineStr">
         <is>
           <t>PS</t>
         </is>
@@ -6879,22 +6877,22 @@
     <row r="108">
       <c r="A108" s="3" t="inlineStr">
         <is>
-          <t>GMHO:0000072</t>
+          <t>GMHO:0000225</t>
         </is>
       </c>
       <c r="B108" s="3" t="inlineStr">
         <is>
-          <t>number of participant drop-out due to adverse events</t>
+          <t>negative psychotic disorder symptom severity scale</t>
         </is>
       </c>
       <c r="C108" s="3" t="inlineStr">
         <is>
-          <t>Number of participant drop-out from the study as a result the participants experiencing some adverse event.</t>
+          <t>A psychotic disorder symptom severity scale that is associated with negative psychotic disorder symptoms.</t>
         </is>
       </c>
       <c r="D108" s="3" t="inlineStr">
         <is>
-          <t>number of participant drop-out from study</t>
+          <t>psychotic disorder symptom severity scale</t>
         </is>
       </c>
       <c r="E108" s="3" t="n"/>
@@ -6915,7 +6913,7 @@
       <c r="P108" s="3" t="n"/>
       <c r="Q108" s="3" t="inlineStr">
         <is>
-          <t>LSR 1; LSR 3</t>
+          <t>LSR 3</t>
         </is>
       </c>
       <c r="R108" s="3" t="inlineStr">
@@ -6940,22 +6938,22 @@
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>GMHO:0000073</t>
+          <t>GMHO:0000071</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>number of participant drop-out due to inefficacy</t>
+          <t xml:space="preserve">neuroleptic-induced parkinsonism following intervention </t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>Number of participant drop-out from the intervention as a result of the intervention failing to produce the desired effect.</t>
+          <t>A drug-induced movement disorder following intervention that involves experiencing slowness of movement, tremors and rigidity.</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>number of participant drop-out from intervention</t>
+          <t>drug-induced movement disorder following intervention</t>
         </is>
       </c>
       <c r="E109" s="2" t="n"/>
@@ -6964,7 +6962,11 @@
       <c r="H109" s="2" t="n"/>
       <c r="I109" s="2" t="n"/>
       <c r="J109" s="2" t="n"/>
-      <c r="K109" s="2" t="n"/>
+      <c r="K109" s="2" t="inlineStr">
+        <is>
+          <t>Based on https://link.springer.com/article/10.1007/s007020100006</t>
+        </is>
+      </c>
       <c r="L109" s="2" t="n"/>
       <c r="M109" s="2" t="n"/>
       <c r="N109" s="2" t="n"/>
@@ -6995,57 +6997,61 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="2" t="inlineStr">
-        <is>
-          <t>GMHO:0000074</t>
-        </is>
-      </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>number of participant drop-out due to side-effects</t>
-        </is>
-      </c>
-      <c r="C110" s="2" t="inlineStr">
-        <is>
-          <t>Number of participant drop-out due to adverse events that are experienced following the intervention.</t>
-        </is>
-      </c>
-      <c r="D110" s="2" t="inlineStr">
+      <c r="A110" s="3" t="inlineStr">
+        <is>
+          <t>GMHO:0000072</t>
+        </is>
+      </c>
+      <c r="B110" s="3" t="inlineStr">
         <is>
           <t>number of participant drop-out due to adverse events</t>
         </is>
       </c>
-      <c r="E110" s="2" t="n"/>
-      <c r="F110" s="2" t="n"/>
-      <c r="G110" s="2" t="n"/>
-      <c r="H110" s="2" t="n"/>
-      <c r="I110" s="2" t="n"/>
-      <c r="J110" s="2" t="n"/>
-      <c r="K110" s="2" t="n"/>
-      <c r="L110" s="2" t="n"/>
-      <c r="M110" s="2" t="n"/>
-      <c r="N110" s="2" t="n"/>
-      <c r="O110" s="2" t="n"/>
-      <c r="P110" s="2" t="n"/>
-      <c r="Q110" s="2" t="inlineStr">
+      <c r="C110" s="3" t="inlineStr">
+        <is>
+          <t>Number of participant drop-out from the study as a result the participants experiencing some adverse event.</t>
+        </is>
+      </c>
+      <c r="D110" s="3" t="inlineStr">
+        <is>
+          <t>number of participant drop-out from study</t>
+        </is>
+      </c>
+      <c r="E110" s="3" t="n"/>
+      <c r="F110" s="3" t="n"/>
+      <c r="G110" s="3" t="n"/>
+      <c r="H110" s="3" t="n"/>
+      <c r="I110" s="3" t="n"/>
+      <c r="J110" s="3" t="inlineStr">
+        <is>
+          <t>Intervention outcomes and spillover effects</t>
+        </is>
+      </c>
+      <c r="K110" s="3" t="n"/>
+      <c r="L110" s="3" t="n"/>
+      <c r="M110" s="3" t="n"/>
+      <c r="N110" s="3" t="n"/>
+      <c r="O110" s="3" t="n"/>
+      <c r="P110" s="3" t="n"/>
+      <c r="Q110" s="3" t="inlineStr">
         <is>
           <t>LSR 1; LSR 3</t>
         </is>
       </c>
-      <c r="R110" s="2" t="inlineStr">
-        <is>
-          <t>Intervention outcomes and spillover effects</t>
-        </is>
-      </c>
-      <c r="S110" s="2" t="n"/>
-      <c r="T110" s="2" t="inlineStr">
-        <is>
-          <t>Obsolete</t>
-        </is>
-      </c>
-      <c r="U110" s="2" t="n"/>
-      <c r="V110" s="2" t="n"/>
-      <c r="W110" s="2" t="inlineStr">
+      <c r="R110" s="3" t="inlineStr">
+        <is>
+          <t>Intervention outcomes and spillover effects</t>
+        </is>
+      </c>
+      <c r="S110" s="3" t="n"/>
+      <c r="T110" s="3" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="U110" s="3" t="n"/>
+      <c r="V110" s="3" t="n"/>
+      <c r="W110" s="3" t="inlineStr">
         <is>
           <t>PS</t>
         </is>
@@ -7054,22 +7060,22 @@
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>GMHO:0000134</t>
+          <t>GMHO:0000073</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>number of participant drop-out from intervention arm</t>
+          <t>number of participant drop-out due to inefficacy</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>Number of intervention participants who discontinue participating in an intervention arm.</t>
+          <t>Number of participant drop-out from the intervention as a result of the intervention failing to produce the desired effect.</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
         <is>
-          <t>number of intervention participants</t>
+          <t>number of participant drop-out from intervention</t>
         </is>
       </c>
       <c r="E111" s="2" t="n"/>
@@ -7086,7 +7092,7 @@
       <c r="P111" s="2" t="n"/>
       <c r="Q111" s="2" t="inlineStr">
         <is>
-          <t>LSR 1</t>
+          <t>LSR 3</t>
         </is>
       </c>
       <c r="R111" s="2" t="inlineStr">
@@ -7109,141 +7115,133 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="3" t="inlineStr">
-        <is>
-          <t>GMHO:0000075</t>
-        </is>
-      </c>
-      <c r="B112" s="3" t="inlineStr">
-        <is>
-          <t>number of participant drop-out from study</t>
-        </is>
-      </c>
-      <c r="C112" s="3" t="inlineStr">
-        <is>
-          <t>Number of study participants who withdraw from or cannot complete a study.</t>
-        </is>
-      </c>
-      <c r="D112" s="3" t="inlineStr">
-        <is>
-          <t>number of study participants</t>
-        </is>
-      </c>
-      <c r="E112" s="3" t="n"/>
-      <c r="F112" s="3" t="n"/>
-      <c r="G112" s="3" t="n"/>
-      <c r="H112" s="3" t="n"/>
-      <c r="I112" s="3" t="n"/>
-      <c r="J112" s="3" t="inlineStr">
-        <is>
-          <t>Intervention outcomes and spillover effects</t>
-        </is>
-      </c>
-      <c r="K112" s="3" t="n"/>
-      <c r="L112" s="3" t="n"/>
-      <c r="M112" s="3" t="n"/>
-      <c r="N112" s="3" t="n"/>
-      <c r="O112" s="3" t="n"/>
-      <c r="P112" s="3" t="n"/>
-      <c r="Q112" s="3" t="inlineStr">
-        <is>
-          <t>LSR 1; LSR 2; LSR 3</t>
-        </is>
-      </c>
-      <c r="R112" s="3" t="inlineStr">
-        <is>
-          <t>Intervention outcomes and spillover effects</t>
-        </is>
-      </c>
-      <c r="S112" s="3" t="n"/>
-      <c r="T112" s="3" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="U112" s="3" t="n"/>
-      <c r="V112" s="3" t="n"/>
-      <c r="W112" s="3" t="inlineStr">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>GMHO:0000074</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>number of participant drop-out due to side-effects</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>Number of participant drop-out due to adverse events that are experienced following the intervention.</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
+        <is>
+          <t>number of participant drop-out due to adverse events</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="n"/>
+      <c r="F112" s="2" t="n"/>
+      <c r="G112" s="2" t="n"/>
+      <c r="H112" s="2" t="n"/>
+      <c r="I112" s="2" t="n"/>
+      <c r="J112" s="2" t="n"/>
+      <c r="K112" s="2" t="n"/>
+      <c r="L112" s="2" t="n"/>
+      <c r="M112" s="2" t="n"/>
+      <c r="N112" s="2" t="n"/>
+      <c r="O112" s="2" t="n"/>
+      <c r="P112" s="2" t="n"/>
+      <c r="Q112" s="2" t="inlineStr">
+        <is>
+          <t>LSR 1; LSR 3</t>
+        </is>
+      </c>
+      <c r="R112" s="2" t="inlineStr">
+        <is>
+          <t>Intervention outcomes and spillover effects</t>
+        </is>
+      </c>
+      <c r="S112" s="2" t="n"/>
+      <c r="T112" s="2" t="inlineStr">
+        <is>
+          <t>Obsolete</t>
+        </is>
+      </c>
+      <c r="U112" s="2" t="n"/>
+      <c r="V112" s="2" t="n"/>
+      <c r="W112" s="2" t="inlineStr">
         <is>
           <t>PS</t>
         </is>
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="3" t="inlineStr">
-        <is>
-          <t>GMHO:0000258</t>
-        </is>
-      </c>
-      <c r="B113" s="3" t="inlineStr">
-        <is>
-          <t>number of participants with drop-out assessment</t>
-        </is>
-      </c>
-      <c r="C113" s="3" t="inlineStr">
-        <is>
-          <t>Number of study participants for whom a drop-out assessment was made.</t>
-        </is>
-      </c>
-      <c r="D113" s="3" t="inlineStr">
-        <is>
-          <t>number of study participants</t>
-        </is>
-      </c>
-      <c r="E113" s="3" t="n"/>
-      <c r="F113" s="3" t="inlineStr">
-        <is>
-          <t>The number of participants in the study who were evaluated to determine whether they dropped out.</t>
-        </is>
-      </c>
-      <c r="G113" s="3" t="n"/>
-      <c r="H113" s="3" t="n"/>
-      <c r="I113" s="3" t="n"/>
-      <c r="J113" s="3" t="inlineStr">
-        <is>
-          <t>Intervention outcomes and spillover effects</t>
-        </is>
-      </c>
-      <c r="K113" s="3" t="n"/>
-      <c r="L113" s="3" t="n"/>
-      <c r="M113" s="3" t="n"/>
-      <c r="N113" s="3" t="n"/>
-      <c r="O113" s="3" t="n"/>
-      <c r="P113" s="3" t="n"/>
-      <c r="Q113" s="3" t="inlineStr">
-        <is>
-          <t>LSR 3</t>
-        </is>
-      </c>
-      <c r="R113" s="3" t="inlineStr">
-        <is>
-          <t>Intervention outcomes and spillover effects</t>
-        </is>
-      </c>
-      <c r="S113" s="3" t="n"/>
-      <c r="T113" s="3" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="U113" s="3" t="n"/>
-      <c r="V113" s="3" t="n"/>
-      <c r="W113" s="3" t="n"/>
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>GMHO:0000134</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>number of participant drop-out from intervention arm</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>Number of intervention participants who discontinue participating in an intervention arm.</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
+        <is>
+          <t>number of intervention participants</t>
+        </is>
+      </c>
+      <c r="E113" s="2" t="n"/>
+      <c r="F113" s="2" t="n"/>
+      <c r="G113" s="2" t="n"/>
+      <c r="H113" s="2" t="n"/>
+      <c r="I113" s="2" t="n"/>
+      <c r="J113" s="2" t="n"/>
+      <c r="K113" s="2" t="n"/>
+      <c r="L113" s="2" t="n"/>
+      <c r="M113" s="2" t="n"/>
+      <c r="N113" s="2" t="n"/>
+      <c r="O113" s="2" t="n"/>
+      <c r="P113" s="2" t="n"/>
+      <c r="Q113" s="2" t="inlineStr">
+        <is>
+          <t>LSR 1</t>
+        </is>
+      </c>
+      <c r="R113" s="2" t="inlineStr">
+        <is>
+          <t>Intervention outcomes and spillover effects</t>
+        </is>
+      </c>
+      <c r="S113" s="2" t="n"/>
+      <c r="T113" s="2" t="inlineStr">
+        <is>
+          <t>Obsolete</t>
+        </is>
+      </c>
+      <c r="U113" s="2" t="n"/>
+      <c r="V113" s="2" t="n"/>
+      <c r="W113" s="2" t="inlineStr">
+        <is>
+          <t>PS</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="3" t="inlineStr">
         <is>
-          <t>GMHO:0000206</t>
+          <t>GMHO:0000075</t>
         </is>
       </c>
       <c r="B114" s="3" t="inlineStr">
         <is>
-          <t>number of participants with measurement</t>
+          <t>number of participant drop-out from study</t>
         </is>
       </c>
       <c r="C114" s="3" t="inlineStr">
         <is>
-          <t>Number of study participants for whom a measurement was made.</t>
+          <t>Number of study participants who withdraw from or cannot complete a study.</t>
         </is>
       </c>
       <c r="D114" s="3" t="inlineStr">
@@ -7256,7 +7254,11 @@
       <c r="G114" s="3" t="n"/>
       <c r="H114" s="3" t="n"/>
       <c r="I114" s="3" t="n"/>
-      <c r="J114" s="3" t="n"/>
+      <c r="J114" s="3" t="inlineStr">
+        <is>
+          <t>Intervention outcomes and spillover effects</t>
+        </is>
+      </c>
       <c r="K114" s="3" t="n"/>
       <c r="L114" s="3" t="n"/>
       <c r="M114" s="3" t="n"/>
@@ -7265,7 +7267,7 @@
       <c r="P114" s="3" t="n"/>
       <c r="Q114" s="3" t="inlineStr">
         <is>
-          <t>LSR 1, LSR 2; LSR 3</t>
+          <t>LSR 1; LSR 2; LSR 3</t>
         </is>
       </c>
       <c r="R114" s="3" t="inlineStr">
@@ -7283,24 +7285,24 @@
       <c r="V114" s="3" t="n"/>
       <c r="W114" s="3" t="inlineStr">
         <is>
-          <t>PS; MS</t>
+          <t>PS</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="3" t="inlineStr">
         <is>
-          <t>GMHO:0000214</t>
+          <t>GMHO:0000258</t>
         </is>
       </c>
       <c r="B115" s="3" t="inlineStr">
         <is>
-          <t>number of participants with specific outcome</t>
+          <t>number of participants with drop-out assessment</t>
         </is>
       </c>
       <c r="C115" s="3" t="inlineStr">
         <is>
-          <t>Number of study participants for whom an outcome has been identified within a study.</t>
+          <t>Number of study participants for whom a drop-out assessment was made.</t>
         </is>
       </c>
       <c r="D115" s="3" t="inlineStr">
@@ -7309,7 +7311,11 @@
         </is>
       </c>
       <c r="E115" s="3" t="n"/>
-      <c r="F115" s="3" t="n"/>
+      <c r="F115" s="3" t="inlineStr">
+        <is>
+          <t>The number of participants in the study who were evaluated to determine whether they dropped out.</t>
+        </is>
+      </c>
       <c r="G115" s="3" t="n"/>
       <c r="H115" s="3" t="n"/>
       <c r="I115" s="3" t="n"/>
@@ -7326,7 +7332,7 @@
       <c r="P115" s="3" t="n"/>
       <c r="Q115" s="3" t="inlineStr">
         <is>
-          <t>LSR 1, LSR 3</t>
+          <t>LSR 3</t>
         </is>
       </c>
       <c r="R115" s="3" t="inlineStr">
@@ -7342,73 +7348,84 @@
       </c>
       <c r="U115" s="3" t="n"/>
       <c r="V115" s="3" t="n"/>
-      <c r="W115" s="3" t="inlineStr">
-        <is>
-          <t>PS</t>
-        </is>
-      </c>
+      <c r="W115" s="3" t="n"/>
     </row>
     <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>BFO:0000038</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>one-dimensional temporal region</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t xml:space="preserve">A one-dimensional temporal region is a temporal region that is extended. </t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr">
-        <is>
-          <t>temporal region</t>
-        </is>
-      </c>
-      <c r="Q116" t="inlineStr">
-        <is>
-          <t>LSR 1</t>
-        </is>
-      </c>
-      <c r="R116" t="inlineStr">
-        <is>
-          <t>Intervention outcomes and spillover effects</t>
-        </is>
-      </c>
-      <c r="T116" t="inlineStr">
-        <is>
-          <t>External</t>
-        </is>
-      </c>
-      <c r="W116" t="inlineStr">
-        <is>
-          <t>PS</t>
+      <c r="A116" s="3" t="inlineStr">
+        <is>
+          <t>GMHO:0000206</t>
+        </is>
+      </c>
+      <c r="B116" s="3" t="inlineStr">
+        <is>
+          <t>number of participants with measurement</t>
+        </is>
+      </c>
+      <c r="C116" s="3" t="inlineStr">
+        <is>
+          <t>Number of study participants for whom a measurement was made.</t>
+        </is>
+      </c>
+      <c r="D116" s="3" t="inlineStr">
+        <is>
+          <t>number of study participants</t>
+        </is>
+      </c>
+      <c r="E116" s="3" t="n"/>
+      <c r="F116" s="3" t="n"/>
+      <c r="G116" s="3" t="n"/>
+      <c r="H116" s="3" t="n"/>
+      <c r="I116" s="3" t="n"/>
+      <c r="J116" s="3" t="n"/>
+      <c r="K116" s="3" t="n"/>
+      <c r="L116" s="3" t="n"/>
+      <c r="M116" s="3" t="n"/>
+      <c r="N116" s="3" t="n"/>
+      <c r="O116" s="3" t="n"/>
+      <c r="P116" s="3" t="n"/>
+      <c r="Q116" s="3" t="inlineStr">
+        <is>
+          <t>LSR 1, LSR 2; LSR 3</t>
+        </is>
+      </c>
+      <c r="R116" s="3" t="inlineStr">
+        <is>
+          <t>Intervention outcomes and spillover effects</t>
+        </is>
+      </c>
+      <c r="S116" s="3" t="n"/>
+      <c r="T116" s="3" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="U116" s="3" t="n"/>
+      <c r="V116" s="3" t="n"/>
+      <c r="W116" s="3" t="inlineStr">
+        <is>
+          <t>PS; MS</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="3" t="inlineStr">
         <is>
-          <t>GMHO:0000184</t>
+          <t>GMHO:0000214</t>
         </is>
       </c>
       <c r="B117" s="3" t="inlineStr">
         <is>
-          <t>pain following intervention</t>
+          <t>number of participants with specific outcome</t>
         </is>
       </c>
       <c r="C117" s="3" t="inlineStr">
         <is>
-          <t>An adverse event following an intervention that has an outcome of pain.</t>
+          <t>Number of study participants for whom an outcome has been identified within a study.</t>
         </is>
       </c>
       <c r="D117" s="3" t="inlineStr">
         <is>
-          <t>adverse event following an intervention</t>
+          <t>number of study participants</t>
         </is>
       </c>
       <c r="E117" s="3" t="n"/>
@@ -7416,22 +7433,14 @@
       <c r="G117" s="3" t="n"/>
       <c r="H117" s="3" t="n"/>
       <c r="I117" s="3" t="n"/>
-      <c r="J117" s="3" t="n"/>
-      <c r="K117" s="3" t="inlineStr">
-        <is>
-          <t>cross-reference: http://purl.obolibrary.org/obo/OAE_0000374</t>
-        </is>
-      </c>
-      <c r="L117" s="3" t="inlineStr">
-        <is>
-          <t>http://purl.obolibrary.org/obo/OAE_0000374</t>
-        </is>
-      </c>
-      <c r="M117" s="3" t="inlineStr">
-        <is>
-          <t>pain</t>
-        </is>
-      </c>
+      <c r="J117" s="3" t="inlineStr">
+        <is>
+          <t>Intervention outcomes and spillover effects</t>
+        </is>
+      </c>
+      <c r="K117" s="3" t="n"/>
+      <c r="L117" s="3" t="n"/>
+      <c r="M117" s="3" t="n"/>
       <c r="N117" s="3" t="n"/>
       <c r="O117" s="3" t="n"/>
       <c r="P117" s="3" t="n"/>
@@ -7455,217 +7464,210 @@
       <c r="V117" s="3" t="n"/>
       <c r="W117" s="3" t="inlineStr">
         <is>
-          <t>PS; MS</t>
+          <t>PS</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
+          <t>BFO:0000038</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>one-dimensional temporal region</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t xml:space="preserve">A one-dimensional temporal region is a temporal region that is extended. </t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>temporal region</t>
+        </is>
+      </c>
+      <c r="Q118" t="inlineStr">
+        <is>
+          <t>LSR 1</t>
+        </is>
+      </c>
+      <c r="R118" t="inlineStr">
+        <is>
+          <t>Intervention outcomes and spillover effects</t>
+        </is>
+      </c>
+      <c r="T118" t="inlineStr">
+        <is>
+          <t>External</t>
+        </is>
+      </c>
+      <c r="W118" t="inlineStr">
+        <is>
+          <t>PS</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="3" t="inlineStr">
+        <is>
+          <t>GMHO:0000184</t>
+        </is>
+      </c>
+      <c r="B119" s="3" t="inlineStr">
+        <is>
+          <t>pain following intervention</t>
+        </is>
+      </c>
+      <c r="C119" s="3" t="inlineStr">
+        <is>
+          <t>An adverse event following an intervention that has an outcome of pain.</t>
+        </is>
+      </c>
+      <c r="D119" s="3" t="inlineStr">
+        <is>
+          <t>adverse event following an intervention</t>
+        </is>
+      </c>
+      <c r="E119" s="3" t="n"/>
+      <c r="F119" s="3" t="n"/>
+      <c r="G119" s="3" t="n"/>
+      <c r="H119" s="3" t="n"/>
+      <c r="I119" s="3" t="n"/>
+      <c r="J119" s="3" t="n"/>
+      <c r="K119" s="3" t="inlineStr">
+        <is>
+          <t>cross-reference: http://purl.obolibrary.org/obo/OAE_0000374</t>
+        </is>
+      </c>
+      <c r="L119" s="3" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/OAE_0000374</t>
+        </is>
+      </c>
+      <c r="M119" s="3" t="inlineStr">
+        <is>
+          <t>pain</t>
+        </is>
+      </c>
+      <c r="N119" s="3" t="n"/>
+      <c r="O119" s="3" t="n"/>
+      <c r="P119" s="3" t="n"/>
+      <c r="Q119" s="3" t="inlineStr">
+        <is>
+          <t>LSR 1, LSR 3</t>
+        </is>
+      </c>
+      <c r="R119" s="3" t="inlineStr">
+        <is>
+          <t>Intervention outcomes and spillover effects</t>
+        </is>
+      </c>
+      <c r="S119" s="3" t="n"/>
+      <c r="T119" s="3" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="U119" s="3" t="n"/>
+      <c r="V119" s="3" t="n"/>
+      <c r="W119" s="3" t="inlineStr">
+        <is>
+          <t>PS; MS</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
           <t>OGMS:0000061</t>
         </is>
       </c>
-      <c r="B118" t="inlineStr">
+      <c r="B120" t="inlineStr">
         <is>
           <t>pathological bodily process</t>
         </is>
       </c>
-      <c r="C118" t="inlineStr">
+      <c r="C120" t="inlineStr">
         <is>
           <t>A bodily process that is clinically abnormal.</t>
         </is>
       </c>
-      <c r="D118" t="inlineStr">
+      <c r="D120" t="inlineStr">
         <is>
           <t>bodily process</t>
         </is>
       </c>
-      <c r="J118" t="inlineStr">
-        <is>
-          <t>Intervention outcomes and spillover effects</t>
-        </is>
-      </c>
-      <c r="Q118" t="inlineStr">
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>Intervention outcomes and spillover effects</t>
+        </is>
+      </c>
+      <c r="Q120" t="inlineStr">
         <is>
           <t>LSR 1; LSR 3</t>
         </is>
       </c>
-      <c r="R118" t="inlineStr">
-        <is>
-          <t>Intervention outcomes and spillover effects</t>
-        </is>
-      </c>
-      <c r="T118" t="inlineStr">
+      <c r="R120" t="inlineStr">
+        <is>
+          <t>Intervention outcomes and spillover effects</t>
+        </is>
+      </c>
+      <c r="T120" t="inlineStr">
         <is>
           <t>External</t>
         </is>
       </c>
-      <c r="W118" t="inlineStr">
-        <is>
-          <t>PS</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
+      <c r="W120" t="inlineStr">
+        <is>
+          <t>PS</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
         <is>
           <t>STATO:0000599</t>
         </is>
       </c>
-      <c r="B119" t="inlineStr">
+      <c r="B121" t="inlineStr">
         <is>
           <t>point estimate</t>
         </is>
       </c>
-      <c r="C119" t="inlineStr">
+      <c r="C121" t="inlineStr">
         <is>
           <t>a point estimate is a data item which provides a particular value evaluating a population parameter.</t>
         </is>
       </c>
-      <c r="D119" t="inlineStr">
+      <c r="D121" t="inlineStr">
         <is>
           <t>estimate</t>
         </is>
       </c>
-      <c r="J119" t="inlineStr">
-        <is>
-          <t>Intervention outcomes and spillover effects</t>
-        </is>
-      </c>
-      <c r="Q119" t="inlineStr">
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>Intervention outcomes and spillover effects</t>
+        </is>
+      </c>
+      <c r="Q121" t="inlineStr">
         <is>
           <t>LSR 3</t>
         </is>
       </c>
-      <c r="R119" t="inlineStr">
-        <is>
-          <t>Intervention outcomes and spillover effects</t>
-        </is>
-      </c>
-      <c r="T119" t="inlineStr">
+      <c r="R121" t="inlineStr">
+        <is>
+          <t>Intervention outcomes and spillover effects</t>
+        </is>
+      </c>
+      <c r="T121" t="inlineStr">
         <is>
           <t>External</t>
         </is>
       </c>
-      <c r="W119" t="inlineStr">
-        <is>
-          <t>PS</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" s="3" t="inlineStr">
-        <is>
-          <t>GMHO:0000076</t>
-        </is>
-      </c>
-      <c r="B120" s="3" t="inlineStr">
-        <is>
-          <t>positive intervention outcome</t>
-        </is>
-      </c>
-      <c r="C120" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">An intervention outcome that is positively influenced by the intervention. </t>
-        </is>
-      </c>
-      <c r="D120" s="3" t="inlineStr">
-        <is>
-          <t>intervention outcome</t>
-        </is>
-      </c>
-      <c r="E120" s="3" t="n"/>
-      <c r="F120" s="3" t="n"/>
-      <c r="G120" s="3" t="n"/>
-      <c r="H120" s="3" t="n"/>
-      <c r="I120" s="3" t="n"/>
-      <c r="J120" s="3" t="n"/>
-      <c r="K120" s="3" t="n"/>
-      <c r="L120" s="3" t="n"/>
-      <c r="M120" s="3" t="n"/>
-      <c r="N120" s="3" t="n"/>
-      <c r="O120" s="3" t="n"/>
-      <c r="P120" s="3" t="n"/>
-      <c r="Q120" s="3" t="inlineStr">
-        <is>
-          <t>LSR 3</t>
-        </is>
-      </c>
-      <c r="R120" s="3" t="inlineStr">
-        <is>
-          <t>Intervention outcomes and spillover effects</t>
-        </is>
-      </c>
-      <c r="S120" s="3" t="n"/>
-      <c r="T120" s="3" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="U120" s="3" t="n"/>
-      <c r="V120" s="3" t="n"/>
-      <c r="W120" s="3" t="inlineStr">
-        <is>
-          <t>PS</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" s="2" t="inlineStr">
-        <is>
-          <t>GMHO:0000077</t>
-        </is>
-      </c>
-      <c r="B121" s="2" t="inlineStr">
-        <is>
-          <t>positive psychotic disorder symptom</t>
-        </is>
-      </c>
-      <c r="C121" s="2" t="inlineStr">
-        <is>
-          <t>A psychotic disorder symptom that is characterized by the presence of hallucinations, delusions, or disorganised thoughts or behaviours.</t>
-        </is>
-      </c>
-      <c r="D121" s="2" t="inlineStr">
-        <is>
-          <t>psychotic disorder symptom</t>
-        </is>
-      </c>
-      <c r="E121" s="2" t="n"/>
-      <c r="F121" s="2" t="n"/>
-      <c r="G121" s="2" t="n"/>
-      <c r="H121" s="2" t="n"/>
-      <c r="I121" s="2" t="n"/>
-      <c r="J121" s="2" t="n"/>
-      <c r="K121" s="2" t="inlineStr">
-        <is>
-          <t>Based on https://www.psychiatry.org/patients-families/schizophrenia/what-is-schizophrenia</t>
-        </is>
-      </c>
-      <c r="L121" s="2" t="n"/>
-      <c r="M121" s="2" t="n"/>
-      <c r="N121" s="2" t="n"/>
-      <c r="O121" s="2" t="n"/>
-      <c r="P121" s="2" t="n"/>
-      <c r="Q121" s="2" t="inlineStr">
-        <is>
-          <t>LSR 3</t>
-        </is>
-      </c>
-      <c r="R121" s="2" t="inlineStr">
-        <is>
-          <t>Intervention outcomes and spillover effects</t>
-        </is>
-      </c>
-      <c r="S121" s="2" t="n"/>
-      <c r="T121" s="2" t="inlineStr">
-        <is>
-          <t>Obsolete</t>
-        </is>
-      </c>
-      <c r="U121" s="2" t="n"/>
-      <c r="V121" s="2" t="n"/>
-      <c r="W121" s="2" t="inlineStr">
+      <c r="W121" t="inlineStr">
         <is>
           <t>PS</t>
         </is>
@@ -7674,22 +7676,22 @@
     <row r="122">
       <c r="A122" s="3" t="inlineStr">
         <is>
-          <t>GMHO:0000078</t>
+          <t>GMHO:0000076</t>
         </is>
       </c>
       <c r="B122" s="3" t="inlineStr">
         <is>
-          <t>positive psychotic disorder symptom severity</t>
+          <t>positive intervention outcome</t>
         </is>
       </c>
       <c r="C122" s="3" t="inlineStr">
         <is>
-          <t>Psychotic disorder symptom severity that is associated with positive psychotic disorder symptoms.</t>
+          <t xml:space="preserve">An intervention outcome that is positively influenced by the intervention. </t>
         </is>
       </c>
       <c r="D122" s="3" t="inlineStr">
         <is>
-          <t>psychotic disorder symptom severity</t>
+          <t>intervention outcome</t>
         </is>
       </c>
       <c r="E122" s="3" t="n"/>
@@ -7697,16 +7699,8 @@
       <c r="G122" s="3" t="n"/>
       <c r="H122" s="3" t="n"/>
       <c r="I122" s="3" t="n"/>
-      <c r="J122" s="3" t="inlineStr">
-        <is>
-          <t>Intervention outcomes and spillover effects</t>
-        </is>
-      </c>
-      <c r="K122" s="3" t="inlineStr">
-        <is>
-          <t>Based on https://www.psychiatry.org/patients-families/schizophrenia/what-is-schizophrenia</t>
-        </is>
-      </c>
+      <c r="J122" s="3" t="n"/>
+      <c r="K122" s="3" t="n"/>
       <c r="L122" s="3" t="n"/>
       <c r="M122" s="3" t="n"/>
       <c r="N122" s="3" t="n"/>
@@ -7722,11 +7716,7 @@
           <t>Intervention outcomes and spillover effects</t>
         </is>
       </c>
-      <c r="S122" s="3" t="inlineStr">
-        <is>
-          <t>A measure for 'positive psychotic disorder symptom severity'</t>
-        </is>
-      </c>
+      <c r="S122" s="3" t="n"/>
       <c r="T122" s="3" t="inlineStr">
         <is>
           <t>Published</t>
@@ -7736,161 +7726,177 @@
       <c r="V122" s="3" t="n"/>
       <c r="W122" s="3" t="inlineStr">
         <is>
+          <t>PS</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>GMHO:0000077</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>positive psychotic disorder symptom</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>A psychotic disorder symptom that is characterized by the presence of hallucinations, delusions, or disorganised thoughts or behaviours.</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
+        <is>
+          <t>psychotic disorder symptom</t>
+        </is>
+      </c>
+      <c r="E123" s="2" t="n"/>
+      <c r="F123" s="2" t="n"/>
+      <c r="G123" s="2" t="n"/>
+      <c r="H123" s="2" t="n"/>
+      <c r="I123" s="2" t="n"/>
+      <c r="J123" s="2" t="n"/>
+      <c r="K123" s="2" t="inlineStr">
+        <is>
+          <t>Based on https://www.psychiatry.org/patients-families/schizophrenia/what-is-schizophrenia</t>
+        </is>
+      </c>
+      <c r="L123" s="2" t="n"/>
+      <c r="M123" s="2" t="n"/>
+      <c r="N123" s="2" t="n"/>
+      <c r="O123" s="2" t="n"/>
+      <c r="P123" s="2" t="n"/>
+      <c r="Q123" s="2" t="inlineStr">
+        <is>
+          <t>LSR 3</t>
+        </is>
+      </c>
+      <c r="R123" s="2" t="inlineStr">
+        <is>
+          <t>Intervention outcomes and spillover effects</t>
+        </is>
+      </c>
+      <c r="S123" s="2" t="n"/>
+      <c r="T123" s="2" t="inlineStr">
+        <is>
+          <t>Obsolete</t>
+        </is>
+      </c>
+      <c r="U123" s="2" t="n"/>
+      <c r="V123" s="2" t="n"/>
+      <c r="W123" s="2" t="inlineStr">
+        <is>
+          <t>PS</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="3" t="inlineStr">
+        <is>
+          <t>GMHO:0000078</t>
+        </is>
+      </c>
+      <c r="B124" s="3" t="inlineStr">
+        <is>
+          <t>positive psychotic disorder symptom severity</t>
+        </is>
+      </c>
+      <c r="C124" s="3" t="inlineStr">
+        <is>
+          <t>Psychotic disorder symptom severity that is associated with positive psychotic disorder symptoms.</t>
+        </is>
+      </c>
+      <c r="D124" s="3" t="inlineStr">
+        <is>
+          <t>psychotic disorder symptom severity</t>
+        </is>
+      </c>
+      <c r="E124" s="3" t="n"/>
+      <c r="F124" s="3" t="n"/>
+      <c r="G124" s="3" t="n"/>
+      <c r="H124" s="3" t="n"/>
+      <c r="I124" s="3" t="n"/>
+      <c r="J124" s="3" t="inlineStr">
+        <is>
+          <t>Intervention outcomes and spillover effects</t>
+        </is>
+      </c>
+      <c r="K124" s="3" t="inlineStr">
+        <is>
+          <t>Based on https://www.psychiatry.org/patients-families/schizophrenia/what-is-schizophrenia</t>
+        </is>
+      </c>
+      <c r="L124" s="3" t="n"/>
+      <c r="M124" s="3" t="n"/>
+      <c r="N124" s="3" t="n"/>
+      <c r="O124" s="3" t="n"/>
+      <c r="P124" s="3" t="n"/>
+      <c r="Q124" s="3" t="inlineStr">
+        <is>
+          <t>LSR 3</t>
+        </is>
+      </c>
+      <c r="R124" s="3" t="inlineStr">
+        <is>
+          <t>Intervention outcomes and spillover effects</t>
+        </is>
+      </c>
+      <c r="S124" s="3" t="inlineStr">
+        <is>
+          <t>A measure for 'positive psychotic disorder symptom severity'</t>
+        </is>
+      </c>
+      <c r="T124" s="3" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="U124" s="3" t="n"/>
+      <c r="V124" s="3" t="n"/>
+      <c r="W124" s="3" t="inlineStr">
+        <is>
           <t>PS; MS</t>
         </is>
       </c>
     </row>
-    <row r="123">
-      <c r="A123" s="3" t="inlineStr">
+    <row r="125">
+      <c r="A125" s="3" t="inlineStr">
         <is>
           <t>GMHO:0000226</t>
         </is>
       </c>
-      <c r="B123" s="3" t="inlineStr">
+      <c r="B125" s="3" t="inlineStr">
         <is>
           <t>positive psychotic disorder symptom severity scale</t>
         </is>
       </c>
-      <c r="C123" s="3" t="inlineStr">
+      <c r="C125" s="3" t="inlineStr">
         <is>
           <t>A psychotic disorder symptom severity scale that that is associated with positive psychotic disorder symptoms.</t>
         </is>
       </c>
-      <c r="D123" s="3" t="inlineStr">
+      <c r="D125" s="3" t="inlineStr">
         <is>
           <t>psychotic disorder symptom severity scale</t>
         </is>
       </c>
-      <c r="E123" s="3" t="n"/>
-      <c r="F123" s="3" t="n"/>
-      <c r="G123" s="3" t="n"/>
-      <c r="H123" s="3" t="n"/>
-      <c r="I123" s="3" t="n"/>
-      <c r="J123" s="3" t="inlineStr">
-        <is>
-          <t>Intervention outcomes and spillover effects</t>
-        </is>
-      </c>
-      <c r="K123" s="3" t="inlineStr">
+      <c r="E125" s="3" t="n"/>
+      <c r="F125" s="3" t="n"/>
+      <c r="G125" s="3" t="n"/>
+      <c r="H125" s="3" t="n"/>
+      <c r="I125" s="3" t="n"/>
+      <c r="J125" s="3" t="inlineStr">
+        <is>
+          <t>Intervention outcomes and spillover effects</t>
+        </is>
+      </c>
+      <c r="K125" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Based on https://www.psychiatry.org/patients-families/schizophrenia/what-is-schizophrenia
 </t>
         </is>
       </c>
-      <c r="L123" s="3" t="n"/>
-      <c r="M123" s="3" t="n"/>
-      <c r="N123" s="3" t="n"/>
-      <c r="O123" s="3" t="n"/>
-      <c r="P123" s="3" t="n"/>
-      <c r="Q123" s="3" t="inlineStr">
-        <is>
-          <t>LSR 3</t>
-        </is>
-      </c>
-      <c r="R123" s="3" t="inlineStr">
-        <is>
-          <t>Intervention outcomes and spillover effects</t>
-        </is>
-      </c>
-      <c r="S123" s="3" t="n"/>
-      <c r="T123" s="3" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="U123" s="3" t="n"/>
-      <c r="V123" s="3" t="n"/>
-      <c r="W123" s="3" t="inlineStr">
-        <is>
-          <t>PS; MS</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" s="2" t="inlineStr">
-        <is>
-          <t>GMHO:0000174</t>
-        </is>
-      </c>
-      <c r="B124" s="2" t="inlineStr">
-        <is>
-          <t>post-traumatic stress symptom</t>
-        </is>
-      </c>
-      <c r="C124" s="2" t="inlineStr">
-        <is>
-          <t>A symptom that related to a post-traumatic stress disorder diagnosis.</t>
-        </is>
-      </c>
-      <c r="D124" s="2" t="inlineStr">
-        <is>
-          <t>symptom</t>
-        </is>
-      </c>
-      <c r="E124" s="2" t="n"/>
-      <c r="F124" s="2" t="n"/>
-      <c r="G124" s="2" t="n"/>
-      <c r="H124" s="2" t="n"/>
-      <c r="I124" s="2" t="n"/>
-      <c r="J124" s="2" t="n"/>
-      <c r="K124" s="2" t="n"/>
-      <c r="L124" s="2" t="n"/>
-      <c r="M124" s="2" t="n"/>
-      <c r="N124" s="2" t="n"/>
-      <c r="O124" s="2" t="n"/>
-      <c r="P124" s="2" t="n"/>
-      <c r="Q124" s="2" t="inlineStr">
-        <is>
-          <t>LSR 2</t>
-        </is>
-      </c>
-      <c r="R124" s="2" t="n"/>
-      <c r="S124" s="2" t="n"/>
-      <c r="T124" s="2" t="inlineStr">
-        <is>
-          <t>Obsolete</t>
-        </is>
-      </c>
-      <c r="U124" s="2" t="n"/>
-      <c r="V124" s="2" t="n"/>
-      <c r="W124" s="2" t="inlineStr">
-        <is>
-          <t>PS; MS</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" s="3" t="inlineStr">
-        <is>
-          <t>GMHO:0000173</t>
-        </is>
-      </c>
-      <c r="B125" s="3" t="inlineStr">
-        <is>
-          <t>post-traumatic stress symptom severity</t>
-        </is>
-      </c>
-      <c r="C125" s="3" t="inlineStr">
-        <is>
-          <t>Symptom severity relating to a post-traumatic stress symptom.</t>
-        </is>
-      </c>
-      <c r="D125" s="3" t="inlineStr">
-        <is>
-          <t>symptom severity</t>
-        </is>
-      </c>
-      <c r="E125" s="3" t="n"/>
-      <c r="F125" s="3" t="n"/>
-      <c r="G125" s="3" t="inlineStr">
-        <is>
-          <t>PTSD severity</t>
-        </is>
-      </c>
-      <c r="H125" s="3" t="n"/>
-      <c r="I125" s="3" t="n"/>
-      <c r="J125" s="3" t="n"/>
-      <c r="K125" s="3" t="n"/>
       <c r="L125" s="3" t="n"/>
       <c r="M125" s="3" t="n"/>
       <c r="N125" s="3" t="n"/>
@@ -7898,10 +7904,14 @@
       <c r="P125" s="3" t="n"/>
       <c r="Q125" s="3" t="inlineStr">
         <is>
-          <t>LSR 2</t>
-        </is>
-      </c>
-      <c r="R125" s="3" t="n"/>
+          <t>LSR 3</t>
+        </is>
+      </c>
+      <c r="R125" s="3" t="inlineStr">
+        <is>
+          <t>Intervention outcomes and spillover effects</t>
+        </is>
+      </c>
       <c r="S125" s="3" t="n"/>
       <c r="T125" s="3" t="inlineStr">
         <is>
@@ -7917,1431 +7927,1415 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="3" t="inlineStr">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>GMHO:0000174</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>post-traumatic stress symptom</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>A symptom that related to a post-traumatic stress disorder diagnosis.</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
+        <is>
+          <t>symptom</t>
+        </is>
+      </c>
+      <c r="E126" s="2" t="n"/>
+      <c r="F126" s="2" t="n"/>
+      <c r="G126" s="2" t="n"/>
+      <c r="H126" s="2" t="n"/>
+      <c r="I126" s="2" t="n"/>
+      <c r="J126" s="2" t="n"/>
+      <c r="K126" s="2" t="n"/>
+      <c r="L126" s="2" t="n"/>
+      <c r="M126" s="2" t="n"/>
+      <c r="N126" s="2" t="n"/>
+      <c r="O126" s="2" t="n"/>
+      <c r="P126" s="2" t="n"/>
+      <c r="Q126" s="2" t="inlineStr">
+        <is>
+          <t>LSR 2</t>
+        </is>
+      </c>
+      <c r="R126" s="2" t="n"/>
+      <c r="S126" s="2" t="n"/>
+      <c r="T126" s="2" t="inlineStr">
+        <is>
+          <t>Obsolete</t>
+        </is>
+      </c>
+      <c r="U126" s="2" t="n"/>
+      <c r="V126" s="2" t="n"/>
+      <c r="W126" s="2" t="inlineStr">
+        <is>
+          <t>PS; MS</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="3" t="inlineStr">
+        <is>
+          <t>GMHO:0000173</t>
+        </is>
+      </c>
+      <c r="B127" s="3" t="inlineStr">
+        <is>
+          <t>post-traumatic stress symptom severity</t>
+        </is>
+      </c>
+      <c r="C127" s="3" t="inlineStr">
+        <is>
+          <t>Symptom severity relating to a post-traumatic stress symptom.</t>
+        </is>
+      </c>
+      <c r="D127" s="3" t="inlineStr">
+        <is>
+          <t>symptom severity</t>
+        </is>
+      </c>
+      <c r="E127" s="3" t="n"/>
+      <c r="F127" s="3" t="n"/>
+      <c r="G127" s="3" t="inlineStr">
+        <is>
+          <t>PTSD severity</t>
+        </is>
+      </c>
+      <c r="H127" s="3" t="n"/>
+      <c r="I127" s="3" t="n"/>
+      <c r="J127" s="3" t="n"/>
+      <c r="K127" s="3" t="n"/>
+      <c r="L127" s="3" t="n"/>
+      <c r="M127" s="3" t="n"/>
+      <c r="N127" s="3" t="n"/>
+      <c r="O127" s="3" t="n"/>
+      <c r="P127" s="3" t="n"/>
+      <c r="Q127" s="3" t="inlineStr">
+        <is>
+          <t>LSR 2</t>
+        </is>
+      </c>
+      <c r="R127" s="3" t="n"/>
+      <c r="S127" s="3" t="n"/>
+      <c r="T127" s="3" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="U127" s="3" t="n"/>
+      <c r="V127" s="3" t="n"/>
+      <c r="W127" s="3" t="inlineStr">
+        <is>
+          <t>PS; MS</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="3" t="inlineStr">
         <is>
           <t>GMHO:0000263</t>
         </is>
       </c>
-      <c r="B126" s="3" t="inlineStr">
+      <c r="B128" s="3" t="inlineStr">
         <is>
           <t>post-traumatic stress symptom severity scale</t>
         </is>
       </c>
-      <c r="C126" s="3" t="inlineStr">
+      <c r="C128" s="3" t="inlineStr">
         <is>
           <t>A measurement scale that is used to measure post-traumatic stress symptom severity.</t>
         </is>
       </c>
-      <c r="D126" s="3" t="inlineStr">
+      <c r="D128" s="3" t="inlineStr">
         <is>
           <t>measurement scale</t>
         </is>
       </c>
-      <c r="E126" s="3" t="n"/>
-      <c r="F126" s="3" t="n"/>
-      <c r="G126" s="3" t="n"/>
-      <c r="H126" s="3" t="n"/>
-      <c r="I126" s="3" t="n"/>
-      <c r="J126" s="3" t="inlineStr">
-        <is>
-          <t>Intervention outcomes and spillover effects</t>
-        </is>
-      </c>
-      <c r="K126" s="3" t="n"/>
-      <c r="L126" s="3" t="n"/>
-      <c r="M126" s="3" t="n"/>
-      <c r="N126" s="3" t="n"/>
-      <c r="O126" s="3" t="n"/>
-      <c r="P126" s="3" t="n"/>
-      <c r="Q126" s="3" t="inlineStr">
+      <c r="E128" s="3" t="n"/>
+      <c r="F128" s="3" t="n"/>
+      <c r="G128" s="3" t="n"/>
+      <c r="H128" s="3" t="n"/>
+      <c r="I128" s="3" t="n"/>
+      <c r="J128" s="3" t="inlineStr">
+        <is>
+          <t>Intervention outcomes and spillover effects</t>
+        </is>
+      </c>
+      <c r="K128" s="3" t="n"/>
+      <c r="L128" s="3" t="n"/>
+      <c r="M128" s="3" t="n"/>
+      <c r="N128" s="3" t="n"/>
+      <c r="O128" s="3" t="n"/>
+      <c r="P128" s="3" t="n"/>
+      <c r="Q128" s="3" t="inlineStr">
         <is>
           <t>LSR 2</t>
         </is>
       </c>
-      <c r="R126" s="3" t="inlineStr">
-        <is>
-          <t>Intervention outcomes and spillover effects</t>
-        </is>
-      </c>
-      <c r="S126" s="3" t="n"/>
-      <c r="T126" s="3" t="inlineStr">
+      <c r="R128" s="3" t="inlineStr">
+        <is>
+          <t>Intervention outcomes and spillover effects</t>
+        </is>
+      </c>
+      <c r="S128" s="3" t="n"/>
+      <c r="T128" s="3" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="U126" s="3" t="n"/>
-      <c r="V126" s="3" t="n"/>
-      <c r="W126" s="3" t="n"/>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
+      <c r="U128" s="3" t="n"/>
+      <c r="V128" s="3" t="n"/>
+      <c r="W128" s="3" t="n"/>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
         <is>
           <t>OBA:1000952</t>
         </is>
       </c>
-      <c r="B127" t="inlineStr">
+      <c r="B129" t="inlineStr">
         <is>
           <t>prolactin level</t>
         </is>
       </c>
-      <c r="C127" t="inlineStr">
+      <c r="C129" t="inlineStr">
         <is>
           <t>The amount of a prolactin.</t>
         </is>
       </c>
-      <c r="D127" t="inlineStr">
+      <c r="D129" t="inlineStr">
         <is>
           <t>protein amount</t>
         </is>
       </c>
-      <c r="Q127" t="inlineStr">
+      <c r="Q129" t="inlineStr">
         <is>
           <t>LSR 3</t>
         </is>
       </c>
-      <c r="R127" t="inlineStr">
-        <is>
-          <t>Intervention outcomes and spillover effects</t>
-        </is>
-      </c>
-      <c r="T127" t="inlineStr">
+      <c r="R129" t="inlineStr">
+        <is>
+          <t>Intervention outcomes and spillover effects</t>
+        </is>
+      </c>
+      <c r="T129" t="inlineStr">
         <is>
           <t>External</t>
         </is>
       </c>
-      <c r="W127" t="inlineStr">
-        <is>
-          <t>PS</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" s="2" t="inlineStr">
+      <c r="W129" t="inlineStr">
+        <is>
+          <t>PS</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
         <is>
           <t>GMHO:0000227</t>
         </is>
       </c>
-      <c r="B128" s="2" t="inlineStr">
+      <c r="B130" s="2" t="inlineStr">
         <is>
           <t>prolactin scale</t>
         </is>
       </c>
-      <c r="C128" s="2" t="inlineStr">
+      <c r="C130" s="2" t="inlineStr">
         <is>
           <t>A measurement scale that is used to measure levels of prolactin.</t>
         </is>
       </c>
-      <c r="D128" s="2" t="inlineStr">
+      <c r="D130" s="2" t="inlineStr">
         <is>
           <t>measurement scale</t>
         </is>
       </c>
-      <c r="E128" s="2" t="n"/>
-      <c r="F128" s="2" t="n"/>
-      <c r="G128" s="2" t="n"/>
-      <c r="H128" s="2" t="n"/>
-      <c r="I128" s="2" t="n"/>
-      <c r="J128" s="2" t="inlineStr">
-        <is>
-          <t>Intervention outcomes and spillover effects</t>
-        </is>
-      </c>
-      <c r="K128" s="2" t="n"/>
-      <c r="L128" s="2" t="n"/>
-      <c r="M128" s="2" t="n"/>
-      <c r="N128" s="2" t="n"/>
-      <c r="O128" s="2" t="n"/>
-      <c r="P128" s="2" t="n"/>
-      <c r="Q128" s="2" t="inlineStr">
+      <c r="E130" s="2" t="n"/>
+      <c r="F130" s="2" t="n"/>
+      <c r="G130" s="2" t="n"/>
+      <c r="H130" s="2" t="n"/>
+      <c r="I130" s="2" t="n"/>
+      <c r="J130" s="2" t="inlineStr">
+        <is>
+          <t>Intervention outcomes and spillover effects</t>
+        </is>
+      </c>
+      <c r="K130" s="2" t="n"/>
+      <c r="L130" s="2" t="n"/>
+      <c r="M130" s="2" t="n"/>
+      <c r="N130" s="2" t="n"/>
+      <c r="O130" s="2" t="n"/>
+      <c r="P130" s="2" t="n"/>
+      <c r="Q130" s="2" t="inlineStr">
         <is>
           <t>LSR 3</t>
         </is>
       </c>
-      <c r="R128" s="2" t="inlineStr">
-        <is>
-          <t>Intervention outcomes and spillover effects</t>
-        </is>
-      </c>
-      <c r="S128" s="2" t="n"/>
-      <c r="T128" s="2" t="inlineStr">
+      <c r="R130" s="2" t="inlineStr">
+        <is>
+          <t>Intervention outcomes and spillover effects</t>
+        </is>
+      </c>
+      <c r="S130" s="2" t="n"/>
+      <c r="T130" s="2" t="inlineStr">
         <is>
           <t>Obsolete</t>
         </is>
       </c>
-      <c r="U128" s="2" t="n"/>
-      <c r="V128" s="2" t="n"/>
-      <c r="W128" s="2" t="inlineStr">
-        <is>
-          <t>PS</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" s="2" t="inlineStr">
+      <c r="U130" s="2" t="n"/>
+      <c r="V130" s="2" t="n"/>
+      <c r="W130" s="2" t="inlineStr">
+        <is>
+          <t>PS</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
         <is>
           <t>GMHO:0000172</t>
         </is>
       </c>
-      <c r="B129" s="2" t="inlineStr">
+      <c r="B131" s="2" t="inlineStr">
         <is>
           <t>psychotic disorder symptom</t>
         </is>
       </c>
-      <c r="C129" s="2" t="inlineStr">
+      <c r="C131" s="2" t="inlineStr">
         <is>
           <t>A symptom that is related to a psychotic disorder diagnosis.</t>
         </is>
       </c>
-      <c r="D129" s="2" t="inlineStr">
+      <c r="D131" s="2" t="inlineStr">
         <is>
           <t>symptom</t>
         </is>
       </c>
-      <c r="E129" s="2" t="inlineStr">
+      <c r="E131" s="2" t="inlineStr">
         <is>
           <t>http://purl.obolibrary.org/obo/</t>
         </is>
       </c>
-      <c r="F129" s="2" t="n"/>
-      <c r="G129" s="2" t="n"/>
-      <c r="H129" s="2" t="n"/>
-      <c r="I129" s="2" t="n"/>
-      <c r="J129" s="2" t="n"/>
-      <c r="K129" s="2" t="n"/>
-      <c r="L129" s="2" t="n"/>
-      <c r="M129" s="2" t="n"/>
-      <c r="N129" s="2" t="n"/>
-      <c r="O129" s="2" t="n"/>
-      <c r="P129" s="2" t="n"/>
-      <c r="Q129" s="2" t="inlineStr">
+      <c r="F131" s="2" t="n"/>
+      <c r="G131" s="2" t="n"/>
+      <c r="H131" s="2" t="n"/>
+      <c r="I131" s="2" t="n"/>
+      <c r="J131" s="2" t="n"/>
+      <c r="K131" s="2" t="n"/>
+      <c r="L131" s="2" t="n"/>
+      <c r="M131" s="2" t="n"/>
+      <c r="N131" s="2" t="n"/>
+      <c r="O131" s="2" t="n"/>
+      <c r="P131" s="2" t="n"/>
+      <c r="Q131" s="2" t="inlineStr">
         <is>
           <t>LSR 3</t>
         </is>
       </c>
-      <c r="R129" s="2" t="inlineStr">
-        <is>
-          <t>Intervention outcomes and spillover effects</t>
-        </is>
-      </c>
-      <c r="S129" s="2" t="n"/>
-      <c r="T129" s="2" t="inlineStr">
+      <c r="R131" s="2" t="inlineStr">
+        <is>
+          <t>Intervention outcomes and spillover effects</t>
+        </is>
+      </c>
+      <c r="S131" s="2" t="n"/>
+      <c r="T131" s="2" t="inlineStr">
         <is>
           <t>Obsolete</t>
         </is>
       </c>
-      <c r="U129" s="2" t="n"/>
-      <c r="V129" s="2" t="n"/>
-      <c r="W129" s="2" t="inlineStr">
-        <is>
-          <t>PS</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" s="3" t="inlineStr">
+      <c r="U131" s="2" t="n"/>
+      <c r="V131" s="2" t="n"/>
+      <c r="W131" s="2" t="inlineStr">
+        <is>
+          <t>PS</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="3" t="inlineStr">
         <is>
           <t>GMHO:0000079</t>
         </is>
       </c>
-      <c r="B130" s="3" t="inlineStr">
+      <c r="B132" s="3" t="inlineStr">
         <is>
           <t>psychotic disorder symptom severity</t>
         </is>
       </c>
-      <c r="C130" s="3" t="inlineStr">
+      <c r="C132" s="3" t="inlineStr">
         <is>
           <t>Symptom severity that is associated with a psychotic disorder symptom.</t>
         </is>
       </c>
-      <c r="D130" s="3" t="inlineStr">
+      <c r="D132" s="3" t="inlineStr">
         <is>
           <t>symptom severity</t>
         </is>
       </c>
-      <c r="E130" s="3" t="n"/>
-      <c r="F130" s="3" t="n"/>
-      <c r="G130" s="3" t="n"/>
-      <c r="H130" s="3" t="n"/>
-      <c r="I130" s="3" t="n"/>
-      <c r="J130" s="3" t="inlineStr">
-        <is>
-          <t>Intervention outcomes and spillover effects</t>
-        </is>
-      </c>
-      <c r="K130" s="3" t="n"/>
-      <c r="L130" s="3" t="n"/>
-      <c r="M130" s="3" t="n"/>
-      <c r="N130" s="3" t="n"/>
-      <c r="O130" s="3" t="n"/>
-      <c r="P130" s="3" t="n"/>
-      <c r="Q130" s="3" t="inlineStr">
+      <c r="E132" s="3" t="n"/>
+      <c r="F132" s="3" t="n"/>
+      <c r="G132" s="3" t="n"/>
+      <c r="H132" s="3" t="n"/>
+      <c r="I132" s="3" t="n"/>
+      <c r="J132" s="3" t="inlineStr">
+        <is>
+          <t>Intervention outcomes and spillover effects</t>
+        </is>
+      </c>
+      <c r="K132" s="3" t="n"/>
+      <c r="L132" s="3" t="n"/>
+      <c r="M132" s="3" t="n"/>
+      <c r="N132" s="3" t="n"/>
+      <c r="O132" s="3" t="n"/>
+      <c r="P132" s="3" t="n"/>
+      <c r="Q132" s="3" t="inlineStr">
         <is>
           <t>LSR 3</t>
         </is>
       </c>
-      <c r="R130" s="3" t="inlineStr">
-        <is>
-          <t>Intervention outcomes and spillover effects</t>
-        </is>
-      </c>
-      <c r="S130" s="3" t="n"/>
-      <c r="T130" s="3" t="inlineStr">
+      <c r="R132" s="3" t="inlineStr">
+        <is>
+          <t>Intervention outcomes and spillover effects</t>
+        </is>
+      </c>
+      <c r="S132" s="3" t="n"/>
+      <c r="T132" s="3" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="U130" s="3" t="n"/>
-      <c r="V130" s="3" t="n"/>
-      <c r="W130" s="3" t="inlineStr">
-        <is>
-          <t>PS</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" s="3" t="inlineStr">
+      <c r="U132" s="3" t="n"/>
+      <c r="V132" s="3" t="n"/>
+      <c r="W132" s="3" t="inlineStr">
+        <is>
+          <t>PS</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="3" t="inlineStr">
         <is>
           <t>GMHO:0000228</t>
         </is>
       </c>
-      <c r="B131" s="3" t="inlineStr">
+      <c r="B133" s="3" t="inlineStr">
         <is>
           <t>psychotic disorder symptom severity scale</t>
         </is>
       </c>
-      <c r="C131" s="3" t="inlineStr">
+      <c r="C133" s="3" t="inlineStr">
         <is>
           <t>A measurement scale that is used to measure psychotic disorder symptom severity.</t>
         </is>
       </c>
-      <c r="D131" s="3" t="inlineStr">
+      <c r="D133" s="3" t="inlineStr">
         <is>
           <t>measurement scale</t>
         </is>
       </c>
-      <c r="E131" s="3" t="n"/>
-      <c r="F131" s="3" t="n"/>
-      <c r="G131" s="3" t="n"/>
-      <c r="H131" s="3" t="n"/>
-      <c r="I131" s="3" t="n"/>
-      <c r="J131" s="3" t="inlineStr">
-        <is>
-          <t>Intervention outcomes and spillover effects</t>
-        </is>
-      </c>
-      <c r="K131" s="3" t="n"/>
-      <c r="L131" s="3" t="n"/>
-      <c r="M131" s="3" t="n"/>
-      <c r="N131" s="3" t="n"/>
-      <c r="O131" s="3" t="n"/>
-      <c r="P131" s="3" t="n"/>
-      <c r="Q131" s="3" t="inlineStr">
+      <c r="E133" s="3" t="n"/>
+      <c r="F133" s="3" t="n"/>
+      <c r="G133" s="3" t="n"/>
+      <c r="H133" s="3" t="n"/>
+      <c r="I133" s="3" t="n"/>
+      <c r="J133" s="3" t="inlineStr">
+        <is>
+          <t>Intervention outcomes and spillover effects</t>
+        </is>
+      </c>
+      <c r="K133" s="3" t="n"/>
+      <c r="L133" s="3" t="n"/>
+      <c r="M133" s="3" t="n"/>
+      <c r="N133" s="3" t="n"/>
+      <c r="O133" s="3" t="n"/>
+      <c r="P133" s="3" t="n"/>
+      <c r="Q133" s="3" t="inlineStr">
         <is>
           <t>LSR 3</t>
         </is>
       </c>
-      <c r="R131" s="3" t="inlineStr">
-        <is>
-          <t>Intervention outcomes and spillover effects</t>
-        </is>
-      </c>
-      <c r="S131" s="3" t="n"/>
-      <c r="T131" s="3" t="inlineStr">
+      <c r="R133" s="3" t="inlineStr">
+        <is>
+          <t>Intervention outcomes and spillover effects</t>
+        </is>
+      </c>
+      <c r="S133" s="3" t="n"/>
+      <c r="T133" s="3" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="U131" s="3" t="n"/>
-      <c r="V131" s="3" t="n"/>
-      <c r="W131" s="3" t="inlineStr">
-        <is>
-          <t>PS</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
+      <c r="U133" s="3" t="n"/>
+      <c r="V133" s="3" t="n"/>
+      <c r="W133" s="3" t="inlineStr">
+        <is>
+          <t>PS</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
         <is>
           <t>OBI:0000071</t>
         </is>
       </c>
-      <c r="B132" t="inlineStr">
+      <c r="B134" t="inlineStr">
         <is>
           <t>quantitative confidence value</t>
         </is>
       </c>
-      <c r="C132" t="inlineStr">
+      <c r="C134" t="inlineStr">
         <is>
           <t>A data item which is used to indicate the degree of uncertainty about a measurement.</t>
         </is>
       </c>
-      <c r="D132" t="inlineStr">
+      <c r="D134" t="inlineStr">
         <is>
           <t>data item</t>
         </is>
       </c>
-      <c r="J132" t="inlineStr">
-        <is>
-          <t>Intervention outcomes and spillover effects</t>
-        </is>
-      </c>
-      <c r="Q132" t="inlineStr">
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>Intervention outcomes and spillover effects</t>
+        </is>
+      </c>
+      <c r="Q134" t="inlineStr">
         <is>
           <t>LSR 1</t>
         </is>
       </c>
-      <c r="R132" t="inlineStr">
-        <is>
-          <t>Intervention outcomes and spillover effects</t>
-        </is>
-      </c>
-      <c r="T132" t="inlineStr">
+      <c r="R134" t="inlineStr">
+        <is>
+          <t>Intervention outcomes and spillover effects</t>
+        </is>
+      </c>
+      <c r="T134" t="inlineStr">
         <is>
           <t>External</t>
         </is>
       </c>
-      <c r="W132" t="inlineStr">
-        <is>
-          <t>PS</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
+      <c r="W134" t="inlineStr">
+        <is>
+          <t>PS</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
         <is>
           <t>ADDICTO:0001308</t>
         </is>
       </c>
-      <c r="B133" t="inlineStr">
+      <c r="B135" t="inlineStr">
         <is>
           <t>relapsed to a disorder</t>
         </is>
       </c>
-      <c r="C133" t="inlineStr">
+      <c r="C135" t="inlineStr">
         <is>
           <t>A personal attribute in which the symptoms of a person suffering from a disorder have reverted from a desired level to an undesired level.</t>
         </is>
       </c>
-      <c r="D133" t="inlineStr">
+      <c r="D135" t="inlineStr">
         <is>
           <t>personal attribute</t>
         </is>
       </c>
-      <c r="J133" t="inlineStr">
+      <c r="J135" t="inlineStr">
         <is>
           <t>intervention outcomes and spillover effects</t>
         </is>
       </c>
-      <c r="Q133" t="inlineStr">
+      <c r="Q135" t="inlineStr">
         <is>
           <t>LSR 3</t>
         </is>
       </c>
-      <c r="R133" t="inlineStr">
-        <is>
-          <t>Intervention outcomes and spillover effects</t>
-        </is>
-      </c>
-      <c r="T133" t="inlineStr">
+      <c r="R135" t="inlineStr">
+        <is>
+          <t>Intervention outcomes and spillover effects</t>
+        </is>
+      </c>
+      <c r="T135" t="inlineStr">
         <is>
           <t>External</t>
         </is>
       </c>
-      <c r="W133" t="inlineStr">
-        <is>
-          <t>PS</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" s="3" t="inlineStr">
+      <c r="W135" t="inlineStr">
+        <is>
+          <t>PS</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="3" t="inlineStr">
         <is>
           <t>GMHO:0000135</t>
         </is>
       </c>
-      <c r="B134" s="3" t="inlineStr">
+      <c r="B136" s="3" t="inlineStr">
         <is>
           <t>reward sensitivity</t>
         </is>
       </c>
-      <c r="C134" s="3" t="inlineStr">
+      <c r="C136" s="3" t="inlineStr">
         <is>
           <t>A bodily disposition to detect, pursue, learn from, and derive pleasure from stimuli perceived as positive.</t>
         </is>
       </c>
-      <c r="D134" s="3" t="inlineStr">
+      <c r="D136" s="3" t="inlineStr">
         <is>
           <t>bodily disposition</t>
         </is>
       </c>
-      <c r="E134" s="3" t="n"/>
-      <c r="F134" s="3" t="n"/>
-      <c r="G134" s="3" t="n"/>
-      <c r="H134" s="3" t="n"/>
-      <c r="I134" s="3" t="n"/>
-      <c r="J134" s="3" t="n"/>
-      <c r="K134" s="3" t="inlineStr">
+      <c r="E136" s="3" t="n"/>
+      <c r="F136" s="3" t="n"/>
+      <c r="G136" s="3" t="n"/>
+      <c r="H136" s="3" t="n"/>
+      <c r="I136" s="3" t="n"/>
+      <c r="J136" s="3" t="n"/>
+      <c r="K136" s="3" t="inlineStr">
         <is>
           <t>Goodnight, J. (Ed.) (2018). . (Vols. 1-5). SAGE Publications, Inc., https://doi.org/10.4135/9781506307633</t>
         </is>
       </c>
-      <c r="L134" s="3" t="n"/>
-      <c r="M134" s="3" t="n"/>
-      <c r="N134" s="3" t="n"/>
-      <c r="O134" s="3" t="n"/>
-      <c r="P134" s="3" t="n"/>
-      <c r="Q134" s="3" t="inlineStr">
+      <c r="L136" s="3" t="n"/>
+      <c r="M136" s="3" t="n"/>
+      <c r="N136" s="3" t="n"/>
+      <c r="O136" s="3" t="n"/>
+      <c r="P136" s="3" t="n"/>
+      <c r="Q136" s="3" t="inlineStr">
         <is>
           <t>LSR 1</t>
         </is>
       </c>
-      <c r="R134" s="3" t="inlineStr">
-        <is>
-          <t>Intervention outcomes and spillover effects</t>
-        </is>
-      </c>
-      <c r="S134" s="3" t="n"/>
-      <c r="T134" s="3" t="inlineStr">
+      <c r="R136" s="3" t="inlineStr">
+        <is>
+          <t>Intervention outcomes and spillover effects</t>
+        </is>
+      </c>
+      <c r="S136" s="3" t="n"/>
+      <c r="T136" s="3" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="U134" s="3" t="n"/>
-      <c r="V134" s="3" t="n"/>
-      <c r="W134" s="3" t="inlineStr">
-        <is>
-          <t>PS</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" s="3" t="inlineStr">
+      <c r="U136" s="3" t="n"/>
+      <c r="V136" s="3" t="n"/>
+      <c r="W136" s="3" t="inlineStr">
+        <is>
+          <t>PS</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="3" t="inlineStr">
         <is>
           <t>GMHO:0000207</t>
         </is>
       </c>
-      <c r="B135" s="3" t="inlineStr">
+      <c r="B137" s="3" t="inlineStr">
         <is>
           <t>reward sensitivity scale</t>
         </is>
       </c>
-      <c r="C135" s="3" t="inlineStr">
+      <c r="C137" s="3" t="inlineStr">
         <is>
           <t>A measurement scale that is used to measure reward sensitivity.</t>
         </is>
       </c>
-      <c r="D135" s="3" t="inlineStr">
+      <c r="D137" s="3" t="inlineStr">
         <is>
           <t>measurement scale</t>
         </is>
       </c>
-      <c r="E135" s="3" t="n"/>
-      <c r="F135" s="3" t="n"/>
-      <c r="G135" s="3" t="n"/>
-      <c r="H135" s="3" t="n"/>
-      <c r="I135" s="3" t="n"/>
-      <c r="J135" s="3" t="n"/>
-      <c r="K135" s="3" t="n"/>
-      <c r="L135" s="3" t="n"/>
-      <c r="M135" s="3" t="n"/>
-      <c r="N135" s="3" t="n"/>
-      <c r="O135" s="3" t="n"/>
-      <c r="P135" s="3" t="n"/>
-      <c r="Q135" s="3" t="inlineStr">
+      <c r="E137" s="3" t="n"/>
+      <c r="F137" s="3" t="n"/>
+      <c r="G137" s="3" t="n"/>
+      <c r="H137" s="3" t="n"/>
+      <c r="I137" s="3" t="n"/>
+      <c r="J137" s="3" t="n"/>
+      <c r="K137" s="3" t="n"/>
+      <c r="L137" s="3" t="n"/>
+      <c r="M137" s="3" t="n"/>
+      <c r="N137" s="3" t="n"/>
+      <c r="O137" s="3" t="n"/>
+      <c r="P137" s="3" t="n"/>
+      <c r="Q137" s="3" t="inlineStr">
         <is>
           <t>LSR 1</t>
         </is>
       </c>
-      <c r="R135" s="3" t="inlineStr">
-        <is>
-          <t>Intervention outcomes and spillover effects</t>
-        </is>
-      </c>
-      <c r="S135" s="3" t="n"/>
-      <c r="T135" s="3" t="inlineStr">
+      <c r="R137" s="3" t="inlineStr">
+        <is>
+          <t>Intervention outcomes and spillover effects</t>
+        </is>
+      </c>
+      <c r="S137" s="3" t="n"/>
+      <c r="T137" s="3" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="U135" s="3" t="n"/>
-      <c r="V135" s="3" t="n"/>
-      <c r="W135" s="3" t="inlineStr">
-        <is>
-          <t>PS</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" s="2" t="inlineStr">
+      <c r="U137" s="3" t="n"/>
+      <c r="V137" s="3" t="n"/>
+      <c r="W137" s="3" t="inlineStr">
+        <is>
+          <t>PS</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
         <is>
           <t>GMHO:0000136</t>
         </is>
       </c>
-      <c r="B136" s="2" t="inlineStr">
+      <c r="B138" s="2" t="inlineStr">
         <is>
           <t>reward-based learning</t>
         </is>
       </c>
-      <c r="C136" s="2" t="inlineStr">
+      <c r="C138" s="2" t="inlineStr">
         <is>
           <t>Associative learning by which information is acquired regarding the positive outcomes of stimuli and behaviours.</t>
         </is>
       </c>
-      <c r="D136" s="2" t="inlineStr">
+      <c r="D138" s="2" t="inlineStr">
         <is>
           <t>associative learning</t>
         </is>
       </c>
-      <c r="E136" s="2" t="n"/>
-      <c r="F136" s="2" t="n"/>
-      <c r="G136" s="2" t="n"/>
-      <c r="H136" s="2" t="n"/>
-      <c r="I136" s="2" t="n"/>
-      <c r="J136" s="2" t="n"/>
-      <c r="K136" s="2" t="n"/>
-      <c r="L136" s="2" t="n"/>
-      <c r="M136" s="2" t="n"/>
-      <c r="N136" s="2" t="n"/>
-      <c r="O136" s="2" t="n"/>
-      <c r="P136" s="2" t="n"/>
-      <c r="Q136" s="2" t="inlineStr">
+      <c r="E138" s="2" t="n"/>
+      <c r="F138" s="2" t="n"/>
+      <c r="G138" s="2" t="n"/>
+      <c r="H138" s="2" t="n"/>
+      <c r="I138" s="2" t="n"/>
+      <c r="J138" s="2" t="n"/>
+      <c r="K138" s="2" t="n"/>
+      <c r="L138" s="2" t="n"/>
+      <c r="M138" s="2" t="n"/>
+      <c r="N138" s="2" t="n"/>
+      <c r="O138" s="2" t="n"/>
+      <c r="P138" s="2" t="n"/>
+      <c r="Q138" s="2" t="inlineStr">
         <is>
           <t>LSR 1</t>
         </is>
       </c>
-      <c r="R136" s="2" t="inlineStr">
-        <is>
-          <t>Intervention outcomes and spillover effects</t>
-        </is>
-      </c>
-      <c r="S136" s="2" t="n"/>
-      <c r="T136" s="2" t="inlineStr">
+      <c r="R138" s="2" t="inlineStr">
+        <is>
+          <t>Intervention outcomes and spillover effects</t>
+        </is>
+      </c>
+      <c r="S138" s="2" t="n"/>
+      <c r="T138" s="2" t="inlineStr">
         <is>
           <t>Obsolete</t>
         </is>
       </c>
-      <c r="U136" s="2" t="n"/>
-      <c r="V136" s="2" t="n"/>
-      <c r="W136" s="2" t="inlineStr">
-        <is>
-          <t>PS</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" s="2" t="inlineStr">
+      <c r="U138" s="2" t="n"/>
+      <c r="V138" s="2" t="n"/>
+      <c r="W138" s="2" t="inlineStr">
+        <is>
+          <t>PS</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
         <is>
           <t>GMHO:0000137</t>
         </is>
       </c>
-      <c r="B137" s="2" t="inlineStr">
+      <c r="B139" s="2" t="inlineStr">
         <is>
           <t>reward-prediction error signalling</t>
         </is>
       </c>
-      <c r="C137" s="2" t="inlineStr">
+      <c r="C139" s="2" t="inlineStr">
         <is>
           <t>A mental process in which the discrepancy between the predicted and received rewards is signalled.</t>
         </is>
       </c>
-      <c r="D137" s="2" t="inlineStr">
+      <c r="D139" s="2" t="inlineStr">
         <is>
           <t>mental process</t>
         </is>
       </c>
-      <c r="E137" s="2" t="n"/>
-      <c r="F137" s="2" t="n"/>
-      <c r="G137" s="2" t="n"/>
-      <c r="H137" s="2" t="n"/>
-      <c r="I137" s="2" t="n"/>
-      <c r="J137" s="2" t="n"/>
-      <c r="K137" s="2" t="inlineStr">
+      <c r="E139" s="2" t="n"/>
+      <c r="F139" s="2" t="n"/>
+      <c r="G139" s="2" t="n"/>
+      <c r="H139" s="2" t="n"/>
+      <c r="I139" s="2" t="n"/>
+      <c r="J139" s="2" t="n"/>
+      <c r="K139" s="2" t="inlineStr">
         <is>
           <t>Based on Schultz, W. (2022). Dopamine reward prediction error coding. Dialogues in clinical neuroscience.
 RDoC - https://www.nimh.nih.gov/research/research-funded-by-nimh/rdoc/definitions-of-the-rdoc-domains-and-constructs</t>
         </is>
       </c>
-      <c r="L137" s="2" t="n"/>
-      <c r="M137" s="2" t="n"/>
-      <c r="N137" s="2" t="n"/>
-      <c r="O137" s="2" t="n"/>
-      <c r="P137" s="2" t="n"/>
-      <c r="Q137" s="2" t="inlineStr">
+      <c r="L139" s="2" t="n"/>
+      <c r="M139" s="2" t="n"/>
+      <c r="N139" s="2" t="n"/>
+      <c r="O139" s="2" t="n"/>
+      <c r="P139" s="2" t="n"/>
+      <c r="Q139" s="2" t="inlineStr">
         <is>
           <t>LSR 1</t>
         </is>
       </c>
-      <c r="R137" s="2" t="inlineStr">
-        <is>
-          <t>Intervention outcomes and spillover effects</t>
-        </is>
-      </c>
-      <c r="S137" s="2" t="n"/>
-      <c r="T137" s="2" t="inlineStr">
+      <c r="R139" s="2" t="inlineStr">
+        <is>
+          <t>Intervention outcomes and spillover effects</t>
+        </is>
+      </c>
+      <c r="S139" s="2" t="n"/>
+      <c r="T139" s="2" t="inlineStr">
         <is>
           <t>Obsolete</t>
         </is>
       </c>
-      <c r="U137" s="2" t="n"/>
-      <c r="V137" s="2" t="n"/>
-      <c r="W137" s="2" t="inlineStr">
-        <is>
-          <t>PS</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" s="3" t="inlineStr">
+      <c r="U139" s="2" t="n"/>
+      <c r="V139" s="2" t="n"/>
+      <c r="W139" s="2" t="inlineStr">
+        <is>
+          <t>PS</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="3" t="inlineStr">
         <is>
           <t>GMHO:0000208</t>
         </is>
       </c>
-      <c r="B138" s="3" t="inlineStr">
+      <c r="B140" s="3" t="inlineStr">
         <is>
           <t>scale directionality</t>
         </is>
       </c>
-      <c r="C138" s="3" t="inlineStr">
+      <c r="C140" s="3" t="inlineStr">
         <is>
           <t>An information content entity about the orientation of a measurement's scoring system in which higher numerical levels can indicate higher or lower levels of a construct.</t>
         </is>
       </c>
-      <c r="D138" s="3" t="inlineStr">
+      <c r="D140" s="3" t="inlineStr">
         <is>
           <t>information content entity</t>
         </is>
       </c>
-      <c r="E138" s="3" t="n"/>
-      <c r="F138" s="3" t="n"/>
-      <c r="G138" s="3" t="n"/>
-      <c r="H138" s="3" t="n"/>
-      <c r="I138" s="3" t="n"/>
-      <c r="J138" s="3" t="n"/>
-      <c r="K138" s="3" t="n"/>
-      <c r="L138" s="3" t="n"/>
-      <c r="M138" s="3" t="n"/>
-      <c r="N138" s="3" t="n"/>
-      <c r="O138" s="3" t="n"/>
-      <c r="P138" s="3" t="n"/>
-      <c r="Q138" s="3" t="inlineStr">
+      <c r="E140" s="3" t="n"/>
+      <c r="F140" s="3" t="n"/>
+      <c r="G140" s="3" t="n"/>
+      <c r="H140" s="3" t="n"/>
+      <c r="I140" s="3" t="n"/>
+      <c r="J140" s="3" t="n"/>
+      <c r="K140" s="3" t="n"/>
+      <c r="L140" s="3" t="n"/>
+      <c r="M140" s="3" t="n"/>
+      <c r="N140" s="3" t="n"/>
+      <c r="O140" s="3" t="n"/>
+      <c r="P140" s="3" t="n"/>
+      <c r="Q140" s="3" t="inlineStr">
         <is>
           <t>LSR 1</t>
         </is>
       </c>
-      <c r="R138" s="3" t="inlineStr">
-        <is>
-          <t>Intervention outcomes and spillover effects</t>
-        </is>
-      </c>
-      <c r="S138" s="3" t="n"/>
-      <c r="T138" s="3" t="inlineStr">
+      <c r="R140" s="3" t="inlineStr">
+        <is>
+          <t>Intervention outcomes and spillover effects</t>
+        </is>
+      </c>
+      <c r="S140" s="3" t="n"/>
+      <c r="T140" s="3" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="U138" s="3" t="n"/>
-      <c r="V138" s="3" t="n"/>
-      <c r="W138" s="3" t="inlineStr">
-        <is>
-          <t>PS</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" s="3" t="inlineStr">
+      <c r="U140" s="3" t="n"/>
+      <c r="V140" s="3" t="n"/>
+      <c r="W140" s="3" t="inlineStr">
+        <is>
+          <t>PS</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="3" t="inlineStr">
         <is>
           <t>GMHO:0000081</t>
         </is>
       </c>
-      <c r="B139" s="3" t="inlineStr">
+      <c r="B141" s="3" t="inlineStr">
         <is>
           <t>serious adverse event following an intervention</t>
         </is>
       </c>
-      <c r="C139" s="3" t="inlineStr">
+      <c r="C141" s="3" t="inlineStr">
         <is>
           <t>An adverse event following an intervention that results in death, a life-threatening event, a persistent or significant disability or a birth defect or requires hospitalisation or extends hospitalisation.</t>
         </is>
       </c>
-      <c r="D139" s="3" t="inlineStr">
+      <c r="D141" s="3" t="inlineStr">
         <is>
           <t>adverse event following an intervention</t>
         </is>
       </c>
-      <c r="E139" s="3" t="n"/>
-      <c r="F139" s="3" t="n"/>
-      <c r="G139" s="3" t="n"/>
-      <c r="H139" s="3" t="n"/>
-      <c r="I139" s="3" t="n"/>
-      <c r="J139" s="3" t="n"/>
-      <c r="K139" s="3" t="inlineStr">
+      <c r="E141" s="3" t="n"/>
+      <c r="F141" s="3" t="n"/>
+      <c r="G141" s="3" t="n"/>
+      <c r="H141" s="3" t="n"/>
+      <c r="I141" s="3" t="n"/>
+      <c r="J141" s="3" t="n"/>
+      <c r="K141" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">Based on https://www.fda.gov/safety/reporting-serious-problems-fda/what-serious-adverse-event
 </t>
         </is>
       </c>
-      <c r="L139" s="3" t="inlineStr">
+      <c r="L141" s="3" t="inlineStr">
         <is>
           <t>http://purl.obolibrary.org/obo/OAE_0000631</t>
         </is>
       </c>
-      <c r="M139" s="3" t="inlineStr">
+      <c r="M141" s="3" t="inlineStr">
         <is>
           <t>serious adverse event</t>
         </is>
       </c>
-      <c r="N139" s="3" t="n"/>
-      <c r="O139" s="3" t="n"/>
-      <c r="P139" s="3" t="n"/>
-      <c r="Q139" s="3" t="inlineStr">
+      <c r="N141" s="3" t="n"/>
+      <c r="O141" s="3" t="n"/>
+      <c r="P141" s="3" t="n"/>
+      <c r="Q141" s="3" t="inlineStr">
         <is>
           <t>LSR 3</t>
         </is>
       </c>
-      <c r="R139" s="3" t="inlineStr">
-        <is>
-          <t>Intervention outcomes and spillover effects</t>
-        </is>
-      </c>
-      <c r="S139" s="3" t="n"/>
-      <c r="T139" s="3" t="inlineStr">
+      <c r="R141" s="3" t="inlineStr">
+        <is>
+          <t>Intervention outcomes and spillover effects</t>
+        </is>
+      </c>
+      <c r="S141" s="3" t="n"/>
+      <c r="T141" s="3" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="U139" s="3" t="n"/>
-      <c r="V139" s="3" t="n"/>
-      <c r="W139" s="3" t="inlineStr">
+      <c r="U141" s="3" t="n"/>
+      <c r="V141" s="3" t="n"/>
+      <c r="W141" s="3" t="inlineStr">
         <is>
           <t>PS; MS</t>
         </is>
       </c>
     </row>
-    <row r="140">
-      <c r="A140" s="2" t="inlineStr">
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
         <is>
           <t>GMHO:0000082</t>
         </is>
       </c>
-      <c r="B140" s="2" t="inlineStr">
+      <c r="B142" s="2" t="inlineStr">
         <is>
           <t>serious psychological adverse event following an intervention</t>
         </is>
       </c>
-      <c r="C140" s="2" t="inlineStr">
+      <c r="C142" s="2" t="inlineStr">
         <is>
           <t>A serious adverse event following an intervention that is associated with multiple, persistent or salient negative mental processes.</t>
         </is>
       </c>
-      <c r="D140" s="2" t="inlineStr">
+      <c r="D142" s="2" t="inlineStr">
         <is>
           <t>serious adverse event following an intervention</t>
         </is>
       </c>
-      <c r="E140" s="2" t="n"/>
-      <c r="F140" s="2" t="n"/>
-      <c r="G140" s="2" t="n"/>
-      <c r="H140" s="2" t="n"/>
-      <c r="I140" s="2" t="n"/>
-      <c r="J140" s="2" t="n"/>
-      <c r="K140" s="2" t="n"/>
-      <c r="L140" s="2" t="n"/>
-      <c r="M140" s="2" t="n"/>
-      <c r="N140" s="2" t="n"/>
-      <c r="O140" s="2" t="n"/>
-      <c r="P140" s="2" t="n"/>
-      <c r="Q140" s="2" t="inlineStr">
+      <c r="E142" s="2" t="n"/>
+      <c r="F142" s="2" t="n"/>
+      <c r="G142" s="2" t="n"/>
+      <c r="H142" s="2" t="n"/>
+      <c r="I142" s="2" t="n"/>
+      <c r="J142" s="2" t="n"/>
+      <c r="K142" s="2" t="n"/>
+      <c r="L142" s="2" t="n"/>
+      <c r="M142" s="2" t="n"/>
+      <c r="N142" s="2" t="n"/>
+      <c r="O142" s="2" t="n"/>
+      <c r="P142" s="2" t="n"/>
+      <c r="Q142" s="2" t="inlineStr">
         <is>
           <t>LSR 3</t>
         </is>
       </c>
-      <c r="R140" s="2" t="inlineStr">
-        <is>
-          <t>Intervention outcomes and spillover effects</t>
-        </is>
-      </c>
-      <c r="S140" s="2" t="n"/>
-      <c r="T140" s="2" t="inlineStr">
+      <c r="R142" s="2" t="inlineStr">
+        <is>
+          <t>Intervention outcomes and spillover effects</t>
+        </is>
+      </c>
+      <c r="S142" s="2" t="n"/>
+      <c r="T142" s="2" t="inlineStr">
         <is>
           <t>Obsolete</t>
         </is>
       </c>
-      <c r="U140" s="2" t="n"/>
-      <c r="V140" s="2" t="n"/>
-      <c r="W140" s="2" t="inlineStr">
-        <is>
-          <t>PS</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" s="2" t="inlineStr">
+      <c r="U142" s="2" t="n"/>
+      <c r="V142" s="2" t="n"/>
+      <c r="W142" s="2" t="inlineStr">
+        <is>
+          <t>PS</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
         <is>
           <t>GMHO:0000083</t>
         </is>
       </c>
-      <c r="B141" s="2" t="inlineStr">
+      <c r="B143" s="2" t="inlineStr">
         <is>
           <t>serious somatic adverse event following an intervention</t>
         </is>
       </c>
-      <c r="C141" s="2" t="inlineStr">
+      <c r="C143" s="2" t="inlineStr">
         <is>
           <t>A serious adverse event following an intervention that is associated with multiple, persistent or salient physical symptoms.</t>
         </is>
       </c>
-      <c r="D141" s="2" t="inlineStr">
+      <c r="D143" s="2" t="inlineStr">
         <is>
           <t>serious adverse event following an intervention</t>
         </is>
       </c>
-      <c r="E141" s="2" t="n"/>
-      <c r="F141" s="2" t="n"/>
-      <c r="G141" s="2" t="n"/>
-      <c r="H141" s="2" t="n"/>
-      <c r="I141" s="2" t="n"/>
-      <c r="J141" s="2" t="n"/>
-      <c r="K141" s="2" t="n"/>
-      <c r="L141" s="2" t="n"/>
-      <c r="M141" s="2" t="n"/>
-      <c r="N141" s="2" t="n"/>
-      <c r="O141" s="2" t="n"/>
-      <c r="P141" s="2" t="n"/>
-      <c r="Q141" s="2" t="inlineStr">
+      <c r="E143" s="2" t="n"/>
+      <c r="F143" s="2" t="n"/>
+      <c r="G143" s="2" t="n"/>
+      <c r="H143" s="2" t="n"/>
+      <c r="I143" s="2" t="n"/>
+      <c r="J143" s="2" t="n"/>
+      <c r="K143" s="2" t="n"/>
+      <c r="L143" s="2" t="n"/>
+      <c r="M143" s="2" t="n"/>
+      <c r="N143" s="2" t="n"/>
+      <c r="O143" s="2" t="n"/>
+      <c r="P143" s="2" t="n"/>
+      <c r="Q143" s="2" t="inlineStr">
         <is>
           <t>LSR 3</t>
         </is>
       </c>
-      <c r="R141" s="2" t="inlineStr">
-        <is>
-          <t>Intervention outcomes and spillover effects</t>
-        </is>
-      </c>
-      <c r="S141" s="2" t="n"/>
-      <c r="T141" s="2" t="inlineStr">
+      <c r="R143" s="2" t="inlineStr">
+        <is>
+          <t>Intervention outcomes and spillover effects</t>
+        </is>
+      </c>
+      <c r="S143" s="2" t="n"/>
+      <c r="T143" s="2" t="inlineStr">
         <is>
           <t>Obsolete</t>
         </is>
       </c>
-      <c r="U141" s="2" t="n"/>
-      <c r="V141" s="2" t="n"/>
-      <c r="W141" s="2" t="inlineStr">
-        <is>
-          <t>PS</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
+      <c r="U143" s="2" t="n"/>
+      <c r="V143" s="2" t="n"/>
+      <c r="W143" s="2" t="inlineStr">
+        <is>
+          <t>PS</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="4" t="inlineStr">
+        <is>
+          <t>GMHO:0000271</t>
+        </is>
+      </c>
+      <c r="B144" s="4" t="inlineStr">
+        <is>
+          <t>social anxiety scale</t>
+        </is>
+      </c>
+      <c r="C144" s="4" t="inlineStr">
+        <is>
+          <t>An anxiety scale that is used to measure social anxiety symptom severity.</t>
+        </is>
+      </c>
+      <c r="D144" s="4" t="inlineStr">
+        <is>
+          <t>anxiety scale</t>
+        </is>
+      </c>
+      <c r="E144" s="4" t="inlineStr"/>
+      <c r="F144" s="4" t="inlineStr"/>
+      <c r="G144" s="4" t="inlineStr"/>
+      <c r="H144" s="4" t="inlineStr"/>
+      <c r="I144" s="4" t="inlineStr"/>
+      <c r="J144" s="4" t="inlineStr">
+        <is>
+          <t>Intervention outcomes and spillover effects</t>
+        </is>
+      </c>
+      <c r="K144" s="4" t="inlineStr"/>
+      <c r="L144" s="4" t="inlineStr"/>
+      <c r="M144" s="4" t="inlineStr"/>
+      <c r="N144" s="4" t="inlineStr"/>
+      <c r="O144" s="4" t="inlineStr"/>
+      <c r="P144" s="4" t="inlineStr"/>
+      <c r="Q144" s="4" t="inlineStr">
+        <is>
+          <t>LSR 6</t>
+        </is>
+      </c>
+      <c r="R144" s="4" t="inlineStr">
+        <is>
+          <t>Intervention outcomes and spillover effects</t>
+        </is>
+      </c>
+      <c r="S144" s="4" t="inlineStr"/>
+      <c r="T144" s="4" t="inlineStr">
+        <is>
+          <t>Proposed</t>
+        </is>
+      </c>
+      <c r="U144" s="4" t="inlineStr"/>
+      <c r="V144" s="4" t="inlineStr"/>
+      <c r="W144" s="4" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" s="4" t="inlineStr">
+        <is>
+          <t>GMHO:0000272</t>
+        </is>
+      </c>
+      <c r="B145" s="4" t="inlineStr">
+        <is>
+          <t>social anxiety symptom severity</t>
+        </is>
+      </c>
+      <c r="C145" s="4" t="inlineStr">
+        <is>
+          <t>Anxiety symptom severity that is associated with social anxiety.</t>
+        </is>
+      </c>
+      <c r="D145" s="4" t="inlineStr">
+        <is>
+          <t>anxiety symptom severity</t>
+        </is>
+      </c>
+      <c r="E145" s="4" t="inlineStr"/>
+      <c r="F145" s="4" t="inlineStr"/>
+      <c r="G145" s="4" t="inlineStr"/>
+      <c r="H145" s="4" t="inlineStr"/>
+      <c r="I145" s="4" t="inlineStr"/>
+      <c r="J145" s="4" t="inlineStr">
+        <is>
+          <t>Intervention outcomes and spillover effects</t>
+        </is>
+      </c>
+      <c r="K145" s="4" t="inlineStr"/>
+      <c r="L145" s="4" t="inlineStr"/>
+      <c r="M145" s="4" t="inlineStr"/>
+      <c r="N145" s="4" t="inlineStr"/>
+      <c r="O145" s="4" t="inlineStr"/>
+      <c r="P145" s="4" t="inlineStr"/>
+      <c r="Q145" s="4" t="inlineStr">
+        <is>
+          <t>LSR 6</t>
+        </is>
+      </c>
+      <c r="R145" s="4" t="inlineStr">
+        <is>
+          <t>Intervention outcomes and spillover effects</t>
+        </is>
+      </c>
+      <c r="S145" s="4" t="inlineStr"/>
+      <c r="T145" s="4" t="inlineStr">
+        <is>
+          <t>Proposed</t>
+        </is>
+      </c>
+      <c r="U145" s="4" t="inlineStr"/>
+      <c r="V145" s="4" t="inlineStr"/>
+      <c r="W145" s="4" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
         <is>
           <t>OBCS:0000077</t>
         </is>
       </c>
-      <c r="B142" t="inlineStr">
+      <c r="B146" t="inlineStr">
         <is>
           <t>standard deviation</t>
         </is>
       </c>
-      <c r="C142" t="inlineStr">
+      <c r="C146" t="inlineStr">
         <is>
           <t>A quantitative confidence value that measures the variability of data around the mean.</t>
         </is>
       </c>
-      <c r="D142" t="inlineStr">
+      <c r="D146" t="inlineStr">
         <is>
           <t>quantitative confidence value</t>
         </is>
       </c>
-      <c r="Q142" t="inlineStr">
+      <c r="Q146" t="inlineStr">
         <is>
           <t>LSR 1; LSR 2</t>
         </is>
       </c>
-      <c r="R142" t="inlineStr">
-        <is>
-          <t>Intervention outcomes and spillover effects</t>
-        </is>
-      </c>
-      <c r="T142" t="inlineStr">
+      <c r="R146" t="inlineStr">
+        <is>
+          <t>Intervention outcomes and spillover effects</t>
+        </is>
+      </c>
+      <c r="T146" t="inlineStr">
         <is>
           <t>External</t>
         </is>
       </c>
-      <c r="W142" t="inlineStr">
-        <is>
-          <t>PS</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
+      <c r="W146" t="inlineStr">
+        <is>
+          <t>PS</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
         <is>
           <t>STATO:0000562</t>
         </is>
       </c>
-      <c r="B143" t="inlineStr">
+      <c r="B147" t="inlineStr">
         <is>
           <t>standard error of estimate</t>
         </is>
       </c>
-      <c r="C143" t="inlineStr">
+      <c r="C147" t="inlineStr">
         <is>
           <t>The standard error is a measure of dispersion applied to estimates across hypothetical repeated random samples.</t>
         </is>
       </c>
-      <c r="D143" t="inlineStr">
+      <c r="D147" t="inlineStr">
         <is>
           <t>estimate</t>
         </is>
       </c>
-      <c r="J143" t="inlineStr">
-        <is>
-          <t>Intervention outcomes and spillover effects</t>
-        </is>
-      </c>
-      <c r="Q143" t="inlineStr">
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>Intervention outcomes and spillover effects</t>
+        </is>
+      </c>
+      <c r="Q147" t="inlineStr">
         <is>
           <t>LSR 3</t>
         </is>
       </c>
-      <c r="R143" t="inlineStr">
-        <is>
-          <t>Intervention outcomes and spillover effects</t>
-        </is>
-      </c>
-      <c r="T143" t="inlineStr">
+      <c r="R147" t="inlineStr">
+        <is>
+          <t>Intervention outcomes and spillover effects</t>
+        </is>
+      </c>
+      <c r="T147" t="inlineStr">
         <is>
           <t>External</t>
         </is>
       </c>
-      <c r="W143" t="inlineStr">
-        <is>
-          <t>PS</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" s="2" t="inlineStr">
+      <c r="W147" t="inlineStr">
+        <is>
+          <t>PS</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
         <is>
           <t>GMHO:0000084</t>
         </is>
       </c>
-      <c r="B144" s="2" t="inlineStr">
+      <c r="B148" s="2" t="inlineStr">
         <is>
           <t>suicidal ideation following intervention</t>
         </is>
       </c>
-      <c r="C144" s="2" t="inlineStr">
+      <c r="C148" s="2" t="inlineStr">
         <is>
           <t>An adverse event following an intervention that involves thoughts about suicide.</t>
         </is>
       </c>
-      <c r="D144" s="2" t="inlineStr">
+      <c r="D148" s="2" t="inlineStr">
         <is>
           <t>adverse event following an intervention</t>
         </is>
       </c>
-      <c r="E144" s="2" t="n"/>
-      <c r="F144" s="2" t="n"/>
-      <c r="G144" s="2" t="n"/>
-      <c r="H144" s="2" t="n"/>
-      <c r="I144" s="2" t="n"/>
-      <c r="J144" s="2" t="n"/>
-      <c r="K144" s="2" t="inlineStr">
+      <c r="E148" s="2" t="n"/>
+      <c r="F148" s="2" t="n"/>
+      <c r="G148" s="2" t="n"/>
+      <c r="H148" s="2" t="n"/>
+      <c r="I148" s="2" t="n"/>
+      <c r="J148" s="2" t="n"/>
+      <c r="K148" s="2" t="inlineStr">
         <is>
           <t>Based on http://purl.obolibrary.org/obo/OAE_0001432</t>
         </is>
       </c>
-      <c r="L144" s="2" t="inlineStr">
+      <c r="L148" s="2" t="inlineStr">
         <is>
           <t>http://purl.obolibrary.org/obo/OAE_0001432</t>
         </is>
       </c>
-      <c r="M144" s="2" t="n"/>
-      <c r="N144" s="2" t="n"/>
-      <c r="O144" s="2" t="n"/>
-      <c r="P144" s="2" t="n"/>
-      <c r="Q144" s="2" t="inlineStr">
+      <c r="M148" s="2" t="n"/>
+      <c r="N148" s="2" t="n"/>
+      <c r="O148" s="2" t="n"/>
+      <c r="P148" s="2" t="n"/>
+      <c r="Q148" s="2" t="inlineStr">
         <is>
           <t>LSR 3</t>
         </is>
       </c>
-      <c r="R144" s="2" t="inlineStr">
-        <is>
-          <t>Intervention outcomes and spillover effects</t>
-        </is>
-      </c>
-      <c r="S144" s="2" t="n"/>
-      <c r="T144" s="2" t="inlineStr">
+      <c r="R148" s="2" t="inlineStr">
+        <is>
+          <t>Intervention outcomes and spillover effects</t>
+        </is>
+      </c>
+      <c r="S148" s="2" t="n"/>
+      <c r="T148" s="2" t="inlineStr">
         <is>
           <t>Obsolete</t>
         </is>
       </c>
-      <c r="U144" s="2" t="n"/>
-      <c r="V144" s="2" t="n"/>
-      <c r="W144" s="2" t="inlineStr">
-        <is>
-          <t>PS</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" s="2" t="inlineStr">
+      <c r="U148" s="2" t="n"/>
+      <c r="V148" s="2" t="n"/>
+      <c r="W148" s="2" t="inlineStr">
+        <is>
+          <t>PS</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
         <is>
           <t>GMHO:0000085</t>
         </is>
       </c>
-      <c r="B145" s="2" t="inlineStr">
+      <c r="B149" s="2" t="inlineStr">
         <is>
           <t>suicide attempt following intervention</t>
         </is>
       </c>
-      <c r="C145" s="2" t="inlineStr">
+      <c r="C149" s="2" t="inlineStr">
         <is>
           <t>An adverse event following an intervention that involves at least one attempted suicide.</t>
         </is>
       </c>
-      <c r="D145" s="2" t="inlineStr">
+      <c r="D149" s="2" t="inlineStr">
         <is>
           <t>adverse event following an intervention</t>
         </is>
       </c>
-      <c r="E145" s="2" t="n"/>
-      <c r="F145" s="2" t="n"/>
-      <c r="G145" s="2" t="n"/>
-      <c r="H145" s="2" t="n"/>
-      <c r="I145" s="2" t="n"/>
-      <c r="J145" s="2" t="n"/>
-      <c r="K145" s="2" t="inlineStr">
+      <c r="E149" s="2" t="n"/>
+      <c r="F149" s="2" t="n"/>
+      <c r="G149" s="2" t="n"/>
+      <c r="H149" s="2" t="n"/>
+      <c r="I149" s="2" t="n"/>
+      <c r="J149" s="2" t="n"/>
+      <c r="K149" s="2" t="inlineStr">
         <is>
           <t>Based on http://purl.obolibrary.org/obo/OAE_0001433</t>
         </is>
       </c>
-      <c r="L145" s="2" t="inlineStr">
+      <c r="L149" s="2" t="inlineStr">
         <is>
           <t>http://purl.obolibrary.org/obo/OAE_0001433</t>
         </is>
       </c>
-      <c r="M145" s="2" t="n"/>
-      <c r="N145" s="2" t="n"/>
-      <c r="O145" s="2" t="n"/>
-      <c r="P145" s="2" t="n"/>
-      <c r="Q145" s="2" t="inlineStr">
+      <c r="M149" s="2" t="n"/>
+      <c r="N149" s="2" t="n"/>
+      <c r="O149" s="2" t="n"/>
+      <c r="P149" s="2" t="n"/>
+      <c r="Q149" s="2" t="inlineStr">
         <is>
           <t>LSR 3</t>
         </is>
       </c>
-      <c r="R145" s="2" t="inlineStr">
-        <is>
-          <t>Intervention outcomes and spillover effects</t>
-        </is>
-      </c>
-      <c r="S145" s="2" t="n"/>
-      <c r="T145" s="2" t="inlineStr">
+      <c r="R149" s="2" t="inlineStr">
+        <is>
+          <t>Intervention outcomes and spillover effects</t>
+        </is>
+      </c>
+      <c r="S149" s="2" t="n"/>
+      <c r="T149" s="2" t="inlineStr">
         <is>
           <t>Obsolete</t>
         </is>
       </c>
-      <c r="U145" s="2" t="n"/>
-      <c r="V145" s="2" t="n"/>
-      <c r="W145" s="2" t="inlineStr">
-        <is>
-          <t>PS</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" s="2" t="inlineStr">
+      <c r="U149" s="2" t="n"/>
+      <c r="V149" s="2" t="n"/>
+      <c r="W149" s="2" t="inlineStr">
+        <is>
+          <t>PS</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
         <is>
           <t>GMHO:0000086</t>
         </is>
       </c>
-      <c r="B146" s="2" t="inlineStr">
+      <c r="B150" s="2" t="inlineStr">
         <is>
           <t>suicide following an intervention</t>
         </is>
       </c>
-      <c r="C146" s="2" t="inlineStr">
+      <c r="C150" s="2" t="inlineStr">
         <is>
           <t>A death following an intervention that involves a participant intentionally ending their own life.</t>
         </is>
       </c>
-      <c r="D146" s="2" t="inlineStr">
+      <c r="D150" s="2" t="inlineStr">
         <is>
           <t>death following an intervention</t>
         </is>
       </c>
-      <c r="E146" s="2" t="n"/>
-      <c r="F146" s="2" t="n"/>
-      <c r="G146" s="2" t="n"/>
-      <c r="H146" s="2" t="n"/>
-      <c r="I146" s="2" t="n"/>
-      <c r="J146" s="2" t="n"/>
-      <c r="K146" s="2" t="n"/>
-      <c r="L146" s="2" t="n"/>
-      <c r="M146" s="2" t="n"/>
-      <c r="N146" s="2" t="n"/>
-      <c r="O146" s="2" t="n"/>
-      <c r="P146" s="2" t="n"/>
-      <c r="Q146" s="2" t="inlineStr">
+      <c r="E150" s="2" t="n"/>
+      <c r="F150" s="2" t="n"/>
+      <c r="G150" s="2" t="n"/>
+      <c r="H150" s="2" t="n"/>
+      <c r="I150" s="2" t="n"/>
+      <c r="J150" s="2" t="n"/>
+      <c r="K150" s="2" t="n"/>
+      <c r="L150" s="2" t="n"/>
+      <c r="M150" s="2" t="n"/>
+      <c r="N150" s="2" t="n"/>
+      <c r="O150" s="2" t="n"/>
+      <c r="P150" s="2" t="n"/>
+      <c r="Q150" s="2" t="inlineStr">
         <is>
           <t>LSR 3</t>
         </is>
       </c>
-      <c r="R146" s="2" t="inlineStr">
-        <is>
-          <t>Intervention outcomes and spillover effects</t>
-        </is>
-      </c>
-      <c r="S146" s="2" t="n"/>
-      <c r="T146" s="2" t="inlineStr">
+      <c r="R150" s="2" t="inlineStr">
+        <is>
+          <t>Intervention outcomes and spillover effects</t>
+        </is>
+      </c>
+      <c r="S150" s="2" t="n"/>
+      <c r="T150" s="2" t="inlineStr">
         <is>
           <t>Obsolete</t>
         </is>
       </c>
-      <c r="U146" s="2" t="n"/>
-      <c r="V146" s="2" t="n"/>
-      <c r="W146" s="2" t="inlineStr">
-        <is>
-          <t>PS</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" s="2" t="inlineStr">
-        <is>
-          <t>OGMS:0000020</t>
-        </is>
-      </c>
-      <c r="B147" s="2" t="inlineStr">
-        <is>
-          <t>symptom</t>
-        </is>
-      </c>
-      <c r="C147" s="2" t="inlineStr">
-        <is>
-          <t>A process experienced by the patient, which can only be experienced by the patient, that is hypothesized to be clinically relevant.</t>
-        </is>
-      </c>
-      <c r="D147" s="2" t="inlineStr">
-        <is>
-          <t>process</t>
-        </is>
-      </c>
-      <c r="E147" s="2" t="n"/>
-      <c r="F147" s="2" t="n"/>
-      <c r="G147" s="2" t="n"/>
-      <c r="H147" s="2" t="n"/>
-      <c r="I147" s="2" t="n"/>
-      <c r="J147" s="2" t="n"/>
-      <c r="K147" s="2" t="n"/>
-      <c r="L147" s="2" t="n"/>
-      <c r="M147" s="2" t="n"/>
-      <c r="N147" s="2" t="n"/>
-      <c r="O147" s="2" t="n"/>
-      <c r="P147" s="2" t="n"/>
-      <c r="Q147" s="2" t="inlineStr">
-        <is>
-          <t>LSR 1</t>
-        </is>
-      </c>
-      <c r="R147" s="2" t="inlineStr">
-        <is>
-          <t>Intervention outcomes and spillover effects</t>
-        </is>
-      </c>
-      <c r="S147" s="2" t="n"/>
-      <c r="T147" s="2" t="inlineStr">
-        <is>
-          <t>Obsolete</t>
-        </is>
-      </c>
-      <c r="U147" s="2" t="n"/>
-      <c r="V147" s="2" t="n"/>
-      <c r="W147" s="2" t="inlineStr">
-        <is>
-          <t>PS</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" s="3" t="inlineStr">
-        <is>
-          <t>GMHO:0000087</t>
-        </is>
-      </c>
-      <c r="B148" s="3" t="inlineStr">
-        <is>
-          <t>symptom severity</t>
-        </is>
-      </c>
-      <c r="C148" s="3" t="inlineStr">
-        <is>
-          <t>A data item that is about the severity dimension associated with a symptom.</t>
-        </is>
-      </c>
-      <c r="D148" s="3" t="inlineStr">
-        <is>
-          <t>data item</t>
-        </is>
-      </c>
-      <c r="E148" s="3" t="n"/>
-      <c r="F148" s="3" t="n"/>
-      <c r="G148" s="3" t="n"/>
-      <c r="H148" s="3" t="n"/>
-      <c r="I148" s="3" t="n"/>
-      <c r="J148" s="3" t="n"/>
-      <c r="K148" s="3" t="n"/>
-      <c r="L148" s="3" t="n"/>
-      <c r="M148" s="3" t="n"/>
-      <c r="N148" s="3" t="n"/>
-      <c r="O148" s="3" t="n"/>
-      <c r="P148" s="3" t="n"/>
-      <c r="Q148" s="3" t="inlineStr">
-        <is>
-          <t>LSR 1; LSR 3</t>
-        </is>
-      </c>
-      <c r="R148" s="3" t="inlineStr">
-        <is>
-          <t>Intervention outcomes and spillover effects</t>
-        </is>
-      </c>
-      <c r="S148" s="3" t="inlineStr">
-        <is>
-          <t>A measure for 'psychotic disorder symptom severity'</t>
-        </is>
-      </c>
-      <c r="T148" s="3" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="U148" s="3" t="n"/>
-      <c r="V148" s="3" t="n"/>
-      <c r="W148" s="3" t="inlineStr">
-        <is>
-          <t>PS</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" s="3" t="inlineStr">
-        <is>
-          <t>GMHO:0000138</t>
-        </is>
-      </c>
-      <c r="B149" s="3" t="inlineStr">
-        <is>
-          <t>temporal reference associated with measurement in intervention</t>
-        </is>
-      </c>
-      <c r="C149" s="3" t="inlineStr">
-        <is>
-          <t>Time point at which a measurement is taken with reference to a temporal part of the intervention evaluation study.</t>
-        </is>
-      </c>
-      <c r="D149" s="3" t="inlineStr">
-        <is>
-          <t>one-dimensional temporal region</t>
-        </is>
-      </c>
-      <c r="E149" s="3" t="n"/>
-      <c r="F149" s="3" t="n"/>
-      <c r="G149" s="3" t="n"/>
-      <c r="H149" s="3" t="n"/>
-      <c r="I149" s="3" t="n"/>
-      <c r="J149" s="3" t="inlineStr">
-        <is>
-          <t>Intervention outcomes and spillover effects</t>
-        </is>
-      </c>
-      <c r="K149" s="3" t="n"/>
-      <c r="L149" s="3" t="n"/>
-      <c r="M149" s="3" t="n"/>
-      <c r="N149" s="3" t="n"/>
-      <c r="O149" s="3" t="n"/>
-      <c r="P149" s="3" t="n"/>
-      <c r="Q149" s="3" t="inlineStr">
-        <is>
-          <t>LSR 1; LSR 2; LSR 3</t>
-        </is>
-      </c>
-      <c r="R149" s="3" t="inlineStr">
-        <is>
-          <t>Intervention outcomes and spillover effects</t>
-        </is>
-      </c>
-      <c r="S149" s="3" t="n"/>
-      <c r="T149" s="3" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="U149" s="3" t="n"/>
-      <c r="V149" s="3" t="n"/>
-      <c r="W149" s="3" t="inlineStr">
-        <is>
-          <t>PS</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" s="3" t="inlineStr">
-        <is>
-          <t>GMHO:0000229</t>
-        </is>
-      </c>
-      <c r="B150" s="3" t="inlineStr">
-        <is>
-          <t>tiredness following intervention</t>
-        </is>
-      </c>
-      <c r="C150" s="3" t="inlineStr">
-        <is>
-          <t>An adverse event following intervention that involves experiencing tiredness.</t>
-        </is>
-      </c>
-      <c r="D150" s="3" t="inlineStr">
-        <is>
-          <t>adverse event following an intervention</t>
-        </is>
-      </c>
-      <c r="E150" s="3" t="n"/>
-      <c r="F150" s="3" t="n"/>
-      <c r="G150" s="3" t="n"/>
-      <c r="H150" s="3" t="n"/>
-      <c r="I150" s="3" t="n"/>
-      <c r="J150" s="3" t="inlineStr">
-        <is>
-          <t>Intervention outcomes and spillover effects</t>
-        </is>
-      </c>
-      <c r="K150" s="3" t="n"/>
-      <c r="L150" s="3" t="n"/>
-      <c r="M150" s="3" t="inlineStr">
-        <is>
-          <t>tiredness</t>
-        </is>
-      </c>
-      <c r="N150" s="3" t="n"/>
-      <c r="O150" s="3" t="n"/>
-      <c r="P150" s="3" t="n"/>
-      <c r="Q150" s="3" t="inlineStr">
-        <is>
-          <t>LSR 3</t>
-        </is>
-      </c>
-      <c r="R150" s="3" t="n"/>
-      <c r="S150" s="3" t="n"/>
-      <c r="T150" s="3" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="U150" s="3" t="n"/>
-      <c r="V150" s="3" t="n"/>
-      <c r="W150" s="3" t="inlineStr">
+      <c r="U150" s="2" t="n"/>
+      <c r="V150" s="2" t="n"/>
+      <c r="W150" s="2" t="inlineStr">
         <is>
           <t>PS</t>
         </is>
@@ -9350,29 +9344,25 @@
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>GMHO:0000088</t>
+          <t>OGMS:0000020</t>
         </is>
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
-          <t>unnatural dealth due to external factors following an intervention</t>
+          <t>symptom</t>
         </is>
       </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
-          <t>Death following an intervention that involves a homicide or accidents.</t>
+          <t>A process experienced by the patient, which can only be experienced by the patient, that is hypothesized to be clinically relevant.</t>
         </is>
       </c>
       <c r="D151" s="2" t="inlineStr">
         <is>
-          <t>death following an intervention</t>
-        </is>
-      </c>
-      <c r="E151" s="2" t="inlineStr">
-        <is>
-          <t>"homicide following an intervention" OR "death due to accidents following an intervention"</t>
-        </is>
-      </c>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="E151" s="2" t="n"/>
       <c r="F151" s="2" t="n"/>
       <c r="G151" s="2" t="n"/>
       <c r="H151" s="2" t="n"/>
@@ -9386,7 +9376,7 @@
       <c r="P151" s="2" t="n"/>
       <c r="Q151" s="2" t="inlineStr">
         <is>
-          <t>LSR 3</t>
+          <t>LSR 1</t>
         </is>
       </c>
       <c r="R151" s="2" t="inlineStr">
@@ -9409,305 +9399,305 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="2" t="inlineStr">
+      <c r="A152" s="3" t="inlineStr">
+        <is>
+          <t>GMHO:0000087</t>
+        </is>
+      </c>
+      <c r="B152" s="3" t="inlineStr">
+        <is>
+          <t>symptom severity</t>
+        </is>
+      </c>
+      <c r="C152" s="3" t="inlineStr">
+        <is>
+          <t>A data item that is about the severity dimension associated with a symptom.</t>
+        </is>
+      </c>
+      <c r="D152" s="3" t="inlineStr">
+        <is>
+          <t>data item</t>
+        </is>
+      </c>
+      <c r="E152" s="3" t="n"/>
+      <c r="F152" s="3" t="n"/>
+      <c r="G152" s="3" t="n"/>
+      <c r="H152" s="3" t="n"/>
+      <c r="I152" s="3" t="n"/>
+      <c r="J152" s="3" t="n"/>
+      <c r="K152" s="3" t="n"/>
+      <c r="L152" s="3" t="n"/>
+      <c r="M152" s="3" t="n"/>
+      <c r="N152" s="3" t="n"/>
+      <c r="O152" s="3" t="n"/>
+      <c r="P152" s="3" t="n"/>
+      <c r="Q152" s="3" t="inlineStr">
+        <is>
+          <t>LSR 1; LSR 3</t>
+        </is>
+      </c>
+      <c r="R152" s="3" t="inlineStr">
+        <is>
+          <t>Intervention outcomes and spillover effects</t>
+        </is>
+      </c>
+      <c r="S152" s="3" t="inlineStr">
+        <is>
+          <t>A measure for 'psychotic disorder symptom severity'</t>
+        </is>
+      </c>
+      <c r="T152" s="3" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="U152" s="3" t="n"/>
+      <c r="V152" s="3" t="n"/>
+      <c r="W152" s="3" t="inlineStr">
+        <is>
+          <t>PS</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="3" t="inlineStr">
+        <is>
+          <t>GMHO:0000138</t>
+        </is>
+      </c>
+      <c r="B153" s="3" t="inlineStr">
+        <is>
+          <t>temporal reference associated with measurement in intervention</t>
+        </is>
+      </c>
+      <c r="C153" s="3" t="inlineStr">
+        <is>
+          <t>Time point at which a measurement is taken with reference to a temporal part of the intervention evaluation study.</t>
+        </is>
+      </c>
+      <c r="D153" s="3" t="inlineStr">
+        <is>
+          <t>one-dimensional temporal region</t>
+        </is>
+      </c>
+      <c r="E153" s="3" t="n"/>
+      <c r="F153" s="3" t="n"/>
+      <c r="G153" s="3" t="n"/>
+      <c r="H153" s="3" t="n"/>
+      <c r="I153" s="3" t="n"/>
+      <c r="J153" s="3" t="inlineStr">
+        <is>
+          <t>Intervention outcomes and spillover effects</t>
+        </is>
+      </c>
+      <c r="K153" s="3" t="n"/>
+      <c r="L153" s="3" t="n"/>
+      <c r="M153" s="3" t="n"/>
+      <c r="N153" s="3" t="n"/>
+      <c r="O153" s="3" t="n"/>
+      <c r="P153" s="3" t="n"/>
+      <c r="Q153" s="3" t="inlineStr">
+        <is>
+          <t>LSR 1; LSR 2; LSR 3</t>
+        </is>
+      </c>
+      <c r="R153" s="3" t="inlineStr">
+        <is>
+          <t>Intervention outcomes and spillover effects</t>
+        </is>
+      </c>
+      <c r="S153" s="3" t="n"/>
+      <c r="T153" s="3" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="U153" s="3" t="n"/>
+      <c r="V153" s="3" t="n"/>
+      <c r="W153" s="3" t="inlineStr">
+        <is>
+          <t>PS</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="3" t="inlineStr">
+        <is>
+          <t>GMHO:0000229</t>
+        </is>
+      </c>
+      <c r="B154" s="3" t="inlineStr">
+        <is>
+          <t>tiredness following intervention</t>
+        </is>
+      </c>
+      <c r="C154" s="3" t="inlineStr">
+        <is>
+          <t>An adverse event following intervention that involves experiencing tiredness.</t>
+        </is>
+      </c>
+      <c r="D154" s="3" t="inlineStr">
+        <is>
+          <t>adverse event following an intervention</t>
+        </is>
+      </c>
+      <c r="E154" s="3" t="n"/>
+      <c r="F154" s="3" t="n"/>
+      <c r="G154" s="3" t="n"/>
+      <c r="H154" s="3" t="n"/>
+      <c r="I154" s="3" t="n"/>
+      <c r="J154" s="3" t="inlineStr">
+        <is>
+          <t>Intervention outcomes and spillover effects</t>
+        </is>
+      </c>
+      <c r="K154" s="3" t="n"/>
+      <c r="L154" s="3" t="n"/>
+      <c r="M154" s="3" t="inlineStr">
+        <is>
+          <t>tiredness</t>
+        </is>
+      </c>
+      <c r="N154" s="3" t="n"/>
+      <c r="O154" s="3" t="n"/>
+      <c r="P154" s="3" t="n"/>
+      <c r="Q154" s="3" t="inlineStr">
+        <is>
+          <t>LSR 3</t>
+        </is>
+      </c>
+      <c r="R154" s="3" t="n"/>
+      <c r="S154" s="3" t="n"/>
+      <c r="T154" s="3" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="U154" s="3" t="n"/>
+      <c r="V154" s="3" t="n"/>
+      <c r="W154" s="3" t="inlineStr">
+        <is>
+          <t>PS</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
+        <is>
+          <t>GMHO:0000088</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t>unnatural dealth due to external factors following an intervention</t>
+        </is>
+      </c>
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>Death following an intervention that involves a homicide or accidents.</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="inlineStr">
+        <is>
+          <t>death following an intervention</t>
+        </is>
+      </c>
+      <c r="E155" s="2" t="inlineStr">
+        <is>
+          <t>"homicide following an intervention" OR "death due to accidents following an intervention"</t>
+        </is>
+      </c>
+      <c r="F155" s="2" t="n"/>
+      <c r="G155" s="2" t="n"/>
+      <c r="H155" s="2" t="n"/>
+      <c r="I155" s="2" t="n"/>
+      <c r="J155" s="2" t="n"/>
+      <c r="K155" s="2" t="n"/>
+      <c r="L155" s="2" t="n"/>
+      <c r="M155" s="2" t="n"/>
+      <c r="N155" s="2" t="n"/>
+      <c r="O155" s="2" t="n"/>
+      <c r="P155" s="2" t="n"/>
+      <c r="Q155" s="2" t="inlineStr">
+        <is>
+          <t>LSR 3</t>
+        </is>
+      </c>
+      <c r="R155" s="2" t="inlineStr">
+        <is>
+          <t>Intervention outcomes and spillover effects</t>
+        </is>
+      </c>
+      <c r="S155" s="2" t="n"/>
+      <c r="T155" s="2" t="inlineStr">
+        <is>
+          <t>Obsolete</t>
+        </is>
+      </c>
+      <c r="U155" s="2" t="n"/>
+      <c r="V155" s="2" t="n"/>
+      <c r="W155" s="2" t="inlineStr">
+        <is>
+          <t>PS</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
         <is>
           <t>GMHO:0000139</t>
         </is>
       </c>
-      <c r="B152" s="2" t="inlineStr">
+      <c r="B156" s="2" t="inlineStr">
         <is>
           <t>upper bound of 95% confidence interval</t>
         </is>
       </c>
-      <c r="C152" s="2" t="inlineStr">
+      <c r="C156" s="2" t="inlineStr">
         <is>
           <t>A quantitative confidence value that denotes the upper endpoint of a 95% confidence interval and indicates the highest value within a true parameter is likely to reside within the confidence interval.</t>
         </is>
       </c>
-      <c r="D152" s="2" t="inlineStr">
+      <c r="D156" s="2" t="inlineStr">
         <is>
           <t>quantitative confidence value</t>
         </is>
       </c>
-      <c r="E152" s="2" t="n"/>
-      <c r="F152" s="2" t="n"/>
-      <c r="G152" s="2" t="n"/>
-      <c r="H152" s="2" t="n"/>
-      <c r="I152" s="2" t="n"/>
-      <c r="J152" s="2" t="n"/>
-      <c r="K152" s="2" t="inlineStr">
+      <c r="E156" s="2" t="n"/>
+      <c r="F156" s="2" t="n"/>
+      <c r="G156" s="2" t="n"/>
+      <c r="H156" s="2" t="n"/>
+      <c r="I156" s="2" t="n"/>
+      <c r="J156" s="2" t="n"/>
+      <c r="K156" s="2" t="inlineStr">
         <is>
           <t>Based on Ross, S. M. (2017). Estimation. Introductory statistics ( p. 329-380). Academic Press.</t>
         </is>
       </c>
-      <c r="L152" s="2" t="n"/>
-      <c r="M152" s="2" t="n"/>
-      <c r="N152" s="2" t="n"/>
-      <c r="O152" s="2" t="n"/>
-      <c r="P152" s="2" t="n"/>
-      <c r="Q152" s="2" t="inlineStr">
+      <c r="L156" s="2" t="n"/>
+      <c r="M156" s="2" t="n"/>
+      <c r="N156" s="2" t="n"/>
+      <c r="O156" s="2" t="n"/>
+      <c r="P156" s="2" t="n"/>
+      <c r="Q156" s="2" t="inlineStr">
         <is>
           <t>LSR 1; LSR 2</t>
         </is>
       </c>
-      <c r="R152" s="2" t="inlineStr">
-        <is>
-          <t>Intervention outcomes and spillover effects</t>
-        </is>
-      </c>
-      <c r="S152" s="2" t="n"/>
-      <c r="T152" s="2" t="inlineStr">
+      <c r="R156" s="2" t="inlineStr">
+        <is>
+          <t>Intervention outcomes and spillover effects</t>
+        </is>
+      </c>
+      <c r="S156" s="2" t="n"/>
+      <c r="T156" s="2" t="inlineStr">
         <is>
           <t>Obsolete</t>
         </is>
       </c>
-      <c r="U152" s="2" t="n"/>
-      <c r="V152" s="2" t="n"/>
-      <c r="W152" s="2" t="inlineStr">
-        <is>
-          <t>PS</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" s="2" t="inlineStr">
-        <is>
-          <t>GMHO:0000175</t>
-        </is>
-      </c>
-      <c r="B153" s="2" t="inlineStr">
-        <is>
-          <t>validity of measurement scale</t>
-        </is>
-      </c>
-      <c r="C153" s="2" t="inlineStr">
-        <is>
-          <t>An attribute of a measurement scale that involves the degree to which the outcomes from the scale represent the intended variable or variables.</t>
-        </is>
-      </c>
-      <c r="D153" s="2" t="inlineStr">
-        <is>
-          <t>specifically dependent continuant</t>
-        </is>
-      </c>
-      <c r="E153" s="2" t="n"/>
-      <c r="F153" s="2" t="n"/>
-      <c r="G153" s="2" t="n"/>
-      <c r="H153" s="2" t="n"/>
-      <c r="I153" s="2" t="n"/>
-      <c r="J153" s="2" t="n"/>
-      <c r="K153" s="2" t="inlineStr">
-        <is>
-          <t>Based on Price, P. (2015). Research methods in psychology, 2nd Canadian Edition. BCcampus.</t>
-        </is>
-      </c>
-      <c r="L153" s="2" t="n"/>
-      <c r="M153" s="2" t="n"/>
-      <c r="N153" s="2" t="n"/>
-      <c r="O153" s="2" t="n"/>
-      <c r="P153" s="2" t="n"/>
-      <c r="Q153" s="2" t="inlineStr">
-        <is>
-          <t>LSR 2</t>
-        </is>
-      </c>
-      <c r="R153" s="2" t="inlineStr">
-        <is>
-          <t>Intervention outcomes and spillover effects</t>
-        </is>
-      </c>
-      <c r="S153" s="2" t="n"/>
-      <c r="T153" s="2" t="inlineStr">
-        <is>
-          <t>Obsolete</t>
-        </is>
-      </c>
-      <c r="U153" s="2" t="n"/>
-      <c r="V153" s="2" t="n"/>
-      <c r="W153" s="2" t="inlineStr">
-        <is>
-          <t>PS</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" s="2" t="inlineStr">
-        <is>
-          <t>GMHO:0000140</t>
-        </is>
-      </c>
-      <c r="B154" s="2" t="inlineStr">
-        <is>
-          <t>vo2 max</t>
-        </is>
-      </c>
-      <c r="C154" s="2" t="inlineStr">
-        <is>
-          <t>A data item about the maximum capacity of an individual's body to transport and use oxygen during incremental exercise, which reflects the physical fitness of the individual.</t>
-        </is>
-      </c>
-      <c r="D154" s="2" t="inlineStr">
-        <is>
-          <t>data item</t>
-        </is>
-      </c>
-      <c r="E154" s="2" t="n"/>
-      <c r="F154" s="2" t="n"/>
-      <c r="G154" s="2" t="n"/>
-      <c r="H154" s="2" t="n"/>
-      <c r="I154" s="2" t="n"/>
-      <c r="J154" s="2" t="n"/>
-      <c r="K154" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Based on http://purl.obolibrary.org/obo/ERO_0001819
-</t>
-        </is>
-      </c>
-      <c r="L154" s="2" t="inlineStr">
-        <is>
-          <t>http://purl.obolibrary.org/obo/ERO_0001819</t>
-        </is>
-      </c>
-      <c r="M154" s="2" t="n"/>
-      <c r="N154" s="2" t="n"/>
-      <c r="O154" s="2" t="n"/>
-      <c r="P154" s="2" t="n"/>
-      <c r="Q154" s="2" t="inlineStr">
-        <is>
-          <t>LSR 2</t>
-        </is>
-      </c>
-      <c r="R154" s="2" t="inlineStr">
-        <is>
-          <t>Intervention outcomes and spillover effects</t>
-        </is>
-      </c>
-      <c r="S154" s="2" t="n"/>
-      <c r="T154" s="2" t="inlineStr">
-        <is>
-          <t>Obsolete</t>
-        </is>
-      </c>
-      <c r="U154" s="2" t="n"/>
-      <c r="V154" s="2" t="n"/>
-      <c r="W154" s="2" t="inlineStr">
-        <is>
-          <t>PS; MS</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" s="3" t="inlineStr">
-        <is>
-          <t>GMHO:0000185</t>
-        </is>
-      </c>
-      <c r="B155" s="3" t="inlineStr">
-        <is>
-          <t>vomiting following intervention</t>
-        </is>
-      </c>
-      <c r="C155" s="3" t="inlineStr">
-        <is>
-          <t>A digestive system adverse event following intervention that has an outcome of vomiting, the retrograde expulsion of gastric contents through the oral cavity.</t>
-        </is>
-      </c>
-      <c r="D155" s="3" t="inlineStr">
-        <is>
-          <t>digestive system adverse event following intervention</t>
-        </is>
-      </c>
-      <c r="E155" s="3" t="n"/>
-      <c r="F155" s="3" t="n"/>
-      <c r="G155" s="3" t="n"/>
-      <c r="H155" s="3" t="n"/>
-      <c r="I155" s="3" t="n"/>
-      <c r="J155" s="3" t="n"/>
-      <c r="K155" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">cross reference: http://purl.obolibrary.org/obo/OAE_0000601
-</t>
-        </is>
-      </c>
-      <c r="L155" s="3" t="inlineStr">
-        <is>
-          <t>http://purl.obolibrary.org/obo/OAE_0000601</t>
-        </is>
-      </c>
-      <c r="M155" s="3" t="inlineStr">
-        <is>
-          <t>vomiting</t>
-        </is>
-      </c>
-      <c r="N155" s="3" t="n"/>
-      <c r="O155" s="3" t="n"/>
-      <c r="P155" s="3" t="n"/>
-      <c r="Q155" s="3" t="inlineStr">
-        <is>
-          <t>LSR 1</t>
-        </is>
-      </c>
-      <c r="R155" s="3" t="inlineStr">
-        <is>
-          <t>Intervention outcomes and spillover effects</t>
-        </is>
-      </c>
-      <c r="S155" s="3" t="n"/>
-      <c r="T155" s="3" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="U155" s="3" t="n"/>
-      <c r="V155" s="3" t="n"/>
-      <c r="W155" s="3" t="inlineStr">
-        <is>
-          <t>PS; MS</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>PATO:0000128</t>
-        </is>
-      </c>
-      <c r="B156" t="inlineStr">
-        <is>
-          <t>weight</t>
-        </is>
-      </c>
-      <c r="C156" t="inlineStr">
-        <is>
-          <t>A physical quality inhering in a bearer that has mass near a gravitational body.</t>
-        </is>
-      </c>
-      <c r="D156" t="inlineStr">
-        <is>
-          <t>force</t>
-        </is>
-      </c>
-      <c r="J156" t="inlineStr">
-        <is>
-          <t>Intervention outcomes and spillover effects</t>
-        </is>
-      </c>
-      <c r="Q156" t="inlineStr">
-        <is>
-          <t>LSR 3</t>
-        </is>
-      </c>
-      <c r="R156" t="inlineStr">
-        <is>
-          <t>Intervention outcomes and spillover effects</t>
-        </is>
-      </c>
-      <c r="T156" t="inlineStr">
-        <is>
-          <t>External</t>
-        </is>
-      </c>
-      <c r="W156" t="inlineStr">
+      <c r="U156" s="2" t="n"/>
+      <c r="V156" s="2" t="n"/>
+      <c r="W156" s="2" t="inlineStr">
         <is>
           <t>PS</t>
         </is>
@@ -9716,22 +9706,22 @@
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>GMHO:0000230</t>
+          <t>GMHO:0000175</t>
         </is>
       </c>
       <c r="B157" s="2" t="inlineStr">
         <is>
-          <t>weight scale</t>
+          <t>validity of measurement scale</t>
         </is>
       </c>
       <c r="C157" s="2" t="inlineStr">
         <is>
-          <t>A measurement scale that is used to measure weight.</t>
+          <t>An attribute of a measurement scale that involves the degree to which the outcomes from the scale represent the intended variable or variables.</t>
         </is>
       </c>
       <c r="D157" s="2" t="inlineStr">
         <is>
-          <t>measurement scale</t>
+          <t>specifically dependent continuant</t>
         </is>
       </c>
       <c r="E157" s="2" t="n"/>
@@ -9739,12 +9729,12 @@
       <c r="G157" s="2" t="n"/>
       <c r="H157" s="2" t="n"/>
       <c r="I157" s="2" t="n"/>
-      <c r="J157" s="2" t="inlineStr">
-        <is>
-          <t>Intervention outcomes and spillover effects</t>
-        </is>
-      </c>
-      <c r="K157" s="2" t="n"/>
+      <c r="J157" s="2" t="n"/>
+      <c r="K157" s="2" t="inlineStr">
+        <is>
+          <t>Based on Price, P. (2015). Research methods in psychology, 2nd Canadian Edition. BCcampus.</t>
+        </is>
+      </c>
       <c r="L157" s="2" t="n"/>
       <c r="M157" s="2" t="n"/>
       <c r="N157" s="2" t="n"/>
@@ -9752,7 +9742,7 @@
       <c r="P157" s="2" t="n"/>
       <c r="Q157" s="2" t="inlineStr">
         <is>
-          <t>LSR 3</t>
+          <t>LSR 2</t>
         </is>
       </c>
       <c r="R157" s="2" t="inlineStr">
@@ -9769,6 +9759,250 @@
       <c r="U157" s="2" t="n"/>
       <c r="V157" s="2" t="n"/>
       <c r="W157" s="2" t="inlineStr">
+        <is>
+          <t>PS</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
+        <is>
+          <t>GMHO:0000140</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>vo2 max</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>A data item about the maximum capacity of an individual's body to transport and use oxygen during incremental exercise, which reflects the physical fitness of the individual.</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr">
+        <is>
+          <t>data item</t>
+        </is>
+      </c>
+      <c r="E158" s="2" t="n"/>
+      <c r="F158" s="2" t="n"/>
+      <c r="G158" s="2" t="n"/>
+      <c r="H158" s="2" t="n"/>
+      <c r="I158" s="2" t="n"/>
+      <c r="J158" s="2" t="n"/>
+      <c r="K158" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Based on http://purl.obolibrary.org/obo/ERO_0001819
+</t>
+        </is>
+      </c>
+      <c r="L158" s="2" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/ERO_0001819</t>
+        </is>
+      </c>
+      <c r="M158" s="2" t="n"/>
+      <c r="N158" s="2" t="n"/>
+      <c r="O158" s="2" t="n"/>
+      <c r="P158" s="2" t="n"/>
+      <c r="Q158" s="2" t="inlineStr">
+        <is>
+          <t>LSR 2</t>
+        </is>
+      </c>
+      <c r="R158" s="2" t="inlineStr">
+        <is>
+          <t>Intervention outcomes and spillover effects</t>
+        </is>
+      </c>
+      <c r="S158" s="2" t="n"/>
+      <c r="T158" s="2" t="inlineStr">
+        <is>
+          <t>Obsolete</t>
+        </is>
+      </c>
+      <c r="U158" s="2" t="n"/>
+      <c r="V158" s="2" t="n"/>
+      <c r="W158" s="2" t="inlineStr">
+        <is>
+          <t>PS; MS</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="3" t="inlineStr">
+        <is>
+          <t>GMHO:0000185</t>
+        </is>
+      </c>
+      <c r="B159" s="3" t="inlineStr">
+        <is>
+          <t>vomiting following intervention</t>
+        </is>
+      </c>
+      <c r="C159" s="3" t="inlineStr">
+        <is>
+          <t>A digestive system adverse event following intervention that has an outcome of vomiting, the retrograde expulsion of gastric contents through the oral cavity.</t>
+        </is>
+      </c>
+      <c r="D159" s="3" t="inlineStr">
+        <is>
+          <t>digestive system adverse event following intervention</t>
+        </is>
+      </c>
+      <c r="E159" s="3" t="n"/>
+      <c r="F159" s="3" t="n"/>
+      <c r="G159" s="3" t="n"/>
+      <c r="H159" s="3" t="n"/>
+      <c r="I159" s="3" t="n"/>
+      <c r="J159" s="3" t="n"/>
+      <c r="K159" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cross reference: http://purl.obolibrary.org/obo/OAE_0000601
+</t>
+        </is>
+      </c>
+      <c r="L159" s="3" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/OAE_0000601</t>
+        </is>
+      </c>
+      <c r="M159" s="3" t="inlineStr">
+        <is>
+          <t>vomiting</t>
+        </is>
+      </c>
+      <c r="N159" s="3" t="n"/>
+      <c r="O159" s="3" t="n"/>
+      <c r="P159" s="3" t="n"/>
+      <c r="Q159" s="3" t="inlineStr">
+        <is>
+          <t>LSR 1</t>
+        </is>
+      </c>
+      <c r="R159" s="3" t="inlineStr">
+        <is>
+          <t>Intervention outcomes and spillover effects</t>
+        </is>
+      </c>
+      <c r="S159" s="3" t="n"/>
+      <c r="T159" s="3" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="U159" s="3" t="n"/>
+      <c r="V159" s="3" t="n"/>
+      <c r="W159" s="3" t="inlineStr">
+        <is>
+          <t>PS; MS</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>PATO:0000128</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>weight</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>A physical quality inhering in a bearer that has mass near a gravitational body.</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>force</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>Intervention outcomes and spillover effects</t>
+        </is>
+      </c>
+      <c r="Q160" t="inlineStr">
+        <is>
+          <t>LSR 3</t>
+        </is>
+      </c>
+      <c r="R160" t="inlineStr">
+        <is>
+          <t>Intervention outcomes and spillover effects</t>
+        </is>
+      </c>
+      <c r="T160" t="inlineStr">
+        <is>
+          <t>External</t>
+        </is>
+      </c>
+      <c r="W160" t="inlineStr">
+        <is>
+          <t>PS</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="inlineStr">
+        <is>
+          <t>GMHO:0000230</t>
+        </is>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
+          <t>weight scale</t>
+        </is>
+      </c>
+      <c r="C161" s="2" t="inlineStr">
+        <is>
+          <t>A measurement scale that is used to measure weight.</t>
+        </is>
+      </c>
+      <c r="D161" s="2" t="inlineStr">
+        <is>
+          <t>measurement scale</t>
+        </is>
+      </c>
+      <c r="E161" s="2" t="n"/>
+      <c r="F161" s="2" t="n"/>
+      <c r="G161" s="2" t="n"/>
+      <c r="H161" s="2" t="n"/>
+      <c r="I161" s="2" t="n"/>
+      <c r="J161" s="2" t="inlineStr">
+        <is>
+          <t>Intervention outcomes and spillover effects</t>
+        </is>
+      </c>
+      <c r="K161" s="2" t="n"/>
+      <c r="L161" s="2" t="n"/>
+      <c r="M161" s="2" t="n"/>
+      <c r="N161" s="2" t="n"/>
+      <c r="O161" s="2" t="n"/>
+      <c r="P161" s="2" t="n"/>
+      <c r="Q161" s="2" t="inlineStr">
+        <is>
+          <t>LSR 3</t>
+        </is>
+      </c>
+      <c r="R161" s="2" t="inlineStr">
+        <is>
+          <t>Intervention outcomes and spillover effects</t>
+        </is>
+      </c>
+      <c r="S161" s="2" t="n"/>
+      <c r="T161" s="2" t="inlineStr">
+        <is>
+          <t>Obsolete</t>
+        </is>
+      </c>
+      <c r="U161" s="2" t="n"/>
+      <c r="V161" s="2" t="n"/>
+      <c r="W161" s="2" t="inlineStr">
         <is>
           <t>PS</t>
         </is>

--- a/Intervention outcomes and spillover effects/Intervention outcomes and spillover effects.xlsx
+++ b/Intervention outcomes and spillover effects/Intervention outcomes and spillover effects.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W161"/>
+  <dimension ref="A1:W162"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4097,22 +4097,22 @@
           <t>measurement scale</t>
         </is>
       </c>
-      <c r="E58" s="4" t="inlineStr"/>
-      <c r="F58" s="4" t="inlineStr"/>
-      <c r="G58" s="4" t="inlineStr"/>
-      <c r="H58" s="4" t="inlineStr"/>
-      <c r="I58" s="4" t="inlineStr"/>
+      <c r="E58" s="4" t="n"/>
+      <c r="F58" s="4" t="n"/>
+      <c r="G58" s="4" t="n"/>
+      <c r="H58" s="4" t="n"/>
+      <c r="I58" s="4" t="n"/>
       <c r="J58" s="4" t="inlineStr">
         <is>
           <t>Intervention outcomes and spillover effects</t>
         </is>
       </c>
-      <c r="K58" s="4" t="inlineStr"/>
-      <c r="L58" s="4" t="inlineStr"/>
-      <c r="M58" s="4" t="inlineStr"/>
-      <c r="N58" s="4" t="inlineStr"/>
-      <c r="O58" s="4" t="inlineStr"/>
-      <c r="P58" s="4" t="inlineStr"/>
+      <c r="K58" s="4" t="n"/>
+      <c r="L58" s="4" t="n"/>
+      <c r="M58" s="4" t="n"/>
+      <c r="N58" s="4" t="n"/>
+      <c r="O58" s="4" t="n"/>
+      <c r="P58" s="4" t="n"/>
       <c r="Q58" s="4" t="inlineStr">
         <is>
           <t>LSR 6</t>
@@ -4123,15 +4123,15 @@
           <t>Intervention outcomes and spillover effects</t>
         </is>
       </c>
-      <c r="S58" s="4" t="inlineStr"/>
+      <c r="S58" s="4" t="n"/>
       <c r="T58" s="4" t="inlineStr">
         <is>
           <t>Proposed</t>
         </is>
       </c>
-      <c r="U58" s="4" t="inlineStr"/>
-      <c r="V58" s="4" t="inlineStr"/>
-      <c r="W58" s="4" t="inlineStr"/>
+      <c r="U58" s="4" t="n"/>
+      <c r="V58" s="4" t="n"/>
+      <c r="W58" s="4" t="n"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -4254,32 +4254,39 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>MF:0000032</t>
+          <t>CMO:0001822</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>bodily disposition</t>
+          <t>blood prolactin level</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>A bodily disposition is a disposition that inheres in some extended organism.</t>
+          <t>The amount of prolactin found in a specified volume of blood, the fluid that circulates through the heart, arteries, capillaries and veins carrying nutrients and oxygen to the body tissues and metabolites away from them. Prolactin is a peptide hormone which is secreted by the anterior pituitary and is involved in lactation, growth regulation for tissues including cells of the immune system, and possibly supression of apoptosis. A peptide hormone is a complex organic compound that contains carbon, hydrogen, oxygen, nitrogen, and sulfur consisting of alpha-amino acids joined by peptide linkages, and that is produced in one part or organ of the body and initiates or regulates the activity of an organ or a group of cells in another part of the body.</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>disposition</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>Intervention outcomes and spillover effects</t>
-        </is>
-      </c>
+          <t>blood peptide hormone level</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr"/>
+      <c r="F61" t="inlineStr"/>
+      <c r="G61" t="inlineStr"/>
+      <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
+      <c r="O61" t="inlineStr"/>
+      <c r="P61" t="inlineStr"/>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>LSR 1</t>
+          <t>LSR 3</t>
         </is>
       </c>
       <c r="R61" t="inlineStr">
@@ -4287,124 +4294,109 @@
           <t>Intervention outcomes and spillover effects</t>
         </is>
       </c>
+      <c r="S61" t="inlineStr"/>
       <c r="T61" t="inlineStr">
         <is>
           <t>External</t>
         </is>
       </c>
-      <c r="W61" t="inlineStr">
-        <is>
-          <t>PS</t>
-        </is>
-      </c>
+      <c r="U61" t="inlineStr"/>
+      <c r="V61" t="inlineStr"/>
+      <c r="W61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
+          <t>MF:0000032</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>bodily disposition</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>A bodily disposition is a disposition that inheres in some extended organism.</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>disposition</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>Intervention outcomes and spillover effects</t>
+        </is>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>LSR 1</t>
+        </is>
+      </c>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t>Intervention outcomes and spillover effects</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>External</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>PS</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
           <t>OGMS:0000060</t>
         </is>
       </c>
-      <c r="B62" t="inlineStr">
+      <c r="B63" t="inlineStr">
         <is>
           <t>bodily process</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr">
+      <c r="C63" t="inlineStr">
         <is>
           <t>A process in which at least one bodily component of an organism participates.</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr">
+      <c r="D63" t="inlineStr">
         <is>
           <t>process</t>
         </is>
       </c>
-      <c r="T62" t="inlineStr">
+      <c r="T63" t="inlineStr">
         <is>
           <t>External</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr">
-        <is>
-          <t>GMHO:0000056</t>
-        </is>
-      </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>body mass index</t>
-        </is>
-      </c>
-      <c r="C63" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">A data item that is derived by dividing the body weight be the square of the body height. </t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="inlineStr">
-        <is>
-          <t>data item</t>
-        </is>
-      </c>
-      <c r="E63" s="2" t="n"/>
-      <c r="F63" s="2" t="n"/>
-      <c r="G63" s="2" t="n"/>
-      <c r="H63" s="2" t="n"/>
-      <c r="I63" s="2" t="n"/>
-      <c r="J63" s="2" t="n"/>
-      <c r="K63" s="2" t="inlineStr">
-        <is>
-          <t>Based on Nuttall F. Q. (2015). Body Mass Index: Obesity, BMI, and Health: A Critical Review. Nutrition today, 50(3), 117–128. https://doi.org/10.1097/NT.0000000000000092</t>
-        </is>
-      </c>
-      <c r="L63" s="2" t="n"/>
-      <c r="M63" s="2" t="n"/>
-      <c r="N63" s="2" t="n"/>
-      <c r="O63" s="2" t="n"/>
-      <c r="P63" s="2" t="n"/>
-      <c r="Q63" s="2" t="inlineStr">
-        <is>
-          <t>LSR 3</t>
-        </is>
-      </c>
-      <c r="R63" s="2" t="inlineStr">
-        <is>
-          <t>Intervention outcomes and spillover effects</t>
-        </is>
-      </c>
-      <c r="S63" s="2" t="n"/>
-      <c r="T63" s="2" t="inlineStr">
-        <is>
-          <t>Obsolete</t>
-        </is>
-      </c>
-      <c r="U63" s="2" t="n"/>
-      <c r="V63" s="2" t="n"/>
-      <c r="W63" s="2" t="inlineStr">
-        <is>
-          <t>PS</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>GMHO:0000057</t>
+          <t>GMHO:0000056</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>body weight</t>
+          <t>body mass index</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Weight of an organism.</t>
+          <t xml:space="preserve">A data item that is derived by dividing the body weight be the square of the body height. </t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>weight</t>
+          <t>data item</t>
         </is>
       </c>
       <c r="E64" s="2" t="n"/>
@@ -4413,7 +4405,11 @@
       <c r="H64" s="2" t="n"/>
       <c r="I64" s="2" t="n"/>
       <c r="J64" s="2" t="n"/>
-      <c r="K64" s="2" t="n"/>
+      <c r="K64" s="2" t="inlineStr">
+        <is>
+          <t>Based on Nuttall F. Q. (2015). Body Mass Index: Obesity, BMI, and Health: A Critical Review. Nutrition today, 50(3), 117–128. https://doi.org/10.1097/NT.0000000000000092</t>
+        </is>
+      </c>
       <c r="L64" s="2" t="n"/>
       <c r="M64" s="2" t="n"/>
       <c r="N64" s="2" t="n"/>
@@ -4436,314 +4432,314 @@
         </is>
       </c>
       <c r="U64" s="2" t="n"/>
-      <c r="V64" s="2" t="inlineStr">
+      <c r="V64" s="2" t="n"/>
+      <c r="W64" s="2" t="inlineStr">
+        <is>
+          <t>PS</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>GMHO:0000057</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>body weight</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>Weight of an organism.</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>weight</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="n"/>
+      <c r="F65" s="2" t="n"/>
+      <c r="G65" s="2" t="n"/>
+      <c r="H65" s="2" t="n"/>
+      <c r="I65" s="2" t="n"/>
+      <c r="J65" s="2" t="n"/>
+      <c r="K65" s="2" t="n"/>
+      <c r="L65" s="2" t="n"/>
+      <c r="M65" s="2" t="n"/>
+      <c r="N65" s="2" t="n"/>
+      <c r="O65" s="2" t="n"/>
+      <c r="P65" s="2" t="n"/>
+      <c r="Q65" s="2" t="inlineStr">
+        <is>
+          <t>LSR 3</t>
+        </is>
+      </c>
+      <c r="R65" s="2" t="inlineStr">
+        <is>
+          <t>Intervention outcomes and spillover effects</t>
+        </is>
+      </c>
+      <c r="S65" s="2" t="n"/>
+      <c r="T65" s="2" t="inlineStr">
+        <is>
+          <t>Obsolete</t>
+        </is>
+      </c>
+      <c r="U65" s="2" t="n"/>
+      <c r="V65" s="2" t="inlineStr">
         <is>
           <t>Parent class needs to be imported as external entity</t>
         </is>
       </c>
-      <c r="W64" s="2" t="inlineStr">
-        <is>
-          <t>PS</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="4" t="inlineStr">
+      <c r="W65" s="2" t="inlineStr">
+        <is>
+          <t>PS</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="4" t="inlineStr">
         <is>
           <t>GMHO:0000270</t>
         </is>
       </c>
-      <c r="B65" s="4" t="inlineStr">
+      <c r="B66" s="4" t="inlineStr">
         <is>
           <t>cognitive bias scale</t>
         </is>
       </c>
-      <c r="C65" s="4" t="inlineStr">
+      <c r="C66" s="4" t="inlineStr">
         <is>
           <t>A measurement scale that is used to measure a cognitive bias.</t>
         </is>
       </c>
-      <c r="D65" s="4" t="inlineStr">
+      <c r="D66" s="4" t="inlineStr">
         <is>
           <t>measurement scale</t>
         </is>
       </c>
-      <c r="E65" s="4" t="inlineStr"/>
-      <c r="F65" s="4" t="inlineStr"/>
-      <c r="G65" s="4" t="inlineStr"/>
-      <c r="H65" s="4" t="inlineStr"/>
-      <c r="I65" s="4" t="inlineStr"/>
-      <c r="J65" s="4" t="inlineStr">
-        <is>
-          <t>Intervention outcomes and spillover effects</t>
-        </is>
-      </c>
-      <c r="K65" s="4" t="inlineStr"/>
-      <c r="L65" s="4" t="inlineStr"/>
-      <c r="M65" s="4" t="inlineStr"/>
-      <c r="N65" s="4" t="inlineStr"/>
-      <c r="O65" s="4" t="inlineStr"/>
-      <c r="P65" s="4" t="inlineStr"/>
-      <c r="Q65" s="4" t="inlineStr">
+      <c r="E66" s="4" t="n"/>
+      <c r="F66" s="4" t="n"/>
+      <c r="G66" s="4" t="n"/>
+      <c r="H66" s="4" t="n"/>
+      <c r="I66" s="4" t="n"/>
+      <c r="J66" s="4" t="inlineStr">
+        <is>
+          <t>Intervention outcomes and spillover effects</t>
+        </is>
+      </c>
+      <c r="K66" s="4" t="n"/>
+      <c r="L66" s="4" t="n"/>
+      <c r="M66" s="4" t="n"/>
+      <c r="N66" s="4" t="n"/>
+      <c r="O66" s="4" t="n"/>
+      <c r="P66" s="4" t="n"/>
+      <c r="Q66" s="4" t="inlineStr">
         <is>
           <t>LSR 6</t>
         </is>
       </c>
-      <c r="R65" s="4" t="inlineStr">
-        <is>
-          <t>Intervention outcomes and spillover effects</t>
-        </is>
-      </c>
-      <c r="S65" s="4" t="inlineStr"/>
-      <c r="T65" s="4" t="inlineStr">
+      <c r="R66" s="4" t="inlineStr">
+        <is>
+          <t>Intervention outcomes and spillover effects</t>
+        </is>
+      </c>
+      <c r="S66" s="4" t="n"/>
+      <c r="T66" s="4" t="inlineStr">
         <is>
           <t>Proposed</t>
         </is>
       </c>
-      <c r="U65" s="4" t="inlineStr"/>
-      <c r="V65" s="4" t="inlineStr"/>
-      <c r="W65" s="4" t="inlineStr"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="3" t="inlineStr">
+      <c r="U66" s="4" t="n"/>
+      <c r="V66" s="4" t="n"/>
+      <c r="W66" s="4" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="3" t="inlineStr">
         <is>
           <t>GMHO:0000257</t>
         </is>
       </c>
-      <c r="B66" s="3" t="inlineStr">
+      <c r="B67" s="3" t="inlineStr">
         <is>
           <t>constipation adverse event following intervention</t>
         </is>
       </c>
-      <c r="C66" s="3" t="inlineStr">
+      <c r="C67" s="3" t="inlineStr">
         <is>
           <t>A digestive system adverse event following an intervention that involves the abnormally delayed or infrequent passage of dry hardened feces.</t>
         </is>
       </c>
-      <c r="D66" s="3" t="inlineStr">
+      <c r="D67" s="3" t="inlineStr">
         <is>
           <t>digestive system adverse event following intervention</t>
         </is>
       </c>
-      <c r="E66" s="3" t="n"/>
-      <c r="F66" s="3" t="n"/>
-      <c r="G66" s="3" t="n"/>
-      <c r="H66" s="3" t="n"/>
-      <c r="I66" s="3" t="n"/>
-      <c r="J66" s="3" t="inlineStr">
-        <is>
-          <t>Intervention outcomes and spillover effects</t>
-        </is>
-      </c>
-      <c r="K66" s="3" t="inlineStr">
+      <c r="E67" s="3" t="n"/>
+      <c r="F67" s="3" t="n"/>
+      <c r="G67" s="3" t="n"/>
+      <c r="H67" s="3" t="n"/>
+      <c r="I67" s="3" t="n"/>
+      <c r="J67" s="3" t="inlineStr">
+        <is>
+          <t>Intervention outcomes and spillover effects</t>
+        </is>
+      </c>
+      <c r="K67" s="3" t="inlineStr">
         <is>
           <t>http://purl.obolibrary.org/obo/SYMP_0019180</t>
         </is>
       </c>
-      <c r="L66" s="3" t="inlineStr">
+      <c r="L67" s="3" t="inlineStr">
         <is>
           <t>SYMP:0019180</t>
         </is>
       </c>
-      <c r="M66" s="3" t="inlineStr">
+      <c r="M67" s="3" t="inlineStr">
         <is>
           <t>constipation</t>
         </is>
       </c>
-      <c r="N66" s="3" t="n"/>
-      <c r="O66" s="3" t="n"/>
-      <c r="P66" s="3" t="n"/>
-      <c r="Q66" s="3" t="inlineStr">
+      <c r="N67" s="3" t="n"/>
+      <c r="O67" s="3" t="n"/>
+      <c r="P67" s="3" t="n"/>
+      <c r="Q67" s="3" t="inlineStr">
         <is>
           <t>LSR 1</t>
         </is>
       </c>
-      <c r="R66" s="3" t="inlineStr">
-        <is>
-          <t>Intervention outcomes and spillover effects</t>
-        </is>
-      </c>
-      <c r="S66" s="3" t="n"/>
-      <c r="T66" s="3" t="inlineStr">
+      <c r="R67" s="3" t="inlineStr">
+        <is>
+          <t>Intervention outcomes and spillover effects</t>
+        </is>
+      </c>
+      <c r="S67" s="3" t="n"/>
+      <c r="T67" s="3" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="U66" s="3" t="n"/>
-      <c r="V66" s="3" t="n"/>
-      <c r="W66" s="3" t="n"/>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
+      <c r="U67" s="3" t="n"/>
+      <c r="V67" s="3" t="n"/>
+      <c r="W67" s="3" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
         <is>
           <t>IAO:0000027</t>
         </is>
       </c>
-      <c r="B67" t="inlineStr">
+      <c r="B68" t="inlineStr">
         <is>
           <t>data item</t>
         </is>
       </c>
-      <c r="C67" t="inlineStr">
+      <c r="C68" t="inlineStr">
         <is>
           <t>An information content entity that is intended to be a truthful statement about something (modulo, e.g., measurement precision or other systematic errors) and is constructed/acquired by a method which reliably tends to produce (approximately) truthful statements.</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr">
+      <c r="D68" t="inlineStr">
         <is>
           <t>information content entity</t>
         </is>
       </c>
-      <c r="J67" t="inlineStr">
-        <is>
-          <t>Intervention outcomes and spillover effects</t>
-        </is>
-      </c>
-      <c r="Q67" t="inlineStr">
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>Intervention outcomes and spillover effects</t>
+        </is>
+      </c>
+      <c r="Q68" t="inlineStr">
         <is>
           <t>LSR 1</t>
         </is>
       </c>
-      <c r="R67" t="inlineStr">
-        <is>
-          <t>Intervention outcomes and spillover effects</t>
-        </is>
-      </c>
-      <c r="T67" t="inlineStr">
+      <c r="R68" t="inlineStr">
+        <is>
+          <t>Intervention outcomes and spillover effects</t>
+        </is>
+      </c>
+      <c r="T68" t="inlineStr">
         <is>
           <t>External</t>
         </is>
       </c>
-      <c r="W67" t="inlineStr">
-        <is>
-          <t>PS</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="3" t="inlineStr">
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>PS</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="3" t="inlineStr">
         <is>
           <t>GMHO:0000256</t>
         </is>
       </c>
-      <c r="B68" s="3" t="inlineStr">
+      <c r="B69" s="3" t="inlineStr">
         <is>
           <t>datatype for outcome</t>
         </is>
       </c>
-      <c r="C68" s="3" t="inlineStr">
+      <c r="C69" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">A directive information entity that indicates how outcomes of an intervention were obtained. </t>
         </is>
       </c>
-      <c r="D68" s="3" t="inlineStr">
+      <c r="D69" s="3" t="inlineStr">
         <is>
           <t>directive information entity</t>
         </is>
       </c>
-      <c r="E68" s="3" t="n"/>
-      <c r="F68" s="3" t="n"/>
-      <c r="G68" s="3" t="n"/>
-      <c r="H68" s="3" t="n"/>
-      <c r="I68" s="3" t="n"/>
-      <c r="J68" s="3" t="inlineStr">
-        <is>
-          <t>Intervention outcomes and spillover effects</t>
-        </is>
-      </c>
-      <c r="K68" s="3" t="n"/>
-      <c r="L68" s="3" t="n"/>
-      <c r="M68" s="3" t="n"/>
-      <c r="N68" s="3" t="n"/>
-      <c r="O68" s="3" t="n"/>
-      <c r="P68" s="3" t="n"/>
-      <c r="Q68" s="3" t="inlineStr">
+      <c r="E69" s="3" t="n"/>
+      <c r="F69" s="3" t="n"/>
+      <c r="G69" s="3" t="n"/>
+      <c r="H69" s="3" t="n"/>
+      <c r="I69" s="3" t="n"/>
+      <c r="J69" s="3" t="inlineStr">
+        <is>
+          <t>Intervention outcomes and spillover effects</t>
+        </is>
+      </c>
+      <c r="K69" s="3" t="n"/>
+      <c r="L69" s="3" t="n"/>
+      <c r="M69" s="3" t="n"/>
+      <c r="N69" s="3" t="n"/>
+      <c r="O69" s="3" t="n"/>
+      <c r="P69" s="3" t="n"/>
+      <c r="Q69" s="3" t="inlineStr">
         <is>
           <t>LSR 3</t>
         </is>
       </c>
-      <c r="R68" s="3" t="n"/>
-      <c r="S68" s="3" t="n"/>
-      <c r="T68" s="3" t="inlineStr">
+      <c r="R69" s="3" t="n"/>
+      <c r="S69" s="3" t="n"/>
+      <c r="T69" s="3" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="U68" s="3" t="n"/>
-      <c r="V68" s="3" t="n"/>
-      <c r="W68" s="3" t="n"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr">
-        <is>
-          <t>GMHO:0000058</t>
-        </is>
-      </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>death due to accidents following an intervention</t>
-        </is>
-      </c>
-      <c r="C69" s="2" t="inlineStr">
-        <is>
-          <t>A death following an intervention that involves a participant dying as a result of an accident.</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="inlineStr">
-        <is>
-          <t>death following an intervention</t>
-        </is>
-      </c>
-      <c r="E69" s="2" t="n"/>
-      <c r="F69" s="2" t="n"/>
-      <c r="G69" s="2" t="n"/>
-      <c r="H69" s="2" t="n"/>
-      <c r="I69" s="2" t="n"/>
-      <c r="J69" s="2" t="n"/>
-      <c r="K69" s="2" t="n"/>
-      <c r="L69" s="2" t="n"/>
-      <c r="M69" s="2" t="n"/>
-      <c r="N69" s="2" t="n"/>
-      <c r="O69" s="2" t="n"/>
-      <c r="P69" s="2" t="n"/>
-      <c r="Q69" s="2" t="inlineStr">
-        <is>
-          <t>LSR 3</t>
-        </is>
-      </c>
-      <c r="R69" s="2" t="inlineStr">
-        <is>
-          <t>Intervention outcomes and spillover effects</t>
-        </is>
-      </c>
-      <c r="S69" s="2" t="n"/>
-      <c r="T69" s="2" t="inlineStr">
-        <is>
-          <t>Obsolete</t>
-        </is>
-      </c>
-      <c r="U69" s="2" t="n"/>
-      <c r="V69" s="2" t="n"/>
-      <c r="W69" s="2" t="inlineStr">
-        <is>
-          <t>PS</t>
-        </is>
-      </c>
+      <c r="U69" s="3" t="n"/>
+      <c r="V69" s="3" t="n"/>
+      <c r="W69" s="3" t="n"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>GMHO:0000059</t>
+          <t>GMHO:0000058</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>death due to natural causes following an intervention</t>
+          <t>death due to accidents following an intervention</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>A death following an intervention that results from an illness or its complications or an internal bodily malfunction that is not directly caused by external events.</t>
+          <t>A death following an intervention that involves a participant dying as a result of an accident.</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
@@ -4757,11 +4753,7 @@
       <c r="H70" s="2" t="n"/>
       <c r="I70" s="2" t="n"/>
       <c r="J70" s="2" t="n"/>
-      <c r="K70" s="2" t="inlineStr">
-        <is>
-          <t>Based on https://en.wikipedia.org/wiki/Manner_of_death</t>
-        </is>
-      </c>
+      <c r="K70" s="2" t="n"/>
       <c r="L70" s="2" t="n"/>
       <c r="M70" s="2" t="n"/>
       <c r="N70" s="2" t="n"/>
@@ -4792,187 +4784,191 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="3" t="inlineStr">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>GMHO:0000059</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>death due to natural causes following an intervention</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>A death following an intervention that results from an illness or its complications or an internal bodily malfunction that is not directly caused by external events.</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>death following an intervention</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="n"/>
+      <c r="F71" s="2" t="n"/>
+      <c r="G71" s="2" t="n"/>
+      <c r="H71" s="2" t="n"/>
+      <c r="I71" s="2" t="n"/>
+      <c r="J71" s="2" t="n"/>
+      <c r="K71" s="2" t="inlineStr">
+        <is>
+          <t>Based on https://en.wikipedia.org/wiki/Manner_of_death</t>
+        </is>
+      </c>
+      <c r="L71" s="2" t="n"/>
+      <c r="M71" s="2" t="n"/>
+      <c r="N71" s="2" t="n"/>
+      <c r="O71" s="2" t="n"/>
+      <c r="P71" s="2" t="n"/>
+      <c r="Q71" s="2" t="inlineStr">
+        <is>
+          <t>LSR 3</t>
+        </is>
+      </c>
+      <c r="R71" s="2" t="inlineStr">
+        <is>
+          <t>Intervention outcomes and spillover effects</t>
+        </is>
+      </c>
+      <c r="S71" s="2" t="n"/>
+      <c r="T71" s="2" t="inlineStr">
+        <is>
+          <t>Obsolete</t>
+        </is>
+      </c>
+      <c r="U71" s="2" t="n"/>
+      <c r="V71" s="2" t="n"/>
+      <c r="W71" s="2" t="inlineStr">
+        <is>
+          <t>PS</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="3" t="inlineStr">
         <is>
           <t>GMHO:0000060</t>
         </is>
       </c>
-      <c r="B71" s="3" t="inlineStr">
+      <c r="B72" s="3" t="inlineStr">
         <is>
           <t>death following an intervention</t>
         </is>
       </c>
-      <c r="C71" s="3" t="inlineStr">
+      <c r="C72" s="3" t="inlineStr">
         <is>
           <t>A serious adverse event following an intervention that has an outcome of death.</t>
         </is>
       </c>
-      <c r="D71" s="3" t="inlineStr">
+      <c r="D72" s="3" t="inlineStr">
         <is>
           <t>serious adverse event following an intervention</t>
         </is>
       </c>
-      <c r="E71" s="3" t="n"/>
-      <c r="F71" s="3" t="n"/>
-      <c r="G71" s="3" t="n"/>
-      <c r="H71" s="3" t="n"/>
-      <c r="I71" s="3" t="n"/>
-      <c r="J71" s="3" t="n"/>
-      <c r="K71" s="3" t="inlineStr">
+      <c r="E72" s="3" t="n"/>
+      <c r="F72" s="3" t="n"/>
+      <c r="G72" s="3" t="n"/>
+      <c r="H72" s="3" t="n"/>
+      <c r="I72" s="3" t="n"/>
+      <c r="J72" s="3" t="n"/>
+      <c r="K72" s="3" t="inlineStr">
         <is>
           <t>Based on http://purl.obolibrary.org/obo/OAE_0000632</t>
         </is>
       </c>
-      <c r="L71" s="3" t="inlineStr">
+      <c r="L72" s="3" t="inlineStr">
         <is>
           <t>http://purl.obolibrary.org/obo/OAE_0000632</t>
         </is>
       </c>
-      <c r="M71" s="3" t="inlineStr">
+      <c r="M72" s="3" t="inlineStr">
         <is>
           <t>death</t>
         </is>
       </c>
-      <c r="N71" s="3" t="n"/>
-      <c r="O71" s="3" t="n"/>
-      <c r="P71" s="3" t="n"/>
-      <c r="Q71" s="3" t="inlineStr">
+      <c r="N72" s="3" t="n"/>
+      <c r="O72" s="3" t="n"/>
+      <c r="P72" s="3" t="n"/>
+      <c r="Q72" s="3" t="inlineStr">
         <is>
           <t>LSR 3</t>
         </is>
       </c>
-      <c r="R71" s="3" t="inlineStr">
-        <is>
-          <t>Intervention outcomes and spillover effects</t>
-        </is>
-      </c>
-      <c r="S71" s="3" t="n"/>
-      <c r="T71" s="3" t="inlineStr">
+      <c r="R72" s="3" t="inlineStr">
+        <is>
+          <t>Intervention outcomes and spillover effects</t>
+        </is>
+      </c>
+      <c r="S72" s="3" t="n"/>
+      <c r="T72" s="3" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="U71" s="3" t="n"/>
-      <c r="V71" s="3" t="n"/>
-      <c r="W71" s="3" t="inlineStr">
+      <c r="U72" s="3" t="n"/>
+      <c r="V72" s="3" t="n"/>
+      <c r="W72" s="3" t="inlineStr">
         <is>
           <t>PS; MS</t>
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
         <is>
           <t>GMHO:0000061</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
+      <c r="B73" s="2" t="inlineStr">
         <is>
           <t>depression symptom</t>
         </is>
       </c>
-      <c r="C72" s="2" t="inlineStr">
+      <c r="C73" s="2" t="inlineStr">
         <is>
           <t>A symptom that is related to a depression diagnosis.</t>
         </is>
       </c>
-      <c r="D72" s="2" t="inlineStr">
+      <c r="D73" s="2" t="inlineStr">
         <is>
           <t>symptom</t>
         </is>
       </c>
-      <c r="E72" s="2" t="n"/>
-      <c r="F72" s="2" t="n"/>
-      <c r="G72" s="2" t="inlineStr">
+      <c r="E73" s="2" t="n"/>
+      <c r="F73" s="2" t="n"/>
+      <c r="G73" s="2" t="inlineStr">
         <is>
           <t>depressive symptom</t>
         </is>
       </c>
-      <c r="H72" s="2" t="n"/>
-      <c r="I72" s="2" t="n"/>
-      <c r="J72" s="2" t="n"/>
-      <c r="K72" s="2" t="n"/>
-      <c r="L72" s="2" t="n"/>
-      <c r="M72" s="2" t="n"/>
-      <c r="N72" s="2" t="n"/>
-      <c r="O72" s="2" t="n"/>
-      <c r="P72" s="2" t="n"/>
-      <c r="Q72" s="2" t="inlineStr">
+      <c r="H73" s="2" t="n"/>
+      <c r="I73" s="2" t="n"/>
+      <c r="J73" s="2" t="n"/>
+      <c r="K73" s="2" t="n"/>
+      <c r="L73" s="2" t="n"/>
+      <c r="M73" s="2" t="n"/>
+      <c r="N73" s="2" t="n"/>
+      <c r="O73" s="2" t="n"/>
+      <c r="P73" s="2" t="n"/>
+      <c r="Q73" s="2" t="inlineStr">
         <is>
           <t>LSR 3</t>
         </is>
       </c>
-      <c r="R72" s="2" t="inlineStr">
-        <is>
-          <t>Intervention outcomes and spillover effects</t>
-        </is>
-      </c>
-      <c r="S72" s="2" t="n"/>
-      <c r="T72" s="2" t="inlineStr">
+      <c r="R73" s="2" t="inlineStr">
+        <is>
+          <t>Intervention outcomes and spillover effects</t>
+        </is>
+      </c>
+      <c r="S73" s="2" t="n"/>
+      <c r="T73" s="2" t="inlineStr">
         <is>
           <t>Obsolete</t>
         </is>
       </c>
-      <c r="U72" s="2" t="n"/>
-      <c r="V72" s="2" t="n"/>
-      <c r="W72" s="2" t="inlineStr">
-        <is>
-          <t>PS</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="3" t="inlineStr">
-        <is>
-          <t>GMHO:0000062</t>
-        </is>
-      </c>
-      <c r="B73" s="3" t="inlineStr">
-        <is>
-          <t>depression symptom severity</t>
-        </is>
-      </c>
-      <c r="C73" s="3" t="inlineStr">
-        <is>
-          <t>Symptom severity that is associated with a depression symptom.</t>
-        </is>
-      </c>
-      <c r="D73" s="3" t="inlineStr">
-        <is>
-          <t>symptom severity</t>
-        </is>
-      </c>
-      <c r="E73" s="3" t="n"/>
-      <c r="F73" s="3" t="n"/>
-      <c r="G73" s="3" t="n"/>
-      <c r="H73" s="3" t="n"/>
-      <c r="I73" s="3" t="n"/>
-      <c r="J73" s="3" t="n"/>
-      <c r="K73" s="3" t="n"/>
-      <c r="L73" s="3" t="n"/>
-      <c r="M73" s="3" t="n"/>
-      <c r="N73" s="3" t="n"/>
-      <c r="O73" s="3" t="n"/>
-      <c r="P73" s="3" t="n"/>
-      <c r="Q73" s="3" t="inlineStr">
-        <is>
-          <t>LSR 3</t>
-        </is>
-      </c>
-      <c r="R73" s="3" t="inlineStr">
-        <is>
-          <t>Intervention outcomes and spillover effects</t>
-        </is>
-      </c>
-      <c r="S73" s="3" t="n"/>
-      <c r="T73" s="3" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="U73" s="3" t="n"/>
-      <c r="V73" s="3" t="n"/>
-      <c r="W73" s="3" t="inlineStr">
+      <c r="U73" s="2" t="n"/>
+      <c r="V73" s="2" t="n"/>
+      <c r="W73" s="2" t="inlineStr">
         <is>
           <t>PS</t>
         </is>
@@ -4981,22 +4977,22 @@
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>GMHO:0000223</t>
+          <t>GMHO:0000062</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>depression symptom severity scale</t>
+          <t>depression symptom severity</t>
         </is>
       </c>
       <c r="C74" s="3" t="inlineStr">
         <is>
-          <t>A measurement scale that is used to measure depression symptom severity.</t>
+          <t>Symptom severity that is associated with a depression symptom.</t>
         </is>
       </c>
       <c r="D74" s="3" t="inlineStr">
         <is>
-          <t>measurement scale</t>
+          <t>symptom severity</t>
         </is>
       </c>
       <c r="E74" s="3" t="n"/>
@@ -5004,11 +5000,7 @@
       <c r="G74" s="3" t="n"/>
       <c r="H74" s="3" t="n"/>
       <c r="I74" s="3" t="n"/>
-      <c r="J74" s="3" t="inlineStr">
-        <is>
-          <t>Intervention outcomes and spillover effects</t>
-        </is>
-      </c>
+      <c r="J74" s="3" t="n"/>
       <c r="K74" s="3" t="n"/>
       <c r="L74" s="3" t="n"/>
       <c r="M74" s="3" t="n"/>
@@ -5020,7 +5012,11 @@
           <t>LSR 3</t>
         </is>
       </c>
-      <c r="R74" s="3" t="n"/>
+      <c r="R74" s="3" t="inlineStr">
+        <is>
+          <t>Intervention outcomes and spillover effects</t>
+        </is>
+      </c>
       <c r="S74" s="3" t="n"/>
       <c r="T74" s="3" t="inlineStr">
         <is>
@@ -5038,22 +5034,22 @@
     <row r="75">
       <c r="A75" s="3" t="inlineStr">
         <is>
-          <t>GMHO:0000178</t>
+          <t>GMHO:0000223</t>
         </is>
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>digestive system adverse event following intervention</t>
+          <t>depression symptom severity scale</t>
         </is>
       </c>
       <c r="C75" s="3" t="inlineStr">
         <is>
-          <t>An adverse event following an intervention that occurs in the digestive system.</t>
+          <t>A measurement scale that is used to measure depression symptom severity.</t>
         </is>
       </c>
       <c r="D75" s="3" t="inlineStr">
         <is>
-          <t>adverse event following an intervention</t>
+          <t>measurement scale</t>
         </is>
       </c>
       <c r="E75" s="3" t="n"/>
@@ -5061,36 +5057,23 @@
       <c r="G75" s="3" t="n"/>
       <c r="H75" s="3" t="n"/>
       <c r="I75" s="3" t="n"/>
-      <c r="J75" s="3" t="n"/>
-      <c r="K75" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">cross reference: http://purl.obolibrary.org/obo/OAE_0000439
-</t>
-        </is>
-      </c>
-      <c r="L75" s="3" t="inlineStr">
-        <is>
-          <t>http://purl.obolibrary.org/obo/OAE_0000439</t>
-        </is>
-      </c>
-      <c r="M75" s="3" t="inlineStr">
-        <is>
-          <t>digestive system adverse event</t>
-        </is>
-      </c>
+      <c r="J75" s="3" t="inlineStr">
+        <is>
+          <t>Intervention outcomes and spillover effects</t>
+        </is>
+      </c>
+      <c r="K75" s="3" t="n"/>
+      <c r="L75" s="3" t="n"/>
+      <c r="M75" s="3" t="n"/>
       <c r="N75" s="3" t="n"/>
       <c r="O75" s="3" t="n"/>
       <c r="P75" s="3" t="n"/>
       <c r="Q75" s="3" t="inlineStr">
         <is>
-          <t>LSR 1</t>
-        </is>
-      </c>
-      <c r="R75" s="3" t="inlineStr">
-        <is>
-          <t>Intervention outcomes and spillover effects</t>
-        </is>
-      </c>
+          <t>LSR 3</t>
+        </is>
+      </c>
+      <c r="R75" s="3" t="n"/>
       <c r="S75" s="3" t="n"/>
       <c r="T75" s="3" t="inlineStr">
         <is>
@@ -5101,121 +5084,121 @@
       <c r="V75" s="3" t="n"/>
       <c r="W75" s="3" t="inlineStr">
         <is>
+          <t>PS</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="3" t="inlineStr">
+        <is>
+          <t>GMHO:0000178</t>
+        </is>
+      </c>
+      <c r="B76" s="3" t="inlineStr">
+        <is>
+          <t>digestive system adverse event following intervention</t>
+        </is>
+      </c>
+      <c r="C76" s="3" t="inlineStr">
+        <is>
+          <t>An adverse event following an intervention that occurs in the digestive system.</t>
+        </is>
+      </c>
+      <c r="D76" s="3" t="inlineStr">
+        <is>
+          <t>adverse event following an intervention</t>
+        </is>
+      </c>
+      <c r="E76" s="3" t="n"/>
+      <c r="F76" s="3" t="n"/>
+      <c r="G76" s="3" t="n"/>
+      <c r="H76" s="3" t="n"/>
+      <c r="I76" s="3" t="n"/>
+      <c r="J76" s="3" t="n"/>
+      <c r="K76" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cross reference: http://purl.obolibrary.org/obo/OAE_0000439
+</t>
+        </is>
+      </c>
+      <c r="L76" s="3" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/OAE_0000439</t>
+        </is>
+      </c>
+      <c r="M76" s="3" t="inlineStr">
+        <is>
+          <t>digestive system adverse event</t>
+        </is>
+      </c>
+      <c r="N76" s="3" t="n"/>
+      <c r="O76" s="3" t="n"/>
+      <c r="P76" s="3" t="n"/>
+      <c r="Q76" s="3" t="inlineStr">
+        <is>
+          <t>LSR 1</t>
+        </is>
+      </c>
+      <c r="R76" s="3" t="inlineStr">
+        <is>
+          <t>Intervention outcomes and spillover effects</t>
+        </is>
+      </c>
+      <c r="S76" s="3" t="n"/>
+      <c r="T76" s="3" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="U76" s="3" t="n"/>
+      <c r="V76" s="3" t="n"/>
+      <c r="W76" s="3" t="inlineStr">
+        <is>
           <t>PS; MS</t>
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
+    <row r="77">
+      <c r="A77" t="inlineStr">
         <is>
           <t>IAO:0000033</t>
         </is>
       </c>
-      <c r="B76" t="inlineStr">
+      <c r="B77" t="inlineStr">
         <is>
           <t>directive information entity</t>
         </is>
       </c>
-      <c r="C76" t="inlineStr">
+      <c r="C77" t="inlineStr">
         <is>
           <t>An information content entity whose concretizations indicate to their bearer how to realize them in a process.</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr">
+      <c r="D77" t="inlineStr">
         <is>
           <t>information content entity</t>
         </is>
       </c>
-      <c r="T76" t="inlineStr">
+      <c r="T77" t="inlineStr">
         <is>
           <t>External</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="3" t="inlineStr">
-        <is>
-          <t>GMHO:0000179</t>
-        </is>
-      </c>
-      <c r="B77" s="3" t="inlineStr">
-        <is>
-          <t>dizziness following intervention</t>
-        </is>
-      </c>
-      <c r="C77" s="3" t="inlineStr">
-        <is>
-          <t>An adverse event following an intervention that involves experiencing dizziness.</t>
-        </is>
-      </c>
-      <c r="D77" s="3" t="inlineStr">
-        <is>
-          <t>adverse event following an intervention</t>
-        </is>
-      </c>
-      <c r="E77" s="3" t="n"/>
-      <c r="F77" s="3" t="n"/>
-      <c r="G77" s="3" t="n"/>
-      <c r="H77" s="3" t="n"/>
-      <c r="I77" s="3" t="n"/>
-      <c r="J77" s="3" t="n"/>
-      <c r="K77" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">cross reference: http://purl.obolibrary.org/obo/OAE_0000388
-</t>
-        </is>
-      </c>
-      <c r="L77" s="3" t="inlineStr">
-        <is>
-          <t>http://purl.obolibrary.org/obo/OAE_0000388</t>
-        </is>
-      </c>
-      <c r="M77" s="3" t="inlineStr">
-        <is>
-          <t>dizziness</t>
-        </is>
-      </c>
-      <c r="N77" s="3" t="n"/>
-      <c r="O77" s="3" t="n"/>
-      <c r="P77" s="3" t="n"/>
-      <c r="Q77" s="3" t="inlineStr">
-        <is>
-          <t>LSR 1, LSR 3</t>
-        </is>
-      </c>
-      <c r="R77" s="3" t="inlineStr">
-        <is>
-          <t>Intervention outcomes and spillover effects</t>
-        </is>
-      </c>
-      <c r="S77" s="3" t="n"/>
-      <c r="T77" s="3" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="U77" s="3" t="n"/>
-      <c r="V77" s="3" t="n"/>
-      <c r="W77" s="3" t="inlineStr">
-        <is>
-          <t>PS; MS</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
         <is>
-          <t>GMHO:0000063</t>
+          <t>GMHO:0000179</t>
         </is>
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>drug-induced movement disorder following intervention</t>
+          <t>dizziness following intervention</t>
         </is>
       </c>
       <c r="C78" s="3" t="inlineStr">
         <is>
-          <t>An adverse event following a pharmacological intervention that involves reduced abilities to control movements.</t>
+          <t>An adverse event following an intervention that involves experiencing dizziness.</t>
         </is>
       </c>
       <c r="D78" s="3" t="inlineStr">
@@ -5225,32 +5208,32 @@
       </c>
       <c r="E78" s="3" t="n"/>
       <c r="F78" s="3" t="n"/>
-      <c r="G78" s="3" t="inlineStr">
-        <is>
-          <t>extrapyramidal symptom following intervention</t>
-        </is>
-      </c>
+      <c r="G78" s="3" t="n"/>
       <c r="H78" s="3" t="n"/>
       <c r="I78" s="3" t="n"/>
       <c r="J78" s="3" t="n"/>
       <c r="K78" s="3" t="inlineStr">
         <is>
-          <t>"Based on https://www.ncbi.nlm.nih.gov/books/NBK534115/
-Based on http://purl.obolibrary.org/obo/OAE_0000581"</t>
+          <t xml:space="preserve">cross reference: http://purl.obolibrary.org/obo/OAE_0000388
+</t>
         </is>
       </c>
       <c r="L78" s="3" t="inlineStr">
         <is>
-          <t>http://purl.obolibrary.org/obo/OAE_0000581</t>
-        </is>
-      </c>
-      <c r="M78" s="3" t="n"/>
+          <t>http://purl.obolibrary.org/obo/OAE_0000388</t>
+        </is>
+      </c>
+      <c r="M78" s="3" t="inlineStr">
+        <is>
+          <t>dizziness</t>
+        </is>
+      </c>
       <c r="N78" s="3" t="n"/>
       <c r="O78" s="3" t="n"/>
       <c r="P78" s="3" t="n"/>
       <c r="Q78" s="3" t="inlineStr">
         <is>
-          <t>LSR 3</t>
+          <t>LSR 1, LSR 3</t>
         </is>
       </c>
       <c r="R78" s="3" t="inlineStr">
@@ -5275,52 +5258,52 @@
     <row r="79">
       <c r="A79" s="3" t="inlineStr">
         <is>
-          <t>GMHO:0000180</t>
+          <t>GMHO:0000063</t>
         </is>
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>dry mouth following intervention</t>
+          <t>drug-induced movement disorder following intervention</t>
         </is>
       </c>
       <c r="C79" s="3" t="inlineStr">
         <is>
-          <t>A digestive system adverse event following intervention that involves experiencing dry mouth.</t>
+          <t>An adverse event following a pharmacological intervention that involves reduced abilities to control movements.</t>
         </is>
       </c>
       <c r="D79" s="3" t="inlineStr">
         <is>
-          <t>digestive system adverse event following intervention</t>
+          <t>adverse event following an intervention</t>
         </is>
       </c>
       <c r="E79" s="3" t="n"/>
       <c r="F79" s="3" t="n"/>
-      <c r="G79" s="3" t="n"/>
+      <c r="G79" s="3" t="inlineStr">
+        <is>
+          <t>extrapyramidal symptom following intervention</t>
+        </is>
+      </c>
       <c r="H79" s="3" t="n"/>
       <c r="I79" s="3" t="n"/>
       <c r="J79" s="3" t="n"/>
       <c r="K79" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">cross reference: http://purl.obolibrary.org/obo/OAE_0000505
-</t>
+          <t>"Based on https://www.ncbi.nlm.nih.gov/books/NBK534115/
+Based on http://purl.obolibrary.org/obo/OAE_0000581"</t>
         </is>
       </c>
       <c r="L79" s="3" t="inlineStr">
         <is>
-          <t>http://purl.obolibrary.org/obo/OAE_0000505</t>
-        </is>
-      </c>
-      <c r="M79" s="3" t="inlineStr">
-        <is>
-          <t>dry mouth</t>
-        </is>
-      </c>
+          <t>http://purl.obolibrary.org/obo/OAE_0000581</t>
+        </is>
+      </c>
+      <c r="M79" s="3" t="n"/>
       <c r="N79" s="3" t="n"/>
       <c r="O79" s="3" t="n"/>
       <c r="P79" s="3" t="n"/>
       <c r="Q79" s="3" t="inlineStr">
         <is>
-          <t>LSR 1</t>
+          <t>LSR 3</t>
         </is>
       </c>
       <c r="R79" s="3" t="inlineStr">
@@ -5343,104 +5326,127 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="2" t="inlineStr">
+      <c r="A80" s="3" t="inlineStr">
+        <is>
+          <t>GMHO:0000180</t>
+        </is>
+      </c>
+      <c r="B80" s="3" t="inlineStr">
+        <is>
+          <t>dry mouth following intervention</t>
+        </is>
+      </c>
+      <c r="C80" s="3" t="inlineStr">
+        <is>
+          <t>A digestive system adverse event following intervention that involves experiencing dry mouth.</t>
+        </is>
+      </c>
+      <c r="D80" s="3" t="inlineStr">
+        <is>
+          <t>digestive system adverse event following intervention</t>
+        </is>
+      </c>
+      <c r="E80" s="3" t="n"/>
+      <c r="F80" s="3" t="n"/>
+      <c r="G80" s="3" t="n"/>
+      <c r="H80" s="3" t="n"/>
+      <c r="I80" s="3" t="n"/>
+      <c r="J80" s="3" t="n"/>
+      <c r="K80" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cross reference: http://purl.obolibrary.org/obo/OAE_0000505
+</t>
+        </is>
+      </c>
+      <c r="L80" s="3" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/OAE_0000505</t>
+        </is>
+      </c>
+      <c r="M80" s="3" t="inlineStr">
+        <is>
+          <t>dry mouth</t>
+        </is>
+      </c>
+      <c r="N80" s="3" t="n"/>
+      <c r="O80" s="3" t="n"/>
+      <c r="P80" s="3" t="n"/>
+      <c r="Q80" s="3" t="inlineStr">
+        <is>
+          <t>LSR 1</t>
+        </is>
+      </c>
+      <c r="R80" s="3" t="inlineStr">
+        <is>
+          <t>Intervention outcomes and spillover effects</t>
+        </is>
+      </c>
+      <c r="S80" s="3" t="n"/>
+      <c r="T80" s="3" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="U80" s="3" t="n"/>
+      <c r="V80" s="3" t="n"/>
+      <c r="W80" s="3" t="inlineStr">
+        <is>
+          <t>PS; MS</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
         <is>
           <t>GMHO:0000064</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
+      <c r="B81" s="2" t="inlineStr">
         <is>
           <t>dyskinesias following an intervention</t>
         </is>
       </c>
-      <c r="C80" s="2" t="inlineStr">
+      <c r="C81" s="2" t="inlineStr">
         <is>
           <t>An adverse event following an intervention that involves dyskinesias.</t>
         </is>
       </c>
-      <c r="D80" s="2" t="inlineStr">
+      <c r="D81" s="2" t="inlineStr">
         <is>
           <t>adverse event following an intervention</t>
         </is>
       </c>
-      <c r="E80" s="2" t="n"/>
-      <c r="F80" s="2" t="n"/>
-      <c r="G80" s="2" t="n"/>
-      <c r="H80" s="2" t="n"/>
-      <c r="I80" s="2" t="n"/>
-      <c r="J80" s="2" t="n"/>
-      <c r="K80" s="2" t="n"/>
-      <c r="L80" s="2" t="n"/>
-      <c r="M80" s="2" t="n"/>
-      <c r="N80" s="2" t="n"/>
-      <c r="O80" s="2" t="n"/>
-      <c r="P80" s="2" t="n"/>
-      <c r="Q80" s="2" t="inlineStr">
+      <c r="E81" s="2" t="n"/>
+      <c r="F81" s="2" t="n"/>
+      <c r="G81" s="2" t="n"/>
+      <c r="H81" s="2" t="n"/>
+      <c r="I81" s="2" t="n"/>
+      <c r="J81" s="2" t="n"/>
+      <c r="K81" s="2" t="n"/>
+      <c r="L81" s="2" t="n"/>
+      <c r="M81" s="2" t="n"/>
+      <c r="N81" s="2" t="n"/>
+      <c r="O81" s="2" t="n"/>
+      <c r="P81" s="2" t="n"/>
+      <c r="Q81" s="2" t="inlineStr">
         <is>
           <t>LSR 3</t>
         </is>
       </c>
-      <c r="R80" s="2" t="inlineStr">
-        <is>
-          <t>Intervention outcomes and spillover effects</t>
-        </is>
-      </c>
-      <c r="S80" s="2" t="n"/>
-      <c r="T80" s="2" t="inlineStr">
+      <c r="R81" s="2" t="inlineStr">
+        <is>
+          <t>Intervention outcomes and spillover effects</t>
+        </is>
+      </c>
+      <c r="S81" s="2" t="n"/>
+      <c r="T81" s="2" t="inlineStr">
         <is>
           <t>Obsolete</t>
         </is>
       </c>
-      <c r="U80" s="2" t="n"/>
-      <c r="V80" s="2" t="n"/>
-      <c r="W80" s="2" t="inlineStr">
-        <is>
-          <t>PS</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>STATO:0000471</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>estimate</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>a estimate is a data item which is computed from a dataset to provide an approximated value (an estimator) for a 'statistical parameter' (a 'characteristics/parameter' of the true underlying distribution) of a real population.</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>statistic</t>
-        </is>
-      </c>
-      <c r="J81" t="inlineStr">
-        <is>
-          <t>Intervention outcomes and spillover effects</t>
-        </is>
-      </c>
-      <c r="Q81" t="inlineStr">
-        <is>
-          <t>LSR 3</t>
-        </is>
-      </c>
-      <c r="R81" t="inlineStr">
-        <is>
-          <t>Intervention outcomes and spillover effects</t>
-        </is>
-      </c>
-      <c r="T81" t="inlineStr">
-        <is>
-          <t>External</t>
-        </is>
-      </c>
-      <c r="W81" t="inlineStr">
+      <c r="U81" s="2" t="n"/>
+      <c r="V81" s="2" t="n"/>
+      <c r="W81" s="2" t="inlineStr">
         <is>
           <t>PS</t>
         </is>
@@ -5449,274 +5455,264 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
+          <t>STATO:0000471</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>estimate</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>a estimate is a data item which is computed from a dataset to provide an approximated value (an estimator) for a 'statistical parameter' (a 'characteristics/parameter' of the true underlying distribution) of a real population.</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>statistic</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>Intervention outcomes and spillover effects</t>
+        </is>
+      </c>
+      <c r="Q82" t="inlineStr">
+        <is>
+          <t>LSR 3</t>
+        </is>
+      </c>
+      <c r="R82" t="inlineStr">
+        <is>
+          <t>Intervention outcomes and spillover effects</t>
+        </is>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>External</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>PS</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
           <t>PATO:0001035</t>
         </is>
       </c>
-      <c r="B82" t="inlineStr">
+      <c r="B83" t="inlineStr">
         <is>
           <t>force</t>
         </is>
       </c>
-      <c r="C82" t="inlineStr">
+      <c r="C83" t="inlineStr">
         <is>
           <t>A physical quality inhering in a bearer by virtue of the bearer's rate of change of momentum.</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr">
+      <c r="D83" t="inlineStr">
         <is>
           <t>physical quality</t>
         </is>
       </c>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t>Intervention outcomes and spillover effects</t>
-        </is>
-      </c>
-      <c r="Q82" t="inlineStr">
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>Intervention outcomes and spillover effects</t>
+        </is>
+      </c>
+      <c r="Q83" t="inlineStr">
         <is>
           <t>LSR 3</t>
         </is>
       </c>
-      <c r="R82" t="inlineStr">
-        <is>
-          <t>Intervention outcomes and spillover effects</t>
-        </is>
-      </c>
-      <c r="T82" t="inlineStr">
+      <c r="R83" t="inlineStr">
+        <is>
+          <t>Intervention outcomes and spillover effects</t>
+        </is>
+      </c>
+      <c r="T83" t="inlineStr">
         <is>
           <t>External</t>
         </is>
       </c>
-      <c r="W82" t="inlineStr">
-        <is>
-          <t>PS</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="3" t="inlineStr">
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>PS</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="3" t="inlineStr">
         <is>
           <t>GMHO:0000181</t>
         </is>
       </c>
-      <c r="B83" s="3" t="inlineStr">
+      <c r="B84" s="3" t="inlineStr">
         <is>
           <t>headache following intervention</t>
         </is>
       </c>
-      <c r="C83" s="3" t="inlineStr">
+      <c r="C84" s="3" t="inlineStr">
         <is>
           <t>A pain following intervention that has an outcome of headache.</t>
         </is>
       </c>
-      <c r="D83" s="3" t="inlineStr">
+      <c r="D84" s="3" t="inlineStr">
         <is>
           <t>pain following intervention</t>
         </is>
       </c>
-      <c r="E83" s="3" t="n"/>
-      <c r="F83" s="3" t="n"/>
-      <c r="G83" s="3" t="n"/>
-      <c r="H83" s="3" t="n"/>
-      <c r="I83" s="3" t="n"/>
-      <c r="J83" s="3" t="n"/>
-      <c r="K83" s="3" t="inlineStr">
+      <c r="E84" s="3" t="n"/>
+      <c r="F84" s="3" t="n"/>
+      <c r="G84" s="3" t="n"/>
+      <c r="H84" s="3" t="n"/>
+      <c r="I84" s="3" t="n"/>
+      <c r="J84" s="3" t="n"/>
+      <c r="K84" s="3" t="inlineStr">
         <is>
           <t>cross-reference: http://purl.obolibrary.org/obo/OAE_0000377</t>
         </is>
       </c>
-      <c r="L83" s="3" t="inlineStr">
+      <c r="L84" s="3" t="inlineStr">
         <is>
           <t>http://purl.obolibrary.org/obo/OAE_0000377</t>
         </is>
       </c>
-      <c r="M83" s="3" t="inlineStr">
+      <c r="M84" s="3" t="inlineStr">
         <is>
           <t>headache</t>
         </is>
       </c>
-      <c r="N83" s="3" t="n"/>
-      <c r="O83" s="3" t="n"/>
-      <c r="P83" s="3" t="n"/>
-      <c r="Q83" s="3" t="inlineStr">
+      <c r="N84" s="3" t="n"/>
+      <c r="O84" s="3" t="n"/>
+      <c r="P84" s="3" t="n"/>
+      <c r="Q84" s="3" t="inlineStr">
         <is>
           <t>LSR 1, LSR 3</t>
         </is>
       </c>
-      <c r="R83" s="3" t="inlineStr">
-        <is>
-          <t>Intervention outcomes and spillover effects</t>
-        </is>
-      </c>
-      <c r="S83" s="3" t="n"/>
-      <c r="T83" s="3" t="inlineStr">
+      <c r="R84" s="3" t="inlineStr">
+        <is>
+          <t>Intervention outcomes and spillover effects</t>
+        </is>
+      </c>
+      <c r="S84" s="3" t="n"/>
+      <c r="T84" s="3" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="U83" s="3" t="n"/>
-      <c r="V83" s="3" t="n"/>
-      <c r="W83" s="3" t="inlineStr">
+      <c r="U84" s="3" t="n"/>
+      <c r="V84" s="3" t="n"/>
+      <c r="W84" s="3" t="inlineStr">
         <is>
           <t>PS; MS</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>BCIO:015092</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>health status attribute</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>A personal attribute that is the state of an individual's mental or physical condition.</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>personal attribute</t>
-        </is>
-      </c>
-      <c r="J84" t="inlineStr">
-        <is>
-          <t>intervention outcomes and spillover effects</t>
-        </is>
-      </c>
-      <c r="Q84" t="inlineStr">
-        <is>
-          <t>LSR 3</t>
-        </is>
-      </c>
-      <c r="R84" t="inlineStr">
-        <is>
-          <t>Intervention outcomes and spillover effects</t>
-        </is>
-      </c>
-      <c r="T84" t="inlineStr">
-        <is>
-          <t>External</t>
-        </is>
-      </c>
-      <c r="W84" t="inlineStr">
-        <is>
-          <t>PS</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
+          <t>BCIO:015092</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>health status attribute</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>A personal attribute that is the state of an individual's mental or physical condition.</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>personal attribute</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>intervention outcomes and spillover effects</t>
+        </is>
+      </c>
+      <c r="Q85" t="inlineStr">
+        <is>
+          <t>LSR 3</t>
+        </is>
+      </c>
+      <c r="R85" t="inlineStr">
+        <is>
+          <t>Intervention outcomes and spillover effects</t>
+        </is>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>External</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>PS</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
           <t>CMO:0000230</t>
         </is>
       </c>
-      <c r="B85" t="inlineStr">
+      <c r="B86" t="inlineStr">
         <is>
           <t>heart electrical conduction measurement</t>
         </is>
       </c>
-      <c r="C85" t="inlineStr">
+      <c r="C86" t="inlineStr">
         <is>
           <t>Any measurement of components of the electrical conduction system of the heart.The electrical conduction system of the heart transmits signals generated usually by the sinoatrial node to cause contraction of the heart muscle.</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr">
+      <c r="D86" t="inlineStr">
         <is>
           <t>heart measurement</t>
         </is>
       </c>
-      <c r="R85" t="inlineStr">
-        <is>
-          <t>Intervention outcomes and spillover effects</t>
-        </is>
-      </c>
-      <c r="T85" t="inlineStr">
+      <c r="R86" t="inlineStr">
+        <is>
+          <t>Intervention outcomes and spillover effects</t>
+        </is>
+      </c>
+      <c r="T86" t="inlineStr">
         <is>
           <t>External</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="2" t="inlineStr">
-        <is>
-          <t>GMHO:0000132</t>
-        </is>
-      </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>heart rate</t>
-        </is>
-      </c>
-      <c r="C86" s="2" t="inlineStr">
-        <is>
-          <t>A data item about the number of heart contractions within a temporal interval.</t>
-        </is>
-      </c>
-      <c r="D86" s="2" t="inlineStr">
-        <is>
-          <t>data item</t>
-        </is>
-      </c>
-      <c r="E86" s="2" t="n"/>
-      <c r="F86" s="2" t="n"/>
-      <c r="G86" s="2" t="n"/>
-      <c r="H86" s="2" t="n"/>
-      <c r="I86" s="2" t="n"/>
-      <c r="J86" s="2" t="n"/>
-      <c r="K86" s="2" t="n"/>
-      <c r="L86" s="2" t="n"/>
-      <c r="M86" s="2" t="n"/>
-      <c r="N86" s="2" t="n"/>
-      <c r="O86" s="2" t="n"/>
-      <c r="P86" s="2" t="n"/>
-      <c r="Q86" s="2" t="inlineStr">
-        <is>
-          <t>LSR 2</t>
-        </is>
-      </c>
-      <c r="R86" s="2" t="inlineStr">
-        <is>
-          <t>Intervention outcomes and spillover effects</t>
-        </is>
-      </c>
-      <c r="S86" s="2" t="n"/>
-      <c r="T86" s="2" t="inlineStr">
-        <is>
-          <t>Obsolete</t>
-        </is>
-      </c>
-      <c r="U86" s="2" t="n"/>
-      <c r="V86" s="2" t="n"/>
-      <c r="W86" s="2" t="inlineStr">
-        <is>
-          <t>PS</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>GMHO:0000065</t>
+          <t>GMHO:0000132</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>homicide following an intervention</t>
+          <t>heart rate</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>A death following an intervention that involves a participant being intentionally killed by another person.</t>
+          <t>A data item about the number of heart contractions within a temporal interval.</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>death following an intervention</t>
+          <t>data item</t>
         </is>
       </c>
       <c r="E87" s="2" t="n"/>
@@ -5733,7 +5729,7 @@
       <c r="P87" s="2" t="n"/>
       <c r="Q87" s="2" t="inlineStr">
         <is>
-          <t>LSR 3</t>
+          <t>LSR 2</t>
         </is>
       </c>
       <c r="R87" s="2" t="inlineStr">
@@ -5758,22 +5754,22 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>GMHO:0000066</t>
+          <t>GMHO:0000065</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>hospitalization</t>
+          <t>homicide following an intervention</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>A health care process that involves a person being admitted to a hospital.</t>
+          <t>A death following an intervention that involves a participant being intentionally killed by another person.</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>health care process</t>
+          <t>death following an intervention</t>
         </is>
       </c>
       <c r="E88" s="2" t="n"/>
@@ -5783,11 +5779,7 @@
       <c r="I88" s="2" t="n"/>
       <c r="J88" s="2" t="n"/>
       <c r="K88" s="2" t="n"/>
-      <c r="L88" s="2" t="inlineStr">
-        <is>
-          <t>http://purl.obolibrary.org/obo/OGMS_0000098</t>
-        </is>
-      </c>
+      <c r="L88" s="2" t="n"/>
       <c r="M88" s="2" t="n"/>
       <c r="N88" s="2" t="n"/>
       <c r="O88" s="2" t="n"/>
@@ -5817,57 +5809,61 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="3" t="inlineStr">
-        <is>
-          <t>GMHO:0000067</t>
-        </is>
-      </c>
-      <c r="B89" s="3" t="inlineStr">
-        <is>
-          <t>human functioning</t>
-        </is>
-      </c>
-      <c r="C89" s="3" t="inlineStr">
-        <is>
-          <t>A bodily disposition to realise processes that influence a person's life quality.</t>
-        </is>
-      </c>
-      <c r="D89" s="3" t="inlineStr">
-        <is>
-          <t>bodily disposition</t>
-        </is>
-      </c>
-      <c r="E89" s="3" t="n"/>
-      <c r="F89" s="3" t="n"/>
-      <c r="G89" s="3" t="n"/>
-      <c r="H89" s="3" t="n"/>
-      <c r="I89" s="3" t="n"/>
-      <c r="J89" s="3" t="n"/>
-      <c r="K89" s="3" t="n"/>
-      <c r="L89" s="3" t="n"/>
-      <c r="M89" s="3" t="n"/>
-      <c r="N89" s="3" t="n"/>
-      <c r="O89" s="3" t="n"/>
-      <c r="P89" s="3" t="n"/>
-      <c r="Q89" s="3" t="inlineStr">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>GMHO:0000066</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>hospitalization</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>A health care process that involves a person being admitted to a hospital.</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>health care process</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="n"/>
+      <c r="F89" s="2" t="n"/>
+      <c r="G89" s="2" t="n"/>
+      <c r="H89" s="2" t="n"/>
+      <c r="I89" s="2" t="n"/>
+      <c r="J89" s="2" t="n"/>
+      <c r="K89" s="2" t="n"/>
+      <c r="L89" s="2" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/OGMS_0000098</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="n"/>
+      <c r="N89" s="2" t="n"/>
+      <c r="O89" s="2" t="n"/>
+      <c r="P89" s="2" t="n"/>
+      <c r="Q89" s="2" t="inlineStr">
         <is>
           <t>LSR 3</t>
         </is>
       </c>
-      <c r="R89" s="3" t="inlineStr">
-        <is>
-          <t>Intervention outcomes and spillover effects</t>
-        </is>
-      </c>
-      <c r="S89" s="3" t="n"/>
-      <c r="T89" s="3" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="U89" s="3" t="n"/>
-      <c r="V89" s="3" t="n"/>
-      <c r="W89" s="3" t="inlineStr">
+      <c r="R89" s="2" t="inlineStr">
+        <is>
+          <t>Intervention outcomes and spillover effects</t>
+        </is>
+      </c>
+      <c r="S89" s="2" t="n"/>
+      <c r="T89" s="2" t="inlineStr">
+        <is>
+          <t>Obsolete</t>
+        </is>
+      </c>
+      <c r="U89" s="2" t="n"/>
+      <c r="V89" s="2" t="n"/>
+      <c r="W89" s="2" t="inlineStr">
         <is>
           <t>PS</t>
         </is>
@@ -5876,22 +5872,22 @@
     <row r="90">
       <c r="A90" s="3" t="inlineStr">
         <is>
-          <t>GMHO:0000224</t>
+          <t>GMHO:0000067</t>
         </is>
       </c>
       <c r="B90" s="3" t="inlineStr">
         <is>
-          <t>human functioning scale</t>
+          <t>human functioning</t>
         </is>
       </c>
       <c r="C90" s="3" t="inlineStr">
         <is>
-          <t>A measurement scale that is used to measure human functioning.</t>
+          <t>A bodily disposition to realise processes that influence a person's life quality.</t>
         </is>
       </c>
       <c r="D90" s="3" t="inlineStr">
         <is>
-          <t>measurement scale</t>
+          <t>bodily disposition</t>
         </is>
       </c>
       <c r="E90" s="3" t="n"/>
@@ -5899,19 +5895,23 @@
       <c r="G90" s="3" t="n"/>
       <c r="H90" s="3" t="n"/>
       <c r="I90" s="3" t="n"/>
-      <c r="J90" s="3" t="inlineStr">
-        <is>
-          <t>Intervention outcomes and spillover effects</t>
-        </is>
-      </c>
+      <c r="J90" s="3" t="n"/>
       <c r="K90" s="3" t="n"/>
       <c r="L90" s="3" t="n"/>
       <c r="M90" s="3" t="n"/>
       <c r="N90" s="3" t="n"/>
       <c r="O90" s="3" t="n"/>
       <c r="P90" s="3" t="n"/>
-      <c r="Q90" s="3" t="n"/>
-      <c r="R90" s="3" t="n"/>
+      <c r="Q90" s="3" t="inlineStr">
+        <is>
+          <t>LSR 3</t>
+        </is>
+      </c>
+      <c r="R90" s="3" t="inlineStr">
+        <is>
+          <t>Intervention outcomes and spillover effects</t>
+        </is>
+      </c>
       <c r="S90" s="3" t="n"/>
       <c r="T90" s="3" t="inlineStr">
         <is>
@@ -5929,22 +5929,22 @@
     <row r="91">
       <c r="A91" s="3" t="inlineStr">
         <is>
-          <t>GMHO:0000234</t>
+          <t>GMHO:0000224</t>
         </is>
       </c>
       <c r="B91" s="3" t="inlineStr">
         <is>
-          <t>hyperprolactinemia following intervention</t>
+          <t>human functioning scale</t>
         </is>
       </c>
       <c r="C91" s="3" t="inlineStr">
         <is>
-          <t>An adverse event following an intervention that involves experiencing hyperprolactinemia.</t>
+          <t>A measurement scale that is used to measure human functioning.</t>
         </is>
       </c>
       <c r="D91" s="3" t="inlineStr">
         <is>
-          <t>adverse event following an intervention</t>
+          <t>measurement scale</t>
         </is>
       </c>
       <c r="E91" s="3" t="n"/>
@@ -5959,24 +5959,12 @@
       </c>
       <c r="K91" s="3" t="n"/>
       <c r="L91" s="3" t="n"/>
-      <c r="M91" s="3" t="inlineStr">
-        <is>
-          <t>hyperprolactinemia</t>
-        </is>
-      </c>
+      <c r="M91" s="3" t="n"/>
       <c r="N91" s="3" t="n"/>
       <c r="O91" s="3" t="n"/>
       <c r="P91" s="3" t="n"/>
-      <c r="Q91" s="3" t="inlineStr">
-        <is>
-          <t>LSR 3</t>
-        </is>
-      </c>
-      <c r="R91" s="3" t="inlineStr">
-        <is>
-          <t>Intervention outcomes and spillover effects</t>
-        </is>
-      </c>
+      <c r="Q91" s="3" t="n"/>
+      <c r="R91" s="3" t="n"/>
       <c r="S91" s="3" t="n"/>
       <c r="T91" s="3" t="inlineStr">
         <is>
@@ -5994,17 +5982,17 @@
     <row r="92">
       <c r="A92" s="3" t="inlineStr">
         <is>
-          <t>GMHO:0000235</t>
+          <t>GMHO:0000234</t>
         </is>
       </c>
       <c r="B92" s="3" t="inlineStr">
         <is>
-          <t>hypotension following intervention</t>
+          <t>hyperprolactinemia following intervention</t>
         </is>
       </c>
       <c r="C92" s="3" t="inlineStr">
         <is>
-          <t>An adverse event following an intervention that involves experiencing low blood pressure.</t>
+          <t>An adverse event following an intervention that involves experiencing hyperprolactinemia.</t>
         </is>
       </c>
       <c r="D92" s="3" t="inlineStr">
@@ -6026,7 +6014,7 @@
       <c r="L92" s="3" t="n"/>
       <c r="M92" s="3" t="inlineStr">
         <is>
-          <t>hypotension</t>
+          <t>hyperprolactinemia</t>
         </is>
       </c>
       <c r="N92" s="3" t="n"/>
@@ -6057,104 +6045,112 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" t="inlineStr">
+      <c r="A93" s="3" t="inlineStr">
+        <is>
+          <t>GMHO:0000235</t>
+        </is>
+      </c>
+      <c r="B93" s="3" t="inlineStr">
+        <is>
+          <t>hypotension following intervention</t>
+        </is>
+      </c>
+      <c r="C93" s="3" t="inlineStr">
+        <is>
+          <t>An adverse event following an intervention that involves experiencing low blood pressure.</t>
+        </is>
+      </c>
+      <c r="D93" s="3" t="inlineStr">
+        <is>
+          <t>adverse event following an intervention</t>
+        </is>
+      </c>
+      <c r="E93" s="3" t="n"/>
+      <c r="F93" s="3" t="n"/>
+      <c r="G93" s="3" t="n"/>
+      <c r="H93" s="3" t="n"/>
+      <c r="I93" s="3" t="n"/>
+      <c r="J93" s="3" t="inlineStr">
+        <is>
+          <t>Intervention outcomes and spillover effects</t>
+        </is>
+      </c>
+      <c r="K93" s="3" t="n"/>
+      <c r="L93" s="3" t="n"/>
+      <c r="M93" s="3" t="inlineStr">
+        <is>
+          <t>hypotension</t>
+        </is>
+      </c>
+      <c r="N93" s="3" t="n"/>
+      <c r="O93" s="3" t="n"/>
+      <c r="P93" s="3" t="n"/>
+      <c r="Q93" s="3" t="inlineStr">
+        <is>
+          <t>LSR 3</t>
+        </is>
+      </c>
+      <c r="R93" s="3" t="inlineStr">
+        <is>
+          <t>Intervention outcomes and spillover effects</t>
+        </is>
+      </c>
+      <c r="S93" s="3" t="n"/>
+      <c r="T93" s="3" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="U93" s="3" t="n"/>
+      <c r="V93" s="3" t="n"/>
+      <c r="W93" s="3" t="inlineStr">
+        <is>
+          <t>PS</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
         <is>
           <t>IAO:0000030</t>
         </is>
       </c>
-      <c r="B93" t="inlineStr">
+      <c r="B94" t="inlineStr">
         <is>
           <t>information content entity</t>
         </is>
       </c>
-      <c r="C93" t="inlineStr">
+      <c r="C94" t="inlineStr">
         <is>
           <t>A generically dependent continuant that is about some thing.</t>
         </is>
       </c>
-      <c r="D93" t="inlineStr">
+      <c r="D94" t="inlineStr">
         <is>
           <t>generically dependent continuant</t>
         </is>
       </c>
-      <c r="J93" t="inlineStr">
-        <is>
-          <t>Intervention outcomes and spillover effects</t>
-        </is>
-      </c>
-      <c r="Q93" t="inlineStr">
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>Intervention outcomes and spillover effects</t>
+        </is>
+      </c>
+      <c r="Q94" t="inlineStr">
         <is>
           <t>LSR 1</t>
         </is>
       </c>
-      <c r="R93" t="inlineStr">
-        <is>
-          <t>Intervention outcomes and spillover effects</t>
-        </is>
-      </c>
-      <c r="T93" t="inlineStr">
+      <c r="R94" t="inlineStr">
+        <is>
+          <t>Intervention outcomes and spillover effects</t>
+        </is>
+      </c>
+      <c r="T94" t="inlineStr">
         <is>
           <t>External</t>
         </is>
       </c>
-      <c r="W93" t="inlineStr">
-        <is>
-          <t>PS</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="3" t="inlineStr">
-        <is>
-          <t>GMHO:0000203</t>
-        </is>
-      </c>
-      <c r="B94" s="3" t="inlineStr">
-        <is>
-          <t>information on available followup data</t>
-        </is>
-      </c>
-      <c r="C94" s="3" t="inlineStr">
-        <is>
-          <t>An information content entity about the followup data available for a study.</t>
-        </is>
-      </c>
-      <c r="D94" s="3" t="inlineStr">
-        <is>
-          <t>information content entity</t>
-        </is>
-      </c>
-      <c r="E94" s="3" t="n"/>
-      <c r="F94" s="3" t="n"/>
-      <c r="G94" s="3" t="n"/>
-      <c r="H94" s="3" t="n"/>
-      <c r="I94" s="3" t="n"/>
-      <c r="J94" s="3" t="n"/>
-      <c r="K94" s="3" t="n"/>
-      <c r="L94" s="3" t="n"/>
-      <c r="M94" s="3" t="n"/>
-      <c r="N94" s="3" t="n"/>
-      <c r="O94" s="3" t="n"/>
-      <c r="P94" s="3" t="n"/>
-      <c r="Q94" s="3" t="inlineStr">
-        <is>
-          <t>LSR 1, LSR 3</t>
-        </is>
-      </c>
-      <c r="R94" s="3" t="inlineStr">
-        <is>
-          <t>Intervention outcomes and spillover effects</t>
-        </is>
-      </c>
-      <c r="S94" s="3" t="n"/>
-      <c r="T94" s="3" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="U94" s="3" t="n"/>
-      <c r="V94" s="3" t="n"/>
-      <c r="W94" s="3" t="inlineStr">
+      <c r="W94" t="inlineStr">
         <is>
           <t>PS</t>
         </is>
@@ -6163,22 +6159,22 @@
     <row r="95">
       <c r="A95" s="3" t="inlineStr">
         <is>
-          <t>GMHO:0000182</t>
+          <t>GMHO:0000203</t>
         </is>
       </c>
       <c r="B95" s="3" t="inlineStr">
         <is>
-          <t>insomnia following intervention</t>
+          <t>information on available followup data</t>
         </is>
       </c>
       <c r="C95" s="3" t="inlineStr">
         <is>
-          <t>An adverse event following an intervention in which there is an inability to fall asleep or to stay asleep as long as desired.</t>
+          <t>An information content entity about the followup data available for a study.</t>
         </is>
       </c>
       <c r="D95" s="3" t="inlineStr">
         <is>
-          <t>adverse event following an intervention</t>
+          <t>information content entity</t>
         </is>
       </c>
       <c r="E95" s="3" t="n"/>
@@ -6187,21 +6183,9 @@
       <c r="H95" s="3" t="n"/>
       <c r="I95" s="3" t="n"/>
       <c r="J95" s="3" t="n"/>
-      <c r="K95" s="3" t="inlineStr">
-        <is>
-          <t>cross-reference: http://purl.obolibrary.org/obo/OAE_0002206</t>
-        </is>
-      </c>
-      <c r="L95" s="3" t="inlineStr">
-        <is>
-          <t>http://purl.obolibrary.org/obo/OAE_0002206</t>
-        </is>
-      </c>
-      <c r="M95" s="3" t="inlineStr">
-        <is>
-          <t>insomnia</t>
-        </is>
-      </c>
+      <c r="K95" s="3" t="n"/>
+      <c r="L95" s="3" t="n"/>
+      <c r="M95" s="3" t="n"/>
       <c r="N95" s="3" t="n"/>
       <c r="O95" s="3" t="n"/>
       <c r="P95" s="3" t="n"/>
@@ -6225,421 +6209,433 @@
       <c r="V95" s="3" t="n"/>
       <c r="W95" s="3" t="inlineStr">
         <is>
+          <t>PS</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="3" t="inlineStr">
+        <is>
+          <t>GMHO:0000182</t>
+        </is>
+      </c>
+      <c r="B96" s="3" t="inlineStr">
+        <is>
+          <t>insomnia following intervention</t>
+        </is>
+      </c>
+      <c r="C96" s="3" t="inlineStr">
+        <is>
+          <t>An adverse event following an intervention in which there is an inability to fall asleep or to stay asleep as long as desired.</t>
+        </is>
+      </c>
+      <c r="D96" s="3" t="inlineStr">
+        <is>
+          <t>adverse event following an intervention</t>
+        </is>
+      </c>
+      <c r="E96" s="3" t="n"/>
+      <c r="F96" s="3" t="n"/>
+      <c r="G96" s="3" t="n"/>
+      <c r="H96" s="3" t="n"/>
+      <c r="I96" s="3" t="n"/>
+      <c r="J96" s="3" t="n"/>
+      <c r="K96" s="3" t="inlineStr">
+        <is>
+          <t>cross-reference: http://purl.obolibrary.org/obo/OAE_0002206</t>
+        </is>
+      </c>
+      <c r="L96" s="3" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/OAE_0002206</t>
+        </is>
+      </c>
+      <c r="M96" s="3" t="inlineStr">
+        <is>
+          <t>insomnia</t>
+        </is>
+      </c>
+      <c r="N96" s="3" t="n"/>
+      <c r="O96" s="3" t="n"/>
+      <c r="P96" s="3" t="n"/>
+      <c r="Q96" s="3" t="inlineStr">
+        <is>
+          <t>LSR 1, LSR 3</t>
+        </is>
+      </c>
+      <c r="R96" s="3" t="inlineStr">
+        <is>
+          <t>Intervention outcomes and spillover effects</t>
+        </is>
+      </c>
+      <c r="S96" s="3" t="n"/>
+      <c r="T96" s="3" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="U96" s="3" t="n"/>
+      <c r="V96" s="3" t="n"/>
+      <c r="W96" s="3" t="inlineStr">
+        <is>
           <t>PS; MS</t>
         </is>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
+    <row r="97">
+      <c r="A97" t="inlineStr">
         <is>
           <t>BCIO:039000</t>
         </is>
       </c>
-      <c r="B96" t="inlineStr">
+      <c r="B97" t="inlineStr">
         <is>
           <t>intervention outcome</t>
         </is>
       </c>
-      <c r="C96" t="inlineStr">
+      <c r="C97" t="inlineStr">
         <is>
           <t>An entity that is influenced by an intervention.</t>
         </is>
       </c>
-      <c r="D96" t="inlineStr">
+      <c r="D97" t="inlineStr">
         <is>
           <t>entity</t>
         </is>
       </c>
-      <c r="Q96" t="inlineStr">
+      <c r="Q97" t="inlineStr">
         <is>
           <t>LSR 1; LSR 2; LSR 3</t>
         </is>
       </c>
-      <c r="R96" t="inlineStr">
-        <is>
-          <t>Intervention outcomes and spillover effects</t>
-        </is>
-      </c>
-      <c r="T96" t="inlineStr">
+      <c r="R97" t="inlineStr">
+        <is>
+          <t>Intervention outcomes and spillover effects</t>
+        </is>
+      </c>
+      <c r="T97" t="inlineStr">
         <is>
           <t>External</t>
         </is>
       </c>
-      <c r="W96" t="inlineStr">
-        <is>
-          <t>PS</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="2" t="inlineStr">
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>PS</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
         <is>
           <t>GMHO:0000133</t>
         </is>
       </c>
-      <c r="B97" s="2" t="inlineStr">
+      <c r="B98" s="2" t="inlineStr">
         <is>
           <t>lower bound of 95% confidence interval</t>
         </is>
       </c>
-      <c r="C97" s="2" t="inlineStr">
+      <c r="C98" s="2" t="inlineStr">
         <is>
           <t>A quantitative confidence value that denotes the lower endpoint of a 95% confidence interval and indicates the lowest value within a true parameter is likely to reside within the confidence interval.</t>
         </is>
       </c>
-      <c r="D97" s="2" t="inlineStr">
+      <c r="D98" s="2" t="inlineStr">
         <is>
           <t>quantitative confidence value</t>
         </is>
       </c>
-      <c r="E97" s="2" t="n"/>
-      <c r="F97" s="2" t="n"/>
-      <c r="G97" s="2" t="n"/>
-      <c r="H97" s="2" t="n"/>
-      <c r="I97" s="2" t="n"/>
-      <c r="J97" s="2" t="n"/>
-      <c r="K97" s="2" t="inlineStr">
+      <c r="E98" s="2" t="n"/>
+      <c r="F98" s="2" t="n"/>
+      <c r="G98" s="2" t="n"/>
+      <c r="H98" s="2" t="n"/>
+      <c r="I98" s="2" t="n"/>
+      <c r="J98" s="2" t="n"/>
+      <c r="K98" s="2" t="inlineStr">
         <is>
           <t>Based on Ross, S. M. (2017). Estimation. Introductory statistics ( p. 329-380). Academic Press.</t>
         </is>
       </c>
-      <c r="L97" s="2" t="n"/>
-      <c r="M97" s="2" t="n"/>
-      <c r="N97" s="2" t="n"/>
-      <c r="O97" s="2" t="n"/>
-      <c r="P97" s="2" t="n"/>
-      <c r="Q97" s="2" t="inlineStr">
+      <c r="L98" s="2" t="n"/>
+      <c r="M98" s="2" t="n"/>
+      <c r="N98" s="2" t="n"/>
+      <c r="O98" s="2" t="n"/>
+      <c r="P98" s="2" t="n"/>
+      <c r="Q98" s="2" t="inlineStr">
         <is>
           <t>LSR 1; LSR 2</t>
         </is>
       </c>
-      <c r="R97" s="2" t="inlineStr">
-        <is>
-          <t>Intervention outcomes and spillover effects</t>
-        </is>
-      </c>
-      <c r="S97" s="2" t="n"/>
-      <c r="T97" s="2" t="inlineStr">
+      <c r="R98" s="2" t="inlineStr">
+        <is>
+          <t>Intervention outcomes and spillover effects</t>
+        </is>
+      </c>
+      <c r="S98" s="2" t="n"/>
+      <c r="T98" s="2" t="inlineStr">
         <is>
           <t>Obsolete</t>
         </is>
       </c>
-      <c r="U97" s="2" t="n"/>
-      <c r="V97" s="2" t="n"/>
-      <c r="W97" s="2" t="inlineStr">
-        <is>
-          <t>PS</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
+      <c r="U98" s="2" t="n"/>
+      <c r="V98" s="2" t="n"/>
+      <c r="W98" s="2" t="inlineStr">
+        <is>
+          <t>PS</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
         <is>
           <t>IAO:0000109</t>
         </is>
       </c>
-      <c r="B98" t="inlineStr">
+      <c r="B99" t="inlineStr">
         <is>
           <t>measurement datum</t>
         </is>
       </c>
-      <c r="C98" t="inlineStr">
+      <c r="C99" t="inlineStr">
         <is>
           <t>A measurement datum is an information content entity that is a recording of the output of a measurement such as produced by a device.</t>
         </is>
       </c>
-      <c r="D98" t="inlineStr">
+      <c r="D99" t="inlineStr">
         <is>
           <t>data item</t>
         </is>
       </c>
-      <c r="Q98" t="inlineStr">
+      <c r="Q99" t="inlineStr">
         <is>
           <t>LSR 1; LSR 2; LSR 3</t>
         </is>
       </c>
-      <c r="R98" t="inlineStr">
-        <is>
-          <t>Intervention outcomes and spillover effects</t>
-        </is>
-      </c>
-      <c r="T98" t="inlineStr">
+      <c r="R99" t="inlineStr">
+        <is>
+          <t>Intervention outcomes and spillover effects</t>
+        </is>
+      </c>
+      <c r="T99" t="inlineStr">
         <is>
           <t>External</t>
         </is>
       </c>
-      <c r="W98" t="inlineStr">
-        <is>
-          <t>PS</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="3" t="inlineStr">
+      <c r="W99" t="inlineStr">
+        <is>
+          <t>PS</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="3" t="inlineStr">
         <is>
           <t>GMHO:0000204</t>
         </is>
       </c>
-      <c r="B99" s="3" t="inlineStr">
+      <c r="B100" s="3" t="inlineStr">
         <is>
           <t>measurement datum at post-intervention</t>
         </is>
       </c>
-      <c r="C99" s="3" t="inlineStr">
+      <c r="C100" s="3" t="inlineStr">
         <is>
           <t>Measurement datum that was recorded as post-intervention data in a study.</t>
         </is>
       </c>
-      <c r="D99" s="3" t="inlineStr">
+      <c r="D100" s="3" t="inlineStr">
         <is>
           <t>measurement datum</t>
         </is>
       </c>
-      <c r="E99" s="3" t="n"/>
-      <c r="F99" s="3" t="n"/>
-      <c r="G99" s="3" t="n"/>
-      <c r="H99" s="3" t="n"/>
-      <c r="I99" s="3" t="n"/>
-      <c r="J99" s="3" t="n"/>
-      <c r="K99" s="3" t="n"/>
-      <c r="L99" s="3" t="n"/>
-      <c r="M99" s="3" t="inlineStr">
+      <c r="E100" s="3" t="n"/>
+      <c r="F100" s="3" t="n"/>
+      <c r="G100" s="3" t="n"/>
+      <c r="H100" s="3" t="n"/>
+      <c r="I100" s="3" t="n"/>
+      <c r="J100" s="3" t="n"/>
+      <c r="K100" s="3" t="n"/>
+      <c r="L100" s="3" t="n"/>
+      <c r="M100" s="3" t="inlineStr">
         <is>
           <t>post-intervention</t>
         </is>
       </c>
-      <c r="N99" s="3" t="n"/>
-      <c r="O99" s="3" t="n"/>
-      <c r="P99" s="3" t="n"/>
-      <c r="Q99" s="3" t="inlineStr">
+      <c r="N100" s="3" t="n"/>
+      <c r="O100" s="3" t="n"/>
+      <c r="P100" s="3" t="n"/>
+      <c r="Q100" s="3" t="inlineStr">
         <is>
           <t>LSR 1, LSR 2, LSR 3</t>
         </is>
       </c>
-      <c r="R99" s="3" t="n"/>
-      <c r="S99" s="3" t="n"/>
-      <c r="T99" s="3" t="inlineStr">
+      <c r="R100" s="3" t="n"/>
+      <c r="S100" s="3" t="n"/>
+      <c r="T100" s="3" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="U99" s="3" t="n"/>
-      <c r="V99" s="3" t="n"/>
-      <c r="W99" s="3" t="inlineStr">
+      <c r="U100" s="3" t="n"/>
+      <c r="V100" s="3" t="n"/>
+      <c r="W100" s="3" t="inlineStr">
         <is>
           <t>PS; MS</t>
         </is>
       </c>
     </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
+    <row r="101">
+      <c r="A101" t="inlineStr">
         <is>
           <t>OBCS:0000011</t>
         </is>
       </c>
-      <c r="B100" t="inlineStr">
+      <c r="B101" t="inlineStr">
         <is>
           <t>measurement scale</t>
         </is>
       </c>
-      <c r="C100" t="inlineStr">
+      <c r="C101" t="inlineStr">
         <is>
           <t>An information content entity that represents a type of scale on which a variable is measured, including nominal, ordinal, interval, ratio.</t>
         </is>
       </c>
-      <c r="D100" t="inlineStr">
+      <c r="D101" t="inlineStr">
         <is>
           <t>information content entity</t>
         </is>
       </c>
-      <c r="Q100" t="inlineStr">
+      <c r="Q101" t="inlineStr">
         <is>
           <t>LSR 1; LSR 2; LSR 3</t>
         </is>
       </c>
-      <c r="R100" t="inlineStr">
-        <is>
-          <t>Intervention outcomes and spillover effects</t>
-        </is>
-      </c>
-      <c r="T100" t="inlineStr">
+      <c r="R101" t="inlineStr">
+        <is>
+          <t>Intervention outcomes and spillover effects</t>
+        </is>
+      </c>
+      <c r="T101" t="inlineStr">
         <is>
           <t>External</t>
         </is>
       </c>
-      <c r="W100" t="inlineStr">
-        <is>
-          <t>PS</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="3" t="inlineStr">
+      <c r="W101" t="inlineStr">
+        <is>
+          <t>PS</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="3" t="inlineStr">
         <is>
           <t>GMHO:0000205</t>
         </is>
       </c>
-      <c r="B101" s="3" t="inlineStr">
+      <c r="B102" s="3" t="inlineStr">
         <is>
           <t>measurement scale at post-intervention</t>
         </is>
       </c>
-      <c r="C101" s="3" t="inlineStr">
+      <c r="C102" s="3" t="inlineStr">
         <is>
           <t>A measurement scale used to measure post-intervention data in a study.</t>
         </is>
       </c>
-      <c r="D101" s="3" t="inlineStr">
+      <c r="D102" s="3" t="inlineStr">
         <is>
           <t>measurement scale</t>
         </is>
       </c>
-      <c r="E101" s="3" t="n"/>
-      <c r="F101" s="3" t="n"/>
-      <c r="G101" s="3" t="n"/>
-      <c r="H101" s="3" t="n"/>
-      <c r="I101" s="3" t="n"/>
-      <c r="J101" s="3" t="n"/>
-      <c r="K101" s="3" t="n"/>
-      <c r="L101" s="3" t="n"/>
-      <c r="M101" s="3" t="n"/>
-      <c r="N101" s="3" t="n"/>
-      <c r="O101" s="3" t="n"/>
-      <c r="P101" s="3" t="n"/>
-      <c r="Q101" s="3" t="n"/>
-      <c r="R101" s="3" t="n"/>
-      <c r="S101" s="3" t="n"/>
-      <c r="T101" s="3" t="inlineStr">
+      <c r="E102" s="3" t="n"/>
+      <c r="F102" s="3" t="n"/>
+      <c r="G102" s="3" t="n"/>
+      <c r="H102" s="3" t="n"/>
+      <c r="I102" s="3" t="n"/>
+      <c r="J102" s="3" t="n"/>
+      <c r="K102" s="3" t="n"/>
+      <c r="L102" s="3" t="n"/>
+      <c r="M102" s="3" t="n"/>
+      <c r="N102" s="3" t="n"/>
+      <c r="O102" s="3" t="n"/>
+      <c r="P102" s="3" t="n"/>
+      <c r="Q102" s="3" t="n"/>
+      <c r="R102" s="3" t="n"/>
+      <c r="S102" s="3" t="n"/>
+      <c r="T102" s="3" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="U101" s="3" t="n"/>
-      <c r="V101" s="3" t="n"/>
-      <c r="W101" s="3" t="inlineStr">
-        <is>
-          <t>PS</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
+      <c r="U102" s="3" t="n"/>
+      <c r="V102" s="3" t="n"/>
+      <c r="W102" s="3" t="inlineStr">
+        <is>
+          <t>PS</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
         <is>
           <t>MF:0000020</t>
         </is>
       </c>
-      <c r="B102" t="inlineStr">
+      <c r="B103" t="inlineStr">
         <is>
           <t>mental process</t>
         </is>
       </c>
-      <c r="C102" t="inlineStr">
+      <c r="C103" t="inlineStr">
         <is>
           <t>A bodily process that occurs in the brain, and that can of itself be conscious, or can give rise to a process that can of itself be conscious or can give rise to behaviour.</t>
         </is>
       </c>
-      <c r="D102" t="inlineStr">
+      <c r="D103" t="inlineStr">
         <is>
           <t>bodily process</t>
         </is>
       </c>
-      <c r="J102" t="inlineStr">
-        <is>
-          <t>Intervention outcomes and spillover effects</t>
-        </is>
-      </c>
-      <c r="Q102" t="inlineStr">
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>Intervention outcomes and spillover effects</t>
+        </is>
+      </c>
+      <c r="Q103" t="inlineStr">
         <is>
           <t xml:space="preserve">LSR 3 </t>
         </is>
       </c>
-      <c r="R102" t="inlineStr">
-        <is>
-          <t>Intervention outcomes and spillover effects</t>
-        </is>
-      </c>
-      <c r="T102" t="inlineStr">
+      <c r="R103" t="inlineStr">
+        <is>
+          <t>Intervention outcomes and spillover effects</t>
+        </is>
+      </c>
+      <c r="T103" t="inlineStr">
         <is>
           <t>External</t>
         </is>
       </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="3" t="inlineStr">
-        <is>
-          <t>GMHO:0000259</t>
-        </is>
-      </c>
-      <c r="B103" s="3" t="inlineStr">
-        <is>
-          <t>mental process scale</t>
-        </is>
-      </c>
-      <c r="C103" s="3" t="inlineStr">
-        <is>
-          <t>A measurement scale that is used to measure mental processes.</t>
-        </is>
-      </c>
-      <c r="D103" s="3" t="inlineStr">
-        <is>
-          <t>measurement scale</t>
-        </is>
-      </c>
-      <c r="E103" s="3" t="n"/>
-      <c r="F103" s="3" t="n"/>
-      <c r="G103" s="3" t="n"/>
-      <c r="H103" s="3" t="n"/>
-      <c r="I103" s="3" t="n"/>
-      <c r="J103" s="3" t="inlineStr">
-        <is>
-          <t>Intervention outcomes and spillover effects</t>
-        </is>
-      </c>
-      <c r="K103" s="3" t="n"/>
-      <c r="L103" s="3" t="n"/>
-      <c r="M103" s="3" t="n"/>
-      <c r="N103" s="3" t="n"/>
-      <c r="O103" s="3" t="n"/>
-      <c r="P103" s="3" t="n"/>
-      <c r="Q103" s="3" t="inlineStr">
-        <is>
-          <t>LSR 3</t>
-        </is>
-      </c>
-      <c r="R103" s="3" t="inlineStr">
-        <is>
-          <t>Intervention outcomes and spillover effects</t>
-        </is>
-      </c>
-      <c r="S103" s="3" t="n"/>
-      <c r="T103" s="3" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="U103" s="3" t="n"/>
-      <c r="V103" s="3" t="n"/>
-      <c r="W103" s="3" t="n"/>
     </row>
     <row r="104">
       <c r="A104" s="3" t="inlineStr">
         <is>
-          <t>GMHO:0000236</t>
+          <t>GMHO:0000259</t>
         </is>
       </c>
       <c r="B104" s="3" t="inlineStr">
         <is>
-          <t>midpoint estimate for the mean difference of an outcome between the intervention and comparison condition</t>
+          <t>mental process scale</t>
         </is>
       </c>
       <c r="C104" s="3" t="inlineStr">
         <is>
-          <t>A point estimate about the mean difference between an intervention and comparison condition in a study.</t>
+          <t>A measurement scale that is used to measure mental processes.</t>
         </is>
       </c>
       <c r="D104" s="3" t="inlineStr">
         <is>
-          <t>point estimate</t>
+          <t>measurement scale</t>
         </is>
       </c>
       <c r="E104" s="3" t="n"/>
@@ -6676,31 +6672,27 @@
       </c>
       <c r="U104" s="3" t="n"/>
       <c r="V104" s="3" t="n"/>
-      <c r="W104" s="3" t="inlineStr">
-        <is>
-          <t>PS</t>
-        </is>
-      </c>
+      <c r="W104" s="3" t="n"/>
     </row>
     <row r="105">
       <c r="A105" s="3" t="inlineStr">
         <is>
-          <t>GMHO:0000183</t>
+          <t>GMHO:0000236</t>
         </is>
       </c>
       <c r="B105" s="3" t="inlineStr">
         <is>
-          <t>nausea following intervention</t>
+          <t>midpoint estimate for the mean difference of an outcome between the intervention and comparison condition</t>
         </is>
       </c>
       <c r="C105" s="3" t="inlineStr">
         <is>
-          <t>A digestive system adverse event following intervention that has an outcome of nausea, a gastric discomfort associated with the inclination to vomit</t>
+          <t>A point estimate about the mean difference between an intervention and comparison condition in a study.</t>
         </is>
       </c>
       <c r="D105" s="3" t="inlineStr">
         <is>
-          <t>digestive system adverse event following intervention</t>
+          <t>point estimate</t>
         </is>
       </c>
       <c r="E105" s="3" t="n"/>
@@ -6708,29 +6700,20 @@
       <c r="G105" s="3" t="n"/>
       <c r="H105" s="3" t="n"/>
       <c r="I105" s="3" t="n"/>
-      <c r="J105" s="3" t="n"/>
-      <c r="K105" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">cross reference: http://purl.obolibrary.org/obo/OAE_0000600
-</t>
-        </is>
-      </c>
-      <c r="L105" s="3" t="inlineStr">
-        <is>
-          <t>http://purl.obolibrary.org/obo/OAE_0000600</t>
-        </is>
-      </c>
-      <c r="M105" s="3" t="inlineStr">
-        <is>
-          <t>nausea</t>
-        </is>
-      </c>
+      <c r="J105" s="3" t="inlineStr">
+        <is>
+          <t>Intervention outcomes and spillover effects</t>
+        </is>
+      </c>
+      <c r="K105" s="3" t="n"/>
+      <c r="L105" s="3" t="n"/>
+      <c r="M105" s="3" t="n"/>
       <c r="N105" s="3" t="n"/>
       <c r="O105" s="3" t="n"/>
       <c r="P105" s="3" t="n"/>
       <c r="Q105" s="3" t="inlineStr">
         <is>
-          <t>LSR 1</t>
+          <t>LSR 3</t>
         </is>
       </c>
       <c r="R105" s="3" t="inlineStr">
@@ -6748,127 +6731,136 @@
       <c r="V105" s="3" t="n"/>
       <c r="W105" s="3" t="inlineStr">
         <is>
+          <t>PS</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="3" t="inlineStr">
+        <is>
+          <t>GMHO:0000183</t>
+        </is>
+      </c>
+      <c r="B106" s="3" t="inlineStr">
+        <is>
+          <t>nausea following intervention</t>
+        </is>
+      </c>
+      <c r="C106" s="3" t="inlineStr">
+        <is>
+          <t>A digestive system adverse event following intervention that has an outcome of nausea, a gastric discomfort associated with the inclination to vomit</t>
+        </is>
+      </c>
+      <c r="D106" s="3" t="inlineStr">
+        <is>
+          <t>digestive system adverse event following intervention</t>
+        </is>
+      </c>
+      <c r="E106" s="3" t="n"/>
+      <c r="F106" s="3" t="n"/>
+      <c r="G106" s="3" t="n"/>
+      <c r="H106" s="3" t="n"/>
+      <c r="I106" s="3" t="n"/>
+      <c r="J106" s="3" t="n"/>
+      <c r="K106" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">cross reference: http://purl.obolibrary.org/obo/OAE_0000600
+</t>
+        </is>
+      </c>
+      <c r="L106" s="3" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/OAE_0000600</t>
+        </is>
+      </c>
+      <c r="M106" s="3" t="inlineStr">
+        <is>
+          <t>nausea</t>
+        </is>
+      </c>
+      <c r="N106" s="3" t="n"/>
+      <c r="O106" s="3" t="n"/>
+      <c r="P106" s="3" t="n"/>
+      <c r="Q106" s="3" t="inlineStr">
+        <is>
+          <t>LSR 1</t>
+        </is>
+      </c>
+      <c r="R106" s="3" t="inlineStr">
+        <is>
+          <t>Intervention outcomes and spillover effects</t>
+        </is>
+      </c>
+      <c r="S106" s="3" t="n"/>
+      <c r="T106" s="3" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="U106" s="3" t="n"/>
+      <c r="V106" s="3" t="n"/>
+      <c r="W106" s="3" t="inlineStr">
+        <is>
           <t>PS; MS</t>
         </is>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" s="2" t="inlineStr">
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
         <is>
           <t>GMHO:0000069</t>
         </is>
       </c>
-      <c r="B106" s="2" t="inlineStr">
+      <c r="B107" s="2" t="inlineStr">
         <is>
           <t>negative psychotic disorder symptom</t>
         </is>
       </c>
-      <c r="C106" s="2" t="inlineStr">
+      <c r="C107" s="2" t="inlineStr">
         <is>
           <t>A psychotic disorder symptom that is characterized by the absence or decrease in ability or motivation to initiate plans, speak, express emotion of find pleasure.</t>
         </is>
       </c>
-      <c r="D106" s="2" t="inlineStr">
+      <c r="D107" s="2" t="inlineStr">
         <is>
           <t>psychotic disorder symptom</t>
         </is>
       </c>
-      <c r="E106" s="2" t="n"/>
-      <c r="F106" s="2" t="n"/>
-      <c r="G106" s="2" t="n"/>
-      <c r="H106" s="2" t="n"/>
-      <c r="I106" s="2" t="n"/>
-      <c r="J106" s="2" t="n"/>
-      <c r="K106" s="2" t="inlineStr">
+      <c r="E107" s="2" t="n"/>
+      <c r="F107" s="2" t="n"/>
+      <c r="G107" s="2" t="n"/>
+      <c r="H107" s="2" t="n"/>
+      <c r="I107" s="2" t="n"/>
+      <c r="J107" s="2" t="n"/>
+      <c r="K107" s="2" t="inlineStr">
         <is>
           <t>Based on https://www.psychiatry.org/patients-families/schizophrenia/what-is-schizophrenia</t>
         </is>
       </c>
-      <c r="L106" s="2" t="n"/>
-      <c r="M106" s="2" t="n"/>
-      <c r="N106" s="2" t="n"/>
-      <c r="O106" s="2" t="n"/>
-      <c r="P106" s="2" t="n"/>
-      <c r="Q106" s="2" t="inlineStr">
+      <c r="L107" s="2" t="n"/>
+      <c r="M107" s="2" t="n"/>
+      <c r="N107" s="2" t="n"/>
+      <c r="O107" s="2" t="n"/>
+      <c r="P107" s="2" t="n"/>
+      <c r="Q107" s="2" t="inlineStr">
         <is>
           <t>LSR 3</t>
         </is>
       </c>
-      <c r="R106" s="2" t="inlineStr">
-        <is>
-          <t>Intervention outcomes and spillover effects</t>
-        </is>
-      </c>
-      <c r="S106" s="2" t="n"/>
-      <c r="T106" s="2" t="inlineStr">
+      <c r="R107" s="2" t="inlineStr">
+        <is>
+          <t>Intervention outcomes and spillover effects</t>
+        </is>
+      </c>
+      <c r="S107" s="2" t="n"/>
+      <c r="T107" s="2" t="inlineStr">
         <is>
           <t>Obsolete</t>
         </is>
       </c>
-      <c r="U106" s="2" t="n"/>
-      <c r="V106" s="2" t="n"/>
-      <c r="W106" s="2" t="inlineStr">
-        <is>
-          <t>PS</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="3" t="inlineStr">
-        <is>
-          <t>GMHO:0000070</t>
-        </is>
-      </c>
-      <c r="B107" s="3" t="inlineStr">
-        <is>
-          <t>negative psychotic disorder symptom severity</t>
-        </is>
-      </c>
-      <c r="C107" s="3" t="inlineStr">
-        <is>
-          <t>Psychotic disorder symptom severity that is associated with negative psychotic disorder symptoms.</t>
-        </is>
-      </c>
-      <c r="D107" s="3" t="inlineStr">
-        <is>
-          <t>psychotic disorder symptom severity</t>
-        </is>
-      </c>
-      <c r="E107" s="3" t="n"/>
-      <c r="F107" s="3" t="n"/>
-      <c r="G107" s="3" t="n"/>
-      <c r="H107" s="3" t="n"/>
-      <c r="I107" s="3" t="n"/>
-      <c r="J107" s="3" t="inlineStr">
-        <is>
-          <t>Intervention outcomes and spillover effects</t>
-        </is>
-      </c>
-      <c r="K107" s="3" t="n"/>
-      <c r="L107" s="3" t="n"/>
-      <c r="M107" s="3" t="n"/>
-      <c r="N107" s="3" t="n"/>
-      <c r="O107" s="3" t="n"/>
-      <c r="P107" s="3" t="n"/>
-      <c r="Q107" s="3" t="inlineStr">
-        <is>
-          <t>LSR 3</t>
-        </is>
-      </c>
-      <c r="R107" s="3" t="inlineStr">
-        <is>
-          <t>Intervention outcomes and spillover effects</t>
-        </is>
-      </c>
-      <c r="S107" s="3" t="n"/>
-      <c r="T107" s="3" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="U107" s="3" t="n"/>
-      <c r="V107" s="3" t="n"/>
-      <c r="W107" s="3" t="inlineStr">
+      <c r="U107" s="2" t="n"/>
+      <c r="V107" s="2" t="n"/>
+      <c r="W107" s="2" t="inlineStr">
         <is>
           <t>PS</t>
         </is>
@@ -6877,22 +6869,22 @@
     <row r="108">
       <c r="A108" s="3" t="inlineStr">
         <is>
-          <t>GMHO:0000225</t>
+          <t>GMHO:0000070</t>
         </is>
       </c>
       <c r="B108" s="3" t="inlineStr">
         <is>
-          <t>negative psychotic disorder symptom severity scale</t>
+          <t>negative psychotic disorder symptom severity</t>
         </is>
       </c>
       <c r="C108" s="3" t="inlineStr">
         <is>
-          <t>A psychotic disorder symptom severity scale that is associated with negative psychotic disorder symptoms.</t>
+          <t>Psychotic disorder symptom severity that is associated with negative psychotic disorder symptoms.</t>
         </is>
       </c>
       <c r="D108" s="3" t="inlineStr">
         <is>
-          <t>psychotic disorder symptom severity scale</t>
+          <t>psychotic disorder symptom severity</t>
         </is>
       </c>
       <c r="E108" s="3" t="n"/>
@@ -6936,179 +6928,183 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="2" t="inlineStr">
+      <c r="A109" s="3" t="inlineStr">
+        <is>
+          <t>GMHO:0000225</t>
+        </is>
+      </c>
+      <c r="B109" s="3" t="inlineStr">
+        <is>
+          <t>negative psychotic disorder symptom severity scale</t>
+        </is>
+      </c>
+      <c r="C109" s="3" t="inlineStr">
+        <is>
+          <t>A psychotic disorder symptom severity scale that is associated with negative psychotic disorder symptoms.</t>
+        </is>
+      </c>
+      <c r="D109" s="3" t="inlineStr">
+        <is>
+          <t>psychotic disorder symptom severity scale</t>
+        </is>
+      </c>
+      <c r="E109" s="3" t="n"/>
+      <c r="F109" s="3" t="n"/>
+      <c r="G109" s="3" t="n"/>
+      <c r="H109" s="3" t="n"/>
+      <c r="I109" s="3" t="n"/>
+      <c r="J109" s="3" t="inlineStr">
+        <is>
+          <t>Intervention outcomes and spillover effects</t>
+        </is>
+      </c>
+      <c r="K109" s="3" t="n"/>
+      <c r="L109" s="3" t="n"/>
+      <c r="M109" s="3" t="n"/>
+      <c r="N109" s="3" t="n"/>
+      <c r="O109" s="3" t="n"/>
+      <c r="P109" s="3" t="n"/>
+      <c r="Q109" s="3" t="inlineStr">
+        <is>
+          <t>LSR 3</t>
+        </is>
+      </c>
+      <c r="R109" s="3" t="inlineStr">
+        <is>
+          <t>Intervention outcomes and spillover effects</t>
+        </is>
+      </c>
+      <c r="S109" s="3" t="n"/>
+      <c r="T109" s="3" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="U109" s="3" t="n"/>
+      <c r="V109" s="3" t="n"/>
+      <c r="W109" s="3" t="inlineStr">
+        <is>
+          <t>PS</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
         <is>
           <t>GMHO:0000071</t>
         </is>
       </c>
-      <c r="B109" s="2" t="inlineStr">
+      <c r="B110" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">neuroleptic-induced parkinsonism following intervention </t>
         </is>
       </c>
-      <c r="C109" s="2" t="inlineStr">
+      <c r="C110" s="2" t="inlineStr">
         <is>
           <t>A drug-induced movement disorder following intervention that involves experiencing slowness of movement, tremors and rigidity.</t>
         </is>
       </c>
-      <c r="D109" s="2" t="inlineStr">
+      <c r="D110" s="2" t="inlineStr">
         <is>
           <t>drug-induced movement disorder following intervention</t>
         </is>
       </c>
-      <c r="E109" s="2" t="n"/>
-      <c r="F109" s="2" t="n"/>
-      <c r="G109" s="2" t="n"/>
-      <c r="H109" s="2" t="n"/>
-      <c r="I109" s="2" t="n"/>
-      <c r="J109" s="2" t="n"/>
-      <c r="K109" s="2" t="inlineStr">
+      <c r="E110" s="2" t="n"/>
+      <c r="F110" s="2" t="n"/>
+      <c r="G110" s="2" t="n"/>
+      <c r="H110" s="2" t="n"/>
+      <c r="I110" s="2" t="n"/>
+      <c r="J110" s="2" t="n"/>
+      <c r="K110" s="2" t="inlineStr">
         <is>
           <t>Based on https://link.springer.com/article/10.1007/s007020100006</t>
         </is>
       </c>
-      <c r="L109" s="2" t="n"/>
-      <c r="M109" s="2" t="n"/>
-      <c r="N109" s="2" t="n"/>
-      <c r="O109" s="2" t="n"/>
-      <c r="P109" s="2" t="n"/>
-      <c r="Q109" s="2" t="inlineStr">
+      <c r="L110" s="2" t="n"/>
+      <c r="M110" s="2" t="n"/>
+      <c r="N110" s="2" t="n"/>
+      <c r="O110" s="2" t="n"/>
+      <c r="P110" s="2" t="n"/>
+      <c r="Q110" s="2" t="inlineStr">
         <is>
           <t>LSR 3</t>
         </is>
       </c>
-      <c r="R109" s="2" t="inlineStr">
-        <is>
-          <t>Intervention outcomes and spillover effects</t>
-        </is>
-      </c>
-      <c r="S109" s="2" t="n"/>
-      <c r="T109" s="2" t="inlineStr">
+      <c r="R110" s="2" t="inlineStr">
+        <is>
+          <t>Intervention outcomes and spillover effects</t>
+        </is>
+      </c>
+      <c r="S110" s="2" t="n"/>
+      <c r="T110" s="2" t="inlineStr">
         <is>
           <t>Obsolete</t>
         </is>
       </c>
-      <c r="U109" s="2" t="n"/>
-      <c r="V109" s="2" t="n"/>
-      <c r="W109" s="2" t="inlineStr">
-        <is>
-          <t>PS</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" s="3" t="inlineStr">
+      <c r="U110" s="2" t="n"/>
+      <c r="V110" s="2" t="n"/>
+      <c r="W110" s="2" t="inlineStr">
+        <is>
+          <t>PS</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="3" t="inlineStr">
         <is>
           <t>GMHO:0000072</t>
         </is>
       </c>
-      <c r="B110" s="3" t="inlineStr">
+      <c r="B111" s="3" t="inlineStr">
         <is>
           <t>number of participant drop-out due to adverse events</t>
         </is>
       </c>
-      <c r="C110" s="3" t="inlineStr">
+      <c r="C111" s="3" t="inlineStr">
         <is>
           <t>Number of participant drop-out from the study as a result the participants experiencing some adverse event.</t>
         </is>
       </c>
-      <c r="D110" s="3" t="inlineStr">
+      <c r="D111" s="3" t="inlineStr">
         <is>
           <t>number of participant drop-out from study</t>
         </is>
       </c>
-      <c r="E110" s="3" t="n"/>
-      <c r="F110" s="3" t="n"/>
-      <c r="G110" s="3" t="n"/>
-      <c r="H110" s="3" t="n"/>
-      <c r="I110" s="3" t="n"/>
-      <c r="J110" s="3" t="inlineStr">
-        <is>
-          <t>Intervention outcomes and spillover effects</t>
-        </is>
-      </c>
-      <c r="K110" s="3" t="n"/>
-      <c r="L110" s="3" t="n"/>
-      <c r="M110" s="3" t="n"/>
-      <c r="N110" s="3" t="n"/>
-      <c r="O110" s="3" t="n"/>
-      <c r="P110" s="3" t="n"/>
-      <c r="Q110" s="3" t="inlineStr">
+      <c r="E111" s="3" t="n"/>
+      <c r="F111" s="3" t="n"/>
+      <c r="G111" s="3" t="n"/>
+      <c r="H111" s="3" t="n"/>
+      <c r="I111" s="3" t="n"/>
+      <c r="J111" s="3" t="inlineStr">
+        <is>
+          <t>Intervention outcomes and spillover effects</t>
+        </is>
+      </c>
+      <c r="K111" s="3" t="n"/>
+      <c r="L111" s="3" t="n"/>
+      <c r="M111" s="3" t="n"/>
+      <c r="N111" s="3" t="n"/>
+      <c r="O111" s="3" t="n"/>
+      <c r="P111" s="3" t="n"/>
+      <c r="Q111" s="3" t="inlineStr">
         <is>
           <t>LSR 1; LSR 3</t>
         </is>
       </c>
-      <c r="R110" s="3" t="inlineStr">
-        <is>
-          <t>Intervention outcomes and spillover effects</t>
-        </is>
-      </c>
-      <c r="S110" s="3" t="n"/>
-      <c r="T110" s="3" t="inlineStr">
+      <c r="R111" s="3" t="inlineStr">
+        <is>
+          <t>Intervention outcomes and spillover effects</t>
+        </is>
+      </c>
+      <c r="S111" s="3" t="n"/>
+      <c r="T111" s="3" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="U110" s="3" t="n"/>
-      <c r="V110" s="3" t="n"/>
-      <c r="W110" s="3" t="inlineStr">
-        <is>
-          <t>PS</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" s="2" t="inlineStr">
-        <is>
-          <t>GMHO:0000073</t>
-        </is>
-      </c>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t>number of participant drop-out due to inefficacy</t>
-        </is>
-      </c>
-      <c r="C111" s="2" t="inlineStr">
-        <is>
-          <t>Number of participant drop-out from the intervention as a result of the intervention failing to produce the desired effect.</t>
-        </is>
-      </c>
-      <c r="D111" s="2" t="inlineStr">
-        <is>
-          <t>number of participant drop-out from intervention</t>
-        </is>
-      </c>
-      <c r="E111" s="2" t="n"/>
-      <c r="F111" s="2" t="n"/>
-      <c r="G111" s="2" t="n"/>
-      <c r="H111" s="2" t="n"/>
-      <c r="I111" s="2" t="n"/>
-      <c r="J111" s="2" t="n"/>
-      <c r="K111" s="2" t="n"/>
-      <c r="L111" s="2" t="n"/>
-      <c r="M111" s="2" t="n"/>
-      <c r="N111" s="2" t="n"/>
-      <c r="O111" s="2" t="n"/>
-      <c r="P111" s="2" t="n"/>
-      <c r="Q111" s="2" t="inlineStr">
-        <is>
-          <t>LSR 3</t>
-        </is>
-      </c>
-      <c r="R111" s="2" t="inlineStr">
-        <is>
-          <t>Intervention outcomes and spillover effects</t>
-        </is>
-      </c>
-      <c r="S111" s="2" t="n"/>
-      <c r="T111" s="2" t="inlineStr">
-        <is>
-          <t>Obsolete</t>
-        </is>
-      </c>
-      <c r="U111" s="2" t="n"/>
-      <c r="V111" s="2" t="n"/>
-      <c r="W111" s="2" t="inlineStr">
+      <c r="U111" s="3" t="n"/>
+      <c r="V111" s="3" t="n"/>
+      <c r="W111" s="3" t="inlineStr">
         <is>
           <t>PS</t>
         </is>
@@ -7117,22 +7113,22 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>GMHO:0000074</t>
+          <t>GMHO:0000073</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>number of participant drop-out due to side-effects</t>
+          <t>number of participant drop-out due to inefficacy</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>Number of participant drop-out due to adverse events that are experienced following the intervention.</t>
+          <t>Number of participant drop-out from the intervention as a result of the intervention failing to produce the desired effect.</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
         <is>
-          <t>number of participant drop-out due to adverse events</t>
+          <t>number of participant drop-out from intervention</t>
         </is>
       </c>
       <c r="E112" s="2" t="n"/>
@@ -7149,7 +7145,7 @@
       <c r="P112" s="2" t="n"/>
       <c r="Q112" s="2" t="inlineStr">
         <is>
-          <t>LSR 1; LSR 3</t>
+          <t>LSR 3</t>
         </is>
       </c>
       <c r="R112" s="2" t="inlineStr">
@@ -7174,22 +7170,22 @@
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>GMHO:0000134</t>
+          <t>GMHO:0000074</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>number of participant drop-out from intervention arm</t>
+          <t>number of participant drop-out due to side-effects</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>Number of intervention participants who discontinue participating in an intervention arm.</t>
+          <t>Number of participant drop-out due to adverse events that are experienced following the intervention.</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
         <is>
-          <t>number of intervention participants</t>
+          <t>number of participant drop-out due to adverse events</t>
         </is>
       </c>
       <c r="E113" s="2" t="n"/>
@@ -7206,7 +7202,7 @@
       <c r="P113" s="2" t="n"/>
       <c r="Q113" s="2" t="inlineStr">
         <is>
-          <t>LSR 1</t>
+          <t>LSR 1; LSR 3</t>
         </is>
       </c>
       <c r="R113" s="2" t="inlineStr">
@@ -7229,61 +7225,57 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="3" t="inlineStr">
-        <is>
-          <t>GMHO:0000075</t>
-        </is>
-      </c>
-      <c r="B114" s="3" t="inlineStr">
-        <is>
-          <t>number of participant drop-out from study</t>
-        </is>
-      </c>
-      <c r="C114" s="3" t="inlineStr">
-        <is>
-          <t>Number of study participants who withdraw from or cannot complete a study.</t>
-        </is>
-      </c>
-      <c r="D114" s="3" t="inlineStr">
-        <is>
-          <t>number of study participants</t>
-        </is>
-      </c>
-      <c r="E114" s="3" t="n"/>
-      <c r="F114" s="3" t="n"/>
-      <c r="G114" s="3" t="n"/>
-      <c r="H114" s="3" t="n"/>
-      <c r="I114" s="3" t="n"/>
-      <c r="J114" s="3" t="inlineStr">
-        <is>
-          <t>Intervention outcomes and spillover effects</t>
-        </is>
-      </c>
-      <c r="K114" s="3" t="n"/>
-      <c r="L114" s="3" t="n"/>
-      <c r="M114" s="3" t="n"/>
-      <c r="N114" s="3" t="n"/>
-      <c r="O114" s="3" t="n"/>
-      <c r="P114" s="3" t="n"/>
-      <c r="Q114" s="3" t="inlineStr">
-        <is>
-          <t>LSR 1; LSR 2; LSR 3</t>
-        </is>
-      </c>
-      <c r="R114" s="3" t="inlineStr">
-        <is>
-          <t>Intervention outcomes and spillover effects</t>
-        </is>
-      </c>
-      <c r="S114" s="3" t="n"/>
-      <c r="T114" s="3" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="U114" s="3" t="n"/>
-      <c r="V114" s="3" t="n"/>
-      <c r="W114" s="3" t="inlineStr">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>GMHO:0000134</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>number of participant drop-out from intervention arm</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>Number of intervention participants who discontinue participating in an intervention arm.</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
+        <is>
+          <t>number of intervention participants</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="n"/>
+      <c r="F114" s="2" t="n"/>
+      <c r="G114" s="2" t="n"/>
+      <c r="H114" s="2" t="n"/>
+      <c r="I114" s="2" t="n"/>
+      <c r="J114" s="2" t="n"/>
+      <c r="K114" s="2" t="n"/>
+      <c r="L114" s="2" t="n"/>
+      <c r="M114" s="2" t="n"/>
+      <c r="N114" s="2" t="n"/>
+      <c r="O114" s="2" t="n"/>
+      <c r="P114" s="2" t="n"/>
+      <c r="Q114" s="2" t="inlineStr">
+        <is>
+          <t>LSR 1</t>
+        </is>
+      </c>
+      <c r="R114" s="2" t="inlineStr">
+        <is>
+          <t>Intervention outcomes and spillover effects</t>
+        </is>
+      </c>
+      <c r="S114" s="2" t="n"/>
+      <c r="T114" s="2" t="inlineStr">
+        <is>
+          <t>Obsolete</t>
+        </is>
+      </c>
+      <c r="U114" s="2" t="n"/>
+      <c r="V114" s="2" t="n"/>
+      <c r="W114" s="2" t="inlineStr">
         <is>
           <t>PS</t>
         </is>
@@ -7292,17 +7284,17 @@
     <row r="115">
       <c r="A115" s="3" t="inlineStr">
         <is>
-          <t>GMHO:0000258</t>
+          <t>GMHO:0000075</t>
         </is>
       </c>
       <c r="B115" s="3" t="inlineStr">
         <is>
-          <t>number of participants with drop-out assessment</t>
+          <t>number of participant drop-out from study</t>
         </is>
       </c>
       <c r="C115" s="3" t="inlineStr">
         <is>
-          <t>Number of study participants for whom a drop-out assessment was made.</t>
+          <t>Number of study participants who withdraw from or cannot complete a study.</t>
         </is>
       </c>
       <c r="D115" s="3" t="inlineStr">
@@ -7311,11 +7303,7 @@
         </is>
       </c>
       <c r="E115" s="3" t="n"/>
-      <c r="F115" s="3" t="inlineStr">
-        <is>
-          <t>The number of participants in the study who were evaluated to determine whether they dropped out.</t>
-        </is>
-      </c>
+      <c r="F115" s="3" t="n"/>
       <c r="G115" s="3" t="n"/>
       <c r="H115" s="3" t="n"/>
       <c r="I115" s="3" t="n"/>
@@ -7332,7 +7320,7 @@
       <c r="P115" s="3" t="n"/>
       <c r="Q115" s="3" t="inlineStr">
         <is>
-          <t>LSR 3</t>
+          <t>LSR 1; LSR 2; LSR 3</t>
         </is>
       </c>
       <c r="R115" s="3" t="inlineStr">
@@ -7348,22 +7336,26 @@
       </c>
       <c r="U115" s="3" t="n"/>
       <c r="V115" s="3" t="n"/>
-      <c r="W115" s="3" t="n"/>
+      <c r="W115" s="3" t="inlineStr">
+        <is>
+          <t>PS</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="3" t="inlineStr">
         <is>
-          <t>GMHO:0000206</t>
+          <t>GMHO:0000258</t>
         </is>
       </c>
       <c r="B116" s="3" t="inlineStr">
         <is>
-          <t>number of participants with measurement</t>
+          <t>number of participants with drop-out assessment</t>
         </is>
       </c>
       <c r="C116" s="3" t="inlineStr">
         <is>
-          <t>Number of study participants for whom a measurement was made.</t>
+          <t>Number of study participants for whom a drop-out assessment was made.</t>
         </is>
       </c>
       <c r="D116" s="3" t="inlineStr">
@@ -7372,11 +7364,19 @@
         </is>
       </c>
       <c r="E116" s="3" t="n"/>
-      <c r="F116" s="3" t="n"/>
+      <c r="F116" s="3" t="inlineStr">
+        <is>
+          <t>The number of participants in the study who were evaluated to determine whether they dropped out.</t>
+        </is>
+      </c>
       <c r="G116" s="3" t="n"/>
       <c r="H116" s="3" t="n"/>
       <c r="I116" s="3" t="n"/>
-      <c r="J116" s="3" t="n"/>
+      <c r="J116" s="3" t="inlineStr">
+        <is>
+          <t>Intervention outcomes and spillover effects</t>
+        </is>
+      </c>
       <c r="K116" s="3" t="n"/>
       <c r="L116" s="3" t="n"/>
       <c r="M116" s="3" t="n"/>
@@ -7385,7 +7385,7 @@
       <c r="P116" s="3" t="n"/>
       <c r="Q116" s="3" t="inlineStr">
         <is>
-          <t>LSR 1, LSR 2; LSR 3</t>
+          <t>LSR 3</t>
         </is>
       </c>
       <c r="R116" s="3" t="inlineStr">
@@ -7401,26 +7401,22 @@
       </c>
       <c r="U116" s="3" t="n"/>
       <c r="V116" s="3" t="n"/>
-      <c r="W116" s="3" t="inlineStr">
-        <is>
-          <t>PS; MS</t>
-        </is>
-      </c>
+      <c r="W116" s="3" t="n"/>
     </row>
     <row r="117">
       <c r="A117" s="3" t="inlineStr">
         <is>
-          <t>GMHO:0000214</t>
+          <t>GMHO:0000206</t>
         </is>
       </c>
       <c r="B117" s="3" t="inlineStr">
         <is>
-          <t>number of participants with specific outcome</t>
+          <t>number of participants with measurement</t>
         </is>
       </c>
       <c r="C117" s="3" t="inlineStr">
         <is>
-          <t>Number of study participants for whom an outcome has been identified within a study.</t>
+          <t>Number of study participants for whom a measurement was made.</t>
         </is>
       </c>
       <c r="D117" s="3" t="inlineStr">
@@ -7433,11 +7429,7 @@
       <c r="G117" s="3" t="n"/>
       <c r="H117" s="3" t="n"/>
       <c r="I117" s="3" t="n"/>
-      <c r="J117" s="3" t="inlineStr">
-        <is>
-          <t>Intervention outcomes and spillover effects</t>
-        </is>
-      </c>
+      <c r="J117" s="3" t="n"/>
       <c r="K117" s="3" t="n"/>
       <c r="L117" s="3" t="n"/>
       <c r="M117" s="3" t="n"/>
@@ -7446,7 +7438,7 @@
       <c r="P117" s="3" t="n"/>
       <c r="Q117" s="3" t="inlineStr">
         <is>
-          <t>LSR 1, LSR 3</t>
+          <t>LSR 1, LSR 2; LSR 3</t>
         </is>
       </c>
       <c r="R117" s="3" t="inlineStr">
@@ -7464,421 +7456,413 @@
       <c r="V117" s="3" t="n"/>
       <c r="W117" s="3" t="inlineStr">
         <is>
-          <t>PS</t>
+          <t>PS; MS</t>
         </is>
       </c>
     </row>
     <row r="118">
-      <c r="A118" t="inlineStr">
+      <c r="A118" s="3" t="inlineStr">
+        <is>
+          <t>GMHO:0000214</t>
+        </is>
+      </c>
+      <c r="B118" s="3" t="inlineStr">
+        <is>
+          <t>number of participants with specific outcome</t>
+        </is>
+      </c>
+      <c r="C118" s="3" t="inlineStr">
+        <is>
+          <t>Number of study participants for whom an outcome has been identified within a study.</t>
+        </is>
+      </c>
+      <c r="D118" s="3" t="inlineStr">
+        <is>
+          <t>number of study participants</t>
+        </is>
+      </c>
+      <c r="E118" s="3" t="n"/>
+      <c r="F118" s="3" t="n"/>
+      <c r="G118" s="3" t="n"/>
+      <c r="H118" s="3" t="n"/>
+      <c r="I118" s="3" t="n"/>
+      <c r="J118" s="3" t="inlineStr">
+        <is>
+          <t>Intervention outcomes and spillover effects</t>
+        </is>
+      </c>
+      <c r="K118" s="3" t="n"/>
+      <c r="L118" s="3" t="n"/>
+      <c r="M118" s="3" t="n"/>
+      <c r="N118" s="3" t="n"/>
+      <c r="O118" s="3" t="n"/>
+      <c r="P118" s="3" t="n"/>
+      <c r="Q118" s="3" t="inlineStr">
+        <is>
+          <t>LSR 1, LSR 3</t>
+        </is>
+      </c>
+      <c r="R118" s="3" t="inlineStr">
+        <is>
+          <t>Intervention outcomes and spillover effects</t>
+        </is>
+      </c>
+      <c r="S118" s="3" t="n"/>
+      <c r="T118" s="3" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="U118" s="3" t="n"/>
+      <c r="V118" s="3" t="n"/>
+      <c r="W118" s="3" t="inlineStr">
+        <is>
+          <t>PS</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
         <is>
           <t>BFO:0000038</t>
         </is>
       </c>
-      <c r="B118" t="inlineStr">
+      <c r="B119" t="inlineStr">
         <is>
           <t>one-dimensional temporal region</t>
         </is>
       </c>
-      <c r="C118" t="inlineStr">
+      <c r="C119" t="inlineStr">
         <is>
           <t xml:space="preserve">A one-dimensional temporal region is a temporal region that is extended. </t>
         </is>
       </c>
-      <c r="D118" t="inlineStr">
+      <c r="D119" t="inlineStr">
         <is>
           <t>temporal region</t>
         </is>
       </c>
-      <c r="Q118" t="inlineStr">
+      <c r="Q119" t="inlineStr">
         <is>
           <t>LSR 1</t>
         </is>
       </c>
-      <c r="R118" t="inlineStr">
-        <is>
-          <t>Intervention outcomes and spillover effects</t>
-        </is>
-      </c>
-      <c r="T118" t="inlineStr">
+      <c r="R119" t="inlineStr">
+        <is>
+          <t>Intervention outcomes and spillover effects</t>
+        </is>
+      </c>
+      <c r="T119" t="inlineStr">
         <is>
           <t>External</t>
         </is>
       </c>
-      <c r="W118" t="inlineStr">
-        <is>
-          <t>PS</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" s="3" t="inlineStr">
+      <c r="W119" t="inlineStr">
+        <is>
+          <t>PS</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="3" t="inlineStr">
         <is>
           <t>GMHO:0000184</t>
         </is>
       </c>
-      <c r="B119" s="3" t="inlineStr">
+      <c r="B120" s="3" t="inlineStr">
         <is>
           <t>pain following intervention</t>
         </is>
       </c>
-      <c r="C119" s="3" t="inlineStr">
+      <c r="C120" s="3" t="inlineStr">
         <is>
           <t>An adverse event following an intervention that has an outcome of pain.</t>
         </is>
       </c>
-      <c r="D119" s="3" t="inlineStr">
+      <c r="D120" s="3" t="inlineStr">
         <is>
           <t>adverse event following an intervention</t>
         </is>
       </c>
-      <c r="E119" s="3" t="n"/>
-      <c r="F119" s="3" t="n"/>
-      <c r="G119" s="3" t="n"/>
-      <c r="H119" s="3" t="n"/>
-      <c r="I119" s="3" t="n"/>
-      <c r="J119" s="3" t="n"/>
-      <c r="K119" s="3" t="inlineStr">
+      <c r="E120" s="3" t="n"/>
+      <c r="F120" s="3" t="n"/>
+      <c r="G120" s="3" t="n"/>
+      <c r="H120" s="3" t="n"/>
+      <c r="I120" s="3" t="n"/>
+      <c r="J120" s="3" t="n"/>
+      <c r="K120" s="3" t="inlineStr">
         <is>
           <t>cross-reference: http://purl.obolibrary.org/obo/OAE_0000374</t>
         </is>
       </c>
-      <c r="L119" s="3" t="inlineStr">
+      <c r="L120" s="3" t="inlineStr">
         <is>
           <t>http://purl.obolibrary.org/obo/OAE_0000374</t>
         </is>
       </c>
-      <c r="M119" s="3" t="inlineStr">
+      <c r="M120" s="3" t="inlineStr">
         <is>
           <t>pain</t>
         </is>
       </c>
-      <c r="N119" s="3" t="n"/>
-      <c r="O119" s="3" t="n"/>
-      <c r="P119" s="3" t="n"/>
-      <c r="Q119" s="3" t="inlineStr">
+      <c r="N120" s="3" t="n"/>
+      <c r="O120" s="3" t="n"/>
+      <c r="P120" s="3" t="n"/>
+      <c r="Q120" s="3" t="inlineStr">
         <is>
           <t>LSR 1, LSR 3</t>
         </is>
       </c>
-      <c r="R119" s="3" t="inlineStr">
-        <is>
-          <t>Intervention outcomes and spillover effects</t>
-        </is>
-      </c>
-      <c r="S119" s="3" t="n"/>
-      <c r="T119" s="3" t="inlineStr">
+      <c r="R120" s="3" t="inlineStr">
+        <is>
+          <t>Intervention outcomes and spillover effects</t>
+        </is>
+      </c>
+      <c r="S120" s="3" t="n"/>
+      <c r="T120" s="3" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="U119" s="3" t="n"/>
-      <c r="V119" s="3" t="n"/>
-      <c r="W119" s="3" t="inlineStr">
+      <c r="U120" s="3" t="n"/>
+      <c r="V120" s="3" t="n"/>
+      <c r="W120" s="3" t="inlineStr">
         <is>
           <t>PS; MS</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>OGMS:0000061</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>pathological bodily process</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>A bodily process that is clinically abnormal.</t>
-        </is>
-      </c>
-      <c r="D120" t="inlineStr">
-        <is>
-          <t>bodily process</t>
-        </is>
-      </c>
-      <c r="J120" t="inlineStr">
-        <is>
-          <t>Intervention outcomes and spillover effects</t>
-        </is>
-      </c>
-      <c r="Q120" t="inlineStr">
-        <is>
-          <t>LSR 1; LSR 3</t>
-        </is>
-      </c>
-      <c r="R120" t="inlineStr">
-        <is>
-          <t>Intervention outcomes and spillover effects</t>
-        </is>
-      </c>
-      <c r="T120" t="inlineStr">
-        <is>
-          <t>External</t>
-        </is>
-      </c>
-      <c r="W120" t="inlineStr">
-        <is>
-          <t>PS</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
+          <t>OGMS:0000061</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>pathological bodily process</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>A bodily process that is clinically abnormal.</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>bodily process</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>Intervention outcomes and spillover effects</t>
+        </is>
+      </c>
+      <c r="Q121" t="inlineStr">
+        <is>
+          <t>LSR 1; LSR 3</t>
+        </is>
+      </c>
+      <c r="R121" t="inlineStr">
+        <is>
+          <t>Intervention outcomes and spillover effects</t>
+        </is>
+      </c>
+      <c r="T121" t="inlineStr">
+        <is>
+          <t>External</t>
+        </is>
+      </c>
+      <c r="W121" t="inlineStr">
+        <is>
+          <t>PS</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
           <t>STATO:0000599</t>
         </is>
       </c>
-      <c r="B121" t="inlineStr">
+      <c r="B122" t="inlineStr">
         <is>
           <t>point estimate</t>
         </is>
       </c>
-      <c r="C121" t="inlineStr">
+      <c r="C122" t="inlineStr">
         <is>
           <t>a point estimate is a data item which provides a particular value evaluating a population parameter.</t>
         </is>
       </c>
-      <c r="D121" t="inlineStr">
+      <c r="D122" t="inlineStr">
         <is>
           <t>estimate</t>
         </is>
       </c>
-      <c r="J121" t="inlineStr">
-        <is>
-          <t>Intervention outcomes and spillover effects</t>
-        </is>
-      </c>
-      <c r="Q121" t="inlineStr">
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>Intervention outcomes and spillover effects</t>
+        </is>
+      </c>
+      <c r="Q122" t="inlineStr">
         <is>
           <t>LSR 3</t>
         </is>
       </c>
-      <c r="R121" t="inlineStr">
-        <is>
-          <t>Intervention outcomes and spillover effects</t>
-        </is>
-      </c>
-      <c r="T121" t="inlineStr">
+      <c r="R122" t="inlineStr">
+        <is>
+          <t>Intervention outcomes and spillover effects</t>
+        </is>
+      </c>
+      <c r="T122" t="inlineStr">
         <is>
           <t>External</t>
         </is>
       </c>
-      <c r="W121" t="inlineStr">
-        <is>
-          <t>PS</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" s="3" t="inlineStr">
+      <c r="W122" t="inlineStr">
+        <is>
+          <t>PS</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="3" t="inlineStr">
         <is>
           <t>GMHO:0000076</t>
         </is>
       </c>
-      <c r="B122" s="3" t="inlineStr">
+      <c r="B123" s="3" t="inlineStr">
         <is>
           <t>positive intervention outcome</t>
         </is>
       </c>
-      <c r="C122" s="3" t="inlineStr">
+      <c r="C123" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">An intervention outcome that is positively influenced by the intervention. </t>
         </is>
       </c>
-      <c r="D122" s="3" t="inlineStr">
+      <c r="D123" s="3" t="inlineStr">
         <is>
           <t>intervention outcome</t>
         </is>
       </c>
-      <c r="E122" s="3" t="n"/>
-      <c r="F122" s="3" t="n"/>
-      <c r="G122" s="3" t="n"/>
-      <c r="H122" s="3" t="n"/>
-      <c r="I122" s="3" t="n"/>
-      <c r="J122" s="3" t="n"/>
-      <c r="K122" s="3" t="n"/>
-      <c r="L122" s="3" t="n"/>
-      <c r="M122" s="3" t="n"/>
-      <c r="N122" s="3" t="n"/>
-      <c r="O122" s="3" t="n"/>
-      <c r="P122" s="3" t="n"/>
-      <c r="Q122" s="3" t="inlineStr">
+      <c r="E123" s="3" t="n"/>
+      <c r="F123" s="3" t="n"/>
+      <c r="G123" s="3" t="n"/>
+      <c r="H123" s="3" t="n"/>
+      <c r="I123" s="3" t="n"/>
+      <c r="J123" s="3" t="n"/>
+      <c r="K123" s="3" t="n"/>
+      <c r="L123" s="3" t="n"/>
+      <c r="M123" s="3" t="n"/>
+      <c r="N123" s="3" t="n"/>
+      <c r="O123" s="3" t="n"/>
+      <c r="P123" s="3" t="n"/>
+      <c r="Q123" s="3" t="inlineStr">
         <is>
           <t>LSR 3</t>
         </is>
       </c>
-      <c r="R122" s="3" t="inlineStr">
-        <is>
-          <t>Intervention outcomes and spillover effects</t>
-        </is>
-      </c>
-      <c r="S122" s="3" t="n"/>
-      <c r="T122" s="3" t="inlineStr">
+      <c r="R123" s="3" t="inlineStr">
+        <is>
+          <t>Intervention outcomes and spillover effects</t>
+        </is>
+      </c>
+      <c r="S123" s="3" t="n"/>
+      <c r="T123" s="3" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="U122" s="3" t="n"/>
-      <c r="V122" s="3" t="n"/>
-      <c r="W122" s="3" t="inlineStr">
-        <is>
-          <t>PS</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" s="2" t="inlineStr">
+      <c r="U123" s="3" t="n"/>
+      <c r="V123" s="3" t="n"/>
+      <c r="W123" s="3" t="inlineStr">
+        <is>
+          <t>PS</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
         <is>
           <t>GMHO:0000077</t>
         </is>
       </c>
-      <c r="B123" s="2" t="inlineStr">
+      <c r="B124" s="2" t="inlineStr">
         <is>
           <t>positive psychotic disorder symptom</t>
         </is>
       </c>
-      <c r="C123" s="2" t="inlineStr">
+      <c r="C124" s="2" t="inlineStr">
         <is>
           <t>A psychotic disorder symptom that is characterized by the presence of hallucinations, delusions, or disorganised thoughts or behaviours.</t>
         </is>
       </c>
-      <c r="D123" s="2" t="inlineStr">
+      <c r="D124" s="2" t="inlineStr">
         <is>
           <t>psychotic disorder symptom</t>
         </is>
       </c>
-      <c r="E123" s="2" t="n"/>
-      <c r="F123" s="2" t="n"/>
-      <c r="G123" s="2" t="n"/>
-      <c r="H123" s="2" t="n"/>
-      <c r="I123" s="2" t="n"/>
-      <c r="J123" s="2" t="n"/>
-      <c r="K123" s="2" t="inlineStr">
+      <c r="E124" s="2" t="n"/>
+      <c r="F124" s="2" t="n"/>
+      <c r="G124" s="2" t="n"/>
+      <c r="H124" s="2" t="n"/>
+      <c r="I124" s="2" t="n"/>
+      <c r="J124" s="2" t="n"/>
+      <c r="K124" s="2" t="inlineStr">
         <is>
           <t>Based on https://www.psychiatry.org/patients-families/schizophrenia/what-is-schizophrenia</t>
         </is>
       </c>
-      <c r="L123" s="2" t="n"/>
-      <c r="M123" s="2" t="n"/>
-      <c r="N123" s="2" t="n"/>
-      <c r="O123" s="2" t="n"/>
-      <c r="P123" s="2" t="n"/>
-      <c r="Q123" s="2" t="inlineStr">
+      <c r="L124" s="2" t="n"/>
+      <c r="M124" s="2" t="n"/>
+      <c r="N124" s="2" t="n"/>
+      <c r="O124" s="2" t="n"/>
+      <c r="P124" s="2" t="n"/>
+      <c r="Q124" s="2" t="inlineStr">
         <is>
           <t>LSR 3</t>
         </is>
       </c>
-      <c r="R123" s="2" t="inlineStr">
-        <is>
-          <t>Intervention outcomes and spillover effects</t>
-        </is>
-      </c>
-      <c r="S123" s="2" t="n"/>
-      <c r="T123" s="2" t="inlineStr">
+      <c r="R124" s="2" t="inlineStr">
+        <is>
+          <t>Intervention outcomes and spillover effects</t>
+        </is>
+      </c>
+      <c r="S124" s="2" t="n"/>
+      <c r="T124" s="2" t="inlineStr">
         <is>
           <t>Obsolete</t>
         </is>
       </c>
-      <c r="U123" s="2" t="n"/>
-      <c r="V123" s="2" t="n"/>
-      <c r="W123" s="2" t="inlineStr">
-        <is>
-          <t>PS</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" s="3" t="inlineStr">
-        <is>
-          <t>GMHO:0000078</t>
-        </is>
-      </c>
-      <c r="B124" s="3" t="inlineStr">
-        <is>
-          <t>positive psychotic disorder symptom severity</t>
-        </is>
-      </c>
-      <c r="C124" s="3" t="inlineStr">
-        <is>
-          <t>Psychotic disorder symptom severity that is associated with positive psychotic disorder symptoms.</t>
-        </is>
-      </c>
-      <c r="D124" s="3" t="inlineStr">
-        <is>
-          <t>psychotic disorder symptom severity</t>
-        </is>
-      </c>
-      <c r="E124" s="3" t="n"/>
-      <c r="F124" s="3" t="n"/>
-      <c r="G124" s="3" t="n"/>
-      <c r="H124" s="3" t="n"/>
-      <c r="I124" s="3" t="n"/>
-      <c r="J124" s="3" t="inlineStr">
-        <is>
-          <t>Intervention outcomes and spillover effects</t>
-        </is>
-      </c>
-      <c r="K124" s="3" t="inlineStr">
-        <is>
-          <t>Based on https://www.psychiatry.org/patients-families/schizophrenia/what-is-schizophrenia</t>
-        </is>
-      </c>
-      <c r="L124" s="3" t="n"/>
-      <c r="M124" s="3" t="n"/>
-      <c r="N124" s="3" t="n"/>
-      <c r="O124" s="3" t="n"/>
-      <c r="P124" s="3" t="n"/>
-      <c r="Q124" s="3" t="inlineStr">
-        <is>
-          <t>LSR 3</t>
-        </is>
-      </c>
-      <c r="R124" s="3" t="inlineStr">
-        <is>
-          <t>Intervention outcomes and spillover effects</t>
-        </is>
-      </c>
-      <c r="S124" s="3" t="inlineStr">
-        <is>
-          <t>A measure for 'positive psychotic disorder symptom severity'</t>
-        </is>
-      </c>
-      <c r="T124" s="3" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="U124" s="3" t="n"/>
-      <c r="V124" s="3" t="n"/>
-      <c r="W124" s="3" t="inlineStr">
-        <is>
-          <t>PS; MS</t>
+      <c r="U124" s="2" t="n"/>
+      <c r="V124" s="2" t="n"/>
+      <c r="W124" s="2" t="inlineStr">
+        <is>
+          <t>PS</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="3" t="inlineStr">
         <is>
-          <t>GMHO:0000226</t>
+          <t>GMHO:0000078</t>
         </is>
       </c>
       <c r="B125" s="3" t="inlineStr">
         <is>
-          <t>positive psychotic disorder symptom severity scale</t>
+          <t>positive psychotic disorder symptom severity</t>
         </is>
       </c>
       <c r="C125" s="3" t="inlineStr">
         <is>
-          <t>A psychotic disorder symptom severity scale that that is associated with positive psychotic disorder symptoms.</t>
+          <t>Psychotic disorder symptom severity that is associated with positive psychotic disorder symptoms.</t>
         </is>
       </c>
       <c r="D125" s="3" t="inlineStr">
         <is>
-          <t>psychotic disorder symptom severity scale</t>
+          <t>psychotic disorder symptom severity</t>
         </is>
       </c>
       <c r="E125" s="3" t="n"/>
@@ -7893,8 +7877,7 @@
       </c>
       <c r="K125" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Based on https://www.psychiatry.org/patients-families/schizophrenia/what-is-schizophrenia
-</t>
+          <t>Based on https://www.psychiatry.org/patients-families/schizophrenia/what-is-schizophrenia</t>
         </is>
       </c>
       <c r="L125" s="3" t="n"/>
@@ -7912,7 +7895,11 @@
           <t>Intervention outcomes and spillover effects</t>
         </is>
       </c>
-      <c r="S125" s="3" t="n"/>
+      <c r="S125" s="3" t="inlineStr">
+        <is>
+          <t>A measure for 'positive psychotic disorder symptom severity'</t>
+        </is>
+      </c>
       <c r="T125" s="3" t="inlineStr">
         <is>
           <t>Published</t>
@@ -7927,110 +7914,119 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="2" t="inlineStr">
+      <c r="A126" s="3" t="inlineStr">
+        <is>
+          <t>GMHO:0000226</t>
+        </is>
+      </c>
+      <c r="B126" s="3" t="inlineStr">
+        <is>
+          <t>positive psychotic disorder symptom severity scale</t>
+        </is>
+      </c>
+      <c r="C126" s="3" t="inlineStr">
+        <is>
+          <t>A psychotic disorder symptom severity scale that that is associated with positive psychotic disorder symptoms.</t>
+        </is>
+      </c>
+      <c r="D126" s="3" t="inlineStr">
+        <is>
+          <t>psychotic disorder symptom severity scale</t>
+        </is>
+      </c>
+      <c r="E126" s="3" t="n"/>
+      <c r="F126" s="3" t="n"/>
+      <c r="G126" s="3" t="n"/>
+      <c r="H126" s="3" t="n"/>
+      <c r="I126" s="3" t="n"/>
+      <c r="J126" s="3" t="inlineStr">
+        <is>
+          <t>Intervention outcomes and spillover effects</t>
+        </is>
+      </c>
+      <c r="K126" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Based on https://www.psychiatry.org/patients-families/schizophrenia/what-is-schizophrenia
+</t>
+        </is>
+      </c>
+      <c r="L126" s="3" t="n"/>
+      <c r="M126" s="3" t="n"/>
+      <c r="N126" s="3" t="n"/>
+      <c r="O126" s="3" t="n"/>
+      <c r="P126" s="3" t="n"/>
+      <c r="Q126" s="3" t="inlineStr">
+        <is>
+          <t>LSR 3</t>
+        </is>
+      </c>
+      <c r="R126" s="3" t="inlineStr">
+        <is>
+          <t>Intervention outcomes and spillover effects</t>
+        </is>
+      </c>
+      <c r="S126" s="3" t="n"/>
+      <c r="T126" s="3" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="U126" s="3" t="n"/>
+      <c r="V126" s="3" t="n"/>
+      <c r="W126" s="3" t="inlineStr">
+        <is>
+          <t>PS; MS</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
         <is>
           <t>GMHO:0000174</t>
         </is>
       </c>
-      <c r="B126" s="2" t="inlineStr">
+      <c r="B127" s="2" t="inlineStr">
         <is>
           <t>post-traumatic stress symptom</t>
         </is>
       </c>
-      <c r="C126" s="2" t="inlineStr">
+      <c r="C127" s="2" t="inlineStr">
         <is>
           <t>A symptom that related to a post-traumatic stress disorder diagnosis.</t>
         </is>
       </c>
-      <c r="D126" s="2" t="inlineStr">
+      <c r="D127" s="2" t="inlineStr">
         <is>
           <t>symptom</t>
         </is>
       </c>
-      <c r="E126" s="2" t="n"/>
-      <c r="F126" s="2" t="n"/>
-      <c r="G126" s="2" t="n"/>
-      <c r="H126" s="2" t="n"/>
-      <c r="I126" s="2" t="n"/>
-      <c r="J126" s="2" t="n"/>
-      <c r="K126" s="2" t="n"/>
-      <c r="L126" s="2" t="n"/>
-      <c r="M126" s="2" t="n"/>
-      <c r="N126" s="2" t="n"/>
-      <c r="O126" s="2" t="n"/>
-      <c r="P126" s="2" t="n"/>
-      <c r="Q126" s="2" t="inlineStr">
+      <c r="E127" s="2" t="n"/>
+      <c r="F127" s="2" t="n"/>
+      <c r="G127" s="2" t="n"/>
+      <c r="H127" s="2" t="n"/>
+      <c r="I127" s="2" t="n"/>
+      <c r="J127" s="2" t="n"/>
+      <c r="K127" s="2" t="n"/>
+      <c r="L127" s="2" t="n"/>
+      <c r="M127" s="2" t="n"/>
+      <c r="N127" s="2" t="n"/>
+      <c r="O127" s="2" t="n"/>
+      <c r="P127" s="2" t="n"/>
+      <c r="Q127" s="2" t="inlineStr">
         <is>
           <t>LSR 2</t>
         </is>
       </c>
-      <c r="R126" s="2" t="n"/>
-      <c r="S126" s="2" t="n"/>
-      <c r="T126" s="2" t="inlineStr">
+      <c r="R127" s="2" t="n"/>
+      <c r="S127" s="2" t="n"/>
+      <c r="T127" s="2" t="inlineStr">
         <is>
           <t>Obsolete</t>
         </is>
       </c>
-      <c r="U126" s="2" t="n"/>
-      <c r="V126" s="2" t="n"/>
-      <c r="W126" s="2" t="inlineStr">
-        <is>
-          <t>PS; MS</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" s="3" t="inlineStr">
-        <is>
-          <t>GMHO:0000173</t>
-        </is>
-      </c>
-      <c r="B127" s="3" t="inlineStr">
-        <is>
-          <t>post-traumatic stress symptom severity</t>
-        </is>
-      </c>
-      <c r="C127" s="3" t="inlineStr">
-        <is>
-          <t>Symptom severity relating to a post-traumatic stress symptom.</t>
-        </is>
-      </c>
-      <c r="D127" s="3" t="inlineStr">
-        <is>
-          <t>symptom severity</t>
-        </is>
-      </c>
-      <c r="E127" s="3" t="n"/>
-      <c r="F127" s="3" t="n"/>
-      <c r="G127" s="3" t="inlineStr">
-        <is>
-          <t>PTSD severity</t>
-        </is>
-      </c>
-      <c r="H127" s="3" t="n"/>
-      <c r="I127" s="3" t="n"/>
-      <c r="J127" s="3" t="n"/>
-      <c r="K127" s="3" t="n"/>
-      <c r="L127" s="3" t="n"/>
-      <c r="M127" s="3" t="n"/>
-      <c r="N127" s="3" t="n"/>
-      <c r="O127" s="3" t="n"/>
-      <c r="P127" s="3" t="n"/>
-      <c r="Q127" s="3" t="inlineStr">
-        <is>
-          <t>LSR 2</t>
-        </is>
-      </c>
-      <c r="R127" s="3" t="n"/>
-      <c r="S127" s="3" t="n"/>
-      <c r="T127" s="3" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="U127" s="3" t="n"/>
-      <c r="V127" s="3" t="n"/>
-      <c r="W127" s="3" t="inlineStr">
+      <c r="U127" s="2" t="n"/>
+      <c r="V127" s="2" t="n"/>
+      <c r="W127" s="2" t="inlineStr">
         <is>
           <t>PS; MS</t>
         </is>
@@ -8039,34 +8035,34 @@
     <row r="128">
       <c r="A128" s="3" t="inlineStr">
         <is>
-          <t>GMHO:0000263</t>
+          <t>GMHO:0000173</t>
         </is>
       </c>
       <c r="B128" s="3" t="inlineStr">
         <is>
-          <t>post-traumatic stress symptom severity scale</t>
+          <t>post-traumatic stress symptom severity</t>
         </is>
       </c>
       <c r="C128" s="3" t="inlineStr">
         <is>
-          <t>A measurement scale that is used to measure post-traumatic stress symptom severity.</t>
+          <t>Symptom severity relating to a post-traumatic stress symptom.</t>
         </is>
       </c>
       <c r="D128" s="3" t="inlineStr">
         <is>
-          <t>measurement scale</t>
+          <t>symptom severity</t>
         </is>
       </c>
       <c r="E128" s="3" t="n"/>
       <c r="F128" s="3" t="n"/>
-      <c r="G128" s="3" t="n"/>
+      <c r="G128" s="3" t="inlineStr">
+        <is>
+          <t>PTSD severity</t>
+        </is>
+      </c>
       <c r="H128" s="3" t="n"/>
       <c r="I128" s="3" t="n"/>
-      <c r="J128" s="3" t="inlineStr">
-        <is>
-          <t>Intervention outcomes and spillover effects</t>
-        </is>
-      </c>
+      <c r="J128" s="3" t="n"/>
       <c r="K128" s="3" t="n"/>
       <c r="L128" s="3" t="n"/>
       <c r="M128" s="3" t="n"/>
@@ -8078,11 +8074,7 @@
           <t>LSR 2</t>
         </is>
       </c>
-      <c r="R128" s="3" t="inlineStr">
-        <is>
-          <t>Intervention outcomes and spillover effects</t>
-        </is>
-      </c>
+      <c r="R128" s="3" t="n"/>
       <c r="S128" s="3" t="n"/>
       <c r="T128" s="3" t="inlineStr">
         <is>
@@ -8091,106 +8083,106 @@
       </c>
       <c r="U128" s="3" t="n"/>
       <c r="V128" s="3" t="n"/>
-      <c r="W128" s="3" t="n"/>
+      <c r="W128" s="3" t="inlineStr">
+        <is>
+          <t>PS; MS</t>
+        </is>
+      </c>
     </row>
     <row r="129">
-      <c r="A129" t="inlineStr">
+      <c r="A129" s="3" t="inlineStr">
+        <is>
+          <t>GMHO:0000263</t>
+        </is>
+      </c>
+      <c r="B129" s="3" t="inlineStr">
+        <is>
+          <t>post-traumatic stress symptom severity scale</t>
+        </is>
+      </c>
+      <c r="C129" s="3" t="inlineStr">
+        <is>
+          <t>A measurement scale that is used to measure post-traumatic stress symptom severity.</t>
+        </is>
+      </c>
+      <c r="D129" s="3" t="inlineStr">
+        <is>
+          <t>measurement scale</t>
+        </is>
+      </c>
+      <c r="E129" s="3" t="n"/>
+      <c r="F129" s="3" t="n"/>
+      <c r="G129" s="3" t="n"/>
+      <c r="H129" s="3" t="n"/>
+      <c r="I129" s="3" t="n"/>
+      <c r="J129" s="3" t="inlineStr">
+        <is>
+          <t>Intervention outcomes and spillover effects</t>
+        </is>
+      </c>
+      <c r="K129" s="3" t="n"/>
+      <c r="L129" s="3" t="n"/>
+      <c r="M129" s="3" t="n"/>
+      <c r="N129" s="3" t="n"/>
+      <c r="O129" s="3" t="n"/>
+      <c r="P129" s="3" t="n"/>
+      <c r="Q129" s="3" t="inlineStr">
+        <is>
+          <t>LSR 2</t>
+        </is>
+      </c>
+      <c r="R129" s="3" t="inlineStr">
+        <is>
+          <t>Intervention outcomes and spillover effects</t>
+        </is>
+      </c>
+      <c r="S129" s="3" t="n"/>
+      <c r="T129" s="3" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="U129" s="3" t="n"/>
+      <c r="V129" s="3" t="n"/>
+      <c r="W129" s="3" t="n"/>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
         <is>
           <t>OBA:1000952</t>
         </is>
       </c>
-      <c r="B129" t="inlineStr">
+      <c r="B130" t="inlineStr">
         <is>
           <t>prolactin level</t>
         </is>
       </c>
-      <c r="C129" t="inlineStr">
+      <c r="C130" t="inlineStr">
         <is>
           <t>The amount of a prolactin.</t>
         </is>
       </c>
-      <c r="D129" t="inlineStr">
+      <c r="D130" t="inlineStr">
         <is>
           <t>protein amount</t>
         </is>
       </c>
-      <c r="Q129" t="inlineStr">
+      <c r="Q130" t="inlineStr">
         <is>
           <t>LSR 3</t>
         </is>
       </c>
-      <c r="R129" t="inlineStr">
-        <is>
-          <t>Intervention outcomes and spillover effects</t>
-        </is>
-      </c>
-      <c r="T129" t="inlineStr">
+      <c r="R130" t="inlineStr">
+        <is>
+          <t>Intervention outcomes and spillover effects</t>
+        </is>
+      </c>
+      <c r="T130" t="inlineStr">
         <is>
           <t>External</t>
         </is>
       </c>
-      <c r="W129" t="inlineStr">
-        <is>
-          <t>PS</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" s="2" t="inlineStr">
-        <is>
-          <t>GMHO:0000227</t>
-        </is>
-      </c>
-      <c r="B130" s="2" t="inlineStr">
-        <is>
-          <t>prolactin scale</t>
-        </is>
-      </c>
-      <c r="C130" s="2" t="inlineStr">
-        <is>
-          <t>A measurement scale that is used to measure levels of prolactin.</t>
-        </is>
-      </c>
-      <c r="D130" s="2" t="inlineStr">
-        <is>
-          <t>measurement scale</t>
-        </is>
-      </c>
-      <c r="E130" s="2" t="n"/>
-      <c r="F130" s="2" t="n"/>
-      <c r="G130" s="2" t="n"/>
-      <c r="H130" s="2" t="n"/>
-      <c r="I130" s="2" t="n"/>
-      <c r="J130" s="2" t="inlineStr">
-        <is>
-          <t>Intervention outcomes and spillover effects</t>
-        </is>
-      </c>
-      <c r="K130" s="2" t="n"/>
-      <c r="L130" s="2" t="n"/>
-      <c r="M130" s="2" t="n"/>
-      <c r="N130" s="2" t="n"/>
-      <c r="O130" s="2" t="n"/>
-      <c r="P130" s="2" t="n"/>
-      <c r="Q130" s="2" t="inlineStr">
-        <is>
-          <t>LSR 3</t>
-        </is>
-      </c>
-      <c r="R130" s="2" t="inlineStr">
-        <is>
-          <t>Intervention outcomes and spillover effects</t>
-        </is>
-      </c>
-      <c r="S130" s="2" t="n"/>
-      <c r="T130" s="2" t="inlineStr">
-        <is>
-          <t>Obsolete</t>
-        </is>
-      </c>
-      <c r="U130" s="2" t="n"/>
-      <c r="V130" s="2" t="n"/>
-      <c r="W130" s="2" t="inlineStr">
+      <c r="W130" t="inlineStr">
         <is>
           <t>PS</t>
         </is>
@@ -8199,34 +8191,34 @@
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>GMHO:0000172</t>
+          <t>GMHO:0000227</t>
         </is>
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>psychotic disorder symptom</t>
+          <t>prolactin scale</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t>A symptom that is related to a psychotic disorder diagnosis.</t>
+          <t>A measurement scale that is used to measure levels of prolactin.</t>
         </is>
       </c>
       <c r="D131" s="2" t="inlineStr">
         <is>
-          <t>symptom</t>
-        </is>
-      </c>
-      <c r="E131" s="2" t="inlineStr">
-        <is>
-          <t>http://purl.obolibrary.org/obo/</t>
-        </is>
-      </c>
+          <t>measurement scale</t>
+        </is>
+      </c>
+      <c r="E131" s="2" t="n"/>
       <c r="F131" s="2" t="n"/>
       <c r="G131" s="2" t="n"/>
       <c r="H131" s="2" t="n"/>
       <c r="I131" s="2" t="n"/>
-      <c r="J131" s="2" t="n"/>
+      <c r="J131" s="2" t="inlineStr">
+        <is>
+          <t>Intervention outcomes and spillover effects</t>
+        </is>
+      </c>
       <c r="K131" s="2" t="n"/>
       <c r="L131" s="2" t="n"/>
       <c r="M131" s="2" t="n"/>
@@ -8258,61 +8250,61 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="3" t="inlineStr">
-        <is>
-          <t>GMHO:0000079</t>
-        </is>
-      </c>
-      <c r="B132" s="3" t="inlineStr">
-        <is>
-          <t>psychotic disorder symptom severity</t>
-        </is>
-      </c>
-      <c r="C132" s="3" t="inlineStr">
-        <is>
-          <t>Symptom severity that is associated with a psychotic disorder symptom.</t>
-        </is>
-      </c>
-      <c r="D132" s="3" t="inlineStr">
-        <is>
-          <t>symptom severity</t>
-        </is>
-      </c>
-      <c r="E132" s="3" t="n"/>
-      <c r="F132" s="3" t="n"/>
-      <c r="G132" s="3" t="n"/>
-      <c r="H132" s="3" t="n"/>
-      <c r="I132" s="3" t="n"/>
-      <c r="J132" s="3" t="inlineStr">
-        <is>
-          <t>Intervention outcomes and spillover effects</t>
-        </is>
-      </c>
-      <c r="K132" s="3" t="n"/>
-      <c r="L132" s="3" t="n"/>
-      <c r="M132" s="3" t="n"/>
-      <c r="N132" s="3" t="n"/>
-      <c r="O132" s="3" t="n"/>
-      <c r="P132" s="3" t="n"/>
-      <c r="Q132" s="3" t="inlineStr">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>GMHO:0000172</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>psychotic disorder symptom</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>A symptom that is related to a psychotic disorder diagnosis.</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
+        <is>
+          <t>symptom</t>
+        </is>
+      </c>
+      <c r="E132" s="2" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/</t>
+        </is>
+      </c>
+      <c r="F132" s="2" t="n"/>
+      <c r="G132" s="2" t="n"/>
+      <c r="H132" s="2" t="n"/>
+      <c r="I132" s="2" t="n"/>
+      <c r="J132" s="2" t="n"/>
+      <c r="K132" s="2" t="n"/>
+      <c r="L132" s="2" t="n"/>
+      <c r="M132" s="2" t="n"/>
+      <c r="N132" s="2" t="n"/>
+      <c r="O132" s="2" t="n"/>
+      <c r="P132" s="2" t="n"/>
+      <c r="Q132" s="2" t="inlineStr">
         <is>
           <t>LSR 3</t>
         </is>
       </c>
-      <c r="R132" s="3" t="inlineStr">
-        <is>
-          <t>Intervention outcomes and spillover effects</t>
-        </is>
-      </c>
-      <c r="S132" s="3" t="n"/>
-      <c r="T132" s="3" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="U132" s="3" t="n"/>
-      <c r="V132" s="3" t="n"/>
-      <c r="W132" s="3" t="inlineStr">
+      <c r="R132" s="2" t="inlineStr">
+        <is>
+          <t>Intervention outcomes and spillover effects</t>
+        </is>
+      </c>
+      <c r="S132" s="2" t="n"/>
+      <c r="T132" s="2" t="inlineStr">
+        <is>
+          <t>Obsolete</t>
+        </is>
+      </c>
+      <c r="U132" s="2" t="n"/>
+      <c r="V132" s="2" t="n"/>
+      <c r="W132" s="2" t="inlineStr">
         <is>
           <t>PS</t>
         </is>
@@ -8321,22 +8313,22 @@
     <row r="133">
       <c r="A133" s="3" t="inlineStr">
         <is>
-          <t>GMHO:0000228</t>
+          <t>GMHO:0000079</t>
         </is>
       </c>
       <c r="B133" s="3" t="inlineStr">
         <is>
-          <t>psychotic disorder symptom severity scale</t>
+          <t>psychotic disorder symptom severity</t>
         </is>
       </c>
       <c r="C133" s="3" t="inlineStr">
         <is>
-          <t>A measurement scale that is used to measure psychotic disorder symptom severity.</t>
+          <t>Symptom severity that is associated with a psychotic disorder symptom.</t>
         </is>
       </c>
       <c r="D133" s="3" t="inlineStr">
         <is>
-          <t>measurement scale</t>
+          <t>symptom severity</t>
         </is>
       </c>
       <c r="E133" s="3" t="n"/>
@@ -8380,47 +8372,61 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>OBI:0000071</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>quantitative confidence value</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>A data item which is used to indicate the degree of uncertainty about a measurement.</t>
-        </is>
-      </c>
-      <c r="D134" t="inlineStr">
-        <is>
-          <t>data item</t>
-        </is>
-      </c>
-      <c r="J134" t="inlineStr">
-        <is>
-          <t>Intervention outcomes and spillover effects</t>
-        </is>
-      </c>
-      <c r="Q134" t="inlineStr">
-        <is>
-          <t>LSR 1</t>
-        </is>
-      </c>
-      <c r="R134" t="inlineStr">
-        <is>
-          <t>Intervention outcomes and spillover effects</t>
-        </is>
-      </c>
-      <c r="T134" t="inlineStr">
-        <is>
-          <t>External</t>
-        </is>
-      </c>
-      <c r="W134" t="inlineStr">
+      <c r="A134" s="3" t="inlineStr">
+        <is>
+          <t>GMHO:0000228</t>
+        </is>
+      </c>
+      <c r="B134" s="3" t="inlineStr">
+        <is>
+          <t>psychotic disorder symptom severity scale</t>
+        </is>
+      </c>
+      <c r="C134" s="3" t="inlineStr">
+        <is>
+          <t>A measurement scale that is used to measure psychotic disorder symptom severity.</t>
+        </is>
+      </c>
+      <c r="D134" s="3" t="inlineStr">
+        <is>
+          <t>measurement scale</t>
+        </is>
+      </c>
+      <c r="E134" s="3" t="n"/>
+      <c r="F134" s="3" t="n"/>
+      <c r="G134" s="3" t="n"/>
+      <c r="H134" s="3" t="n"/>
+      <c r="I134" s="3" t="n"/>
+      <c r="J134" s="3" t="inlineStr">
+        <is>
+          <t>Intervention outcomes and spillover effects</t>
+        </is>
+      </c>
+      <c r="K134" s="3" t="n"/>
+      <c r="L134" s="3" t="n"/>
+      <c r="M134" s="3" t="n"/>
+      <c r="N134" s="3" t="n"/>
+      <c r="O134" s="3" t="n"/>
+      <c r="P134" s="3" t="n"/>
+      <c r="Q134" s="3" t="inlineStr">
+        <is>
+          <t>LSR 3</t>
+        </is>
+      </c>
+      <c r="R134" s="3" t="inlineStr">
+        <is>
+          <t>Intervention outcomes and spillover effects</t>
+        </is>
+      </c>
+      <c r="S134" s="3" t="n"/>
+      <c r="T134" s="3" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="U134" s="3" t="n"/>
+      <c r="V134" s="3" t="n"/>
+      <c r="W134" s="3" t="inlineStr">
         <is>
           <t>PS</t>
         </is>
@@ -8429,106 +8435,92 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
+          <t>OBI:0000071</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>quantitative confidence value</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>A data item which is used to indicate the degree of uncertainty about a measurement.</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>data item</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>Intervention outcomes and spillover effects</t>
+        </is>
+      </c>
+      <c r="Q135" t="inlineStr">
+        <is>
+          <t>LSR 1</t>
+        </is>
+      </c>
+      <c r="R135" t="inlineStr">
+        <is>
+          <t>Intervention outcomes and spillover effects</t>
+        </is>
+      </c>
+      <c r="T135" t="inlineStr">
+        <is>
+          <t>External</t>
+        </is>
+      </c>
+      <c r="W135" t="inlineStr">
+        <is>
+          <t>PS</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
           <t>ADDICTO:0001308</t>
         </is>
       </c>
-      <c r="B135" t="inlineStr">
+      <c r="B136" t="inlineStr">
         <is>
           <t>relapsed to a disorder</t>
         </is>
       </c>
-      <c r="C135" t="inlineStr">
+      <c r="C136" t="inlineStr">
         <is>
           <t>A personal attribute in which the symptoms of a person suffering from a disorder have reverted from a desired level to an undesired level.</t>
         </is>
       </c>
-      <c r="D135" t="inlineStr">
+      <c r="D136" t="inlineStr">
         <is>
           <t>personal attribute</t>
         </is>
       </c>
-      <c r="J135" t="inlineStr">
+      <c r="J136" t="inlineStr">
         <is>
           <t>intervention outcomes and spillover effects</t>
         </is>
       </c>
-      <c r="Q135" t="inlineStr">
+      <c r="Q136" t="inlineStr">
         <is>
           <t>LSR 3</t>
         </is>
       </c>
-      <c r="R135" t="inlineStr">
-        <is>
-          <t>Intervention outcomes and spillover effects</t>
-        </is>
-      </c>
-      <c r="T135" t="inlineStr">
+      <c r="R136" t="inlineStr">
+        <is>
+          <t>Intervention outcomes and spillover effects</t>
+        </is>
+      </c>
+      <c r="T136" t="inlineStr">
         <is>
           <t>External</t>
         </is>
       </c>
-      <c r="W135" t="inlineStr">
-        <is>
-          <t>PS</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" s="3" t="inlineStr">
-        <is>
-          <t>GMHO:0000135</t>
-        </is>
-      </c>
-      <c r="B136" s="3" t="inlineStr">
-        <is>
-          <t>reward sensitivity</t>
-        </is>
-      </c>
-      <c r="C136" s="3" t="inlineStr">
-        <is>
-          <t>A bodily disposition to detect, pursue, learn from, and derive pleasure from stimuli perceived as positive.</t>
-        </is>
-      </c>
-      <c r="D136" s="3" t="inlineStr">
-        <is>
-          <t>bodily disposition</t>
-        </is>
-      </c>
-      <c r="E136" s="3" t="n"/>
-      <c r="F136" s="3" t="n"/>
-      <c r="G136" s="3" t="n"/>
-      <c r="H136" s="3" t="n"/>
-      <c r="I136" s="3" t="n"/>
-      <c r="J136" s="3" t="n"/>
-      <c r="K136" s="3" t="inlineStr">
-        <is>
-          <t>Goodnight, J. (Ed.) (2018). . (Vols. 1-5). SAGE Publications, Inc., https://doi.org/10.4135/9781506307633</t>
-        </is>
-      </c>
-      <c r="L136" s="3" t="n"/>
-      <c r="M136" s="3" t="n"/>
-      <c r="N136" s="3" t="n"/>
-      <c r="O136" s="3" t="n"/>
-      <c r="P136" s="3" t="n"/>
-      <c r="Q136" s="3" t="inlineStr">
-        <is>
-          <t>LSR 1</t>
-        </is>
-      </c>
-      <c r="R136" s="3" t="inlineStr">
-        <is>
-          <t>Intervention outcomes and spillover effects</t>
-        </is>
-      </c>
-      <c r="S136" s="3" t="n"/>
-      <c r="T136" s="3" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="U136" s="3" t="n"/>
-      <c r="V136" s="3" t="n"/>
-      <c r="W136" s="3" t="inlineStr">
+      <c r="W136" t="inlineStr">
         <is>
           <t>PS</t>
         </is>
@@ -8537,22 +8529,22 @@
     <row r="137">
       <c r="A137" s="3" t="inlineStr">
         <is>
-          <t>GMHO:0000207</t>
+          <t>GMHO:0000135</t>
         </is>
       </c>
       <c r="B137" s="3" t="inlineStr">
         <is>
-          <t>reward sensitivity scale</t>
+          <t>reward sensitivity</t>
         </is>
       </c>
       <c r="C137" s="3" t="inlineStr">
         <is>
-          <t>A measurement scale that is used to measure reward sensitivity.</t>
+          <t>A bodily disposition to detect, pursue, learn from, and derive pleasure from stimuli perceived as positive.</t>
         </is>
       </c>
       <c r="D137" s="3" t="inlineStr">
         <is>
-          <t>measurement scale</t>
+          <t>bodily disposition</t>
         </is>
       </c>
       <c r="E137" s="3" t="n"/>
@@ -8561,7 +8553,11 @@
       <c r="H137" s="3" t="n"/>
       <c r="I137" s="3" t="n"/>
       <c r="J137" s="3" t="n"/>
-      <c r="K137" s="3" t="n"/>
+      <c r="K137" s="3" t="inlineStr">
+        <is>
+          <t>Goodnight, J. (Ed.) (2018). . (Vols. 1-5). SAGE Publications, Inc., https://doi.org/10.4135/9781506307633</t>
+        </is>
+      </c>
       <c r="L137" s="3" t="n"/>
       <c r="M137" s="3" t="n"/>
       <c r="N137" s="3" t="n"/>
@@ -8592,57 +8588,57 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="2" t="inlineStr">
-        <is>
-          <t>GMHO:0000136</t>
-        </is>
-      </c>
-      <c r="B138" s="2" t="inlineStr">
-        <is>
-          <t>reward-based learning</t>
-        </is>
-      </c>
-      <c r="C138" s="2" t="inlineStr">
-        <is>
-          <t>Associative learning by which information is acquired regarding the positive outcomes of stimuli and behaviours.</t>
-        </is>
-      </c>
-      <c r="D138" s="2" t="inlineStr">
-        <is>
-          <t>associative learning</t>
-        </is>
-      </c>
-      <c r="E138" s="2" t="n"/>
-      <c r="F138" s="2" t="n"/>
-      <c r="G138" s="2" t="n"/>
-      <c r="H138" s="2" t="n"/>
-      <c r="I138" s="2" t="n"/>
-      <c r="J138" s="2" t="n"/>
-      <c r="K138" s="2" t="n"/>
-      <c r="L138" s="2" t="n"/>
-      <c r="M138" s="2" t="n"/>
-      <c r="N138" s="2" t="n"/>
-      <c r="O138" s="2" t="n"/>
-      <c r="P138" s="2" t="n"/>
-      <c r="Q138" s="2" t="inlineStr">
+      <c r="A138" s="3" t="inlineStr">
+        <is>
+          <t>GMHO:0000207</t>
+        </is>
+      </c>
+      <c r="B138" s="3" t="inlineStr">
+        <is>
+          <t>reward sensitivity scale</t>
+        </is>
+      </c>
+      <c r="C138" s="3" t="inlineStr">
+        <is>
+          <t>A measurement scale that is used to measure reward sensitivity.</t>
+        </is>
+      </c>
+      <c r="D138" s="3" t="inlineStr">
+        <is>
+          <t>measurement scale</t>
+        </is>
+      </c>
+      <c r="E138" s="3" t="n"/>
+      <c r="F138" s="3" t="n"/>
+      <c r="G138" s="3" t="n"/>
+      <c r="H138" s="3" t="n"/>
+      <c r="I138" s="3" t="n"/>
+      <c r="J138" s="3" t="n"/>
+      <c r="K138" s="3" t="n"/>
+      <c r="L138" s="3" t="n"/>
+      <c r="M138" s="3" t="n"/>
+      <c r="N138" s="3" t="n"/>
+      <c r="O138" s="3" t="n"/>
+      <c r="P138" s="3" t="n"/>
+      <c r="Q138" s="3" t="inlineStr">
         <is>
           <t>LSR 1</t>
         </is>
       </c>
-      <c r="R138" s="2" t="inlineStr">
-        <is>
-          <t>Intervention outcomes and spillover effects</t>
-        </is>
-      </c>
-      <c r="S138" s="2" t="n"/>
-      <c r="T138" s="2" t="inlineStr">
-        <is>
-          <t>Obsolete</t>
-        </is>
-      </c>
-      <c r="U138" s="2" t="n"/>
-      <c r="V138" s="2" t="n"/>
-      <c r="W138" s="2" t="inlineStr">
+      <c r="R138" s="3" t="inlineStr">
+        <is>
+          <t>Intervention outcomes and spillover effects</t>
+        </is>
+      </c>
+      <c r="S138" s="3" t="n"/>
+      <c r="T138" s="3" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="U138" s="3" t="n"/>
+      <c r="V138" s="3" t="n"/>
+      <c r="W138" s="3" t="inlineStr">
         <is>
           <t>PS</t>
         </is>
@@ -8651,22 +8647,22 @@
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>GMHO:0000137</t>
+          <t>GMHO:0000136</t>
         </is>
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>reward-prediction error signalling</t>
+          <t>reward-based learning</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
-          <t>A mental process in which the discrepancy between the predicted and received rewards is signalled.</t>
+          <t>Associative learning by which information is acquired regarding the positive outcomes of stimuli and behaviours.</t>
         </is>
       </c>
       <c r="D139" s="2" t="inlineStr">
         <is>
-          <t>mental process</t>
+          <t>associative learning</t>
         </is>
       </c>
       <c r="E139" s="2" t="n"/>
@@ -8675,12 +8671,7 @@
       <c r="H139" s="2" t="n"/>
       <c r="I139" s="2" t="n"/>
       <c r="J139" s="2" t="n"/>
-      <c r="K139" s="2" t="inlineStr">
-        <is>
-          <t>Based on Schultz, W. (2022). Dopamine reward prediction error coding. Dialogues in clinical neuroscience.
-RDoC - https://www.nimh.nih.gov/research/research-funded-by-nimh/rdoc/definitions-of-the-rdoc-domains-and-constructs</t>
-        </is>
-      </c>
+      <c r="K139" s="2" t="n"/>
       <c r="L139" s="2" t="n"/>
       <c r="M139" s="2" t="n"/>
       <c r="N139" s="2" t="n"/>
@@ -8711,57 +8702,62 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="3" t="inlineStr">
-        <is>
-          <t>GMHO:0000208</t>
-        </is>
-      </c>
-      <c r="B140" s="3" t="inlineStr">
-        <is>
-          <t>scale directionality</t>
-        </is>
-      </c>
-      <c r="C140" s="3" t="inlineStr">
-        <is>
-          <t>An information content entity about the orientation of a measurement's scoring system in which higher numerical levels can indicate higher or lower levels of a construct.</t>
-        </is>
-      </c>
-      <c r="D140" s="3" t="inlineStr">
-        <is>
-          <t>information content entity</t>
-        </is>
-      </c>
-      <c r="E140" s="3" t="n"/>
-      <c r="F140" s="3" t="n"/>
-      <c r="G140" s="3" t="n"/>
-      <c r="H140" s="3" t="n"/>
-      <c r="I140" s="3" t="n"/>
-      <c r="J140" s="3" t="n"/>
-      <c r="K140" s="3" t="n"/>
-      <c r="L140" s="3" t="n"/>
-      <c r="M140" s="3" t="n"/>
-      <c r="N140" s="3" t="n"/>
-      <c r="O140" s="3" t="n"/>
-      <c r="P140" s="3" t="n"/>
-      <c r="Q140" s="3" t="inlineStr">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>GMHO:0000137</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>reward-prediction error signalling</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>A mental process in which the discrepancy between the predicted and received rewards is signalled.</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
+        <is>
+          <t>mental process</t>
+        </is>
+      </c>
+      <c r="E140" s="2" t="n"/>
+      <c r="F140" s="2" t="n"/>
+      <c r="G140" s="2" t="n"/>
+      <c r="H140" s="2" t="n"/>
+      <c r="I140" s="2" t="n"/>
+      <c r="J140" s="2" t="n"/>
+      <c r="K140" s="2" t="inlineStr">
+        <is>
+          <t>Based on Schultz, W. (2022). Dopamine reward prediction error coding. Dialogues in clinical neuroscience.
+RDoC - https://www.nimh.nih.gov/research/research-funded-by-nimh/rdoc/definitions-of-the-rdoc-domains-and-constructs</t>
+        </is>
+      </c>
+      <c r="L140" s="2" t="n"/>
+      <c r="M140" s="2" t="n"/>
+      <c r="N140" s="2" t="n"/>
+      <c r="O140" s="2" t="n"/>
+      <c r="P140" s="2" t="n"/>
+      <c r="Q140" s="2" t="inlineStr">
         <is>
           <t>LSR 1</t>
         </is>
       </c>
-      <c r="R140" s="3" t="inlineStr">
-        <is>
-          <t>Intervention outcomes and spillover effects</t>
-        </is>
-      </c>
-      <c r="S140" s="3" t="n"/>
-      <c r="T140" s="3" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="U140" s="3" t="n"/>
-      <c r="V140" s="3" t="n"/>
-      <c r="W140" s="3" t="inlineStr">
+      <c r="R140" s="2" t="inlineStr">
+        <is>
+          <t>Intervention outcomes and spillover effects</t>
+        </is>
+      </c>
+      <c r="S140" s="2" t="n"/>
+      <c r="T140" s="2" t="inlineStr">
+        <is>
+          <t>Obsolete</t>
+        </is>
+      </c>
+      <c r="U140" s="2" t="n"/>
+      <c r="V140" s="2" t="n"/>
+      <c r="W140" s="2" t="inlineStr">
         <is>
           <t>PS</t>
         </is>
@@ -8770,22 +8766,22 @@
     <row r="141">
       <c r="A141" s="3" t="inlineStr">
         <is>
-          <t>GMHO:0000081</t>
+          <t>GMHO:0000208</t>
         </is>
       </c>
       <c r="B141" s="3" t="inlineStr">
         <is>
-          <t>serious adverse event following an intervention</t>
+          <t>scale directionality</t>
         </is>
       </c>
       <c r="C141" s="3" t="inlineStr">
         <is>
-          <t>An adverse event following an intervention that results in death, a life-threatening event, a persistent or significant disability or a birth defect or requires hospitalisation or extends hospitalisation.</t>
+          <t>An information content entity about the orientation of a measurement's scoring system in which higher numerical levels can indicate higher or lower levels of a construct.</t>
         </is>
       </c>
       <c r="D141" s="3" t="inlineStr">
         <is>
-          <t>adverse event following an intervention</t>
+          <t>information content entity</t>
         </is>
       </c>
       <c r="E141" s="3" t="n"/>
@@ -8794,28 +8790,15 @@
       <c r="H141" s="3" t="n"/>
       <c r="I141" s="3" t="n"/>
       <c r="J141" s="3" t="n"/>
-      <c r="K141" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Based on https://www.fda.gov/safety/reporting-serious-problems-fda/what-serious-adverse-event
-</t>
-        </is>
-      </c>
-      <c r="L141" s="3" t="inlineStr">
-        <is>
-          <t>http://purl.obolibrary.org/obo/OAE_0000631</t>
-        </is>
-      </c>
-      <c r="M141" s="3" t="inlineStr">
-        <is>
-          <t>serious adverse event</t>
-        </is>
-      </c>
+      <c r="K141" s="3" t="n"/>
+      <c r="L141" s="3" t="n"/>
+      <c r="M141" s="3" t="n"/>
       <c r="N141" s="3" t="n"/>
       <c r="O141" s="3" t="n"/>
       <c r="P141" s="3" t="n"/>
       <c r="Q141" s="3" t="inlineStr">
         <is>
-          <t>LSR 3</t>
+          <t>LSR 1</t>
         </is>
       </c>
       <c r="R141" s="3" t="inlineStr">
@@ -8833,81 +8816,94 @@
       <c r="V141" s="3" t="n"/>
       <c r="W141" s="3" t="inlineStr">
         <is>
+          <t>PS</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="3" t="inlineStr">
+        <is>
+          <t>GMHO:0000081</t>
+        </is>
+      </c>
+      <c r="B142" s="3" t="inlineStr">
+        <is>
+          <t>serious adverse event following an intervention</t>
+        </is>
+      </c>
+      <c r="C142" s="3" t="inlineStr">
+        <is>
+          <t>An adverse event following an intervention that results in death, a life-threatening event, a persistent or significant disability or a birth defect or requires hospitalisation or extends hospitalisation.</t>
+        </is>
+      </c>
+      <c r="D142" s="3" t="inlineStr">
+        <is>
+          <t>adverse event following an intervention</t>
+        </is>
+      </c>
+      <c r="E142" s="3" t="n"/>
+      <c r="F142" s="3" t="n"/>
+      <c r="G142" s="3" t="n"/>
+      <c r="H142" s="3" t="n"/>
+      <c r="I142" s="3" t="n"/>
+      <c r="J142" s="3" t="n"/>
+      <c r="K142" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Based on https://www.fda.gov/safety/reporting-serious-problems-fda/what-serious-adverse-event
+</t>
+        </is>
+      </c>
+      <c r="L142" s="3" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/OAE_0000631</t>
+        </is>
+      </c>
+      <c r="M142" s="3" t="inlineStr">
+        <is>
+          <t>serious adverse event</t>
+        </is>
+      </c>
+      <c r="N142" s="3" t="n"/>
+      <c r="O142" s="3" t="n"/>
+      <c r="P142" s="3" t="n"/>
+      <c r="Q142" s="3" t="inlineStr">
+        <is>
+          <t>LSR 3</t>
+        </is>
+      </c>
+      <c r="R142" s="3" t="inlineStr">
+        <is>
+          <t>Intervention outcomes and spillover effects</t>
+        </is>
+      </c>
+      <c r="S142" s="3" t="n"/>
+      <c r="T142" s="3" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="U142" s="3" t="n"/>
+      <c r="V142" s="3" t="n"/>
+      <c r="W142" s="3" t="inlineStr">
+        <is>
           <t>PS; MS</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" s="2" t="inlineStr">
-        <is>
-          <t>GMHO:0000082</t>
-        </is>
-      </c>
-      <c r="B142" s="2" t="inlineStr">
-        <is>
-          <t>serious psychological adverse event following an intervention</t>
-        </is>
-      </c>
-      <c r="C142" s="2" t="inlineStr">
-        <is>
-          <t>A serious adverse event following an intervention that is associated with multiple, persistent or salient negative mental processes.</t>
-        </is>
-      </c>
-      <c r="D142" s="2" t="inlineStr">
-        <is>
-          <t>serious adverse event following an intervention</t>
-        </is>
-      </c>
-      <c r="E142" s="2" t="n"/>
-      <c r="F142" s="2" t="n"/>
-      <c r="G142" s="2" t="n"/>
-      <c r="H142" s="2" t="n"/>
-      <c r="I142" s="2" t="n"/>
-      <c r="J142" s="2" t="n"/>
-      <c r="K142" s="2" t="n"/>
-      <c r="L142" s="2" t="n"/>
-      <c r="M142" s="2" t="n"/>
-      <c r="N142" s="2" t="n"/>
-      <c r="O142" s="2" t="n"/>
-      <c r="P142" s="2" t="n"/>
-      <c r="Q142" s="2" t="inlineStr">
-        <is>
-          <t>LSR 3</t>
-        </is>
-      </c>
-      <c r="R142" s="2" t="inlineStr">
-        <is>
-          <t>Intervention outcomes and spillover effects</t>
-        </is>
-      </c>
-      <c r="S142" s="2" t="n"/>
-      <c r="T142" s="2" t="inlineStr">
-        <is>
-          <t>Obsolete</t>
-        </is>
-      </c>
-      <c r="U142" s="2" t="n"/>
-      <c r="V142" s="2" t="n"/>
-      <c r="W142" s="2" t="inlineStr">
-        <is>
-          <t>PS</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>GMHO:0000083</t>
+          <t>GMHO:0000082</t>
         </is>
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>serious somatic adverse event following an intervention</t>
+          <t>serious psychological adverse event following an intervention</t>
         </is>
       </c>
       <c r="C143" s="2" t="inlineStr">
         <is>
-          <t>A serious adverse event following an intervention that is associated with multiple, persistent or salient physical symptoms.</t>
+          <t>A serious adverse event following an intervention that is associated with multiple, persistent or salient negative mental processes.</t>
         </is>
       </c>
       <c r="D143" s="2" t="inlineStr">
@@ -8952,268 +8948,260 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="4" t="inlineStr">
-        <is>
-          <t>GMHO:0000271</t>
-        </is>
-      </c>
-      <c r="B144" s="4" t="inlineStr">
-        <is>
-          <t>social anxiety scale</t>
-        </is>
-      </c>
-      <c r="C144" s="4" t="inlineStr">
-        <is>
-          <t>An anxiety scale that is used to measure social anxiety symptom severity.</t>
-        </is>
-      </c>
-      <c r="D144" s="4" t="inlineStr">
-        <is>
-          <t>anxiety scale</t>
-        </is>
-      </c>
-      <c r="E144" s="4" t="inlineStr"/>
-      <c r="F144" s="4" t="inlineStr"/>
-      <c r="G144" s="4" t="inlineStr"/>
-      <c r="H144" s="4" t="inlineStr"/>
-      <c r="I144" s="4" t="inlineStr"/>
-      <c r="J144" s="4" t="inlineStr">
-        <is>
-          <t>Intervention outcomes and spillover effects</t>
-        </is>
-      </c>
-      <c r="K144" s="4" t="inlineStr"/>
-      <c r="L144" s="4" t="inlineStr"/>
-      <c r="M144" s="4" t="inlineStr"/>
-      <c r="N144" s="4" t="inlineStr"/>
-      <c r="O144" s="4" t="inlineStr"/>
-      <c r="P144" s="4" t="inlineStr"/>
-      <c r="Q144" s="4" t="inlineStr">
-        <is>
-          <t>LSR 6</t>
-        </is>
-      </c>
-      <c r="R144" s="4" t="inlineStr">
-        <is>
-          <t>Intervention outcomes and spillover effects</t>
-        </is>
-      </c>
-      <c r="S144" s="4" t="inlineStr"/>
-      <c r="T144" s="4" t="inlineStr">
-        <is>
-          <t>Proposed</t>
-        </is>
-      </c>
-      <c r="U144" s="4" t="inlineStr"/>
-      <c r="V144" s="4" t="inlineStr"/>
-      <c r="W144" s="4" t="inlineStr"/>
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>GMHO:0000083</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>serious somatic adverse event following an intervention</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>A serious adverse event following an intervention that is associated with multiple, persistent or salient physical symptoms.</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
+        <is>
+          <t>serious adverse event following an intervention</t>
+        </is>
+      </c>
+      <c r="E144" s="2" t="n"/>
+      <c r="F144" s="2" t="n"/>
+      <c r="G144" s="2" t="n"/>
+      <c r="H144" s="2" t="n"/>
+      <c r="I144" s="2" t="n"/>
+      <c r="J144" s="2" t="n"/>
+      <c r="K144" s="2" t="n"/>
+      <c r="L144" s="2" t="n"/>
+      <c r="M144" s="2" t="n"/>
+      <c r="N144" s="2" t="n"/>
+      <c r="O144" s="2" t="n"/>
+      <c r="P144" s="2" t="n"/>
+      <c r="Q144" s="2" t="inlineStr">
+        <is>
+          <t>LSR 3</t>
+        </is>
+      </c>
+      <c r="R144" s="2" t="inlineStr">
+        <is>
+          <t>Intervention outcomes and spillover effects</t>
+        </is>
+      </c>
+      <c r="S144" s="2" t="n"/>
+      <c r="T144" s="2" t="inlineStr">
+        <is>
+          <t>Obsolete</t>
+        </is>
+      </c>
+      <c r="U144" s="2" t="n"/>
+      <c r="V144" s="2" t="n"/>
+      <c r="W144" s="2" t="inlineStr">
+        <is>
+          <t>PS</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="4" t="inlineStr">
         <is>
+          <t>GMHO:0000271</t>
+        </is>
+      </c>
+      <c r="B145" s="4" t="inlineStr">
+        <is>
+          <t>social anxiety scale</t>
+        </is>
+      </c>
+      <c r="C145" s="4" t="inlineStr">
+        <is>
+          <t>An anxiety scale that is used to measure social anxiety symptom severity.</t>
+        </is>
+      </c>
+      <c r="D145" s="4" t="inlineStr">
+        <is>
+          <t>anxiety scale</t>
+        </is>
+      </c>
+      <c r="E145" s="4" t="n"/>
+      <c r="F145" s="4" t="n"/>
+      <c r="G145" s="4" t="n"/>
+      <c r="H145" s="4" t="n"/>
+      <c r="I145" s="4" t="n"/>
+      <c r="J145" s="4" t="inlineStr">
+        <is>
+          <t>Intervention outcomes and spillover effects</t>
+        </is>
+      </c>
+      <c r="K145" s="4" t="n"/>
+      <c r="L145" s="4" t="n"/>
+      <c r="M145" s="4" t="n"/>
+      <c r="N145" s="4" t="n"/>
+      <c r="O145" s="4" t="n"/>
+      <c r="P145" s="4" t="n"/>
+      <c r="Q145" s="4" t="inlineStr">
+        <is>
+          <t>LSR 6</t>
+        </is>
+      </c>
+      <c r="R145" s="4" t="inlineStr">
+        <is>
+          <t>Intervention outcomes and spillover effects</t>
+        </is>
+      </c>
+      <c r="S145" s="4" t="n"/>
+      <c r="T145" s="4" t="inlineStr">
+        <is>
+          <t>Proposed</t>
+        </is>
+      </c>
+      <c r="U145" s="4" t="n"/>
+      <c r="V145" s="4" t="n"/>
+      <c r="W145" s="4" t="n"/>
+    </row>
+    <row r="146">
+      <c r="A146" s="4" t="inlineStr">
+        <is>
           <t>GMHO:0000272</t>
         </is>
       </c>
-      <c r="B145" s="4" t="inlineStr">
+      <c r="B146" s="4" t="inlineStr">
         <is>
           <t>social anxiety symptom severity</t>
         </is>
       </c>
-      <c r="C145" s="4" t="inlineStr">
+      <c r="C146" s="4" t="inlineStr">
         <is>
           <t>Anxiety symptom severity that is associated with social anxiety.</t>
         </is>
       </c>
-      <c r="D145" s="4" t="inlineStr">
+      <c r="D146" s="4" t="inlineStr">
         <is>
           <t>anxiety symptom severity</t>
         </is>
       </c>
-      <c r="E145" s="4" t="inlineStr"/>
-      <c r="F145" s="4" t="inlineStr"/>
-      <c r="G145" s="4" t="inlineStr"/>
-      <c r="H145" s="4" t="inlineStr"/>
-      <c r="I145" s="4" t="inlineStr"/>
-      <c r="J145" s="4" t="inlineStr">
-        <is>
-          <t>Intervention outcomes and spillover effects</t>
-        </is>
-      </c>
-      <c r="K145" s="4" t="inlineStr"/>
-      <c r="L145" s="4" t="inlineStr"/>
-      <c r="M145" s="4" t="inlineStr"/>
-      <c r="N145" s="4" t="inlineStr"/>
-      <c r="O145" s="4" t="inlineStr"/>
-      <c r="P145" s="4" t="inlineStr"/>
-      <c r="Q145" s="4" t="inlineStr">
+      <c r="E146" s="4" t="n"/>
+      <c r="F146" s="4" t="n"/>
+      <c r="G146" s="4" t="n"/>
+      <c r="H146" s="4" t="n"/>
+      <c r="I146" s="4" t="n"/>
+      <c r="J146" s="4" t="inlineStr">
+        <is>
+          <t>Intervention outcomes and spillover effects</t>
+        </is>
+      </c>
+      <c r="K146" s="4" t="n"/>
+      <c r="L146" s="4" t="n"/>
+      <c r="M146" s="4" t="n"/>
+      <c r="N146" s="4" t="n"/>
+      <c r="O146" s="4" t="n"/>
+      <c r="P146" s="4" t="n"/>
+      <c r="Q146" s="4" t="inlineStr">
         <is>
           <t>LSR 6</t>
         </is>
       </c>
-      <c r="R145" s="4" t="inlineStr">
-        <is>
-          <t>Intervention outcomes and spillover effects</t>
-        </is>
-      </c>
-      <c r="S145" s="4" t="inlineStr"/>
-      <c r="T145" s="4" t="inlineStr">
+      <c r="R146" s="4" t="inlineStr">
+        <is>
+          <t>Intervention outcomes and spillover effects</t>
+        </is>
+      </c>
+      <c r="S146" s="4" t="n"/>
+      <c r="T146" s="4" t="inlineStr">
         <is>
           <t>Proposed</t>
         </is>
       </c>
-      <c r="U145" s="4" t="inlineStr"/>
-      <c r="V145" s="4" t="inlineStr"/>
-      <c r="W145" s="4" t="inlineStr"/>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>OBCS:0000077</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>standard deviation</t>
-        </is>
-      </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>A quantitative confidence value that measures the variability of data around the mean.</t>
-        </is>
-      </c>
-      <c r="D146" t="inlineStr">
-        <is>
-          <t>quantitative confidence value</t>
-        </is>
-      </c>
-      <c r="Q146" t="inlineStr">
-        <is>
-          <t>LSR 1; LSR 2</t>
-        </is>
-      </c>
-      <c r="R146" t="inlineStr">
-        <is>
-          <t>Intervention outcomes and spillover effects</t>
-        </is>
-      </c>
-      <c r="T146" t="inlineStr">
-        <is>
-          <t>External</t>
-        </is>
-      </c>
-      <c r="W146" t="inlineStr">
-        <is>
-          <t>PS</t>
-        </is>
-      </c>
+      <c r="U146" s="4" t="n"/>
+      <c r="V146" s="4" t="n"/>
+      <c r="W146" s="4" t="n"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
+          <t>OBCS:0000077</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>standard deviation</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>A quantitative confidence value that measures the variability of data around the mean.</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>quantitative confidence value</t>
+        </is>
+      </c>
+      <c r="Q147" t="inlineStr">
+        <is>
+          <t>LSR 1; LSR 2</t>
+        </is>
+      </c>
+      <c r="R147" t="inlineStr">
+        <is>
+          <t>Intervention outcomes and spillover effects</t>
+        </is>
+      </c>
+      <c r="T147" t="inlineStr">
+        <is>
+          <t>External</t>
+        </is>
+      </c>
+      <c r="W147" t="inlineStr">
+        <is>
+          <t>PS</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
           <t>STATO:0000562</t>
         </is>
       </c>
-      <c r="B147" t="inlineStr">
+      <c r="B148" t="inlineStr">
         <is>
           <t>standard error of estimate</t>
         </is>
       </c>
-      <c r="C147" t="inlineStr">
+      <c r="C148" t="inlineStr">
         <is>
           <t>The standard error is a measure of dispersion applied to estimates across hypothetical repeated random samples.</t>
         </is>
       </c>
-      <c r="D147" t="inlineStr">
+      <c r="D148" t="inlineStr">
         <is>
           <t>estimate</t>
         </is>
       </c>
-      <c r="J147" t="inlineStr">
-        <is>
-          <t>Intervention outcomes and spillover effects</t>
-        </is>
-      </c>
-      <c r="Q147" t="inlineStr">
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>Intervention outcomes and spillover effects</t>
+        </is>
+      </c>
+      <c r="Q148" t="inlineStr">
         <is>
           <t>LSR 3</t>
         </is>
       </c>
-      <c r="R147" t="inlineStr">
-        <is>
-          <t>Intervention outcomes and spillover effects</t>
-        </is>
-      </c>
-      <c r="T147" t="inlineStr">
+      <c r="R148" t="inlineStr">
+        <is>
+          <t>Intervention outcomes and spillover effects</t>
+        </is>
+      </c>
+      <c r="T148" t="inlineStr">
         <is>
           <t>External</t>
         </is>
       </c>
-      <c r="W147" t="inlineStr">
-        <is>
-          <t>PS</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" s="2" t="inlineStr">
-        <is>
-          <t>GMHO:0000084</t>
-        </is>
-      </c>
-      <c r="B148" s="2" t="inlineStr">
-        <is>
-          <t>suicidal ideation following intervention</t>
-        </is>
-      </c>
-      <c r="C148" s="2" t="inlineStr">
-        <is>
-          <t>An adverse event following an intervention that involves thoughts about suicide.</t>
-        </is>
-      </c>
-      <c r="D148" s="2" t="inlineStr">
-        <is>
-          <t>adverse event following an intervention</t>
-        </is>
-      </c>
-      <c r="E148" s="2" t="n"/>
-      <c r="F148" s="2" t="n"/>
-      <c r="G148" s="2" t="n"/>
-      <c r="H148" s="2" t="n"/>
-      <c r="I148" s="2" t="n"/>
-      <c r="J148" s="2" t="n"/>
-      <c r="K148" s="2" t="inlineStr">
-        <is>
-          <t>Based on http://purl.obolibrary.org/obo/OAE_0001432</t>
-        </is>
-      </c>
-      <c r="L148" s="2" t="inlineStr">
-        <is>
-          <t>http://purl.obolibrary.org/obo/OAE_0001432</t>
-        </is>
-      </c>
-      <c r="M148" s="2" t="n"/>
-      <c r="N148" s="2" t="n"/>
-      <c r="O148" s="2" t="n"/>
-      <c r="P148" s="2" t="n"/>
-      <c r="Q148" s="2" t="inlineStr">
-        <is>
-          <t>LSR 3</t>
-        </is>
-      </c>
-      <c r="R148" s="2" t="inlineStr">
-        <is>
-          <t>Intervention outcomes and spillover effects</t>
-        </is>
-      </c>
-      <c r="S148" s="2" t="n"/>
-      <c r="T148" s="2" t="inlineStr">
-        <is>
-          <t>Obsolete</t>
-        </is>
-      </c>
-      <c r="U148" s="2" t="n"/>
-      <c r="V148" s="2" t="n"/>
-      <c r="W148" s="2" t="inlineStr">
+      <c r="W148" t="inlineStr">
         <is>
           <t>PS</t>
         </is>
@@ -9222,17 +9210,17 @@
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>GMHO:0000085</t>
+          <t>GMHO:0000084</t>
         </is>
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t>suicide attempt following intervention</t>
+          <t>suicidal ideation following intervention</t>
         </is>
       </c>
       <c r="C149" s="2" t="inlineStr">
         <is>
-          <t>An adverse event following an intervention that involves at least one attempted suicide.</t>
+          <t>An adverse event following an intervention that involves thoughts about suicide.</t>
         </is>
       </c>
       <c r="D149" s="2" t="inlineStr">
@@ -9248,12 +9236,12 @@
       <c r="J149" s="2" t="n"/>
       <c r="K149" s="2" t="inlineStr">
         <is>
-          <t>Based on http://purl.obolibrary.org/obo/OAE_0001433</t>
+          <t>Based on http://purl.obolibrary.org/obo/OAE_0001432</t>
         </is>
       </c>
       <c r="L149" s="2" t="inlineStr">
         <is>
-          <t>http://purl.obolibrary.org/obo/OAE_0001433</t>
+          <t>http://purl.obolibrary.org/obo/OAE_0001432</t>
         </is>
       </c>
       <c r="M149" s="2" t="n"/>
@@ -9287,22 +9275,22 @@
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>GMHO:0000086</t>
+          <t>GMHO:0000085</t>
         </is>
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>suicide following an intervention</t>
+          <t>suicide attempt following intervention</t>
         </is>
       </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t>A death following an intervention that involves a participant intentionally ending their own life.</t>
+          <t>An adverse event following an intervention that involves at least one attempted suicide.</t>
         </is>
       </c>
       <c r="D150" s="2" t="inlineStr">
         <is>
-          <t>death following an intervention</t>
+          <t>adverse event following an intervention</t>
         </is>
       </c>
       <c r="E150" s="2" t="n"/>
@@ -9311,8 +9299,16 @@
       <c r="H150" s="2" t="n"/>
       <c r="I150" s="2" t="n"/>
       <c r="J150" s="2" t="n"/>
-      <c r="K150" s="2" t="n"/>
-      <c r="L150" s="2" t="n"/>
+      <c r="K150" s="2" t="inlineStr">
+        <is>
+          <t>Based on http://purl.obolibrary.org/obo/OAE_0001433</t>
+        </is>
+      </c>
+      <c r="L150" s="2" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/OAE_0001433</t>
+        </is>
+      </c>
       <c r="M150" s="2" t="n"/>
       <c r="N150" s="2" t="n"/>
       <c r="O150" s="2" t="n"/>
@@ -9344,22 +9340,22 @@
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>OGMS:0000020</t>
+          <t>GMHO:0000086</t>
         </is>
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
-          <t>symptom</t>
+          <t>suicide following an intervention</t>
         </is>
       </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
-          <t>A process experienced by the patient, which can only be experienced by the patient, that is hypothesized to be clinically relevant.</t>
+          <t>A death following an intervention that involves a participant intentionally ending their own life.</t>
         </is>
       </c>
       <c r="D151" s="2" t="inlineStr">
         <is>
-          <t>process</t>
+          <t>death following an intervention</t>
         </is>
       </c>
       <c r="E151" s="2" t="n"/>
@@ -9376,7 +9372,7 @@
       <c r="P151" s="2" t="n"/>
       <c r="Q151" s="2" t="inlineStr">
         <is>
-          <t>LSR 1</t>
+          <t>LSR 3</t>
         </is>
       </c>
       <c r="R151" s="2" t="inlineStr">
@@ -9399,61 +9395,57 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="3" t="inlineStr">
-        <is>
-          <t>GMHO:0000087</t>
-        </is>
-      </c>
-      <c r="B152" s="3" t="inlineStr">
-        <is>
-          <t>symptom severity</t>
-        </is>
-      </c>
-      <c r="C152" s="3" t="inlineStr">
-        <is>
-          <t>A data item that is about the severity dimension associated with a symptom.</t>
-        </is>
-      </c>
-      <c r="D152" s="3" t="inlineStr">
-        <is>
-          <t>data item</t>
-        </is>
-      </c>
-      <c r="E152" s="3" t="n"/>
-      <c r="F152" s="3" t="n"/>
-      <c r="G152" s="3" t="n"/>
-      <c r="H152" s="3" t="n"/>
-      <c r="I152" s="3" t="n"/>
-      <c r="J152" s="3" t="n"/>
-      <c r="K152" s="3" t="n"/>
-      <c r="L152" s="3" t="n"/>
-      <c r="M152" s="3" t="n"/>
-      <c r="N152" s="3" t="n"/>
-      <c r="O152" s="3" t="n"/>
-      <c r="P152" s="3" t="n"/>
-      <c r="Q152" s="3" t="inlineStr">
-        <is>
-          <t>LSR 1; LSR 3</t>
-        </is>
-      </c>
-      <c r="R152" s="3" t="inlineStr">
-        <is>
-          <t>Intervention outcomes and spillover effects</t>
-        </is>
-      </c>
-      <c r="S152" s="3" t="inlineStr">
-        <is>
-          <t>A measure for 'psychotic disorder symptom severity'</t>
-        </is>
-      </c>
-      <c r="T152" s="3" t="inlineStr">
-        <is>
-          <t>Published</t>
-        </is>
-      </c>
-      <c r="U152" s="3" t="n"/>
-      <c r="V152" s="3" t="n"/>
-      <c r="W152" s="3" t="inlineStr">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
+          <t>OGMS:0000020</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>symptom</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>A process experienced by the patient, which can only be experienced by the patient, that is hypothesized to be clinically relevant.</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
+        <is>
+          <t>process</t>
+        </is>
+      </c>
+      <c r="E152" s="2" t="n"/>
+      <c r="F152" s="2" t="n"/>
+      <c r="G152" s="2" t="n"/>
+      <c r="H152" s="2" t="n"/>
+      <c r="I152" s="2" t="n"/>
+      <c r="J152" s="2" t="n"/>
+      <c r="K152" s="2" t="n"/>
+      <c r="L152" s="2" t="n"/>
+      <c r="M152" s="2" t="n"/>
+      <c r="N152" s="2" t="n"/>
+      <c r="O152" s="2" t="n"/>
+      <c r="P152" s="2" t="n"/>
+      <c r="Q152" s="2" t="inlineStr">
+        <is>
+          <t>LSR 1</t>
+        </is>
+      </c>
+      <c r="R152" s="2" t="inlineStr">
+        <is>
+          <t>Intervention outcomes and spillover effects</t>
+        </is>
+      </c>
+      <c r="S152" s="2" t="n"/>
+      <c r="T152" s="2" t="inlineStr">
+        <is>
+          <t>Obsolete</t>
+        </is>
+      </c>
+      <c r="U152" s="2" t="n"/>
+      <c r="V152" s="2" t="n"/>
+      <c r="W152" s="2" t="inlineStr">
         <is>
           <t>PS</t>
         </is>
@@ -9462,22 +9454,22 @@
     <row r="153">
       <c r="A153" s="3" t="inlineStr">
         <is>
-          <t>GMHO:0000138</t>
+          <t>GMHO:0000087</t>
         </is>
       </c>
       <c r="B153" s="3" t="inlineStr">
         <is>
-          <t>temporal reference associated with measurement in intervention</t>
+          <t>symptom severity</t>
         </is>
       </c>
       <c r="C153" s="3" t="inlineStr">
         <is>
-          <t>Time point at which a measurement is taken with reference to a temporal part of the intervention evaluation study.</t>
+          <t>A data item that is about the severity dimension associated with a symptom.</t>
         </is>
       </c>
       <c r="D153" s="3" t="inlineStr">
         <is>
-          <t>one-dimensional temporal region</t>
+          <t>data item</t>
         </is>
       </c>
       <c r="E153" s="3" t="n"/>
@@ -9485,11 +9477,7 @@
       <c r="G153" s="3" t="n"/>
       <c r="H153" s="3" t="n"/>
       <c r="I153" s="3" t="n"/>
-      <c r="J153" s="3" t="inlineStr">
-        <is>
-          <t>Intervention outcomes and spillover effects</t>
-        </is>
-      </c>
+      <c r="J153" s="3" t="n"/>
       <c r="K153" s="3" t="n"/>
       <c r="L153" s="3" t="n"/>
       <c r="M153" s="3" t="n"/>
@@ -9498,7 +9486,7 @@
       <c r="P153" s="3" t="n"/>
       <c r="Q153" s="3" t="inlineStr">
         <is>
-          <t>LSR 1; LSR 2; LSR 3</t>
+          <t>LSR 1; LSR 3</t>
         </is>
       </c>
       <c r="R153" s="3" t="inlineStr">
@@ -9506,7 +9494,11 @@
           <t>Intervention outcomes and spillover effects</t>
         </is>
       </c>
-      <c r="S153" s="3" t="n"/>
+      <c r="S153" s="3" t="inlineStr">
+        <is>
+          <t>A measure for 'psychotic disorder symptom severity'</t>
+        </is>
+      </c>
       <c r="T153" s="3" t="inlineStr">
         <is>
           <t>Published</t>
@@ -9523,22 +9515,22 @@
     <row r="154">
       <c r="A154" s="3" t="inlineStr">
         <is>
-          <t>GMHO:0000229</t>
+          <t>GMHO:0000138</t>
         </is>
       </c>
       <c r="B154" s="3" t="inlineStr">
         <is>
-          <t>tiredness following intervention</t>
+          <t>temporal reference associated with measurement in intervention</t>
         </is>
       </c>
       <c r="C154" s="3" t="inlineStr">
         <is>
-          <t>An adverse event following intervention that involves experiencing tiredness.</t>
+          <t>Time point at which a measurement is taken with reference to a temporal part of the intervention evaluation study.</t>
         </is>
       </c>
       <c r="D154" s="3" t="inlineStr">
         <is>
-          <t>adverse event following an intervention</t>
+          <t>one-dimensional temporal region</t>
         </is>
       </c>
       <c r="E154" s="3" t="n"/>
@@ -9553,20 +9545,20 @@
       </c>
       <c r="K154" s="3" t="n"/>
       <c r="L154" s="3" t="n"/>
-      <c r="M154" s="3" t="inlineStr">
-        <is>
-          <t>tiredness</t>
-        </is>
-      </c>
+      <c r="M154" s="3" t="n"/>
       <c r="N154" s="3" t="n"/>
       <c r="O154" s="3" t="n"/>
       <c r="P154" s="3" t="n"/>
       <c r="Q154" s="3" t="inlineStr">
         <is>
-          <t>LSR 3</t>
-        </is>
-      </c>
-      <c r="R154" s="3" t="n"/>
+          <t>LSR 1; LSR 2; LSR 3</t>
+        </is>
+      </c>
+      <c r="R154" s="3" t="inlineStr">
+        <is>
+          <t>Intervention outcomes and spillover effects</t>
+        </is>
+      </c>
       <c r="S154" s="3" t="n"/>
       <c r="T154" s="3" t="inlineStr">
         <is>
@@ -9582,61 +9574,61 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="2" t="inlineStr">
-        <is>
-          <t>GMHO:0000088</t>
-        </is>
-      </c>
-      <c r="B155" s="2" t="inlineStr">
-        <is>
-          <t>unnatural dealth due to external factors following an intervention</t>
-        </is>
-      </c>
-      <c r="C155" s="2" t="inlineStr">
-        <is>
-          <t>Death following an intervention that involves a homicide or accidents.</t>
-        </is>
-      </c>
-      <c r="D155" s="2" t="inlineStr">
-        <is>
-          <t>death following an intervention</t>
-        </is>
-      </c>
-      <c r="E155" s="2" t="inlineStr">
-        <is>
-          <t>"homicide following an intervention" OR "death due to accidents following an intervention"</t>
-        </is>
-      </c>
-      <c r="F155" s="2" t="n"/>
-      <c r="G155" s="2" t="n"/>
-      <c r="H155" s="2" t="n"/>
-      <c r="I155" s="2" t="n"/>
-      <c r="J155" s="2" t="n"/>
-      <c r="K155" s="2" t="n"/>
-      <c r="L155" s="2" t="n"/>
-      <c r="M155" s="2" t="n"/>
-      <c r="N155" s="2" t="n"/>
-      <c r="O155" s="2" t="n"/>
-      <c r="P155" s="2" t="n"/>
-      <c r="Q155" s="2" t="inlineStr">
+      <c r="A155" s="3" t="inlineStr">
+        <is>
+          <t>GMHO:0000229</t>
+        </is>
+      </c>
+      <c r="B155" s="3" t="inlineStr">
+        <is>
+          <t>tiredness following intervention</t>
+        </is>
+      </c>
+      <c r="C155" s="3" t="inlineStr">
+        <is>
+          <t>An adverse event following intervention that involves experiencing tiredness.</t>
+        </is>
+      </c>
+      <c r="D155" s="3" t="inlineStr">
+        <is>
+          <t>adverse event following an intervention</t>
+        </is>
+      </c>
+      <c r="E155" s="3" t="n"/>
+      <c r="F155" s="3" t="n"/>
+      <c r="G155" s="3" t="n"/>
+      <c r="H155" s="3" t="n"/>
+      <c r="I155" s="3" t="n"/>
+      <c r="J155" s="3" t="inlineStr">
+        <is>
+          <t>Intervention outcomes and spillover effects</t>
+        </is>
+      </c>
+      <c r="K155" s="3" t="n"/>
+      <c r="L155" s="3" t="n"/>
+      <c r="M155" s="3" t="inlineStr">
+        <is>
+          <t>tiredness</t>
+        </is>
+      </c>
+      <c r="N155" s="3" t="n"/>
+      <c r="O155" s="3" t="n"/>
+      <c r="P155" s="3" t="n"/>
+      <c r="Q155" s="3" t="inlineStr">
         <is>
           <t>LSR 3</t>
         </is>
       </c>
-      <c r="R155" s="2" t="inlineStr">
-        <is>
-          <t>Intervention outcomes and spillover effects</t>
-        </is>
-      </c>
-      <c r="S155" s="2" t="n"/>
-      <c r="T155" s="2" t="inlineStr">
-        <is>
-          <t>Obsolete</t>
-        </is>
-      </c>
-      <c r="U155" s="2" t="n"/>
-      <c r="V155" s="2" t="n"/>
-      <c r="W155" s="2" t="inlineStr">
+      <c r="R155" s="3" t="n"/>
+      <c r="S155" s="3" t="n"/>
+      <c r="T155" s="3" t="inlineStr">
+        <is>
+          <t>Published</t>
+        </is>
+      </c>
+      <c r="U155" s="3" t="n"/>
+      <c r="V155" s="3" t="n"/>
+      <c r="W155" s="3" t="inlineStr">
         <is>
           <t>PS</t>
         </is>
@@ -9645,35 +9637,35 @@
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>GMHO:0000139</t>
+          <t>GMHO:0000088</t>
         </is>
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>upper bound of 95% confidence interval</t>
+          <t>unnatural dealth due to external factors following an intervention</t>
         </is>
       </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
-          <t>A quantitative confidence value that denotes the upper endpoint of a 95% confidence interval and indicates the highest value within a true parameter is likely to reside within the confidence interval.</t>
+          <t>Death following an intervention that involves a homicide or accidents.</t>
         </is>
       </c>
       <c r="D156" s="2" t="inlineStr">
         <is>
-          <t>quantitative confidence value</t>
-        </is>
-      </c>
-      <c r="E156" s="2" t="n"/>
+          <t>death following an intervention</t>
+        </is>
+      </c>
+      <c r="E156" s="2" t="inlineStr">
+        <is>
+          <t>"homicide following an intervention" OR "death due to accidents following an intervention"</t>
+        </is>
+      </c>
       <c r="F156" s="2" t="n"/>
       <c r="G156" s="2" t="n"/>
       <c r="H156" s="2" t="n"/>
       <c r="I156" s="2" t="n"/>
       <c r="J156" s="2" t="n"/>
-      <c r="K156" s="2" t="inlineStr">
-        <is>
-          <t>Based on Ross, S. M. (2017). Estimation. Introductory statistics ( p. 329-380). Academic Press.</t>
-        </is>
-      </c>
+      <c r="K156" s="2" t="n"/>
       <c r="L156" s="2" t="n"/>
       <c r="M156" s="2" t="n"/>
       <c r="N156" s="2" t="n"/>
@@ -9681,7 +9673,7 @@
       <c r="P156" s="2" t="n"/>
       <c r="Q156" s="2" t="inlineStr">
         <is>
-          <t>LSR 1; LSR 2</t>
+          <t>LSR 3</t>
         </is>
       </c>
       <c r="R156" s="2" t="inlineStr">
@@ -9706,22 +9698,22 @@
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>GMHO:0000175</t>
+          <t>GMHO:0000139</t>
         </is>
       </c>
       <c r="B157" s="2" t="inlineStr">
         <is>
-          <t>validity of measurement scale</t>
+          <t>upper bound of 95% confidence interval</t>
         </is>
       </c>
       <c r="C157" s="2" t="inlineStr">
         <is>
-          <t>An attribute of a measurement scale that involves the degree to which the outcomes from the scale represent the intended variable or variables.</t>
+          <t>A quantitative confidence value that denotes the upper endpoint of a 95% confidence interval and indicates the highest value within a true parameter is likely to reside within the confidence interval.</t>
         </is>
       </c>
       <c r="D157" s="2" t="inlineStr">
         <is>
-          <t>specifically dependent continuant</t>
+          <t>quantitative confidence value</t>
         </is>
       </c>
       <c r="E157" s="2" t="n"/>
@@ -9732,7 +9724,7 @@
       <c r="J157" s="2" t="n"/>
       <c r="K157" s="2" t="inlineStr">
         <is>
-          <t>Based on Price, P. (2015). Research methods in psychology, 2nd Canadian Edition. BCcampus.</t>
+          <t>Based on Ross, S. M. (2017). Estimation. Introductory statistics ( p. 329-380). Academic Press.</t>
         </is>
       </c>
       <c r="L157" s="2" t="n"/>
@@ -9742,7 +9734,7 @@
       <c r="P157" s="2" t="n"/>
       <c r="Q157" s="2" t="inlineStr">
         <is>
-          <t>LSR 2</t>
+          <t>LSR 1; LSR 2</t>
         </is>
       </c>
       <c r="R157" s="2" t="inlineStr">
@@ -9767,22 +9759,22 @@
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>GMHO:0000140</t>
+          <t>GMHO:0000175</t>
         </is>
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>vo2 max</t>
+          <t>validity of measurement scale</t>
         </is>
       </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
-          <t>A data item about the maximum capacity of an individual's body to transport and use oxygen during incremental exercise, which reflects the physical fitness of the individual.</t>
+          <t>An attribute of a measurement scale that involves the degree to which the outcomes from the scale represent the intended variable or variables.</t>
         </is>
       </c>
       <c r="D158" s="2" t="inlineStr">
         <is>
-          <t>data item</t>
+          <t>specifically dependent continuant</t>
         </is>
       </c>
       <c r="E158" s="2" t="n"/>
@@ -9793,15 +9785,10 @@
       <c r="J158" s="2" t="n"/>
       <c r="K158" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Based on http://purl.obolibrary.org/obo/ERO_0001819
-</t>
-        </is>
-      </c>
-      <c r="L158" s="2" t="inlineStr">
-        <is>
-          <t>http://purl.obolibrary.org/obo/ERO_0001819</t>
-        </is>
-      </c>
+          <t>Based on Price, P. (2015). Research methods in psychology, 2nd Canadian Edition. BCcampus.</t>
+        </is>
+      </c>
+      <c r="L158" s="2" t="n"/>
       <c r="M158" s="2" t="n"/>
       <c r="N158" s="2" t="n"/>
       <c r="O158" s="2" t="n"/>
@@ -9826,183 +9813,249 @@
       <c r="V158" s="2" t="n"/>
       <c r="W158" s="2" t="inlineStr">
         <is>
+          <t>PS</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
+        <is>
+          <t>GMHO:0000140</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
+          <t>vo2 max</t>
+        </is>
+      </c>
+      <c r="C159" s="2" t="inlineStr">
+        <is>
+          <t>A data item about the maximum capacity of an individual's body to transport and use oxygen during incremental exercise, which reflects the physical fitness of the individual.</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="inlineStr">
+        <is>
+          <t>data item</t>
+        </is>
+      </c>
+      <c r="E159" s="2" t="n"/>
+      <c r="F159" s="2" t="n"/>
+      <c r="G159" s="2" t="n"/>
+      <c r="H159" s="2" t="n"/>
+      <c r="I159" s="2" t="n"/>
+      <c r="J159" s="2" t="n"/>
+      <c r="K159" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Based on http://purl.obolibrary.org/obo/ERO_0001819
+</t>
+        </is>
+      </c>
+      <c r="L159" s="2" t="inlineStr">
+        <is>
+          <t>http://purl.obolibrary.org/obo/ERO_0001819</t>
+        </is>
+      </c>
+      <c r="M159" s="2" t="n"/>
+      <c r="N159" s="2" t="n"/>
+      <c r="O159" s="2" t="n"/>
+      <c r="P159" s="2" t="n"/>
+      <c r="Q159" s="2" t="inlineStr">
+        <is>
+          <t>LSR 2</t>
+        </is>
+      </c>
+      <c r="R159" s="2" t="inlineStr">
+        <is>
+          <t>Intervention outcomes and spillover effects</t>
+        </is>
+      </c>
+      <c r="S159" s="2" t="n"/>
+      <c r="T159" s="2" t="inlineStr">
+        <is>
+          <t>Obsolete</t>
+        </is>
+      </c>
+      <c r="U159" s="2" t="n"/>
+      <c r="V159" s="2" t="n"/>
+      <c r="W159" s="2" t="inlineStr">
+        <is>
           <t>PS; MS</t>
         </is>
       </c>
     </row>
-    <row r="159">
-      <c r="A159" s="3" t="inlineStr">
+    <row r="160">
+      <c r="A160" s="3" t="inlineStr">
         <is>
           <t>GMHO:0000185</t>
         </is>
       </c>
-      <c r="B159" s="3" t="inlineStr">
+      <c r="B160" s="3" t="inlineStr">
         <is>
           <t>vomiting following intervention</t>
         </is>
       </c>
-      <c r="C159" s="3" t="inlineStr">
+      <c r="C160" s="3" t="inlineStr">
         <is>
           <t>A digestive system adverse event following intervention that has an outcome of vomiting, the retrograde expulsion of gastric contents through the oral cavity.</t>
         </is>
       </c>
-      <c r="D159" s="3" t="inlineStr">
+      <c r="D160" s="3" t="inlineStr">
         <is>
           <t>digestive system adverse event following intervention</t>
         </is>
       </c>
-      <c r="E159" s="3" t="n"/>
-      <c r="F159" s="3" t="n"/>
-      <c r="G159" s="3" t="n"/>
-      <c r="H159" s="3" t="n"/>
-      <c r="I159" s="3" t="n"/>
-      <c r="J159" s="3" t="n"/>
-      <c r="K159" s="3" t="inlineStr">
+      <c r="E160" s="3" t="n"/>
+      <c r="F160" s="3" t="n"/>
+      <c r="G160" s="3" t="n"/>
+      <c r="H160" s="3" t="n"/>
+      <c r="I160" s="3" t="n"/>
+      <c r="J160" s="3" t="n"/>
+      <c r="K160" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">cross reference: http://purl.obolibrary.org/obo/OAE_0000601
 </t>
         </is>
       </c>
-      <c r="L159" s="3" t="inlineStr">
+      <c r="L160" s="3" t="inlineStr">
         <is>
           <t>http://purl.obolibrary.org/obo/OAE_0000601</t>
         </is>
       </c>
-      <c r="M159" s="3" t="inlineStr">
+      <c r="M160" s="3" t="inlineStr">
         <is>
           <t>vomiting</t>
         </is>
       </c>
-      <c r="N159" s="3" t="n"/>
-      <c r="O159" s="3" t="n"/>
-      <c r="P159" s="3" t="n"/>
-      <c r="Q159" s="3" t="inlineStr">
+      <c r="N160" s="3" t="n"/>
+      <c r="O160" s="3" t="n"/>
+      <c r="P160" s="3" t="n"/>
+      <c r="Q160" s="3" t="inlineStr">
         <is>
           <t>LSR 1</t>
         </is>
       </c>
-      <c r="R159" s="3" t="inlineStr">
-        <is>
-          <t>Intervention outcomes and spillover effects</t>
-        </is>
-      </c>
-      <c r="S159" s="3" t="n"/>
-      <c r="T159" s="3" t="inlineStr">
+      <c r="R160" s="3" t="inlineStr">
+        <is>
+          <t>Intervention outcomes and spillover effects</t>
+        </is>
+      </c>
+      <c r="S160" s="3" t="n"/>
+      <c r="T160" s="3" t="inlineStr">
         <is>
           <t>Published</t>
         </is>
       </c>
-      <c r="U159" s="3" t="n"/>
-      <c r="V159" s="3" t="n"/>
-      <c r="W159" s="3" t="inlineStr">
+      <c r="U160" s="3" t="n"/>
+      <c r="V160" s="3" t="n"/>
+      <c r="W160" s="3" t="inlineStr">
         <is>
           <t>PS; MS</t>
         </is>
       </c>
     </row>
-    <row r="160">
-      <c r="A160" t="inlineStr">
+    <row r="161">
+      <c r="A161" t="inlineStr">
         <is>
           <t>PATO:0000128</t>
         </is>
       </c>
-      <c r="B160" t="inlineStr">
+      <c r="B161" t="inlineStr">
         <is>
           <t>weight</t>
         </is>
       </c>
-      <c r="C160" t="inlineStr">
+      <c r="C161" t="inlineStr">
         <is>
           <t>A physical quality inhering in a bearer that has mass near a gravitational body.</t>
         </is>
       </c>
-      <c r="D160" t="inlineStr">
+      <c r="D161" t="inlineStr">
         <is>
           <t>force</t>
         </is>
       </c>
-      <c r="J160" t="inlineStr">
-        <is>
-          <t>Intervention outcomes and spillover effects</t>
-        </is>
-      </c>
-      <c r="Q160" t="inlineStr">
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>Intervention outcomes and spillover effects</t>
+        </is>
+      </c>
+      <c r="Q161" t="inlineStr">
         <is>
           <t>LSR 3</t>
         </is>
       </c>
-      <c r="R160" t="inlineStr">
-        <is>
-          <t>Intervention outcomes and spillover effects</t>
-        </is>
-      </c>
-      <c r="T160" t="inlineStr">
+      <c r="R161" t="inlineStr">
+        <is>
+          <t>Intervention outcomes and spillover effects</t>
+        </is>
+      </c>
+      <c r="T161" t="inlineStr">
         <is>
           <t>External</t>
         </is>
       </c>
-      <c r="W160" t="inlineStr">
-        <is>
-          <t>PS</t>
-        </is>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" s="2" t="inlineStr">
+      <c r="W161" t="inlineStr">
+        <is>
+          <t>PS</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="inlineStr">
         <is>
           <t>GMHO:0000230</t>
         </is>
       </c>
-      <c r="B161" s="2" t="inlineStr">
+      <c r="B162" s="2" t="inlineStr">
         <is>
           <t>weight scale</t>
         </is>
       </c>
-      <c r="C161" s="2" t="inlineStr">
+      <c r="C162" s="2" t="inlineStr">
         <is>
           <t>A measurement scale that is used to measure weight.</t>
         </is>
       </c>
-      <c r="D161" s="2" t="inlineStr">
+      <c r="D162" s="2" t="inlineStr">
         <is>
           <t>measurement scale</t>
         </is>
       </c>
-      <c r="E161" s="2" t="n"/>
-      <c r="F161" s="2" t="n"/>
-      <c r="G161" s="2" t="n"/>
-      <c r="H161" s="2" t="n"/>
-      <c r="I161" s="2" t="n"/>
-      <c r="J161" s="2" t="inlineStr">
-        <is>
-          <t>Intervention outcomes and spillover effects</t>
-        </is>
-      </c>
-      <c r="K161" s="2" t="n"/>
-      <c r="L161" s="2" t="n"/>
-      <c r="M161" s="2" t="n"/>
-      <c r="N161" s="2" t="n"/>
-      <c r="O161" s="2" t="n"/>
-      <c r="P161" s="2" t="n"/>
-      <c r="Q161" s="2" t="inlineStr">
+      <c r="E162" s="2" t="n"/>
+      <c r="F162" s="2" t="n"/>
+      <c r="G162" s="2" t="n"/>
+      <c r="H162" s="2" t="n"/>
+      <c r="I162" s="2" t="n"/>
+      <c r="J162" s="2" t="inlineStr">
+        <is>
+          <t>Intervention outcomes and spillover effects</t>
+        </is>
+      </c>
+      <c r="K162" s="2" t="n"/>
+      <c r="L162" s="2" t="n"/>
+      <c r="M162" s="2" t="n"/>
+      <c r="N162" s="2" t="n"/>
+      <c r="O162" s="2" t="n"/>
+      <c r="P162" s="2" t="n"/>
+      <c r="Q162" s="2" t="inlineStr">
         <is>
           <t>LSR 3</t>
         </is>
       </c>
-      <c r="R161" s="2" t="inlineStr">
-        <is>
-          <t>Intervention outcomes and spillover effects</t>
-        </is>
-      </c>
-      <c r="S161" s="2" t="n"/>
-      <c r="T161" s="2" t="inlineStr">
+      <c r="R162" s="2" t="inlineStr">
+        <is>
+          <t>Intervention outcomes and spillover effects</t>
+        </is>
+      </c>
+      <c r="S162" s="2" t="n"/>
+      <c r="T162" s="2" t="inlineStr">
         <is>
           <t>Obsolete</t>
         </is>
       </c>
-      <c r="U161" s="2" t="n"/>
-      <c r="V161" s="2" t="n"/>
-      <c r="W161" s="2" t="inlineStr">
+      <c r="U162" s="2" t="n"/>
+      <c r="V162" s="2" t="n"/>
+      <c r="W162" s="2" t="inlineStr">
         <is>
           <t>PS</t>
         </is>
